--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -689,10 +689,10 @@
         <v>0.7799142811192761</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.8080379773288264</v>
+        <v>0.8080376637696582</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2182483994985938</v>
+        <v>0.2182483290736392</v>
       </c>
     </row>
     <row r="4">
@@ -742,13 +742,13 @@
         <v>0.3347931928537671</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.7605620048012858</v>
+        <v>0.760562149163108</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.031862271467704</v>
+        <v>1.031862463749532</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2665764888835123</v>
+        <v>0.2665765288369479</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.962238198420496</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.679269698059737</v>
+        <v>2.679270062354253</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5437863900589888</v>
+        <v>0.543786441010486</v>
       </c>
     </row>
     <row r="6">
@@ -848,7 +848,7 @@
         <v>0.2264403169559062</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.255623993101787</v>
+        <v>0.2556239083108767</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>0.3119185439397616</v>
@@ -907,10 +907,10 @@
         <v>0.2262509055575741</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2337111912183685</v>
+        <v>0.233711081627316</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.513782248173986</v>
+        <v>0.5137820831774234</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>0.6437319149283676</v>
@@ -960,19 +960,19 @@
         <v>0.1205983771082659</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1968337610097921</v>
+        <v>0.1968336464019833</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.4201325826783964</v>
+        <v>0.4201324213152617</v>
       </c>
       <c r="N8" s="6" t="n">
         <v>0.4755471156377615</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3436275426224642</v>
+        <v>0.3436276870681019</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1034677185086605</v>
+        <v>0.1034677580511398</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.329395029278567</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.089275422225814</v>
+        <v>1.089275271874336</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2783954957132815</v>
+        <v>0.2783954650473617</v>
       </c>
     </row>
     <row r="10">
@@ -1081,10 +1081,10 @@
         <v>0.8568221916336818</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.511630649787596</v>
+        <v>1.511630915221222</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3593102488878379</v>
+        <v>0.3593102967726167</v>
       </c>
     </row>
     <row r="11">
@@ -1113,34 +1113,34 @@
         <v>154.67</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.01066789210248964</v>
+        <v>0.01065084261840599</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.0181857922004296</v>
+        <v>0.01816861589296614</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.02398281560362414</v>
+        <v>0.02396554150314767</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.02107612743849274</v>
+        <v>0.02105890237245567</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-0.04891910342687056</v>
+        <v>-0.04893514770683138</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3253599586674232</v>
+        <v>0.3253376004786483</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4501081076596072</v>
+        <v>0.4500836450292078</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.578673275007314</v>
+        <v>0.5786467664728852</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.302115426630493</v>
+        <v>1.302076591044014</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3204106899760575</v>
+        <v>0.3204032650353128</v>
       </c>
     </row>
     <row r="12">
@@ -1249,10 +1249,10 @@
         <v>0.667452058862966</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.96479280873354</v>
+        <v>2.964793110704789</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5827299927667153</v>
+        <v>0.5827300329486336</v>
       </c>
     </row>
     <row r="14">
@@ -1299,16 +1299,16 @@
         <v>0.4512169702577657</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4527741153832447</v>
+        <v>0.4527742464422722</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7176842127044878</v>
+        <v>0.7176843959179615</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.311421134607436</v>
+        <v>1.311420802843777</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3221874380157463</v>
+        <v>0.3221873747568624</v>
       </c>
     </row>
     <row r="15">
@@ -1361,10 +1361,10 @@
         <v>0.3144203085311212</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.028902545713761</v>
+        <v>1.02890237970263</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2659612009972099</v>
+        <v>0.2659611664689117</v>
       </c>
     </row>
     <row r="16">
@@ -1529,10 +1529,10 @@
         <v>0.5484111186288985</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.534399092100397</v>
+        <v>2.53439933214227</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.5232523693507594</v>
+        <v>0.5232524038351072</v>
       </c>
     </row>
     <row r="19">
@@ -1582,13 +1582,13 @@
         <v>0.191992558672281</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.225738815810046</v>
+        <v>0.2257387159957502</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1962939806074318</v>
+        <v>0.1962940756838414</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.06156348739121942</v>
+        <v>0.06156351551408434</v>
       </c>
     </row>
     <row r="20">
@@ -1641,10 +1641,10 @@
         <v>0.3507295192821345</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2559757731264143</v>
+        <v>0.2559755816663718</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.07893120519632069</v>
+        <v>0.07893115037248588</v>
       </c>
     </row>
     <row r="21">
@@ -1747,16 +1747,16 @@
         <v>0.1281466370425597</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1812278219463916</v>
+        <v>0.1812276805183719</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>0.1658585681447444</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7946304730260325</v>
+        <v>0.7946306362516411</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2152296185275528</v>
+        <v>0.2152296553701585</v>
       </c>
     </row>
     <row r="23">
@@ -1803,16 +1803,16 @@
         <v>0.1340714556710767</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1673939545428915</v>
+        <v>0.1673938795688166</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1521993796768515</v>
+        <v>0.152199452711941</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8879568986057398</v>
+        <v>0.8879565064213353</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.235939915886342</v>
+        <v>0.235939830305929</v>
       </c>
     </row>
     <row r="24">
@@ -1865,10 +1865,10 @@
         <v>0.588710634750039</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.2829970304638725</v>
+        <v>0.2829971151134079</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.08661380197202639</v>
+        <v>0.08661382586954902</v>
       </c>
     </row>
     <row r="25">
@@ -1915,16 +1915,16 @@
         <v>0.08897152942565123</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1217609095235412</v>
+        <v>0.1217607776132794</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1120592556117526</v>
+        <v>0.112059385250235</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.6791949442949536</v>
+        <v>0.6791950920867433</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1885944717893018</v>
+        <v>0.1885945066600792</v>
       </c>
     </row>
     <row r="26">
@@ -1953,34 +1953,34 @@
         <v>133.01</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.01586756070491879</v>
+        <v>-0.01583425443058128</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.01462811250536822</v>
+        <v>-0.01459476428403239</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.007643853052042404</v>
+        <v>-0.007610268460425451</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.01448216843934003</v>
+        <v>-0.01444881527877762</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.1455417151332605</v>
+        <v>0.1455804840276755</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.06733866289525925</v>
+        <v>0.06737485049062575</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1056358693566866</v>
+        <v>0.1056732877062012</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.09901300435663973</v>
+        <v>0.09905019856664854</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6771868840113111</v>
+        <v>0.6772436455245423</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1881204904137768</v>
+        <v>0.1881338935625856</v>
       </c>
     </row>
     <row r="27">
@@ -2024,19 +2024,19 @@
         <v>0.07029646204223305</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1414666715604893</v>
+        <v>0.1414667727586045</v>
       </c>
       <c r="M27" s="6" t="n">
         <v>0.1130401293267402</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1431284326051845</v>
+        <v>0.143128331112222</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.142349250667966</v>
+        <v>1.142348894195174</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2891301249854279</v>
+        <v>0.2891300534845058</v>
       </c>
     </row>
     <row r="28">
@@ -2086,13 +2086,13 @@
         <v>0.1797676152908976</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.4595270714141015</v>
+        <v>0.4595269344027935</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.270141500556228</v>
+        <v>1.270141666288864</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3142691366904795</v>
+        <v>0.3142691686734025</v>
       </c>
     </row>
     <row r="29">
@@ -2145,10 +2145,10 @@
         <v>0.1314212219792492</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4216088437415528</v>
+        <v>0.4216086783926127</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1244151939945586</v>
+        <v>0.1244151504005537</v>
       </c>
     </row>
     <row r="30">
@@ -2195,16 +2195,16 @@
         <v>0.03707137247853587</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1247097831940027</v>
+        <v>0.1247098978544803</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2060063265339362</v>
+        <v>0.2060064583693164</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.3913619338444343</v>
+        <v>0.3913621093185431</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1163834059256812</v>
+        <v>0.1163834528572454</v>
       </c>
     </row>
     <row r="31">
@@ -2251,16 +2251,16 @@
         <v>0.005609342619908197</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1291064288258332</v>
+        <v>0.1291065594364631</v>
       </c>
       <c r="N31" s="6" t="n">
         <v>0.09410059227111911</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2394344807462208</v>
+        <v>0.2394342446728304</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.07417372403092681</v>
+        <v>0.07417365583212265</v>
       </c>
     </row>
     <row r="32">
@@ -2425,10 +2425,10 @@
         <v>0.3029708506937354</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5616902990164667</v>
+        <v>0.5616901024897523</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1601967311538599</v>
+        <v>0.160196682486579</v>
       </c>
     </row>
     <row r="35">
@@ -2475,16 +2475,16 @@
         <v>0.04577228207439621</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1688142550425002</v>
+        <v>0.1688141562676755</v>
       </c>
       <c r="N35" s="6" t="n">
         <v>0.2470162422883753</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3385513483003941</v>
+        <v>0.3385510892076276</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1020763395140063</v>
+        <v>0.1020762684072769</v>
       </c>
     </row>
     <row r="36">
@@ -2531,16 +2531,16 @@
         <v>0.07322856697281521</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.09339906483382743</v>
+        <v>0.09339913522359256</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>0.09325281447598921</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.6096842767689001</v>
+        <v>0.6096841242114384</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1719621000532308</v>
+        <v>0.1719620630290823</v>
       </c>
     </row>
     <row r="37">
@@ -2587,16 +2587,16 @@
         <v>0.05212708305715297</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1713391261765778</v>
+        <v>0.1713390092114107</v>
       </c>
       <c r="N37" s="6" t="n">
         <v>0.2654763786259509</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.8289000879191262</v>
+        <v>0.8288998027705667</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2229160933316909</v>
+        <v>0.2229160297756803</v>
       </c>
     </row>
     <row r="38">
@@ -2681,34 +2681,34 @@
         <v>64.20999999999999</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.009979967840326176</v>
+        <v>-0.01002160838362942</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.0005094980493214329</v>
+        <v>0.0004674163158964184</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.01506009474994285</v>
+        <v>0.01501740101400029</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.02200697149110398</v>
+        <v>0.02196398556741541</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.008148690452775886</v>
+        <v>0.008106287412597668</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.1947734242459387</v>
+        <v>0.194723171712764</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.05502014055549931</v>
+        <v>0.05497576608789112</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.01588134043435474</v>
+        <v>0.01583861215656923</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.8638201207626206</v>
+        <v>0.8637417279221458</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.2306503095550079</v>
+        <v>0.2306330554711451</v>
       </c>
     </row>
     <row r="40">
@@ -2870,7 +2870,7 @@
         <v>0.09796714996985401</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.0907556974513104</v>
+        <v>0.09075560291833451</v>
       </c>
       <c r="O42" s="6" t="n">
         <v>0.3103948801703222</v>
@@ -2926,13 +2926,13 @@
         <v>0.1302466058922123</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1626317541545088</v>
+        <v>0.1626316671417833</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.5962326834169862</v>
+        <v>0.5962330114525469</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1686883988186494</v>
+        <v>0.1686884788761773</v>
       </c>
     </row>
     <row r="44">
@@ -2976,7 +2976,7 @@
         <v>0.05086778133418868</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.02415917818882574</v>
+        <v>0.02415908682580503</v>
       </c>
       <c r="M44" s="6" t="n">
         <v>0.03546527993676407</v>
@@ -3038,7 +3038,7 @@
         <v>0.03859017754181493</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>-0.01921706737213924</v>
+        <v>-0.01921716968611864</v>
       </c>
       <c r="O45" s="6" t="n">
         <v>0.01163785501843906</v>
@@ -3094,13 +3094,13 @@
         <v>-0.02352861618097801</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-0.07036702348165735</v>
+        <v>-0.07036696165254519</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.1753096414534518</v>
+        <v>0.1753097402802157</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.05531983188912237</v>
+        <v>0.05531986146823287</v>
       </c>
     </row>
     <row r="47">
@@ -3150,13 +3150,13 @@
         <v>0.1038007786400301</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.1422404266257944</v>
+        <v>0.1422405148680923</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.9805075299547608</v>
+        <v>0.98050726466856</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.2558145175615365</v>
+        <v>0.255814461490004</v>
       </c>
     </row>
     <row r="48">
@@ -3209,10 +3209,10 @@
         <v>0.0220273484117155</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1339525862532467</v>
+        <v>0.1339529961236887</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.04279345962606884</v>
+        <v>0.04279358526629107</v>
       </c>
     </row>
     <row r="49">
@@ -3265,10 +3265,10 @@
         <v>-0.1340450690537156</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.05241902305848978</v>
+        <v>0.05241891175437563</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01717629348270022</v>
+        <v>0.01717625762375441</v>
       </c>
     </row>
     <row r="50">
@@ -3315,7 +3315,7 @@
         <v>0.08685723960865999</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.09920484676749575</v>
+        <v>-0.09920490314940478</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>-0.1727666600219941</v>
@@ -3427,16 +3427,16 @@
         <v>-0.07640784216740126</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.006297891572330849</v>
+        <v>0.006297981240340311</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.05771788948399426</v>
+        <v>0.05771779041813208</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.505323874532484</v>
+        <v>0.5053237742063126</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.1460669356876325</v>
+        <v>0.1460669102267749</v>
       </c>
     </row>
     <row r="53">
@@ -3489,10 +3489,10 @@
         <v>0.17881408722577</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>1.099300090397734</v>
+        <v>1.099299691577555</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.2804368809799773</v>
+        <v>0.2804367998951591</v>
       </c>
     </row>
     <row r="54">
@@ -3539,16 +3539,16 @@
         <v>-0.05143633727196661</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.02370955630632343</v>
+        <v>-0.02370962121664932</v>
       </c>
       <c r="N54" s="6" t="n">
         <v>-0.005619632069683078</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.7269803709409952</v>
+        <v>0.726980167831375</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.1997639283163721</v>
+        <v>0.1997638812817506</v>
       </c>
     </row>
     <row r="55">
@@ -3654,7 +3654,7 @@
         <v>0.05812150966393848</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.2530581176000797</v>
+        <v>0.2530580333335619</v>
       </c>
       <c r="O56" s="6" t="n">
         <v>0.1569109381043947</v>
@@ -3745,34 +3745,34 @@
         <v>19.37</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.005871732149236308</v>
+        <v>-0.005851271446658757</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.01396929229819732</v>
+        <v>-0.01394899825597473</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.01432054853212295</v>
+        <v>-0.01430026171929866</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.005638661223493768</v>
+        <v>0.005659358827830197</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.01141520789353501</v>
+        <v>0.01143602438816682</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.04076304191862246</v>
+        <v>0.04078446243722467</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.05507687769590708</v>
+        <v>-0.05505742971158822</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.1833480356113326</v>
+        <v>-0.1833312276465126</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1656606473098625</v>
+        <v>0.1656846384150168</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.05242392306840715</v>
+        <v>0.05243114319141795</v>
       </c>
     </row>
     <row r="59">
@@ -3819,16 +3819,16 @@
         <v>-0.08599407821122274</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.1501063305390812</v>
+        <v>-0.1501062791605733</v>
       </c>
       <c r="N59" s="6" t="n">
         <v>-0.1305694137774253</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.03476233919221938</v>
+        <v>0.03476226303107377</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.0114557119376435</v>
+        <v>0.01145568712240341</v>
       </c>
     </row>
     <row r="60">
@@ -3928,7 +3928,7 @@
         <v>0.007327837714197871</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.0865154034454827</v>
+        <v>-0.08651547123782521</v>
       </c>
       <c r="M61" s="6" t="n">
         <v>-0.08649994652869564</v>
@@ -3937,10 +3937,10 @@
         <v>-0.1721642087216253</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1034488570147916</v>
+        <v>0.1034489559344649</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.03335783430632522</v>
+        <v>0.03335786518509098</v>
       </c>
     </row>
     <row r="62">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1455417151332605</v>
+        <v>0.1455804840276755</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.0865154034454827</v>
+        <v>-0.08651547123782521</v>
       </c>
     </row>
     <row r="49">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3253599586674232</v>
+        <v>0.3253376004786483</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1833480356113326</v>
+        <v>-0.1833312276465126</v>
       </c>
     </row>
     <row r="60">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.7605620048012858</v>
+        <v>0.760562149163108</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.7176842127044878</v>
+        <v>0.7176843959179615</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.07036702348165735</v>
+        <v>-0.07036696165254519</v>
       </c>
     </row>
     <row r="66">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.01921706737213924</v>
+        <v>-0.01921716968611864</v>
       </c>
     </row>
     <row r="68">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.96479280873354</v>
+        <v>2.964793110704789</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.679269698059737</v>
+        <v>2.679270062354253</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.534399092100397</v>
+        <v>2.53439933214227</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.03476233919221938</v>
+        <v>0.03476226303107377</v>
       </c>
     </row>
     <row r="76">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.05241902305848978</v>
+        <v>0.05241891175437563</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.511630649787596</v>
+        <v>1.511630915221222</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1034488570147916</v>
+        <v>0.1034489559344649</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.311421134607436</v>
+        <v>1.311420802843777</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1339525862532467</v>
+        <v>0.1339529961236887</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.302115426630493</v>
+        <v>1.302076591044014</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.270141500556228</v>
+        <v>1.270141666288864</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1656606473098625</v>
+        <v>0.1656846384150168</v>
       </c>
     </row>
     <row r="81">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1753096414534518</v>
+        <v>0.1753097402802157</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.142349250667966</v>
+        <v>1.142348894195174</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1962939806074318</v>
+        <v>0.1962940756838414</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -745,10 +745,10 @@
         <v>0.760562149163108</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.031862463749532</v>
+        <v>1.031861886904156</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2665765288369479</v>
+        <v>0.266576408976656</v>
       </c>
     </row>
     <row r="5">
@@ -848,13 +848,13 @@
         <v>0.2264403169559062</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.2556239083108767</v>
+        <v>0.255623993101787</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>0.3119185439397616</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5097710717165607</v>
+        <v>0.509770949127341</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>0.6653965177983405</v>
@@ -907,16 +907,16 @@
         <v>0.2262509055575741</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.233711081627316</v>
+        <v>0.2337111912183685</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5137820831774234</v>
+        <v>0.513782248173986</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.6437319149283676</v>
+        <v>0.6437317203878568</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1801675322144818</v>
+        <v>0.1801674856557129</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
         <v>0.1205983771082659</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1968336464019833</v>
+        <v>0.1968337610097921</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>0.4201324213152617</v>
@@ -969,10 +969,10 @@
         <v>0.4755471156377615</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3436276870681019</v>
+        <v>0.3436278315137704</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1034677580511398</v>
+        <v>0.1034677975936247</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.329395029278567</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.089275271874336</v>
+        <v>1.089275422225814</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2783954650473617</v>
+        <v>0.2783954957132815</v>
       </c>
     </row>
     <row r="10">
@@ -1131,16 +1131,16 @@
         <v>0.3253376004786483</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4500836450292078</v>
+        <v>0.4500835413074016</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5786467664728852</v>
+        <v>0.5786466435440154</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.302076591044014</v>
+        <v>1.302076852454847</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3204032650353128</v>
+        <v>0.3204033150144932</v>
       </c>
     </row>
     <row r="12">
@@ -1249,10 +1249,10 @@
         <v>0.667452058862966</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.964793110704789</v>
+        <v>2.964793412676084</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5827300329486336</v>
+        <v>0.5827300731305558</v>
       </c>
     </row>
     <row r="14">
@@ -1299,16 +1299,16 @@
         <v>0.4512169702577657</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4527742464422722</v>
+        <v>0.4527741153832447</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7176843959179615</v>
+        <v>0.7176842127044878</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.311420802843777</v>
+        <v>1.311421134607436</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3221873747568624</v>
+        <v>0.3221874380157463</v>
       </c>
     </row>
     <row r="15">
@@ -1529,10 +1529,10 @@
         <v>0.5484111186288985</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.53439933214227</v>
+        <v>2.534399092100397</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.5232524038351072</v>
+        <v>0.5232523693507594</v>
       </c>
     </row>
     <row r="19">
@@ -1576,7 +1576,7 @@
         <v>0.1142430316265477</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2569254322450725</v>
+        <v>0.2569253272869882</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>0.191992558672281</v>
@@ -1585,10 +1585,10 @@
         <v>0.2257387159957502</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1962940756838414</v>
+        <v>0.1962938855310372</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.06156351551408434</v>
+        <v>0.06156345926835738</v>
       </c>
     </row>
     <row r="20">
@@ -1641,10 +1641,10 @@
         <v>0.3507295192821345</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2559755816663718</v>
+        <v>0.2559756773963857</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.07893115037248588</v>
+        <v>0.07893117778440195</v>
       </c>
     </row>
     <row r="21">
@@ -1691,7 +1691,7 @@
         <v>0.09994511820069629</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2280284456503152</v>
+        <v>0.2280285488945597</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>0.2531516326049295</v>
@@ -1747,16 +1747,16 @@
         <v>0.1281466370425597</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1812276805183719</v>
+        <v>0.1812278219463916</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>0.1658585681447444</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7946306362516411</v>
+        <v>0.7946309627029473</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2152296553701585</v>
+        <v>0.2152297290553831</v>
       </c>
     </row>
     <row r="23">
@@ -1803,16 +1803,16 @@
         <v>0.1340714556710767</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1673938795688166</v>
+        <v>0.1673939545428915</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.152199452711941</v>
+        <v>0.1521993796768515</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8879565064213353</v>
+        <v>0.8879567025135173</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.235939830305929</v>
+        <v>0.2359398730961326</v>
       </c>
     </row>
     <row r="24">
@@ -1865,10 +1865,10 @@
         <v>0.588710634750039</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.2829971151134079</v>
+        <v>0.2829969458143484</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.08661382586954902</v>
+        <v>0.08661377807450599</v>
       </c>
     </row>
     <row r="25">
@@ -1977,10 +1977,10 @@
         <v>0.09905019856664854</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6772436455245423</v>
+        <v>0.6772434841637318</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1881338935625856</v>
+        <v>0.1881338554607361</v>
       </c>
     </row>
     <row r="27">
@@ -2024,13 +2024,13 @@
         <v>0.07029646204223305</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1414667727586045</v>
+        <v>0.1414666715604893</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1130401293267402</v>
+        <v>0.1130402255472376</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.143128331112222</v>
+        <v>0.1431284326051845</v>
       </c>
       <c r="O27" s="6" t="n">
         <v>1.142348894195174</v>
@@ -2089,10 +2089,10 @@
         <v>0.4595269344027935</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.270141666288864</v>
+        <v>1.270141500556228</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3142691686734025</v>
+        <v>0.3142691366904795</v>
       </c>
     </row>
     <row r="29">
@@ -2139,7 +2139,7 @@
         <v>0.04668740551097428</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1043611483474245</v>
+        <v>0.1043612481320224</v>
       </c>
       <c r="N29" s="6" t="n">
         <v>0.1314212219792492</v>
@@ -2192,7 +2192,7 @@
         <v>-0.0008282407921043067</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.03707137247853587</v>
+        <v>0.03707146996629529</v>
       </c>
       <c r="M30" s="6" t="n">
         <v>0.1247098978544803</v>
@@ -2307,16 +2307,16 @@
         <v>0.002526666725571003</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1787946615967617</v>
+        <v>0.1787945715476975</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>0.1583233335340049</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3401016493618083</v>
+        <v>0.3401017657418313</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.102501647798418</v>
+        <v>0.1025016797136993</v>
       </c>
     </row>
     <row r="33">
@@ -2425,10 +2425,10 @@
         <v>0.3029708506937354</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5616901024897523</v>
+        <v>0.5616902990164667</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.160196682486579</v>
+        <v>0.1601967311538599</v>
       </c>
     </row>
     <row r="35">
@@ -2475,16 +2475,16 @@
         <v>0.04577228207439621</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1688141562676755</v>
+        <v>0.1688142550425002</v>
       </c>
       <c r="N35" s="6" t="n">
         <v>0.2470162422883753</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3385510892076276</v>
+        <v>0.3385513483003941</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1020762684072769</v>
+        <v>0.1020763395140063</v>
       </c>
     </row>
     <row r="36">
@@ -2531,16 +2531,16 @@
         <v>0.07322856697281521</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.09339913522359256</v>
+        <v>0.09339906483382743</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>0.09325281447598921</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.6096841242114384</v>
+        <v>0.6096839716540055</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1719620630290823</v>
+        <v>0.1719620260049386</v>
       </c>
     </row>
     <row r="37">
@@ -2587,16 +2587,16 @@
         <v>0.05212708305715297</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1713390092114107</v>
+        <v>0.1713391261765778</v>
       </c>
       <c r="N37" s="6" t="n">
         <v>0.2654763786259509</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.8288998027705667</v>
+        <v>0.8289000879191262</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2229160297756803</v>
+        <v>0.2229160933316909</v>
       </c>
     </row>
     <row r="38">
@@ -2755,7 +2755,7 @@
         <v>0.0179943111460803</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1413485120968303</v>
+        <v>0.1413486021859638</v>
       </c>
       <c r="N40" s="6" t="n">
         <v>0.1929944163042134</v>
@@ -2873,10 +2873,10 @@
         <v>0.09075560291833451</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.3103948801703222</v>
+        <v>0.3103951530447566</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.09429411221067929</v>
+        <v>0.09429418816866475</v>
       </c>
     </row>
     <row r="43">
@@ -2926,7 +2926,7 @@
         <v>0.1302466058922123</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1626316671417833</v>
+        <v>0.1626317541545088</v>
       </c>
       <c r="O43" s="6" t="n">
         <v>0.5962330114525469</v>
@@ -2976,7 +2976,7 @@
         <v>0.05086778133418868</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.02415908682580503</v>
+        <v>0.02415917818882574</v>
       </c>
       <c r="M44" s="6" t="n">
         <v>0.03546527993676407</v>
@@ -3041,10 +3041,10 @@
         <v>-0.01921716968611864</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.01163785501843906</v>
+        <v>0.01163774616571045</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.003864332703456652</v>
+        <v>0.003864296698024017</v>
       </c>
     </row>
     <row r="46">
@@ -3097,10 +3097,10 @@
         <v>-0.07036696165254519</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.1753097402802157</v>
+        <v>0.1753096414534518</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.05531986146823287</v>
+        <v>0.05531983188912237</v>
       </c>
     </row>
     <row r="47">
@@ -3150,13 +3150,13 @@
         <v>0.1038007786400301</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.1422405148680923</v>
+        <v>0.1422404266257944</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.98050726466856</v>
+        <v>0.9805071320254861</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.255814461490004</v>
+        <v>0.2558144334542416</v>
       </c>
     </row>
     <row r="48">
@@ -3203,7 +3203,7 @@
         <v>-0.02334682770671714</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.07440634813163904</v>
+        <v>0.07440644012020092</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0.0220273484117155</v>
@@ -3315,7 +3315,7 @@
         <v>0.08685723960865999</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.09920490314940478</v>
+        <v>-0.09920484676749575</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>-0.1727666600219941</v>
@@ -3601,10 +3601,10 @@
         <v>0.1945236933980603</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1.164224606392485</v>
+        <v>1.164224800351887</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.2935030095034934</v>
+        <v>0.293503048145056</v>
       </c>
     </row>
     <row r="56">
@@ -3654,13 +3654,13 @@
         <v>0.05812150966393848</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.2530580333335619</v>
+        <v>0.2530581176000797</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.1569109381043947</v>
+        <v>0.1569110099354967</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.04978406386544476</v>
+        <v>0.04978408559202196</v>
       </c>
     </row>
     <row r="57">
@@ -3710,13 +3710,13 @@
         <v>-0.02051833114483048</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.08641468215655701</v>
+        <v>0.08641455691387012</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.3568122026868521</v>
+        <v>0.3568123003589894</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.1070653217762316</v>
+        <v>0.1070653483408104</v>
       </c>
     </row>
     <row r="58">
@@ -3822,13 +3822,13 @@
         <v>-0.1501062791605733</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1305694137774253</v>
+        <v>-0.1305694675452015</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.03476226303107377</v>
+        <v>0.0347624153533761</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.01145568712240341</v>
+        <v>0.01145573675288603</v>
       </c>
     </row>
     <row r="60">
@@ -3875,16 +3875,16 @@
         <v>-0.06792440406997369</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.03510699735768508</v>
+        <v>-0.03510706615291015</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1124011024099953</v>
+        <v>-0.1124011606248065</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.253305150326042</v>
+        <v>0.2533050342577425</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.07816594017575018</v>
+        <v>0.07816590689284997</v>
       </c>
     </row>
     <row r="61">
@@ -3934,13 +3934,13 @@
         <v>-0.08649994652869564</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.1721642087216253</v>
+        <v>-0.1721642643974406</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1034489559344649</v>
+        <v>0.1034488570147916</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.03335786518509098</v>
+        <v>0.03335783430632522</v>
       </c>
     </row>
     <row r="62">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2569254322450725</v>
+        <v>0.2569253272869882</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1721642087216253</v>
+        <v>-0.1721642643974406</v>
       </c>
     </row>
     <row r="62">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1305694137774253</v>
+        <v>-0.1305694675452015</v>
       </c>
     </row>
     <row r="64">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.7176843959179615</v>
+        <v>0.7176842127044878</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1124011024099953</v>
+        <v>-0.1124011606248065</v>
       </c>
     </row>
     <row r="65">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.964793110704789</v>
+        <v>2.964793412676084</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.01163785501843906</v>
+        <v>0.01163774616571045</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.53439933214227</v>
+        <v>2.534399092100397</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.03476226303107377</v>
+        <v>0.0347624153533761</v>
       </c>
     </row>
     <row r="76">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1034489559344649</v>
+        <v>0.1034488570147916</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.311420802843777</v>
+        <v>1.311421134607436</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.302076591044014</v>
+        <v>1.302076852454847</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1569109381043947</v>
+        <v>0.1569110099354967</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.270141666288864</v>
+        <v>1.270141500556228</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.164224606392485</v>
+        <v>1.164224800351887</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1753097402802157</v>
+        <v>0.1753096414534518</v>
       </c>
     </row>
     <row r="82">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1962940756838414</v>
+        <v>0.1962938855310372</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -493,10 +493,10 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>16.56</v>
+        <v>16.3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.02602231054378579</v>
+        <v>-0.01570049741949309</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.06701024339586703</v>
+        <v>0.03197208979596855</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.1227118281994837</v>
+        <v>0.08197807441597171</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.1905103988209815</v>
+        <v>0.1845929481052861</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3080568456189587</v>
+        <v>0.3177040733920622</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.3904281845596043</v>
+        <v>0.5583173209957417</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7864076211639559</v>
+        <v>0.7621620796822213</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1.05382612303641</v>
+        <v>1</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.407407203910378</v>
+        <v>2.075471443483193</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.5047857818684167</v>
+        <v>0.4542438403115807</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>39.77</v>
+        <v>39.23</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.01290643946258307</v>
+        <v>-0.0135780967893333</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.01221683713544097</v>
+        <v>-0.01109147080963135</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.007734564848518088</v>
+        <v>-0.0542430092774947</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.2085942562754242</v>
+        <v>0.1279471224590254</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3330338350387942</v>
+        <v>0.3556578122779603</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3107218277520876</v>
+        <v>0.3318261013936057</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4873256286897041</v>
+        <v>0.4808369308216673</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7799142811192761</v>
+        <v>0.7371968229828241</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.8080376637696582</v>
+        <v>0.8293010768228757</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2182483290736392</v>
+        <v>0.2230054621555577</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>163.81</v>
+        <v>573.73</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.003467619584420323</v>
+        <v>0.01185159095498634</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.00880645789371215</v>
+        <v>0.05229083910638499</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.01158509755893433</v>
+        <v>0.03222261327142917</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.07854880360970617</v>
+        <v>-0.01539391033184712</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2289821983098801</v>
+        <v>-0.04084190479572314</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.2970321384628321</v>
+        <v>0.5075940302433244</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.3347931928537671</v>
+        <v>0.5615661691385256</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.760562149163108</v>
+        <v>0.9408985562696393</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.031861886904156</v>
+        <v>2.867205401750015</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.266576408976656</v>
+        <v>0.569636466569392</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>567.01</v>
+        <v>161.93</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.02607679119856665</v>
+        <v>-0.01147674080234351</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.02513066981646972</v>
+        <v>-0.008996335836061187</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.01175908614330279</v>
+        <v>-0.04240102406232449</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.01511179565229881</v>
+        <v>0.02897628328194379</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.09644163100698233</v>
+        <v>0.2620801676011537</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.4207216263949596</v>
+        <v>0.3071689584811568</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5729378401263647</v>
+        <v>0.3150993278673451</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.962238198420496</v>
+        <v>0.7226636910873359</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.679270062354253</v>
+        <v>1.071876369692184</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.543786441010486</v>
+        <v>0.2748368612886449</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>70.93000000000001</v>
+        <v>94.38</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.001407834377581851</v>
+        <v>0.04103235650831261</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.001977671815762472</v>
+        <v>0.05759748445416779</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.02568684983780201</v>
+        <v>-0.02014122142392927</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.01618907169072847</v>
+        <v>0.07213448326906602</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2264403169559062</v>
+        <v>0.1649738133216709</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.255623993101787</v>
+        <v>0.1844993678495279</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3119185439397616</v>
+        <v>0.4371473590769412</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.509770949127341</v>
+        <v>0.8848935168466907</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6653965177983405</v>
+        <v>1.730913441463207</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1853298393538045</v>
+        <v>0.3977708473178709</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>211.92</v>
+        <v>193.91</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.008839621211494064</v>
+        <v>0.01677938668967349</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.01421393282642081</v>
+        <v>0.006174773940788025</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.007679337930309171</v>
+        <v>0.06118321127331683</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.1144885878056472</v>
+        <v>0.1653245839824891</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2363636153222182</v>
+        <v>0.1571970742089035</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2262509055575741</v>
+        <v>0.1920035748609386</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2337111912183685</v>
+        <v>0.4692599213972073</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.513782248173986</v>
+        <v>0.5418093449417154</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.6437317203878568</v>
+        <v>0.3586814592448035</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1801674856557129</v>
+        <v>0.1075734833613913</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>190.71</v>
+        <v>70.38</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.008422997461470016</v>
+        <v>-0.007754166775573501</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.02565345923324958</v>
+        <v>0.003994276539110553</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.006172910568631895</v>
+        <v>-0.04336009860865442</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.1091015417189676</v>
+        <v>-0.001985243850152751</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1205983771082659</v>
+        <v>0.2339830523495059</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.1968337610097921</v>
+        <v>0.284928093674135</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.4201324213152617</v>
+        <v>0.251270806960979</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.4755471156377615</v>
+        <v>0.487993027850691</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.3436278315137704</v>
+        <v>0.6955245130041994</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1034677975936247</v>
+        <v>0.1924349345320844</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>110.75</v>
+        <v>207.33</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.006993623131301141</v>
+        <v>-0.02165909955431111</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.04145751149014942</v>
+        <v>-0.016554432083843</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.00779432651114742</v>
+        <v>-0.04191308836066021</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.02910493296840833</v>
+        <v>0.04865709772146176</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.09501681499253722</v>
+        <v>0.2422667004701433</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.4591567559091367</v>
+        <v>0.2384257651581065</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.3147291225215165</v>
+        <v>0.2223305333468273</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.329395029278567</v>
+        <v>0.4616247083759673</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.089275422225814</v>
+        <v>0.6481906429046367</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2783954957132815</v>
+        <v>0.1812336621235247</v>
       </c>
     </row>
     <row r="10">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>90.66</v>
+        <v>98.5</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.006465713291952002</v>
+        <v>-0.007956500234091557</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.03982201418928433</v>
+        <v>0.04464947548621101</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.04154765649575343</v>
+        <v>-0.04182882221893358</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.07941428703401665</v>
+        <v>0.1129943502824859</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.00829179347400455</v>
+        <v>0.2394551063736847</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.03185216130393309</v>
+        <v>-0.02562636107001093</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.3854325519966197</v>
+        <v>0.3339273566760261</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.8568221916336818</v>
+        <v>0.5852715745905757</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.511630915221222</v>
+        <v>3.111172338906194</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3593102967726167</v>
+        <v>0.6019731306835652</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>154.67</v>
+        <v>154.54</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.01065084261840599</v>
+        <v>-0.0008405307063525935</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.01816861589296614</v>
+        <v>0.01825122840939719</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.02396554150314767</v>
+        <v>0.01697806303156857</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.02105890237245567</v>
+        <v>0.01331059505877752</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-0.04893514770683138</v>
+        <v>0.0003310754291956375</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3253376004786483</v>
+        <v>0.3627683649153985</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4500835413074016</v>
+        <v>0.4367375571115113</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5786466435440154</v>
+        <v>0.5596093312930568</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.302076852454847</v>
+        <v>1.336746340676706</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3204033150144932</v>
+        <v>0.3269987805055903</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>427.53</v>
+        <v>495.98</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.005304666695162386</v>
+        <v>0.009217618611816247</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.02204107306665959</v>
+        <v>0.04873875344664147</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.02937426287882183</v>
+        <v>0.01028663635526139</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.09022059271573446</v>
+        <v>-0.0893935290204152</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.02606101193610832</v>
+        <v>-0.1681141333150975</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1155963429872124</v>
+        <v>0.5424056682740872</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.4152100524714475</v>
+        <v>0.4437511065359732</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.686901318166441</v>
+        <v>0.694682153373875</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.2874642713187028</v>
+        <v>1.460785001758269</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.08787349378588938</v>
+        <v>0.3500749847253546</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>99.29000000000001</v>
+        <v>428.57</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.02042225416692445</v>
+        <v>0.002432597824459926</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.001513027302828096</v>
+        <v>0.003958963694891793</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.00261177426680026</v>
+        <v>0.05639775381479128</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.2633923596158334</v>
+        <v>0.1037653463263331</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1232143680144002</v>
+        <v>-0.002884972991364587</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>-0.07484011411747349</v>
+        <v>0.1479656677438106</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.3188627175254046</v>
+        <v>0.4436895684109619</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.667452058862966</v>
+        <v>0.7079626316260272</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.964793412676084</v>
+        <v>0.2782045878132156</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5827300731305558</v>
+        <v>0.08525915300504705</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>491.45</v>
+        <v>111.19</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.02702086326636177</v>
+        <v>0.001802005419282882</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.01994441296318117</v>
+        <v>0.02630613069827903</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.01360817018203053</v>
+        <v>0.02093470482629423</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.06488436186468072</v>
+        <v>0.01063448313069526</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>-0.2369785136923589</v>
+        <v>0.04560848477091306</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.4512169702577657</v>
+        <v>0.2185205747003425</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4527741153832447</v>
+        <v>0.3883842641420387</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7176842127044878</v>
+        <v>0.579872193563151</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.311421134607436</v>
+        <v>0.8323040117547906</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3221874380157463</v>
+        <v>0.223674314699327</v>
       </c>
     </row>
     <row r="15">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>94.59</v>
+        <v>110.18</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.007658449006197721</v>
+        <v>-0.005146724106764977</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.04028004585068057</v>
+        <v>-0.01493069460641705</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.002741192835141737</v>
+        <v>0.01933577609487358</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.03420467653673798</v>
+        <v>-0.04539939305924712</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.0437854267918143</v>
+        <v>0.1384583766779859</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.4666866198161983</v>
+        <v>0.4167417392450008</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2728825433955198</v>
+        <v>0.2974964446122748</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3144203085311212</v>
+        <v>0.2792812432814875</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.02890237970263</v>
+        <v>1.098239022357925</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2659611664689117</v>
+        <v>0.2802211170652118</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>27.79</v>
+        <v>98.41</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.023198588039121</v>
+        <v>-0.00856335337323999</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.0364077403434524</v>
+        <v>0.03950570999789993</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.009269102624062997</v>
+        <v>-0.06738052698207908</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.04004497117026773</v>
+        <v>0.0947825601325134</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1205645875181562</v>
+        <v>0.2509216467855004</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.4280576681887558</v>
+        <v>-0.0292956566558642</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2082609093707541</v>
+        <v>0.2522071969220399</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2351111518012152</v>
+        <v>0.4741929297507788</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3457627810602957</v>
+        <v>2.596867310194209</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.10405193787137</v>
+        <v>0.5321741784141569</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>110.99</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.001262962486022312</v>
+        <v>-0.006131665335817549</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.02116105778544974</v>
+        <v>-0.02276501955805665</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.03535448715877498</v>
+        <v>0.01676403922891789</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.02266653563200749</v>
+        <v>-0.03924370360523011</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.0068898018767245</v>
+        <v>0.09242831107073513</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1585594397508008</v>
+        <v>0.4280979542355605</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.3531193395948253</v>
+        <v>0.2566672952342508</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5989490097960306</v>
+        <v>0.2650942787961621</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.7547473330976813</v>
+        <v>1.025467934419773</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2061598385123551</v>
+        <v>0.265246440120209</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>99.26000000000001</v>
+        <v>27.23</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.0219725665038677</v>
+        <v>-0.02015118225412227</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.003913691757918891</v>
+        <v>-0.0247134861093169</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.03471749130851498</v>
+        <v>-0.009097525624618519</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.2738706939008904</v>
+        <v>-0.001832886479128937</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1488425970281919</v>
+        <v>0.1538135212750593</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>-0.06252356714123164</v>
+        <v>0.3717883636745891</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2284175382375464</v>
+        <v>0.1762419002564581</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.5484111186288985</v>
+        <v>0.1823707655391555</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.534399092100397</v>
+        <v>0.3500247614892222</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.5232523693507594</v>
+        <v>0.1052162067438587</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>57.42</v>
+        <v>31.76</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.01000003156990836</v>
+        <v>0.01049952021959455</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.01002638012529933</v>
+        <v>-0.003138743865473637</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.008075826753270565</v>
+        <v>0.0399475860111782</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.01700317215797953</v>
+        <v>0.1194923965233143</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1142430316265477</v>
+        <v>0.09615240423470617</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2569253272869882</v>
+        <v>0.1034564999671641</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.191992558672281</v>
+        <v>0.3048555547266474</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2257387159957502</v>
+        <v>0.4110794833421747</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1962938855310372</v>
+        <v>0.2828911477020941</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.06156345926835738</v>
+        <v>0.0865839092461691</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>31.43</v>
+        <v>56.95</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.01007873054564468</v>
+        <v>-0.008185256373972716</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02111759597238372</v>
+        <v>-0.00835799302952589</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.002222212534102153</v>
+        <v>-0.0008771795975534014</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.09895104496360929</v>
+        <v>-0.002102662213535056</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.06038211504326374</v>
+        <v>0.09241526192361116</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1126523979656706</v>
+        <v>0.2766966678519367</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2727916910005277</v>
+        <v>0.2010209373161254</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3507295192821345</v>
+        <v>0.2085605727286821</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2559756773963857</v>
+        <v>0.1892389933604923</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.07893117778440195</v>
+        <v>0.05947256107073118</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>55.72</v>
+        <v>55.97</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.005413263472930252</v>
+        <v>0.004486719212545731</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.008689346988623337</v>
+        <v>0.00196921964106056</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01771691727311642</v>
+        <v>0.02490387465942945</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.03230086972659829</v>
+        <v>0.04914068812022387</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.0662262387473207</v>
+        <v>0.08445122726393839</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.09994511820069629</v>
+        <v>0.1053003446257199</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2280285488945597</v>
+        <v>0.2446699086573025</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2531516326049295</v>
+        <v>0.2762755252712941</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6985170455054195</v>
+        <v>0.7260106088445308</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1931360554271127</v>
+        <v>0.1995393159525582</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>75.27</v>
+        <v>119.95</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.005342512111803588</v>
+        <v>0.01121222534871746</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01305509490535139</v>
+        <v>0.03610607606790595</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.005476837154315461</v>
+        <v>-0.008185922549850289</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.03301644162042705</v>
+        <v>0.03637462555881488</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.0818832979789208</v>
+        <v>0.01216008213632214</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1281466370425597</v>
+        <v>0.09048885566992149</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1812278219463916</v>
+        <v>0.2245819818569381</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1658585681447444</v>
+        <v>0.4318323310015413</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7946309627029473</v>
+        <v>1.373721557431835</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2152297290553831</v>
+        <v>0.3339613850242129</v>
       </c>
     </row>
     <row r="23">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>69.34</v>
+        <v>74.31</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.003327965931237742</v>
+        <v>-0.01275407369851511</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.01285418149556428</v>
+        <v>0.02327175362288547</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.008728520406855234</v>
+        <v>-0.0002691278349004067</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.0274895740529546</v>
+        <v>-0.02493113172423622</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.09027802561583509</v>
+        <v>0.06231634340051251</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.1340714556710767</v>
+        <v>0.1581985633760177</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1673939545428915</v>
+        <v>0.1649052784000498</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1521993796768515</v>
+        <v>0.1617050584531476</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8879567025135173</v>
+        <v>0.8640882685783282</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2359398730961326</v>
+        <v>0.2307093246148979</v>
       </c>
     </row>
     <row r="24">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>74.18000000000001</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.003760391925055284</v>
+        <v>-0.005257473551415259</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.02484552908151294</v>
+        <v>-0.01231425753204862</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.03171910045445736</v>
+        <v>-0.03655823940780201</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.03473284668674204</v>
+        <v>-0.002972587682110395</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.1054409651563527</v>
+        <v>-0.03869242411185825</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.04721499187198175</v>
+        <v>0.07448456019113592</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.2004044839169432</v>
+        <v>0.1645264204904957</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.588710634750039</v>
+        <v>0.4414827603526339</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.2829969458143484</v>
+        <v>0.3260340108876301</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.08661377807450599</v>
+        <v>0.09863025399006009</v>
       </c>
     </row>
     <row r="25">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>145.56</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01562181399115536</v>
+        <v>-0.01355631470516916</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.003308489946795223</v>
+        <v>0.02165802305797992</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.01076316305035507</v>
+        <v>-0.0005844668921745066</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.01248301502090166</v>
+        <v>-0.02243818304178735</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.1275527650539514</v>
+        <v>0.07097544347706419</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.08897152942565123</v>
+        <v>0.161529390486713</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1217607776132794</v>
+        <v>0.1523306633392316</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.112059385250235</v>
+        <v>0.1453142186276402</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.6791950920867433</v>
+        <v>0.9438445509768034</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1885945066600792</v>
+        <v>0.2480170267923056</v>
       </c>
     </row>
     <row r="26">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>133.01</v>
+        <v>193.29</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.01583425443058128</v>
+        <v>-0.01613566791917764</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.01459476428403239</v>
+        <v>0.009927341567185</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.007610268460425451</v>
+        <v>-0.01773557025517802</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.01444881527877762</v>
+        <v>0.02677287270190076</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.1455804840276755</v>
+        <v>0.07660263318391025</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.06737485049062575</v>
+        <v>0.1540831280028023</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1056732877062012</v>
+        <v>0.09030702057901352</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.09905019856664854</v>
+        <v>0.1253303268742494</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6772434841637318</v>
+        <v>1.131458338521429</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1881338554607361</v>
+        <v>0.2869419256820018</v>
       </c>
     </row>
     <row r="27">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>196.46</v>
+        <v>143.07</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.008078313967732065</v>
+        <v>-0.01710628109465773</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.006764411849684349</v>
+        <v>-0.005214851632633022</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.009921389742874487</v>
+        <v>-0.01555077739187793</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.03947093499400633</v>
+        <v>-0.03383302569479885</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.07029646204223305</v>
+        <v>0.09032681421291744</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1414666715604893</v>
+        <v>0.08589935647953251</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1130402255472376</v>
+        <v>0.1146601703523074</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1431284326051845</v>
+        <v>0.1107978777849807</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.142348894195174</v>
+        <v>0.6665856738739588</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2891300534845058</v>
+        <v>0.1856118956707713</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2048,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>118.62</v>
+        <v>181.97</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.002027415937933208</v>
+        <v>0.01664895042227865</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.001010570316206105</v>
+        <v>0.03704336897920468</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.006033128987787628</v>
+        <v>0.01426897891053569</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.09975896602394241</v>
+        <v>-0.02392314343344126</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.07733261946376224</v>
+        <v>-0.03494555458690696</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.009559797760272604</v>
+        <v>0.1021453209552861</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.1797676152908976</v>
+        <v>0.1888316128935785</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.4595269344027935</v>
+        <v>0.2685790899719309</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.270141500556228</v>
+        <v>0.895001272011722</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3142691366904795</v>
+        <v>0.237475193900438</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>93.25</v>
+        <v>24.04</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.01081994992455992</v>
+        <v>0.01563163658811995</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.01468722948661039</v>
+        <v>0.02778971965970101</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.0295555879501137</v>
+        <v>0.001249507969992347</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.02580444201006649</v>
+        <v>0.001666704813639397</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.04797425486860396</v>
+        <v>-0.03881509916104497</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.04668740551097428</v>
+        <v>0.02314426556211968</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1043612481320224</v>
+        <v>0.2150044599094483</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1314212219792492</v>
+        <v>0.2937587064428935</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4216086783926127</v>
+        <v>0.6423394953121422</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1244151504005537</v>
+        <v>0.1798341946751709</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>84.17</v>
+        <v>130.41</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.006818178292200106</v>
+        <v>-0.01954733442675949</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02569743299441596</v>
+        <v>-0.01703470670104335</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.03286223888850515</v>
+        <v>-0.03557164262070212</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.04188958872048065</v>
+        <v>-0.0400441825321749</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.0008282407921043067</v>
+        <v>0.1012733926611669</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.03707146996629529</v>
+        <v>0.05537705691741812</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1247098978544803</v>
+        <v>0.09869399966691628</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2060064583693164</v>
+        <v>0.09377401595148704</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.3913621093185431</v>
+        <v>0.6645290096017822</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1163834528572454</v>
+        <v>0.1851239900887047</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>74.47</v>
+        <v>233.45</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.008784720575573002</v>
+        <v>-0.008536523011602459</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.009180447149899518</v>
+        <v>0.001072041180409933</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.01128516300537774</v>
+        <v>-0.02991895753522966</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.001876415875930348</v>
+        <v>-0.01252064916042128</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.06608844172302319</v>
+        <v>0.0386524044625034</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.005609342619908197</v>
+        <v>0.03889544770130637</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1291065594364631</v>
+        <v>0.1865315754684489</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.09410059227111911</v>
+        <v>0.1363733023434974</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2394342446728304</v>
+        <v>0.3691718008964413</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.07417365583212265</v>
+        <v>0.1104166930784283</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>235.46</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.002837412252110094</v>
+        <v>-0.0001072615145358835</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01282910239720736</v>
+        <v>-0.01155522046143242</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.01756578415004817</v>
+        <v>-0.03617945087128016</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.01869000318260028</v>
+        <v>-0.03478261556341222</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.01028346336990027</v>
+        <v>0.05009187437033735</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.002526666725571003</v>
+        <v>0.05934686592066329</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1787945715476975</v>
+        <v>0.1209597775756002</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1583233335340049</v>
+        <v>0.1203949762268566</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3401017657418313</v>
+        <v>0.4509971933808001</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1025016797136993</v>
+        <v>0.1321106019129019</v>
       </c>
     </row>
     <row r="33">
@@ -2342,37 +2342,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>290.87</v>
+        <v>287.61</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.008690676142903642</v>
+        <v>-0.01120778980420989</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01202407697051189</v>
+        <v>0.001636730093854677</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.01454476014163908</v>
+        <v>0.0002086508820753341</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.009684839888112196</v>
+        <v>-0.006116592374676322</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.03556675470204085</v>
+        <v>0.06293887066458459</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.1782791638905572</v>
+        <v>0.1675800073627234</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.07122600237482568</v>
+        <v>0.05544948752866974</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.03767256840843269</v>
+        <v>0.0200382822659595</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.7018898185283531</v>
+        <v>0.6865653398836455</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1939252765147901</v>
+        <v>0.1903309438710237</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>23.67</v>
+        <v>63.91</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.002541273375320285</v>
+        <v>-0.004672157628687668</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.006714219384152953</v>
+        <v>0.0003130452019837193</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.007963140368705046</v>
+        <v>0.005032232962043803</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.01045150498338687</v>
+        <v>0.006773791875812396</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.07209292187952021</v>
+        <v>0.04523862628571651</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.005258706222803666</v>
+        <v>0.2021129220862761</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.1915167337000405</v>
+        <v>0.04866847591191115</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.3029708506937354</v>
+        <v>0.00190074787826866</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5616902990164667</v>
+        <v>0.9001315173743343</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1601967311538599</v>
+        <v>0.2385909065963518</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>105.52</v>
+        <v>74.11</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.01189104217764636</v>
+        <v>-0.004834169523975751</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.009852707654730453</v>
+        <v>-0.01291956842097353</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.02422787831856443</v>
+        <v>-0.02486841302168996</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.07527827465900394</v>
+        <v>-0.004566774369742288</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.05866941959258631</v>
+        <v>0.04428568679490197</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.04577228207439621</v>
+        <v>0.02233708115867894</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1688142550425002</v>
+        <v>0.1364783039752977</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.2470162422883753</v>
+        <v>0.09491778715319232</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3385513483003941</v>
+        <v>0.2426716245196499</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1020763395140063</v>
+        <v>0.07510808345954989</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>64.79000000000001</v>
+        <v>82.97</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.001848755812843716</v>
+        <v>-0.01425682516748505</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.03153961976421404</v>
+        <v>0.0004823455369606933</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.04664505902957827</v>
+        <v>-0.04959910286014013</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.03629335593591942</v>
+        <v>-0.04883643210237087</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.033750762030341</v>
+        <v>-0.01971973382275938</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.07322856697281521</v>
+        <v>0.09115168361766046</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.09339906483382743</v>
+        <v>0.1015157910132678</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.09325281447598921</v>
+        <v>0.1839438485193794</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.6096839716540055</v>
+        <v>0.4208287690074275</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1719620260049386</v>
+        <v>0.1242094908175355</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>178.99</v>
+        <v>54.81</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.008167242660048535</v>
+        <v>-0.006345150019747781</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.001116116666763145</v>
+        <v>0.01650599470639991</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.01072230841292054</v>
+        <v>-0.01474024229875859</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.04160414029883408</v>
+        <v>-0.06611002460736537</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.08775580703392161</v>
+        <v>-0.02838226716910697</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.05212708305715297</v>
+        <v>0.06448460399009659</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1713391261765778</v>
+        <v>0.1413659774569282</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.2654763786259509</v>
+        <v>0.1861879374848869</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.8289000879191262</v>
+        <v>0.7832817164547279</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2229160933316909</v>
+        <v>0.2126626056522343</v>
       </c>
     </row>
     <row r="38">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>28.8</v>
+        <v>59.5</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.01337083602204392</v>
+        <v>0.004049977814116534</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.01302265469982988</v>
+        <v>0.01901011512167172</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.02603992105885777</v>
+        <v>-0.001007410542437026</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.1377246131337508</v>
+        <v>-0.0266645025296004</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.02857140132359093</v>
+        <v>-0.0157347966001713</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.05417275105302122</v>
+        <v>0.02742783977083207</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.07900002643995951</v>
+        <v>0.1463664109895471</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1180550994535934</v>
+        <v>0.1748144972418435</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.5114988374582785</v>
+        <v>0.6536235852820245</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1476318848757938</v>
+        <v>0.18253014156926</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>64.20999999999999</v>
+        <v>103.77</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.01002160838362942</v>
+        <v>-0.01658453426528794</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.0004674163158964184</v>
+        <v>0.01032029566782455</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.01501740101400029</v>
+        <v>-0.03729477909190604</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.02196398556741541</v>
+        <v>-0.07694361916711334</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.008106287412597668</v>
+        <v>-0.0871314262212155</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.194723171712764</v>
+        <v>0.1198912264679297</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.05497576608789112</v>
+        <v>0.1360441630376696</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.01583861215656923</v>
+        <v>0.2203256602454855</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.8637417279221458</v>
+        <v>0.3744414860936403</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.2306330554711451</v>
+        <v>0.1118394644329928</v>
       </c>
     </row>
     <row r="40">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2734,37 +2734,37 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>55.16</v>
+        <v>28.27</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.008593915386817974</v>
+        <v>-0.0184027358797586</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.002712014502884164</v>
+        <v>0.01362499377666793</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.02181237019949533</v>
+        <v>-0.06048520058474272</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.05838173227624499</v>
+        <v>-0.1312231203941401</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.04084830938626383</v>
+        <v>0.0205776057445759</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.0179943111460803</v>
+        <v>0.1151873780021084</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1413486021859638</v>
+        <v>0.03906491587264371</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.1929944163042134</v>
+        <v>0.09075967144791997</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.7275271940266179</v>
+        <v>0.5557615448596001</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.1998905441893197</v>
+        <v>0.158726690631628</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>104.57</v>
+        <v>47.5</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.02225336438831083</v>
+        <v>0.03126353851009656</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.04502283383722172</v>
+        <v>0.08101960592977964</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.01160875414876461</v>
+        <v>-0.01329454503038607</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.02519607543945312</v>
+        <v>0.05767090094383809</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.04526896066799857</v>
+        <v>0.03440770675211402</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.2211278421034955</v>
+        <v>-0.02624023803461284</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>-0.0311291712408025</v>
+        <v>0.04094323442573589</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>-0.02106319164620341</v>
+        <v>0.1983506587308117</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.4457658956519428</v>
+        <v>1.214577574837437</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.130748426228092</v>
+        <v>0.3034577720638751</v>
       </c>
     </row>
     <row r="42">
@@ -2846,37 +2846,37 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>96.02</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.006621218650893268</v>
+        <v>-0.0009372666219221726</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.0125462900812926</v>
+        <v>-0.003842188316267925</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.02517769905516343</v>
+        <v>-0.03345087853727169</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.02931663545854502</v>
+        <v>-0.02539876046173839</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.007974151463466805</v>
+        <v>0.01367473726861901</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.02472073776768524</v>
+        <v>0.04553772063685502</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.09796714996985401</v>
+        <v>0.1066541547177819</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.09075560291833451</v>
+        <v>0.08392481056134149</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.3103951530447566</v>
+        <v>0.3242515831530275</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.09429418816866475</v>
+        <v>0.09813778117808125</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>59.26</v>
+        <v>63.77</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.005770539089512194</v>
+        <v>-0.0157431770852039</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.001013472260481985</v>
+        <v>-0.01361177180735218</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.007536438952257085</v>
+        <v>-0.07284091902370371</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.038611309079846</v>
+        <v>-0.05497929334036877</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.03639290640315862</v>
+        <v>0.01408300074347424</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>-0.01078633131521167</v>
+        <v>0.07913371701274374</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1302466058922123</v>
+        <v>0.06971650430368181</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1626317541545088</v>
+        <v>0.07083019989520323</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.5962330114525469</v>
+        <v>0.6209838720234271</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1686884788761773</v>
+        <v>0.174698005267683</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>87.59</v>
+        <v>102.66</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.009915749425464249</v>
+        <v>-0.01826523896231191</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.008056127899174426</v>
+        <v>-0.03315122087916234</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.001368176352008144</v>
+        <v>0.007952922927083828</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.05154306675559228</v>
+        <v>-0.00029212950222679</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.05086778133418868</v>
+        <v>0.07348927021472496</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.02415917818882574</v>
+        <v>0.1672075267670885</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.03546527993676407</v>
+        <v>-0.06143281362114794</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.01522071105444556</v>
+        <v>-0.06672193154063732</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.4056219756362527</v>
+        <v>0.4112434422762465</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1201843806873473</v>
+        <v>0.1216757022652415</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>71.73</v>
+        <v>18.31</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.007160939728855453</v>
+        <v>0.03038823828182768</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.005683338455554132</v>
+        <v>0.06206494831959164</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.01048412924861986</v>
+        <v>0.03739375986836802</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.0220858234613196</v>
+        <v>0.000546460617418143</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.07432719106906349</v>
+        <v>-0.1257550605724144</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.03852714527555967</v>
+        <v>0.05330716518259293</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.03859017754181493</v>
+        <v>0.1079030588156</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>-0.01921716968611864</v>
+        <v>0.2698683960322041</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.01163774616571045</v>
+        <v>0.2399043901806452</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.003864296698024017</v>
+        <v>0.07430945813590495</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>13.33</v>
+        <v>71.37</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.001498161587428326</v>
+        <v>-0.005018828851299117</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.00224548905255384</v>
+        <v>0.001684249074835442</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.003009778929107698</v>
+        <v>-0.01721288836027801</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.0285493738016982</v>
+        <v>-0.02963970380316228</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.06980238205707034</v>
+        <v>0.08569024815587434</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.08019332556919223</v>
+        <v>-0.01899022766460412</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>-0.02352861618097801</v>
+        <v>0.03630716253886046</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-0.07036696165254519</v>
+        <v>-0.04090950800343462</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.1753096414534518</v>
+        <v>0.04393352739070222</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.05531983188912237</v>
+        <v>0.01443513342225988</v>
       </c>
     </row>
     <row r="47">
@@ -3126,37 +3126,37 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>225.61</v>
+        <v>223.53</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.00163729146022995</v>
+        <v>-0.009219457583562685</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.03096815774868833</v>
+        <v>-0.008560311705391288</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.04942275178448885</v>
+        <v>-0.0459667269832762</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.09990023497257317</v>
+        <v>-0.1085543418572408</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-0.02505346665852537</v>
+        <v>-0.01572242592232631</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.08525363284287069</v>
+        <v>-0.07583779524290513</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.1038007786400301</v>
+        <v>0.09533678555021718</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.1422404266257944</v>
+        <v>0.1366911666344395</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.9805071320254861</v>
+        <v>1.037672268484427</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.2558144334542416</v>
+        <v>0.2677825750135663</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>47.87</v>
+        <v>13.14</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.005195345086226655</v>
+        <v>-0.01425353199330526</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.006640375678426791</v>
+        <v>-0.01573033948661606</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.01522323943993553</v>
+        <v>-0.01867064925989104</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0.0012549164791964</v>
+        <v>-0.02013419143636008</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.01334722596038107</v>
+        <v>0.07572968786926682</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.02334682770671714</v>
+        <v>0.08471494866921314</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.07440644012020092</v>
+        <v>-0.04259754001786076</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>0.0220273484117155</v>
+        <v>-0.08304638371607587</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1339529961236887</v>
+        <v>0.1659366951456824</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.04279358526629107</v>
+        <v>0.05250699367640488</v>
       </c>
     </row>
     <row r="49">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -3238,37 +3238,37 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>18.98</v>
+        <v>85.7</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.0005266050027575853</v>
+        <v>-0.02157779961946227</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.04885995415672484</v>
+        <v>-0.002560535677276654</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.05374419144462206</v>
+        <v>-0.02491753847553424</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.04709306957695503</v>
+        <v>-0.05637527817426113</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.08376628864578151</v>
+        <v>0.02549151446847153</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.1331343010290345</v>
+        <v>0.03668043570430379</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>-0.09273425081178566</v>
+        <v>0.00521468423293614</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.1340450690537156</v>
+        <v>-0.01202462534912219</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.05241891175437563</v>
+        <v>0.4336496384182218</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.01717625762375441</v>
+        <v>0.1275808109966179</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>27.45</v>
+        <v>43.45</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.01665771582795261</v>
+        <v>0.008588647078887623</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0.01254150294847522</v>
+        <v>0.02091163911961158</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.003738204021443869</v>
+        <v>0.003232495617854436</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0.02662876318453455</v>
+        <v>-0.003668879733382369</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.1025455747810378</v>
+        <v>0.004766798516600002</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.08685723960865999</v>
+        <v>-0.05791259799145432</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.09920484676749575</v>
+        <v>0.03846100195062041</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.1727666600219941</v>
+        <v>0.08113466889117271</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.2724423514458192</v>
+        <v>0.5052759923154011</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.08362588799993276</v>
+        <v>0.1460547839709621</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>45.27</v>
+        <v>47.38</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.001770343737240276</v>
+        <v>-0.01023601158769105</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0.0002209928546486051</v>
+        <v>-0.0151735508828752</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.009625872577592065</v>
+        <v>-0.02730441472706546</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.02140073280782429</v>
+        <v>-0.0008434648328660144</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>0.009139541726120637</v>
+        <v>0.002551422763866773</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.06602023276972047</v>
+        <v>-0.02384357520648572</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.0006754221957898654</v>
+        <v>0.07175395842102539</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.01785805722952927</v>
+        <v>0.01370169017710099</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.2782235719014956</v>
+        <v>0.1365200299073068</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.08526452578959365</v>
+        <v>0.04357988150523462</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>43.08</v>
+        <v>253.27</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0.001162050968541273</v>
+        <v>0.001383860928552805</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0.008191020186471221</v>
+        <v>0.004880221469184542</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>0.007248103109027237</v>
+        <v>-0.04372286790330937</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.02335068612660951</v>
+        <v>-0.1170030466509449</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.01331158159496793</v>
+        <v>-0.06559974644764943</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.07640784216740126</v>
+        <v>-0.09257446652410972</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.006297981240340311</v>
+        <v>0.08752646038941614</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.05771779041813208</v>
+        <v>0.1661454306734349</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.5053237742063126</v>
+        <v>1.182242734771697</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.1460669102267749</v>
+        <v>0.2970827552985098</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>252.92</v>
+        <v>26.7</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.003977452589168928</v>
+        <v>-0.02732240361219163</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.03388215778469827</v>
+        <v>0.01714288620721716</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.0726699155792947</v>
+        <v>-0.04283920685477638</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.1034067090206388</v>
+        <v>0.02597604483295335</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.09787048785980845</v>
+        <v>0.1144245820178387</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.1187246602366264</v>
+        <v>0.06262174024597789</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.08369958194634819</v>
+        <v>-0.1090153882639195</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.17881408722577</v>
+        <v>-0.2032337400884392</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>1.099299691577555</v>
+        <v>0.26659382966547</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.2804367998951591</v>
+        <v>0.08196311605740836</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>112.03</v>
+        <v>44.95</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.01190684871074466</v>
+        <v>-0.00706869210489125</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.008496319166499289</v>
+        <v>0.01147619603939298</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>0.005655271497205572</v>
+        <v>-0.02027027644997359</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-8.927290386229192e-05</v>
+        <v>-0.02768762258211688</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-0.00697155659820714</v>
+        <v>0.0206630297115018</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.05143633727196661</v>
+        <v>-0.05606884142867063</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.02370962121664932</v>
+        <v>0.002059927800903916</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.005619632069683078</v>
+        <v>-0.009741339145669881</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.726980167831375</v>
+        <v>0.2764263230791328</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.1997638812817506</v>
+        <v>0.08475564108631506</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>46.06</v>
+        <v>18.53</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.007877474930886752</v>
+        <v>-0.02370910782107416</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0.01075272507676694</v>
+        <v>-0.02984291536335337</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.0002170245626098577</v>
+        <v>-0.08471227866112707</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.08401975885619772</v>
+        <v>-0.07280459741154144</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.08392994249123709</v>
+        <v>0.06862748117565709</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.1271555623700106</v>
+        <v>0.09644976952117768</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.01913093674887401</v>
+        <v>-0.1087061149282547</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.1945236933980603</v>
+        <v>-0.1628264193024984</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1.164224800351887</v>
+        <v>0.06210750629553297</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.293503048145056</v>
+        <v>0.02028811106855533</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>17.77</v>
+        <v>111.52</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0.007941083588286713</v>
+        <v>-0.004552371166540725</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.01659044182619263</v>
+        <v>0.00577200041036896</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.01023310424186086</v>
+        <v>-0.01466693459651336</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.03633405948424429</v>
+        <v>0.002426936117450929</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.2286712222590733</v>
+        <v>0.006482335681745166</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.0150527826355944</v>
+        <v>-0.04506287775799223</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.05812150966393848</v>
+        <v>-0.03208290959387627</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.2530581176000797</v>
+        <v>-0.01652592349878257</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.1569110099354967</v>
+        <v>0.7227123704266443</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.04978408559202196</v>
+        <v>0.1987747610899522</v>
       </c>
     </row>
     <row r="57">
@@ -3686,37 +3686,37 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>35.95</v>
+        <v>35.61</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.003909505285661696</v>
+        <v>-0.009457584015920117</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0.005594426935369379</v>
+        <v>0.01308674436710855</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.002497229475627361</v>
+        <v>-0.006694501366374617</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.03073603086973553</v>
+        <v>-0.05317734558742682</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.1025953484651687</v>
+        <v>-0.07025551034790967</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.03129605649027367</v>
+        <v>-0.01280661857892429</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.02051833114483048</v>
+        <v>-0.03004477716466425</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.08641455691387012</v>
+        <v>0.04900752210569514</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.3568123003589894</v>
+        <v>0.388658014840203</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.1070653483408104</v>
+        <v>0.1156597581662262</v>
       </c>
     </row>
     <row r="58">
@@ -3742,37 +3742,37 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>19.37</v>
+        <v>19.31</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.005851271446658757</v>
+        <v>-0.003201005540754864</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.01394899825597473</v>
+        <v>0.01402301881182599</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.01430026171929866</v>
+        <v>-0.02940885712787167</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.005659358827830197</v>
+        <v>0.01295906335369734</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.01143602438816682</v>
+        <v>0.0192693370286745</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.04078446243722467</v>
+        <v>0.0547966731439824</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.05505742971158822</v>
+        <v>-0.05455276361633499</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.1833312276465126</v>
+        <v>-0.1870927805776553</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1656846384150168</v>
+        <v>0.1763896197593489</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.05243114319141795</v>
+        <v>0.05564297328935841</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>53.63</v>
+        <v>100.75</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.005193818959179919</v>
+        <v>-0.02421307506053272</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.02826594668257154</v>
+        <v>0.00188944357616494</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.04521981811696707</v>
+        <v>-0.05292345740530724</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.008870810142709629</v>
+        <v>-0.0907039961638193</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>0.07702234386631335</v>
+        <v>-0.02318343648630483</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.08599407821122274</v>
+        <v>-0.04120455833381431</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.1501062791605733</v>
+        <v>-0.04128495582673952</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1305694675452015</v>
+        <v>-0.1510582855156206</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.0347624153533761</v>
+        <v>0.2682645453730856</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.01145573675288603</v>
+        <v>0.08243863249387484</v>
       </c>
     </row>
     <row r="60">
@@ -3840,51 +3840,51 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>103.25</v>
+        <v>51.74</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0.009582510893726859</v>
+        <v>-0.03524145724420102</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.01290629535195542</v>
+        <v>-0.04696996120939889</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.03051643192488263</v>
+        <v>-0.07126184654905809</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.05802390817385805</v>
+        <v>-0.04854724784469255</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.01261469178427499</v>
+        <v>0.03927486544082792</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.06792440406997369</v>
+        <v>-0.08635717948241239</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.03510706615291015</v>
+        <v>-0.1664974055921418</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1124011606248065</v>
+        <v>-0.1689897176092191</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2533050342577425</v>
+        <v>0.03673743031449295</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.07816590689284997</v>
+        <v>0.01209883787666199</v>
       </c>
     </row>
     <row r="61">
@@ -3896,51 +3896,51 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>93.91</v>
+        <v>49.13</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.003097638400122005</v>
+        <v>0.02268942822262909</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.02593091904406331</v>
+        <v>0.0484421772982695</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.03672165637610092</v>
+        <v>0.005731885419453464</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.05608598172150703</v>
+        <v>-0.06862557216843157</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>0.007327837714197871</v>
+        <v>-0.2272727327271257</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.08651547123782521</v>
+        <v>-0.07789034921664106</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.08649994652869564</v>
+        <v>0.0323597585751132</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.1721642643974406</v>
+        <v>0.1338564272319895</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1034488570147916</v>
+        <v>-0.1106946086589776</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.03335783430632522</v>
+        <v>-0.03835013479058325</v>
       </c>
     </row>
     <row r="62">
@@ -3952,51 +3952,51 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>48.04</v>
+        <v>91.05</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.006705777171803318</v>
+        <v>-0.03045469597298622</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.01253855274859705</v>
+        <v>-0.01418360274942365</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.02595293566944612</v>
+        <v>-0.07243276635182205</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.09986880500335049</v>
+        <v>-0.09976266955488355</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.3180011463587297</v>
+        <v>-0.01459133358363296</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1244760005342106</v>
+        <v>-0.07168526754113436</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0</v>
+        <v>-0.09010697209442187</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.143265121184724</v>
+        <v>-0.2177256522549379</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1727050566337196</v>
+        <v>0.1065213434611187</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.0612424202847941</v>
+        <v>0.03431605290294826</v>
       </c>
     </row>
   </sheetData>
@@ -4015,7 +4015,7 @@
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -4113,17 +4113,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -4158,17 +4158,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4602,21 +4602,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.2738706939008904</v>
+        <v>0.1845929481052861</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1377246131337508</v>
+        <v>-0.1312231203941401</v>
       </c>
     </row>
     <row r="18">
@@ -4647,21 +4647,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.2633923596158334</v>
+        <v>0.1653245839824891</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1034067090206388</v>
+        <v>-0.1170030466509449</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.2085942562754242</v>
+        <v>0.1279471224590254</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.09990023497257317</v>
+        <v>-0.1085543418572408</v>
       </c>
     </row>
     <row r="20">
@@ -4737,21 +4737,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1905103988209815</v>
+        <v>0.1194923965233143</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09986880500335049</v>
+        <v>-0.09976266955488355</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1144885878056472</v>
+        <v>0.1129943502824859</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.07527827465900394</v>
+        <v>-0.0907039961638193</v>
       </c>
     </row>
     <row r="22">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1091015417189676</v>
+        <v>0.1037653463263331</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.06488436186468072</v>
+        <v>-0.0893935290204152</v>
       </c>
     </row>
     <row r="23">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.09975896602394241</v>
+        <v>0.0947825601325134</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.05838173227624499</v>
+        <v>-0.07694361916711334</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.09895104496360929</v>
+        <v>0.07213448326906602</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.05802390817385805</v>
+        <v>-0.07280459741154144</v>
       </c>
     </row>
     <row r="25">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.09022059271573446</v>
+        <v>0.05767090094383809</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.05608598172150703</v>
+        <v>-0.06862557216843157</v>
       </c>
     </row>
     <row r="26">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.08401975885619772</v>
+        <v>0.04914068812022387</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.05154306675559228</v>
+        <v>-0.06611002460736537</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3330338350387942</v>
+        <v>0.3556578122779603</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.3180011463587297</v>
+        <v>-0.2272727327271257</v>
       </c>
     </row>
     <row r="32">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.3080568456189587</v>
+        <v>0.3177040733920622</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.2369785136923589</v>
+        <v>-0.1681141333150975</v>
       </c>
     </row>
     <row r="33">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2363636153222182</v>
+        <v>0.2620801676011537</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.2286712222590733</v>
+        <v>-0.1257550605724144</v>
       </c>
     </row>
     <row r="34">
@@ -5248,21 +5248,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2289821983098801</v>
+        <v>0.2509216467855004</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1054409651563527</v>
+        <v>-0.0871314262212155</v>
       </c>
     </row>
     <row r="35">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2264403169559062</v>
+        <v>0.2422667004701433</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1025953484651687</v>
+        <v>-0.07025551034790967</v>
       </c>
     </row>
     <row r="36">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1488425970281919</v>
+        <v>0.2394551063736847</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.09787048785980845</v>
+        <v>-0.06559974644764943</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1455804840276755</v>
+        <v>0.2339830523495059</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.09644163100698233</v>
+        <v>-0.04084190479572314</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1275527650539514</v>
+        <v>0.1649738133216709</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.08775580703392161</v>
+        <v>-0.03881509916104497</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1232143680144002</v>
+        <v>0.1571970742089035</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.08392994249123709</v>
+        <v>-0.03869242411185825</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1205983771082659</v>
+        <v>0.1538135212750593</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.07733261946376224</v>
+        <v>-0.03494555458690696</v>
       </c>
     </row>
     <row r="41"/>
@@ -5624,21 +5624,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.4666866198161983</v>
+        <v>0.5583173209957417</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5646,21 +5646,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1271555623700106</v>
+        <v>-0.09257446652410972</v>
       </c>
     </row>
     <row r="46">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4591567559091367</v>
+        <v>0.5424056682740872</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5691,21 +5691,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1244760005342106</v>
+        <v>-0.08635717948241239</v>
       </c>
     </row>
     <row r="47">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4512169702577657</v>
+        <v>0.5075940302433244</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5736,21 +5736,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1187246602366264</v>
+        <v>-0.07789034921664106</v>
       </c>
     </row>
     <row r="48">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4280576681887558</v>
+        <v>0.4280979542355605</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.08651547123782521</v>
+        <v>-0.07583779524290513</v>
       </c>
     </row>
     <row r="49">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4207216263949596</v>
+        <v>0.4167417392450008</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.08599407821122274</v>
+        <v>-0.07168526754113436</v>
       </c>
     </row>
     <row r="50">
@@ -5849,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3904281845596043</v>
+        <v>0.3717883636745891</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.08525363284287069</v>
+        <v>-0.05791259799145432</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3253376004786483</v>
+        <v>0.3627683649153985</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.07640784216740126</v>
+        <v>-0.05606884142867063</v>
       </c>
     </row>
     <row r="52">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3107218277520876</v>
+        <v>0.3318261013936057</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.07484011411747349</v>
+        <v>-0.04506287775799223</v>
       </c>
     </row>
     <row r="53">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2970321384628321</v>
+        <v>0.3071689584811568</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.06792440406997369</v>
+        <v>-0.04120455833381431</v>
       </c>
     </row>
     <row r="54">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2569253272869882</v>
+        <v>0.284928093674135</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.06602023276972047</v>
+        <v>-0.0292956566558642</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>1.05382612303641</v>
+        <v>1</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.1833312276465126</v>
+        <v>-0.2177256522549379</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.962238198420496</v>
+        <v>0.9408985562696393</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1727666600219941</v>
+        <v>-0.2032337400884392</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.8568221916336818</v>
+        <v>0.8848935168466907</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1721642643974406</v>
+        <v>-0.1870927805776553</v>
       </c>
     </row>
     <row r="62">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.7799142811192761</v>
+        <v>0.7371968229828241</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6292,21 +6292,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1340450690537156</v>
+        <v>-0.1689897176092191</v>
       </c>
     </row>
     <row r="63">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.760562149163108</v>
+        <v>0.7226636910873359</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6337,21 +6337,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1305694675452015</v>
+        <v>-0.1628264193024984</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.7176842127044878</v>
+        <v>0.7079626316260272</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1124011606248065</v>
+        <v>-0.1510582855156206</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.686901318166441</v>
+        <v>0.694682153373875</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.07036696165254519</v>
+        <v>-0.08304638371607587</v>
       </c>
     </row>
     <row r="66">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.667452058862966</v>
+        <v>0.5852715745905757</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.02106319164620341</v>
+        <v>-0.06672193154063732</v>
       </c>
     </row>
     <row r="67">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5989490097960306</v>
+        <v>0.579872193563151</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.01921716968611864</v>
+        <v>-0.04090950800343462</v>
       </c>
     </row>
     <row r="68">
@@ -6540,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.588710634750039</v>
+        <v>0.5596093312930568</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.005619632069683078</v>
+        <v>-0.01652592349878257</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.964793412676084</v>
+        <v>3.111172338906194</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1727050566337196</v>
+        <v>-0.1106946086589776</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.679270062354253</v>
+        <v>2.867205401750015</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6713,21 +6713,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.01163774616571045</v>
+        <v>0.03673743031449295</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.534399092100397</v>
+        <v>2.596867310194209</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6758,21 +6758,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.0347624153533761</v>
+        <v>0.04393352739070222</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>2.407407203910378</v>
+        <v>2.075471443483193</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.05241891175437563</v>
+        <v>0.06210750629553297</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.511630915221222</v>
+        <v>1.730913441463207</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1034488570147916</v>
+        <v>0.1065213434611187</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.311421134607436</v>
+        <v>1.460785001758269</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1339529961236887</v>
+        <v>0.1365200299073068</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.302076852454847</v>
+        <v>1.373721557431835</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6938,21 +6938,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1569110099354967</v>
+        <v>0.1659366951456824</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.270141500556228</v>
+        <v>1.336746340676706</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1656846384150168</v>
+        <v>0.1763896197593489</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.164224800351887</v>
+        <v>1.214577574837437</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,21 +7028,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1753096414534518</v>
+        <v>0.1892389933604923</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.142348894195174</v>
+        <v>1.182242734771697</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,21 +7073,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1962938855310372</v>
+        <v>0.2399043901806452</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -689,10 +689,10 @@
         <v>0.7371968229828241</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.8293010768228757</v>
+        <v>0.8293009141249108</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2230054621555577</v>
+        <v>0.2230054258975376</v>
       </c>
     </row>
     <row r="4">
@@ -745,10 +745,10 @@
         <v>0.9408985562696393</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.867205401750015</v>
+        <v>2.867205004002972</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.569636466569392</v>
+        <v>0.5696364127563478</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.7226636910873359</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.071876369692184</v>
+        <v>1.071876774194052</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2748368612886449</v>
+        <v>0.2748369442527103</v>
       </c>
     </row>
     <row r="6">
@@ -913,10 +913,10 @@
         <v>0.5418093449417154</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3586814592448035</v>
+        <v>0.3586817497709618</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1075734833613913</v>
+        <v>0.107573562305342</v>
       </c>
     </row>
     <row r="8">
@@ -969,10 +969,10 @@
         <v>0.487993027850691</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6955245130041994</v>
+        <v>0.695524201367286</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1924349345320844</v>
+        <v>0.1924348614756817</v>
       </c>
     </row>
     <row r="9">
@@ -1025,10 +1025,10 @@
         <v>0.4616247083759673</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.6481906429046367</v>
+        <v>0.6481905429408303</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1812336621235247</v>
+        <v>0.1812336382426676</v>
       </c>
     </row>
     <row r="10">
@@ -1081,10 +1081,10 @@
         <v>0.5852715745905757</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>3.111172338906194</v>
+        <v>3.111172666190555</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.6019731306835652</v>
+        <v>0.6019731731938027</v>
       </c>
     </row>
     <row r="11">
@@ -1137,10 +1137,10 @@
         <v>0.5596093312930568</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.336746340676706</v>
+        <v>1.336746610247214</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3269987805055903</v>
+        <v>0.3269988315337677</v>
       </c>
     </row>
     <row r="12">
@@ -1193,10 +1193,10 @@
         <v>0.694682153373875</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.460785001758269</v>
+        <v>1.460784815462409</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3500749847253546</v>
+        <v>0.3500749506558216</v>
       </c>
     </row>
     <row r="13">
@@ -1249,10 +1249,10 @@
         <v>0.7079626316260272</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2782045878132156</v>
+        <v>0.2782044714732328</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.08525915300504705</v>
+        <v>0.08525912007890568</v>
       </c>
     </row>
     <row r="14">
@@ -1361,10 +1361,10 @@
         <v>0.2792812432814875</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.098239022357925</v>
+        <v>1.098239174786805</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2802211170652118</v>
+        <v>0.2802211480662344</v>
       </c>
     </row>
     <row r="16">
@@ -1470,7 +1470,7 @@
         <v>0.2566672952342508</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2650942787961621</v>
+        <v>0.2650944086820115</v>
       </c>
       <c r="O17" s="6" t="n">
         <v>1.025467934419773</v>
@@ -1576,13 +1576,13 @@
         <v>0.09615240423470617</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1034564999671641</v>
+        <v>0.1034564268431555</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>0.3048555547266474</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.4110794833421747</v>
+        <v>0.4110793637638395</v>
       </c>
       <c r="O19" s="6" t="n">
         <v>0.2828911477020941</v>
@@ -1635,16 +1635,16 @@
         <v>0.2766966678519367</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2010209373161254</v>
+        <v>0.201021033936237</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>0.2085605727286821</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1892389933604923</v>
+        <v>0.1892387091593783</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05947256107073118</v>
+        <v>0.05947247667409661</v>
       </c>
     </row>
     <row r="21">
@@ -1688,19 +1688,19 @@
         <v>0.08445122726393839</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1053003446257199</v>
+        <v>0.1053004278912795</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2446699086573025</v>
+        <v>0.2446698030696572</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2762755252712941</v>
+        <v>0.2762754142532411</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.7260106088445308</v>
+        <v>0.7260102027552027</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1995393159525582</v>
+        <v>0.1995392218781746</v>
       </c>
     </row>
     <row r="22">
@@ -1744,19 +1744,19 @@
         <v>0.01216008213632214</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.09048885566992149</v>
+        <v>0.09048878003327498</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2245819818569381</v>
+        <v>0.2245818864751348</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.4318323310015413</v>
+        <v>0.431832200602583</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>1.373721557431835</v>
+        <v>1.373721915816523</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.3339613850242129</v>
+        <v>0.3339614521580783</v>
       </c>
     </row>
     <row r="23">
@@ -1806,13 +1806,13 @@
         <v>0.1649052784000498</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1617050584531476</v>
+        <v>0.1617049198942129</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8640882685783282</v>
+        <v>0.8640880901985022</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2307093246148979</v>
+        <v>0.2307092853582229</v>
       </c>
     </row>
     <row r="24">
@@ -1865,10 +1865,10 @@
         <v>0.4414827603526339</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3260340108876301</v>
+        <v>0.3260339199859605</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.09863025399006009</v>
+        <v>0.09863022888579542</v>
       </c>
     </row>
     <row r="25">
@@ -1915,7 +1915,7 @@
         <v>0.161529390486713</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1523306633392316</v>
+        <v>0.1523307373948874</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>0.1453142186276402</v>
@@ -1977,10 +1977,10 @@
         <v>0.1253303268742494</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.131458338521429</v>
+        <v>1.131458517843785</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2869419256820018</v>
+        <v>0.2869419617726989</v>
       </c>
     </row>
     <row r="27">
@@ -2089,10 +2089,10 @@
         <v>0.2685790899719309</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.895001272011722</v>
+        <v>0.8950011214518443</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.237475193900438</v>
+        <v>0.2374751611275279</v>
       </c>
     </row>
     <row r="29">
@@ -2145,10 +2145,10 @@
         <v>0.2937587064428935</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6423394953121422</v>
+        <v>0.6423391743065112</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1798341946751709</v>
+        <v>0.1798341178064833</v>
       </c>
     </row>
     <row r="30">
@@ -2201,10 +2201,10 @@
         <v>0.09377401595148704</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6645290096017822</v>
+        <v>0.6645291716939186</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1851239900887047</v>
+        <v>0.1851240285578997</v>
       </c>
     </row>
     <row r="31">
@@ -2251,16 +2251,16 @@
         <v>0.03889544770130637</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1865315754684489</v>
+        <v>0.1865314834479119</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1363733023434974</v>
+        <v>0.1363732179384907</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3691718008964413</v>
+        <v>0.3691715558366797</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1104166930784283</v>
+        <v>0.1104166268295066</v>
       </c>
     </row>
     <row r="32">
@@ -2307,16 +2307,16 @@
         <v>0.05934686592066329</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1209597775756002</v>
+        <v>0.1209598803933079</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1203949762268566</v>
+        <v>0.12039507894098</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4509971933808001</v>
+        <v>0.4509973656553068</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1321106019129019</v>
+        <v>0.1321106467174424</v>
       </c>
     </row>
     <row r="33">
@@ -2425,10 +2425,10 @@
         <v>0.00190074787826866</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.9001315173743343</v>
+        <v>0.9001313018687465</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.2385909065963518</v>
+        <v>0.2385908597709492</v>
       </c>
     </row>
     <row r="35">
@@ -2478,13 +2478,13 @@
         <v>0.1364783039752977</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.09491778715319232</v>
+        <v>0.09491791057057375</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.2426716245196499</v>
+        <v>0.24267170400664</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.07510808345954989</v>
+        <v>0.07510810638250121</v>
       </c>
     </row>
     <row r="36">
@@ -2531,16 +2531,16 @@
         <v>0.09115168361766046</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.1015157910132678</v>
+        <v>0.1015156794425087</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.1839438485193794</v>
+        <v>0.1839439774129443</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.4208287690074275</v>
+        <v>0.4208289546392883</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1242094908175355</v>
+        <v>0.1242095397770102</v>
       </c>
     </row>
     <row r="37">
@@ -2590,13 +2590,13 @@
         <v>0.1413659774569282</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1861879374848869</v>
+        <v>0.1861878395568077</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.7832817164547279</v>
+        <v>0.783281827119708</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2126626056522343</v>
+        <v>0.2126626307369379</v>
       </c>
     </row>
     <row r="38">
@@ -2649,10 +2649,10 @@
         <v>0.1748144972418435</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.6536235852820245</v>
+        <v>0.653623760595974</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.18253014156926</v>
+        <v>0.1825301833591053</v>
       </c>
     </row>
     <row r="39">
@@ -2702,13 +2702,13 @@
         <v>0.1360441630376696</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.2203256602454855</v>
+        <v>0.2203257697343111</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.3744414860936403</v>
+        <v>0.3744416249835918</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.1118394644329928</v>
+        <v>0.1118395018841625</v>
       </c>
     </row>
     <row r="40">
@@ -2870,13 +2870,13 @@
         <v>0.1066541547177819</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.08392481056134149</v>
+        <v>0.08392499744185256</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.3242515831530275</v>
+        <v>0.3242514436843817</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.09813778117808125</v>
+        <v>0.09813774262654618</v>
       </c>
     </row>
     <row r="43">
@@ -2923,16 +2923,16 @@
         <v>0.07913371701274374</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.06971650430368181</v>
+        <v>0.06971657275488385</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.07083019989520323</v>
+        <v>0.07083026848901031</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.6209838720234271</v>
+        <v>0.6209841863862107</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.174698005267683</v>
+        <v>0.1746980812053727</v>
       </c>
     </row>
     <row r="44">
@@ -3041,10 +3041,10 @@
         <v>0.2698683960322041</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.2399043901806452</v>
+        <v>0.2399044702540285</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.07430945813590495</v>
+        <v>0.07430948126230952</v>
       </c>
     </row>
     <row r="46">
@@ -3097,10 +3097,10 @@
         <v>-0.04090950800343462</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.04393352739070222</v>
+        <v>0.04393364388913956</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.01443513342225988</v>
+        <v>0.01443517115777349</v>
       </c>
     </row>
     <row r="47">
@@ -3153,10 +3153,10 @@
         <v>0.1366911666344395</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>1.037672268484427</v>
+        <v>1.037672126767117</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.2677825750135663</v>
+        <v>0.2677825456227196</v>
       </c>
     </row>
     <row r="48">
@@ -3206,13 +3206,13 @@
         <v>-0.04259754001786076</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.08304638371607587</v>
+        <v>-0.0830463226922441</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1659366951456824</v>
+        <v>0.1659365964826145</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.05250699367640488</v>
+        <v>0.0525069639882374</v>
       </c>
     </row>
     <row r="49">
@@ -3259,10 +3259,10 @@
         <v>0.03668043570430379</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.00521468423293614</v>
+        <v>0.005214594277611173</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.01202462534912219</v>
+        <v>-0.01202471224545909</v>
       </c>
       <c r="O49" s="6" t="n">
         <v>0.4336496384182218</v>
@@ -3321,10 +3321,10 @@
         <v>0.08113466889117271</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.5052759923154011</v>
+        <v>0.5052760917809291</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1460547839709621</v>
+        <v>0.1460548092139391</v>
       </c>
     </row>
     <row r="51">
@@ -3374,7 +3374,7 @@
         <v>0.07175395842102539</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.01370169017710099</v>
+        <v>0.01370177291136132</v>
       </c>
       <c r="O51" s="6" t="n">
         <v>0.1365200299073068</v>
@@ -3427,16 +3427,16 @@
         <v>-0.09257446652410972</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.08752646038941614</v>
+        <v>0.08752653164452462</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.1661454306734349</v>
+        <v>0.1661453487436695</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>1.182242734771697</v>
+        <v>1.18224302167958</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.2970827552985098</v>
+        <v>0.2970828121426676</v>
       </c>
     </row>
     <row r="53">
@@ -3486,13 +3486,13 @@
         <v>-0.1090153882639195</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>-0.2032337400884392</v>
+        <v>-0.2032338307891363</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.26659382966547</v>
+        <v>0.266593944267836</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.08196311605740836</v>
+        <v>0.08196314868968724</v>
       </c>
     </row>
     <row r="54">
@@ -3601,10 +3601,10 @@
         <v>-0.1628264193024984</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.06210750629553297</v>
+        <v>0.06210739017966938</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.02028811106855533</v>
+        <v>0.02028807388724707</v>
       </c>
     </row>
     <row r="56">
@@ -3657,10 +3657,10 @@
         <v>-0.01652592349878257</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.7227123704266443</v>
+        <v>0.7227129795205847</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.1987747610899522</v>
+        <v>0.1987749023722636</v>
       </c>
     </row>
     <row r="57">
@@ -3713,10 +3713,10 @@
         <v>0.04900752210569514</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.388658014840203</v>
+        <v>0.3886581181279356</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.1156597581662262</v>
+        <v>0.1156597858269757</v>
       </c>
     </row>
     <row r="58">
@@ -3819,16 +3819,16 @@
         <v>-0.04120455833381431</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.04128495582673952</v>
+        <v>-0.04128488622435222</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1510582855156206</v>
+        <v>-0.1510583400914997</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.2682645453730856</v>
+        <v>0.2682646671779869</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.08243863249387484</v>
+        <v>0.08243866714656267</v>
       </c>
     </row>
     <row r="60">
@@ -3881,10 +3881,10 @@
         <v>-0.1689897176092191</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.03673743031449295</v>
+        <v>0.03673735106962184</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.01209883787666199</v>
+        <v>0.01209881208946917</v>
       </c>
     </row>
     <row r="61">
@@ -3937,10 +3937,10 @@
         <v>0.1338564272319895</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>-0.1106946086589776</v>
+        <v>-0.1106945472523587</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>-0.03835013479058325</v>
+        <v>-0.03835011265657984</v>
       </c>
     </row>
     <row r="62">
@@ -3984,7 +3984,7 @@
         <v>-0.01459133358363296</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.07168526754113436</v>
+        <v>-0.07168519533058848</v>
       </c>
       <c r="M62" s="6" t="n">
         <v>-0.09010697209442187</v>
@@ -3993,10 +3993,10 @@
         <v>-0.2177256522549379</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>0.1065213434611187</v>
+        <v>0.1065214460569559</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>0.03431605290294826</v>
+        <v>0.03431608486995263</v>
       </c>
     </row>
   </sheetData>
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.07168526754113436</v>
+        <v>-0.07168519533058848</v>
       </c>
     </row>
     <row r="50">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2032337400884392</v>
+        <v>-0.2032338307891363</v>
       </c>
     </row>
     <row r="61">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1510582855156206</v>
+        <v>-0.1510583400914997</v>
       </c>
     </row>
     <row r="65">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.08304638371607587</v>
+        <v>-0.0830463226922441</v>
       </c>
     </row>
     <row r="66">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.111172338906194</v>
+        <v>3.111172666190555</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1106946086589776</v>
+        <v>-0.1106945472523587</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.867205401750015</v>
+        <v>2.867205004002972</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.03673743031449295</v>
+        <v>0.03673735106962184</v>
       </c>
     </row>
     <row r="75">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.04393352739070222</v>
+        <v>0.04393364388913956</v>
       </c>
     </row>
     <row r="76">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.06210750629553297</v>
+        <v>0.06210739017966938</v>
       </c>
     </row>
     <row r="77">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1065213434611187</v>
+        <v>0.1065214460569559</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.460785001758269</v>
+        <v>1.460784815462409</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.373721557431835</v>
+        <v>1.373721915816523</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1659366951456824</v>
+        <v>0.1659365964826145</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.336746340676706</v>
+        <v>1.336746610247214</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1892389933604923</v>
+        <v>0.1892387091593783</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.182242734771697</v>
+        <v>1.18224302167958</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2399043901806452</v>
+        <v>0.2399044702540285</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -490,12 +490,12 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.01570049741949309</v>
+        <v>-0.01226986901545934</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.03197208979596855</v>
+        <v>-0.0289505153465065</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.08197807441597171</v>
+        <v>0.06905710045654145</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.1845929481052861</v>
+        <v>0.1700581477953975</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3177040733920622</v>
+        <v>0.3015360170104044</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5583173209957417</v>
+        <v>0.5692007819013811</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7621620796822213</v>
+        <v>0.8233296172795852</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1</v>
+        <v>0.9189510992431646</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.075471443483193</v>
+        <v>2.037735811710868</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4542438403115807</v>
+        <v>0.4482715530915167</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>39.23</v>
+        <v>38.6</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.0135780967893333</v>
+        <v>-0.01605916582886913</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.01109147080963135</v>
+        <v>-0.03980105120528776</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.0542430092774947</v>
+        <v>-0.04996314399772939</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1279471224590254</v>
+        <v>0.1098332325732603</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3556578122779603</v>
+        <v>0.3274916531260985</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3318261013936057</v>
+        <v>0.2818372654801797</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4808369308216673</v>
+        <v>0.4819770858513499</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7371968229828241</v>
+        <v>0.7138820653594284</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.8293009141249108</v>
+        <v>0.7999240274792483</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2230054258975376</v>
+        <v>0.2164232847917735</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>573.73</v>
+        <v>95.27</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.01185159095498634</v>
+        <v>0.009429957782884024</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.05229083910638499</v>
+        <v>0.05973298137977978</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.03222261327142917</v>
+        <v>-0.002826086140606865</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.01539391033184712</v>
+        <v>0.08224466618386739</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.04084190479572314</v>
+        <v>0.1928344319429605</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5075940302433244</v>
+        <v>0.1623753799502441</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5615661691385256</v>
+        <v>0.4624092642460784</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.9408985562696393</v>
+        <v>0.9022979877554096</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.867205004002972</v>
+        <v>1.756665535645811</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5696364127563478</v>
+        <v>0.4021506970420319</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>161.93</v>
+        <v>574.29</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.01147674080234351</v>
+        <v>0.0009760646604806134</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.008996335836061187</v>
+        <v>0.04325315797736873</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.04240102406232449</v>
+        <v>0.03332306141974684</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.02897628328194379</v>
+        <v>-0.01443287112322811</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.2620801676011537</v>
+        <v>-0.02829060669363592</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.3071689584811568</v>
+        <v>0.4562212773228167</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3150993278673451</v>
+        <v>0.5611841327505613</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7226636910873359</v>
+        <v>0.9343774756852821</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.071876774194052</v>
+        <v>2.870979646142213</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2748369442527103</v>
+        <v>0.5701469355686981</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>94.38</v>
+        <v>159.38</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.04103235650831261</v>
+        <v>-0.01574747056324755</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.05759748445416779</v>
+        <v>-0.03622174766426201</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.02014122142392927</v>
+        <v>-0.05350670787750955</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.07213448326906602</v>
+        <v>0.01277250955068165</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1649738133216709</v>
+        <v>0.2143131175831314</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.1844993678495279</v>
+        <v>0.2550067336383881</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.4371473590769412</v>
+        <v>0.3207710932588266</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.8848935168466907</v>
+        <v>0.6857176518055275</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.730913441463207</v>
+        <v>1.039249756615742</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3977708473178709</v>
+        <v>0.2681096469267428</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>193.91</v>
+        <v>195.01</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.01677938668967349</v>
+        <v>0.005672687452697334</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.006174773940788025</v>
+        <v>0.009577504709322282</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.06118321127331683</v>
+        <v>0.0571939033339286</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.1653245839824891</v>
+        <v>0.1719351061283665</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1571970742089035</v>
+        <v>0.1945492101268345</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1920035748609386</v>
+        <v>0.2158779884097399</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4692599213972073</v>
+        <v>0.4729821544547015</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5418093449417154</v>
+        <v>0.5464698135162032</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3586817497709618</v>
+        <v>0.3663889805979699</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.107573562305342</v>
+        <v>0.1096638812938833</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>70.38</v>
+        <v>100.11</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.007754166775573501</v>
+        <v>0.01634518386143724</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.003994276539110553</v>
+        <v>0.01438847029909018</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.04336009860865442</v>
+        <v>-0.005167411877761374</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.001985243850152751</v>
+        <v>0.1311864475745939</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2339830523495059</v>
+        <v>0.2887011248914635</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.284928093674135</v>
+        <v>-0.02149273756748038</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.251270806960979</v>
+        <v>0.291287110823844</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.487993027850691</v>
+        <v>0.6301047697667759</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.695524201367286</v>
+        <v>3.178370539305554</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1924348614756817</v>
+        <v>0.6106542278098561</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>207.33</v>
+        <v>495.65</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.02165909955431111</v>
+        <v>-0.0006653838512311605</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.016554432083843</v>
+        <v>0.03888071170752405</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.04191308836066021</v>
+        <v>0.01006705085983262</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.04865709772146176</v>
+        <v>-0.08999943186103165</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2422667004701433</v>
+        <v>-0.1412685644336509</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.2384257651581065</v>
+        <v>0.4982736806758969</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2223305333468273</v>
+        <v>0.447249079221482</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.4616247083759673</v>
+        <v>0.6884879275121565</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.6481905429408303</v>
+        <v>1.459147635156747</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1812336382426676</v>
+        <v>0.3497754789224914</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>98.5</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.007956500234091557</v>
+        <v>-0.01506106280136676</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.04464947548621101</v>
+        <v>-0.03008257295588379</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.04182882221893358</v>
+        <v>-0.0479329485069816</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.1129943502824859</v>
+        <v>-0.01701640676921634</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.2394551063736847</v>
+        <v>0.1903768760148632</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>-0.02562636107001093</v>
+        <v>0.2593808750343316</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.3339273566760261</v>
+        <v>0.2445445854999959</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5852715745905757</v>
+        <v>0.4634300375420353</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>3.111172666190555</v>
+        <v>0.6699879583609072</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.6019731731938027</v>
+        <v>0.1864181442742121</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>154.54</v>
+        <v>110.96</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.0008405307063525935</v>
+        <v>0.007079313642552654</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.01825122840939719</v>
+        <v>0.01444507104341985</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.01697806303156857</v>
+        <v>0.01231638049998884</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.01331059505877752</v>
+        <v>-0.03864147595934253</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.0003310754291956375</v>
+        <v>0.1668945562915991</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3627683649153985</v>
+        <v>0.4183816224346126</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4367375571115113</v>
+        <v>0.3019325312667482</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5596093312930568</v>
+        <v>0.292837676557081</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.336746610247214</v>
+        <v>1.113093268002212</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3269988315337677</v>
+        <v>0.2832350760480551</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>495.98</v>
+        <v>154.16</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.009217618611816247</v>
+        <v>-0.002458843280262579</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.04873875344664147</v>
+        <v>0.0127447275380943</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.01028663635526139</v>
+        <v>0.01447747335510896</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.0893935290204152</v>
+        <v>0.01081902311129834</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>-0.1681141333150975</v>
+        <v>0.01176874938723738</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.5424056682740872</v>
+        <v>0.3387599128794934</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.4437511065359732</v>
+        <v>0.4316247128044373</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.694682153373875</v>
+        <v>0.5482365510853715</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.460784815462409</v>
+        <v>1.331000916546931</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3500749506558216</v>
+        <v>0.3259103114923383</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>428.57</v>
+        <v>429.35</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.002432597824459926</v>
+        <v>0.001820003187266384</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.003958963694891793</v>
+        <v>-0.01656049450529096</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.05639775381479128</v>
+        <v>0.06043766282749785</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.1037653463263331</v>
+        <v>0.1057742027746411</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-0.002884972991364587</v>
+        <v>0.02043970553420227</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1479656677438106</v>
+        <v>0.1324910625481566</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4436895684109619</v>
+        <v>0.4335014640238939</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.7079626316260272</v>
+        <v>0.7196261762205589</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2782044714732328</v>
+        <v>0.2805308076852924</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.08525912007890568</v>
+        <v>0.08591711274314218</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>111.19</v>
+        <v>205.49</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.001802005419282882</v>
+        <v>-0.008874723009890118</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.02630613069827903</v>
+        <v>-0.03886808905508776</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.02093470482629423</v>
+        <v>-0.04525386994248193</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.01063448313069526</v>
+        <v>0.03935055644682861</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.04560848477091306</v>
+        <v>0.2135032424982086</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.2185205747003425</v>
+        <v>0.2007065868156697</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.3883842641420387</v>
+        <v>0.2322190073472024</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.579872193563151</v>
+        <v>0.4412549958877068</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8323040117547906</v>
+        <v>0.6335633084047101</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.223674314699327</v>
+        <v>0.1777288759896727</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>110.18</v>
+        <v>111.1</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.005146724106764977</v>
+        <v>-0.0008094609704913935</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01493069460641705</v>
+        <v>0.007618323250645043</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.01933577609487358</v>
+        <v>0.02302025815033271</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.04539939305924712</v>
+        <v>0.00981641396116828</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1384583766779859</v>
+        <v>0.04407475472798739</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.4167417392450008</v>
+        <v>0.2077399831952609</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2974964446122748</v>
+        <v>0.3847072194275327</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.2792812432814875</v>
+        <v>0.6073726931290087</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.098239174786805</v>
+        <v>0.8308207180811742</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2802211480662344</v>
+        <v>0.2233440277384586</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>98.41</v>
+        <v>99.47</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.00856335337323999</v>
+        <v>0.0107712378736744</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.03950570999789993</v>
+        <v>0.01884670714994563</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.06738052698207908</v>
+        <v>-0.02880293888871255</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.0947825601325134</v>
+        <v>0.1065747235076508</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.2509216467855004</v>
+        <v>0.2819951787022772</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>-0.0292956566558642</v>
+        <v>-0.02899259224834472</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2522071969220399</v>
+        <v>0.2227535497908577</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4741929297507788</v>
+        <v>0.4987647409439147</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>2.596867310194209</v>
+        <v>2.635610277042516</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.5321741784141569</v>
+        <v>0.5376557176558776</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>94.01000000000001</v>
+        <v>94.48</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.006131665335817549</v>
+        <v>0.004999481012903706</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.02276501955805665</v>
+        <v>0.0100492028245236</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.01676403922891789</v>
+        <v>0.008755067934680838</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.03924370360523011</v>
+        <v>-0.03444042074337672</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.09242831107073513</v>
+        <v>0.1211910533472085</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.4280979542355605</v>
+        <v>0.429174368698803</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.2566672952342508</v>
+        <v>0.2557703893241372</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2650944086820115</v>
+        <v>0.2739769756510266</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.025467934419773</v>
+        <v>1.0355940555976</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.265246440120209</v>
+        <v>0.2673514264676664</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>27.23</v>
+        <v>27.36</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.02015118225412227</v>
+        <v>0.004774185468258585</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.0247134861093169</v>
+        <v>-0.002915449057909525</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.009097525624618519</v>
+        <v>-0.004366773430994009</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.001832886479128937</v>
+        <v>0.002932548449136041</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1538135212750593</v>
+        <v>0.1793103323538441</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.3717883636745891</v>
+        <v>0.3762576340720791</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1762419002564581</v>
+        <v>0.1757627878010344</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1823707655391555</v>
+        <v>0.1818574972438194</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.3500247614892222</v>
+        <v>0.3564700300873134</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1052162067438587</v>
+        <v>0.1069722508593762</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>31.76</v>
+        <v>31.87</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.01049952021959455</v>
+        <v>0.003463495263187344</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.003138743865473637</v>
+        <v>-0.002503909915359093</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.0399475860111782</v>
+        <v>0.04150328241605972</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.1194923965233143</v>
+        <v>0.1233697531358471</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.09615240423470617</v>
+        <v>0.1258346367742422</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1034564268431555</v>
+        <v>0.1068976191881539</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.3048555547266474</v>
+        <v>0.310963449206485</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.4110793637638395</v>
+        <v>0.420896104450504</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2828911477020941</v>
+        <v>0.2873343359338283</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.0865839092461691</v>
+        <v>0.08783689522549598</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>56.95</v>
+        <v>56.19</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.008185256373972716</v>
+        <v>0.003930630716593386</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.00835799302952589</v>
+        <v>0.007169702538404321</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.0008771795975534014</v>
+        <v>0.01279738807373532</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.002102662213535056</v>
+        <v>0.05326447273497714</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.09241526192361116</v>
+        <v>0.09832069545112287</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.2766966678519367</v>
+        <v>0.1162233612060712</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.201021033936237</v>
+        <v>0.255623054054918</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.2085605727286821</v>
+        <v>0.2767199987241356</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1892387091593783</v>
+        <v>0.7327945114753056</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05947247667409661</v>
+        <v>0.2011088157434207</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>55.97</v>
+        <v>56.74</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.004486719212545731</v>
+        <v>-0.003687429001920428</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.00196921964106056</v>
+        <v>-0.01578490586862535</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.02490387465942945</v>
+        <v>-0.01167040882644266</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.04914068812022387</v>
+        <v>-0.005782337797828108</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.08445122726393839</v>
+        <v>0.0677202513620494</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1053004278912795</v>
+        <v>0.2680255254692037</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2446698030696572</v>
+        <v>0.1975938542727964</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2762754142532411</v>
+        <v>0.1822654589382349</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.7260102027552027</v>
+        <v>0.1848534758530176</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1995392218781746</v>
+        <v>0.0581686295648185</v>
       </c>
     </row>
     <row r="22">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>119.95</v>
+        <v>119.19</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01121222534871746</v>
+        <v>-0.006335927687967091</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.03610607606790595</v>
+        <v>-0.002260142684878841</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.008185922549850289</v>
+        <v>-0.009309243952415835</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.03637462555881488</v>
+        <v>0.02980823087363027</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.01216008213632214</v>
+        <v>0.02731738656827365</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.09048878003327498</v>
+        <v>0.06510889935618147</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2245818864751348</v>
+        <v>0.2012870038006798</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.431832200602583</v>
+        <v>0.4350491766445133</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>1.373721915816523</v>
+        <v>1.358681829292578</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.3339614521580783</v>
+        <v>0.3311381196423833</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>74.31</v>
+        <v>73.77</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.01275407369851511</v>
+        <v>-0.0002710973331445654</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.02327175362288547</v>
+        <v>-0.00659851170304504</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.0002691278349004067</v>
+        <v>-0.02831930423779105</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.02493113172423622</v>
+        <v>-0.003242879154661926</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.06231634340051251</v>
+        <v>-0.0575358293431979</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.1581985633760177</v>
+        <v>0.03719879400141535</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1649052784000498</v>
+        <v>0.1567780583564404</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1617049198942129</v>
+        <v>0.49503504275513</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8640880901985022</v>
+        <v>0.3256743448495794</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2307092853582229</v>
+        <v>0.0985309162360104</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>73.79000000000001</v>
+        <v>73.45</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.005257473551415259</v>
+        <v>-0.01157314814434551</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.01231425753204862</v>
+        <v>-0.01064117643129514</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.03655823940780201</v>
+        <v>-0.01515158025032348</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.002972587682110395</v>
+        <v>-0.03621574818773099</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>-0.03869242411185825</v>
+        <v>0.03705156734506931</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.07448456019113592</v>
+        <v>0.1476235053518082</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1645264204904957</v>
+        <v>0.1537332871148362</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.4414827603526339</v>
+        <v>0.1601236542907336</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.3260339199859605</v>
+        <v>0.8425147225765248</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.09863022888579542</v>
+        <v>0.2259431243394578</v>
       </c>
     </row>
     <row r="25">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>68.40000000000001</v>
+        <v>67.67</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01355631470516916</v>
+        <v>-0.01067256345977419</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.02165802305797992</v>
+        <v>-0.00994879766432244</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.0005844668921745066</v>
+        <v>-0.01499270487701576</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.02243818304178735</v>
+        <v>-0.032871273569126</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.07097544347706419</v>
+        <v>0.04522063883824279</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.161529390486713</v>
+        <v>0.1516469995852865</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1523307373948874</v>
+        <v>0.1407876202441256</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1453142186276402</v>
+        <v>0.1418656713968034</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.9438445509768034</v>
+        <v>0.9230985381693011</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2480170267923056</v>
+        <v>0.2435612457101448</v>
       </c>
     </row>
     <row r="26">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>193.29</v>
+        <v>142.94</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.01613566791917764</v>
+        <v>-0.0009086801996024407</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.009927341567185</v>
+        <v>-0.01277706285316715</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.01773557025517802</v>
+        <v>-0.02243194331770026</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.02677287270190076</v>
+        <v>-0.03471096249385985</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.07660263318391025</v>
+        <v>0.08120252571396391</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1540831280028023</v>
+        <v>0.1006633436623521</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.09030702057901352</v>
+        <v>0.1061516198681149</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1253303268742494</v>
+        <v>0.1146748151770767</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.131458517843785</v>
+        <v>0.6650712804711683</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2869419617726989</v>
+        <v>0.1852526728245578</v>
       </c>
     </row>
     <row r="27">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>143.07</v>
+        <v>191.63</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.01710628109465773</v>
+        <v>-0.00858807212468049</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.005214851632633022</v>
+        <v>0.004244825110070849</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.01555077739187793</v>
+        <v>-0.01708043555795502</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.03383302569479885</v>
+        <v>0.01795487321547151</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.09032681421291744</v>
+        <v>0.06634962599072391</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.08589935647953251</v>
+        <v>0.1447828537039761</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1146601703523074</v>
+        <v>0.07421971361814128</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1107978777849807</v>
+        <v>0.1039782078242055</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.6665856738739588</v>
+        <v>1.113153398361779</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1856118956707713</v>
+        <v>0.2832472478809802</v>
       </c>
     </row>
     <row r="28">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>181.97</v>
+        <v>180.13</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.01664895042227865</v>
+        <v>-0.01011153665740194</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.03704336897920468</v>
+        <v>0.02620638144764897</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.01426897891053569</v>
+        <v>-0.003871022181906381</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.02392314343344126</v>
+        <v>-0.03379278034905575</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.03494555458690696</v>
+        <v>-0.03604781072208796</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1021453209552861</v>
+        <v>0.07935306841196677</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.1888316128935785</v>
+        <v>0.1824116048415474</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.2685790899719309</v>
+        <v>0.2586232484826154</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.8950011214518443</v>
+        <v>0.8758398971839521</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2374751611275279</v>
+        <v>0.2332901309756608</v>
       </c>
     </row>
     <row r="29">
@@ -2118,37 +2118,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>24.04</v>
+        <v>23.84</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.01563163658811995</v>
+        <v>-0.008319498973491046</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.02778971965970101</v>
+        <v>0.0214224505883116</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.001249507969992347</v>
+        <v>-0.00334447840513763</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.001666704813639397</v>
+        <v>-0.006666660308837891</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.03881509916104497</v>
+        <v>-0.03992664775251586</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.02314426556211968</v>
+        <v>0.004409217916488739</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.2150044599094483</v>
+        <v>0.2055016825774747</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2937587064428935</v>
+        <v>0.2933201328519186</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6423391743065112</v>
+        <v>0.6286759474550803</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1798341178064833</v>
+        <v>0.1765531770377184</v>
       </c>
     </row>
     <row r="30">
@@ -2174,37 +2174,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>130.41</v>
+        <v>129.38</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01954733442675949</v>
+        <v>-0.007898157736162537</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01703470670104335</v>
+        <v>-0.02984399902012391</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.03557164262070212</v>
+        <v>-0.0456590846572924</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.0400441825321749</v>
+        <v>-0.04762606499828259</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.1012733926611669</v>
+        <v>0.08781828110674073</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.05537705691741812</v>
+        <v>0.06630341209501145</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.09869399966691628</v>
+        <v>0.08373384649461557</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.09377401595148704</v>
+        <v>0.09150468778592047</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6645291716939186</v>
+        <v>0.6513827793633438</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1851240285578997</v>
+        <v>0.1819957558764698</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>233.45</v>
+        <v>64.14</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.008536523011602459</v>
+        <v>0.003598803673688922</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.001072041180409933</v>
+        <v>0.0001559665781825093</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02991895753522966</v>
+        <v>0.009442846482151657</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.01252064916042128</v>
+        <v>0.01039697309658894</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.0386524044625034</v>
+        <v>0.0683938124095953</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.03889544770130637</v>
+        <v>0.1925332322599511</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1865314834479119</v>
+        <v>0.05192463317120199</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1363732179384907</v>
+        <v>0.002677437641250169</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3691715558366797</v>
+        <v>0.9069695013784032</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1104166268295066</v>
+        <v>0.2400748960524943</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>93.23999999999999</v>
+        <v>287.93</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.0001072615145358835</v>
+        <v>0.001112643303491589</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01155522046143242</v>
+        <v>0.001878903231917528</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03617945087128016</v>
+        <v>-0.001110172850715574</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.03478261556341222</v>
+        <v>-0.005010754656730509</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.05009187437033735</v>
+        <v>0.07589118126132632</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.05934686592066329</v>
+        <v>0.1654725323579898</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1209598803933079</v>
+        <v>0.05322257492535254</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.12039507894098</v>
+        <v>0.01031616036404781</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4509973656553068</v>
+        <v>0.6884418855149683</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1321106467174424</v>
+        <v>0.1907722514900265</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>287.61</v>
+        <v>231.33</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.01120778980420989</v>
+        <v>-0.009081152901696199</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.001636730093854677</v>
+        <v>-0.02433574071669065</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.0002086508820753341</v>
+        <v>-0.03824885459166294</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.006116592374676322</v>
+        <v>-0.02148810013266322</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.06293887066458459</v>
+        <v>0.0136702409088103</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.1675800073627234</v>
+        <v>0.02497769251270276</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.05544948752866974</v>
+        <v>0.1763476760014162</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.0200382822659595</v>
+        <v>0.1436601925773946</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.6865653398836455</v>
+        <v>0.3567378995894734</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1903309438710237</v>
+        <v>0.1070451126704413</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>63.91</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.004672157628687668</v>
+        <v>-0.01051046492912744</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.0003130452019837193</v>
+        <v>-0.01809277314609004</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.005032232962043803</v>
+        <v>-0.04105599195333198</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.006773791875812396</v>
+        <v>-0.04492749903151705</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.04523862628571651</v>
+        <v>0.01196487685156966</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.2021129220862761</v>
+        <v>0.04490677738877835</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.04866847591191115</v>
+        <v>0.1247422111804892</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.00190074787826866</v>
+        <v>0.1118867037500824</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.9001313018687465</v>
+        <v>0.4357467087313305</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.2385908597709492</v>
+        <v>0.1281303325742675</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>74.11</v>
+        <v>54.19</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.004834169523975751</v>
+        <v>-0.01131185424279446</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.01291956842097353</v>
+        <v>-0.001658072118863374</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.02486841302168996</v>
+        <v>-0.03593667480278739</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.004566774369742288</v>
+        <v>-0.07667405188781373</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.04428568679490197</v>
+        <v>-0.05046302816536596</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.02233708115867894</v>
+        <v>0.03994300716627119</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1364783039752977</v>
+        <v>0.1373793820836591</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.09491791057057375</v>
+        <v>0.1885837223508744</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.24267170400664</v>
+        <v>0.7631094936043517</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.07510810638250121</v>
+        <v>0.2080727678277812</v>
       </c>
     </row>
     <row r="36">
@@ -2510,37 +2510,37 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>82.97</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.01425682516748505</v>
+        <v>-0.01518623740740732</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.0004823455369606933</v>
+        <v>-0.01932309909083663</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.04959910286014013</v>
+        <v>-0.06317360764863844</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.04883643210237087</v>
+        <v>-0.06328102785774081</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.01971973382275938</v>
+        <v>-0.04741399667899049</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.09115168361766046</v>
+        <v>0.07038078852172536</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.1015156794425087</v>
+        <v>0.09663880432204919</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.1839439774129443</v>
+        <v>0.1709248047755842</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.4208289546392883</v>
+        <v>0.399251817412406</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1242095397770102</v>
+        <v>0.1184896247645253</v>
       </c>
     </row>
     <row r="37">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2566,37 +2566,37 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>54.81</v>
+        <v>58.77</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.006345150019747781</v>
+        <v>-0.01226889986951807</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.01650599470639991</v>
+        <v>0.002387845592664917</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.01474024229875859</v>
+        <v>-0.02342970821305967</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.06611002460736537</v>
+        <v>-0.0386062582875123</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.02838226716910697</v>
+        <v>-0.03607784329044628</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.06448460399009659</v>
+        <v>0.01092487908727402</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1413659774569282</v>
+        <v>0.1333791504976878</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1861878395568077</v>
+        <v>0.1699347735405643</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.783281827119708</v>
+        <v>0.6333357894184433</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2126626307369379</v>
+        <v>0.1776741963169939</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>59.5</v>
+        <v>73.34</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.004049977814116534</v>
+        <v>-0.01039001843367127</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.01901011512167172</v>
+        <v>-0.02912370334886383</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.001007410542437026</v>
+        <v>-0.03207074584710501</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.0266645025296004</v>
+        <v>-0.0149093439335295</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.0157347966001713</v>
+        <v>0.01732824049399917</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.02742783977083207</v>
+        <v>0.005809803486216847</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1463664109895471</v>
+        <v>0.1219731223288738</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1748144972418435</v>
+        <v>0.07780694191080251</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.653623760595974</v>
+        <v>0.2297604007561382</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1825301833591053</v>
+        <v>0.07137169430080226</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>103.77</v>
+        <v>46.86</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.01658453426528794</v>
+        <v>-0.01347367136101973</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.01032029566782455</v>
+        <v>0.05731049036590963</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.03729477909190604</v>
+        <v>-0.02476584069935117</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.07694361916711334</v>
+        <v>0.04342019081640713</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.0871314262212155</v>
+        <v>0.06210339403445997</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.1198912264679297</v>
+        <v>-0.08243585489778893</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1360441630376696</v>
+        <v>0.02009028629301546</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.2203257697343111</v>
+        <v>0.1698105229797358</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.3744416249835918</v>
+        <v>1.184739084390594</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.1118395018841625</v>
+        <v>0.2975771607550288</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>28.27</v>
+        <v>101.83</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.0184027358797586</v>
+        <v>-0.008084958128255271</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.01362499377666793</v>
+        <v>-0.0153741671440879</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.06048520058474272</v>
+        <v>-0.005469260298192391</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.1312231203941401</v>
+        <v>-0.008374725775688541</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.0205776057445759</v>
+        <v>0.09574071054764777</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.1151873780021084</v>
+        <v>0.1612027662719449</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.03906491587264371</v>
+        <v>-0.07367803149549468</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.09075967144791997</v>
+        <v>-0.07845547728873148</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.5557615448596001</v>
+        <v>0.3998335981366683</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.158726690631628</v>
+        <v>0.1186446184384962</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>47.5</v>
+        <v>102.16</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.03126353851009656</v>
+        <v>-0.01551501429160551</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.08101960592977964</v>
+        <v>-0.01180106039583262</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.01329454503038607</v>
+        <v>-0.05258275129985546</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.05767090094383809</v>
+        <v>-0.0912648521076932</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.03440770675211402</v>
+        <v>-0.1145199561595223</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>-0.02624023803461284</v>
+        <v>0.09276240307063066</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.04094323442573589</v>
+        <v>0.1217146431992859</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1983506587308117</v>
+        <v>0.2127115617771393</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.214577574837437</v>
+        <v>0.3531167333238614</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.3034577720638751</v>
+        <v>0.1060593250596711</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>95.93000000000001</v>
+        <v>28.02</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.0009372666219221726</v>
+        <v>-0.008843296637844333</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.003842188316267925</v>
+        <v>-0.01094244499743113</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.03345087853727169</v>
+        <v>-0.05846773379489123</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.02539876046173839</v>
+        <v>-0.1389059720525955</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.01367473726861901</v>
+        <v>-0.01890752865113521</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.04553772063685502</v>
+        <v>0.08731082499155129</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.1066541547177819</v>
+        <v>0.02800232268043712</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.08392499744185256</v>
+        <v>0.09621660488833106</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.3242514436843817</v>
+        <v>0.5420034840206556</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.09813774262654618</v>
+        <v>0.1553009177070834</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>63.77</v>
+        <v>94.94</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.0157431770852039</v>
+        <v>-0.01032000271677391</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.01361177180735218</v>
+        <v>-0.008770060018754022</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.07284091902370371</v>
+        <v>-0.03721730195953432</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.05497929334036877</v>
+        <v>-0.03545664790154446</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.01408300074347424</v>
+        <v>-0.01938360212996848</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.07913371701274374</v>
+        <v>0.0324301847194064</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.06971657275488385</v>
+        <v>0.09942461213931808</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.07083026848901031</v>
+        <v>0.07519483407803929</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.6209841863862107</v>
+        <v>0.3105851651878673</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1746980812053727</v>
+        <v>0.09434707784703078</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>102.66</v>
+        <v>62.86</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.01826523896231191</v>
+        <v>-0.01427003043562503</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.03315122087916234</v>
+        <v>-0.03633301586102267</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.007952922927083828</v>
+        <v>-0.07721670469977182</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.00029212950222679</v>
+        <v>-0.06846476758669762</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.07348927021472496</v>
+        <v>-0.01401051175815882</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.1672075267670885</v>
+        <v>0.05554644530115005</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>-0.06143281362114794</v>
+        <v>0.04693482409217231</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>-0.06672193154063732</v>
+        <v>0.05784614855244996</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.4112434422762465</v>
+        <v>0.5978525377723891</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1216757022652415</v>
+        <v>0.169083592869425</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>18.31</v>
+        <v>70.97</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.03038823828182768</v>
+        <v>-0.005604616932679884</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.06206494831959164</v>
+        <v>-0.003789958606999266</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.03739375986836802</v>
+        <v>-0.01988678868358862</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0.000546460617418143</v>
+        <v>-0.03507820155002739</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.1257550605724144</v>
+        <v>0.06977028214501457</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.05330716518259293</v>
+        <v>-0.01995050118837394</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.1079030588156</v>
+        <v>0.04456472464708439</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.2698683960322041</v>
+        <v>-0.03642535849006567</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.2399044702540285</v>
+        <v>0.03808267986649594</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.07430948126230952</v>
+        <v>0.01253640834101688</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>71.37</v>
+        <v>18.01</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.005018828851299117</v>
+        <v>-0.01638444816006479</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.001684249074835442</v>
+        <v>0.03684509837229699</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.01721288836027801</v>
+        <v>0.01866515373359179</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.02963970380316228</v>
+        <v>-0.01584694099830419</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.08569024815587434</v>
+        <v>-0.1246563026902113</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.01899022766460412</v>
+        <v>0.005475558209631748</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.03630716253886046</v>
+        <v>0.09105733950731554</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-0.04090950800343462</v>
+        <v>0.2646864142765684</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.04393364388913956</v>
+        <v>0.2195892409762938</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.01443517115777349</v>
+        <v>0.06840979640671518</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>223.53</v>
+        <v>13.06</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.009219457583562685</v>
+        <v>-0.006088274095571666</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.008560311705391288</v>
+        <v>-0.02098948499013864</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.0459667269832762</v>
+        <v>-0.02318619809991274</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.1085543418572408</v>
+        <v>-0.02609988305577449</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-0.01572242592232631</v>
+        <v>0.05729115678485486</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.07583779524290513</v>
+        <v>0.0739256119407854</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.09533678555021718</v>
+        <v>-0.05223023857155773</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.1366911666344395</v>
+        <v>-0.08233579209265307</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>1.037672126767117</v>
+        <v>0.1588381529675504</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.2677825456227196</v>
+        <v>0.05036666044826044</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>13.14</v>
+        <v>219.45</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.01425353199330526</v>
+        <v>-0.01825259183704953</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.01573033948661606</v>
+        <v>-0.01754934975437838</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.01867064925989104</v>
+        <v>-0.07162199672076119</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.02013419143636008</v>
+        <v>-0.1248255356002306</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.07572968786926682</v>
+        <v>-0.0470642505716703</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.08471494866921314</v>
+        <v>-0.09191879630144695</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>-0.04259754001786076</v>
+        <v>0.08447199358028024</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.0830463226922441</v>
+        <v>0.1240189270113663</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1659365964826145</v>
+        <v>1.000479050878361</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.0525069639882374</v>
+        <v>0.2600216362452403</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>85.7</v>
+        <v>46.9</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.02157779961946227</v>
+        <v>-0.01013084701172262</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.002560535677276654</v>
+        <v>-0.03259071846691974</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.02491753847553424</v>
+        <v>-0.03398553526489279</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.05637527817426113</v>
+        <v>-0.01096576683140715</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.02549151446847153</v>
+        <v>-0.01031953389390161</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.03668043570430379</v>
+        <v>-0.03491845844472663</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.005214594277611173</v>
+        <v>0.06042063871637438</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.01202471224545909</v>
+        <v>0.009185522033383631</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.4336496384182218</v>
+        <v>0.1250061193585577</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.1275808109966179</v>
+        <v>0.04004379726753204</v>
       </c>
     </row>
     <row r="50">
@@ -3294,37 +3294,37 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>43.45</v>
+        <v>42.94</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.008588647078887623</v>
+        <v>-0.01173767841830453</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0.02091163911961158</v>
+        <v>0.006327641653384841</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0.003232495617854436</v>
+        <v>-0.0131004301726696</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.003668879733382369</v>
+        <v>-0.01536349402122095</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.004766798516600002</v>
+        <v>-0.01741262459364967</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.05791259799145432</v>
+        <v>-0.07115650286653941</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.03846100195062041</v>
+        <v>0.02555173297538893</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.08113466889117271</v>
+        <v>0.06112381738485961</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.5052760917809291</v>
+        <v>0.4876075467868086</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1460548092139391</v>
+        <v>0.14155311721772</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>47.38</v>
+        <v>84.3</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.01023601158769105</v>
+        <v>-0.01633598537150349</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.0151735508828752</v>
+        <v>-0.02407958170637536</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.02730441472706546</v>
+        <v>-0.04454267432448122</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.0008434648328660144</v>
+        <v>-0.07179031782619549</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>0.002551422763866773</v>
+        <v>-0.004103597518102742</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.02384357520648572</v>
+        <v>0.02232959916565735</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.07175395842102539</v>
+        <v>-0.0213533391335109</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.01370177291136132</v>
+        <v>-0.01998249881637293</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.1365200299073068</v>
+        <v>0.4102294689034649</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.04357988150523462</v>
+        <v>0.1214069979053136</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>253.27</v>
+        <v>44.57</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0.001383860928552805</v>
+        <v>-0.008453861216139003</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0.004880221469184542</v>
+        <v>-0.002908301250478251</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.04372286790330937</v>
+        <v>-0.02387210153811836</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.1170030466509449</v>
+        <v>-0.03590741647954188</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.06559974644764943</v>
+        <v>0.004733973886007048</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.09257446652410972</v>
+        <v>-0.05950621926870503</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.08752653164452462</v>
+        <v>-0.003654932735081884</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.1661453487436695</v>
+        <v>-0.01873207378944985</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>1.18224302167958</v>
+        <v>0.2656355920911952</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.2970828121426676</v>
+        <v>0.08169019529033084</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>26.7</v>
+        <v>246.7</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.02732240361219163</v>
+        <v>-0.02594072418126114</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>0.01714288620721716</v>
+        <v>-0.01402825495160531</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.04283920685477638</v>
+        <v>-0.07481716634123359</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.02597604483295335</v>
+        <v>-0.1399086270706666</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.1144245820178387</v>
+        <v>-0.0973962395945942</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.06262174024597789</v>
+        <v>-0.1250421981505007</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.1090153882639195</v>
+        <v>0.06848086298315725</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>-0.2032338307891363</v>
+        <v>0.1487032787114699</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.266593944267836</v>
+        <v>1.125634057357708</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.08196314868968724</v>
+        <v>0.2857686524181051</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>44.95</v>
+        <v>110.83</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.00706869210489125</v>
+        <v>-0.006187184655502942</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.01147619603939298</v>
+        <v>-0.01414335851083337</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.02027027644997359</v>
+        <v>-0.01580675579121926</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.02768762258211688</v>
+        <v>-0.003775264439957904</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.0206630297115018</v>
+        <v>-0.003244272399765324</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.05606884142867063</v>
+        <v>-0.05177848445236843</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.002059927800903916</v>
+        <v>-0.03914597573575229</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.009741339145669881</v>
+        <v>-0.02811263895600613</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.2764263230791328</v>
+        <v>0.7120538326575692</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.08475564108631506</v>
+        <v>0.1962973445959157</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>18.53</v>
+        <v>26.05</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.02370910782107416</v>
+        <v>-0.02434462574177643</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.02984291536335337</v>
+        <v>-0.02813018927751876</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.08471227866112707</v>
+        <v>-0.05711600577396148</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.07280459741154144</v>
+        <v>0.0009990420014671653</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>0.06862748117565709</v>
+        <v>0.0959707950872668</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.09644976952117768</v>
+        <v>0.03142548180998661</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.1087061149282547</v>
+        <v>-0.1342905195010418</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-0.1628264193024984</v>
+        <v>-0.2299300437807121</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.06210739017966938</v>
+        <v>0.2357591887278352</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.02028807388724707</v>
+        <v>0.07311092459787383</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>111.52</v>
+        <v>35.18</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.004552371166540725</v>
+        <v>-0.01207526812147208</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.00577200041036896</v>
+        <v>-0.0002841239534920881</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.01466693459651336</v>
+        <v>-0.01262982737719176</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.002426936117450929</v>
+        <v>-0.06461048300294259</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>0.006482335681745166</v>
+        <v>-0.06439146151823372</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.04506287775799223</v>
+        <v>-0.02472724334732646</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.03208290959387627</v>
+        <v>-0.04149750548095754</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.01652592349878257</v>
+        <v>0.04522688585896639</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.7227129795205847</v>
+        <v>0.3718895969819764</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.1987749023722636</v>
+        <v>0.1111509304988321</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>35.61</v>
+        <v>17.92</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.009457584015920117</v>
+        <v>-0.0331354720821504</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0.01308674436710855</v>
+        <v>-0.06711791526247368</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.006694501366374617</v>
+        <v>-0.1057202749613323</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.05317734558742682</v>
+        <v>-0.1035276547887095</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.07025551034790967</v>
+        <v>0.04041818122005858</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.01280661857892429</v>
+        <v>0.0538204190983933</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.03004477716466425</v>
+        <v>-0.1386537969535606</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.04900752210569514</v>
+        <v>-0.1889542669780362</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.3886581181279356</v>
+        <v>0.0269139604041253</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.1156597858269757</v>
+        <v>0.008892017796256368</v>
       </c>
     </row>
     <row r="58">
@@ -3742,37 +3742,37 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>19.31</v>
+        <v>19.22</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.003201005540754864</v>
+        <v>-0.00445426729634435</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>0.01402301881182599</v>
+        <v>0.002660437918090564</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.02940885712787167</v>
+        <v>-0.01803406274917996</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.01295906335369734</v>
+        <v>0.008447072925265475</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.0192693370286745</v>
+        <v>-0.01405489387285686</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.0547966731439824</v>
+        <v>0.0457563410783659</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.05455276361633499</v>
+        <v>-0.06489590880477003</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.1870927805776553</v>
+        <v>-0.1961523824140317</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1763896197593489</v>
+        <v>0.1711495298418055</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.05564297328935841</v>
+        <v>0.05407322752452748</v>
       </c>
     </row>
     <row r="59">
@@ -3798,37 +3798,37 @@
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>100.75</v>
+        <v>99.23</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.02421307506053272</v>
+        <v>-0.01508681531579559</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>0.00188944357616494</v>
+        <v>-0.01917559402118496</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.05292345740530724</v>
+        <v>-0.06386789285911709</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.0907039961638193</v>
+        <v>-0.1044223770410868</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.02318343648630483</v>
+        <v>-0.0714520594966328</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.04120455833381431</v>
+        <v>-0.05252786354941374</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.04128488622435222</v>
+        <v>-0.04636953902114538</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1510583400914997</v>
+        <v>-0.1385811262121519</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.2682646671779869</v>
+        <v>0.2491305923727236</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.08243866714656267</v>
+        <v>0.07696754283207663</v>
       </c>
     </row>
     <row r="60">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>51.74</v>
+        <v>51.48</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.03524145724420102</v>
+        <v>-0.005025166752916421</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.04696996120939889</v>
+        <v>-0.05402423237100895</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.07126184654905809</v>
+        <v>-0.07059035729368202</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.04854724784469255</v>
+        <v>-0.05332845658179419</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>0.03927486544082792</v>
+        <v>0.01212896705219313</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.08635717948241239</v>
+        <v>-0.1001435084338044</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.1664974055921418</v>
+        <v>-0.1634324036941409</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1689897176092191</v>
+        <v>-0.1725039494877623</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.03673735106962184</v>
+        <v>0.03152749415487976</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.01209881208946917</v>
+        <v>0.01040061686571514</v>
       </c>
     </row>
     <row r="61">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>49.13</v>
+        <v>47.74</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.02268942822262909</v>
+        <v>-0.02829227273415491</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>0.0484421772982695</v>
+        <v>0.009942907047844729</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0.005731885419453464</v>
+        <v>-0.021320154302084</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.06862557216843157</v>
+        <v>-0.09497627149825982</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.2272727327271257</v>
+        <v>-0.2278829004580598</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.07789034921664106</v>
+        <v>-0.1175600180228585</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.0323597585751132</v>
+        <v>0.005687812319792318</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.1338564272319895</v>
+        <v>0.1374791586834032</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>-0.1106945472523587</v>
+        <v>-0.1358550196654661</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>-0.03835011265657984</v>
+        <v>-0.0475060982024027</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>91.05</v>
+        <v>90.31</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.03045469597298622</v>
+        <v>-0.00812746258496444</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.01418360274942365</v>
+        <v>-0.02704160896878816</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.07243276635182205</v>
+        <v>-0.07193505472842143</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.09976266955488355</v>
+        <v>-0.1070793147756646</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.01459133358363296</v>
+        <v>-0.06036821120074631</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.07168519533058848</v>
+        <v>-0.07377224339911492</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.09010697209442187</v>
+        <v>-0.08310014718128966</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>-0.2177256522549379</v>
+        <v>-0.1986346927845513</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>0.1065214460569559</v>
+        <v>0.09752792911874364</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>0.03431608486995263</v>
+        <v>0.03150624162540905</v>
       </c>
     </row>
   </sheetData>
@@ -4181,17 +4181,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4602,21 +4602,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1845929481052861</v>
+        <v>0.1719351061283665</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1312231203941401</v>
+        <v>-0.1399086270706666</v>
       </c>
     </row>
     <row r="18">
@@ -4647,21 +4647,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1653245839824891</v>
+        <v>0.1700581477953975</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1170030466509449</v>
+        <v>-0.1389059720525955</v>
       </c>
     </row>
     <row r="19">
@@ -4692,21 +4692,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1279471224590254</v>
+        <v>0.1311864475745939</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1085543418572408</v>
+        <v>-0.1248255356002306</v>
       </c>
     </row>
     <row r="20">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1194923965233143</v>
+        <v>0.1233697531358471</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09976266955488355</v>
+        <v>-0.1070793147756646</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1129943502824859</v>
+        <v>0.1098332325732603</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.0907039961638193</v>
+        <v>-0.1044223770410868</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1037653463263331</v>
+        <v>0.1065747235076508</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.0893935290204152</v>
+        <v>-0.1035276547887095</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.0947825601325134</v>
+        <v>0.1057742027746411</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.07694361916711334</v>
+        <v>-0.09497627149825982</v>
       </c>
     </row>
     <row r="24">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.07213448326906602</v>
+        <v>0.08224466618386739</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.07280459741154144</v>
+        <v>-0.0912648521076932</v>
       </c>
     </row>
     <row r="25">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.05767090094383809</v>
+        <v>0.05326447273497714</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.06862557216843157</v>
+        <v>-0.08999943186103165</v>
       </c>
     </row>
     <row r="26">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.04914068812022387</v>
+        <v>0.04342019081640713</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.06611002460736537</v>
+        <v>-0.07667405188781373</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3556578122779603</v>
+        <v>0.3274916531260985</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2272727327271257</v>
+        <v>-0.2278829004580598</v>
       </c>
     </row>
     <row r="32">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.3177040733920622</v>
+        <v>0.3015360170104044</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1681141333150975</v>
+        <v>-0.1412685644336509</v>
       </c>
     </row>
     <row r="33">
@@ -5203,21 +5203,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2620801676011537</v>
+        <v>0.2887011248914635</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1257550605724144</v>
+        <v>-0.1246563026902113</v>
       </c>
     </row>
     <row r="34">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2509216467855004</v>
+        <v>0.2819951787022772</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.0871314262212155</v>
+        <v>-0.1145199561595223</v>
       </c>
     </row>
     <row r="35">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2422667004701433</v>
+        <v>0.2143131175831314</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.07025551034790967</v>
+        <v>-0.0973962395945942</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2394551063736847</v>
+        <v>0.2135032424982086</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.06559974644764943</v>
+        <v>-0.0714520594966328</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.2339830523495059</v>
+        <v>0.1945492101268345</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.04084190479572314</v>
+        <v>-0.06439146151823372</v>
       </c>
     </row>
     <row r="38">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1649738133216709</v>
+        <v>0.1928344319429605</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.03881509916104497</v>
+        <v>-0.06036821120074631</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1571970742089035</v>
+        <v>0.1903768760148632</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.03869242411185825</v>
+        <v>-0.0575358293431979</v>
       </c>
     </row>
     <row r="40">
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1538135212750593</v>
+        <v>0.1793103323538441</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.03494555458690696</v>
+        <v>-0.05046302816536596</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5583173209957417</v>
+        <v>0.5692007819013811</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.09257446652410972</v>
+        <v>-0.1250421981505007</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5424056682740872</v>
+        <v>0.4982736806758969</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5691,21 +5691,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.08635717948241239</v>
+        <v>-0.1175600180228585</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5075940302433244</v>
+        <v>0.4562212773228167</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5736,21 +5736,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.07789034921664106</v>
+        <v>-0.1001435084338044</v>
       </c>
     </row>
     <row r="48">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4280979542355605</v>
+        <v>0.429174368698803</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.07583779524290513</v>
+        <v>-0.09191879630144695</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4167417392450008</v>
+        <v>0.4183816224346126</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.07168519533058848</v>
+        <v>-0.08243585489778893</v>
       </c>
     </row>
     <row r="50">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3717883636745891</v>
+        <v>0.3762576340720791</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.05791259799145432</v>
+        <v>-0.07377224339911492</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3627683649153985</v>
+        <v>0.3387599128794934</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.05606884142867063</v>
+        <v>-0.07115650286653941</v>
       </c>
     </row>
     <row r="52">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3318261013936057</v>
+        <v>0.2818372654801797</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.04506287775799223</v>
+        <v>-0.05950621926870503</v>
       </c>
     </row>
     <row r="53">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.3071689584811568</v>
+        <v>0.2680255254692037</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.04120455833381431</v>
+        <v>-0.05252786354941374</v>
       </c>
     </row>
     <row r="54">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.284928093674135</v>
+        <v>0.2593808750343316</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.0292956566558642</v>
+        <v>-0.05177848445236843</v>
       </c>
     </row>
     <row r="55"/>
@@ -6135,21 +6135,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>1</v>
+        <v>0.9343774756852821</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6157,21 +6157,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2177256522549379</v>
+        <v>-0.2299300437807121</v>
       </c>
     </row>
     <row r="60">
@@ -6180,21 +6180,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.9408985562696393</v>
+        <v>0.9189510992431646</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6202,21 +6202,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2032338307891363</v>
+        <v>-0.1986346927845513</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.8848935168466907</v>
+        <v>0.9022979877554096</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1870927805776553</v>
+        <v>-0.1961523824140317</v>
       </c>
     </row>
     <row r="62">
@@ -6270,21 +6270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.7371968229828241</v>
+        <v>0.7196261762205589</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6292,21 +6292,21 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1689897176092191</v>
+        <v>-0.1889542669780362</v>
       </c>
     </row>
     <row r="63">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.7226636910873359</v>
+        <v>0.7138820653594284</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6337,21 +6337,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1628264193024984</v>
+        <v>-0.1725039494877623</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.7079626316260272</v>
+        <v>0.6884879275121565</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1510583400914997</v>
+        <v>-0.1385811262121519</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.694682153373875</v>
+        <v>0.6857176518055275</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.0830463226922441</v>
+        <v>-0.08233579209265307</v>
       </c>
     </row>
     <row r="66">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.5852715745905757</v>
+        <v>0.6301047697667759</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.06672193154063732</v>
+        <v>-0.07845547728873148</v>
       </c>
     </row>
     <row r="67">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.579872193563151</v>
+        <v>0.6073726931290087</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.04090950800343462</v>
+        <v>-0.03642535849006567</v>
       </c>
     </row>
     <row r="68">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.5596093312930568</v>
+        <v>0.5482365510853715</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.01652592349878257</v>
+        <v>-0.02811263895600613</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.111172666190555</v>
+        <v>3.178370539305554</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1106945472523587</v>
+        <v>-0.1358550196654661</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.867205004002972</v>
+        <v>2.870979646142213</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6713,21 +6713,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.03673735106962184</v>
+        <v>0.0269139604041253</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.596867310194209</v>
+        <v>2.635610277042516</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6758,21 +6758,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.04393364388913956</v>
+        <v>0.03152749415487976</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>2.075471443483193</v>
+        <v>2.037735811710868</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6803,21 +6803,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.06210739017966938</v>
+        <v>0.03808267986649594</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.730913441463207</v>
+        <v>1.756665535645811</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1065214460569559</v>
+        <v>0.09752792911874364</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.460784815462409</v>
+        <v>1.459147635156747</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1365200299073068</v>
+        <v>0.1250061193585577</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.373721915816523</v>
+        <v>1.358681829292578</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1659365964826145</v>
+        <v>0.1588381529675504</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.336746610247214</v>
+        <v>1.331000916546931</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1763896197593489</v>
+        <v>0.1711495298418055</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.214577574837437</v>
+        <v>1.184739084390594</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1892387091593783</v>
+        <v>0.1848534758530176</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.18224302167958</v>
+        <v>1.125634057357708</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2399044702540285</v>
+        <v>0.2195892409762938</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -489,13 +489,13 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>16.1</v>
+        <v>15.92</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.01226986901545934</v>
+        <v>-0.01118014291372016</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.0289505153465065</v>
+        <v>-0.01363068907521714</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.06905710045654145</v>
+        <v>0.07422404886107348</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.1700581477953975</v>
+        <v>0.1536231779896946</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3015360170104044</v>
+        <v>0.2736000061035155</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5692007819013811</v>
+        <v>0.5562073107203438</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.8233296172795852</v>
+        <v>0.7663376121530259</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9189510992431646</v>
+        <v>0.9367396057334156</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.037735811710868</v>
+        <v>2.003773491201815</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4482715530915167</v>
+        <v>0.4428540187319319</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>38.6</v>
+        <v>37.88</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.01605916582886913</v>
+        <v>-0.01865278327636655</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.03980105120528776</v>
+        <v>-0.05981632644945711</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.04996314399772939</v>
+        <v>-0.06699501251803286</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1098332325732603</v>
+        <v>0.07430524308851139</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3274916531260985</v>
+        <v>0.327739054342352</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2818372654801797</v>
+        <v>0.2743626030966451</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4819770858513499</v>
+        <v>0.434165304416291</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7138820653594284</v>
+        <v>0.6998458500628668</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.7999240274792483</v>
+        <v>0.7663501204825063</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2164232847917735</v>
+        <v>0.2088124679584211</v>
       </c>
     </row>
     <row r="4">
@@ -704,51 +704,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>95.27</v>
+        <v>560.28</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.009429957782884024</v>
+        <v>-0.02439525199202008</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.05973298137977978</v>
+        <v>0.01389803483576735</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.002826086140606865</v>
+        <v>-0.02219890175065442</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.08224466618386739</v>
+        <v>-0.01603404274294096</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1928344319429605</v>
+        <v>-0.01861929962285869</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.1623753799502441</v>
+        <v>0.4101126223328033</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4624092642460784</v>
+        <v>0.5023346047505155</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.9022979877554096</v>
+        <v>0.868242648151998</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.756665535645811</v>
+        <v>2.776546510641252</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4021506970420319</v>
+        <v>0.5572736885715217</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>574.29</v>
+        <v>156.82</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.0009760646604806134</v>
+        <v>-0.01606222537435631</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.04325315797736873</v>
+        <v>-0.045990980253245</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.03332306141974684</v>
+        <v>-0.06782374542646741</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.01443287112322811</v>
+        <v>-0.007656720017874541</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.02829060669363592</v>
+        <v>0.2182688237468962</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.4562212773228167</v>
+        <v>0.2318445414978014</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5611841327505613</v>
+        <v>0.2903995190644055</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.9343774756852821</v>
+        <v>0.6777183233486406</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.870979646142213</v>
+        <v>1.006494671561847</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5701469355686981</v>
+        <v>0.2612833718871301</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>159.38</v>
+        <v>195.47</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.01574747056324755</v>
+        <v>0.002358887886902972</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.03622174766426201</v>
+        <v>0.01632610284279346</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.05350670787750955</v>
+        <v>0.0539170751829583</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.01277250955068165</v>
+        <v>0.1110669548024814</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2143131175831314</v>
+        <v>0.1692841787504875</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.2550067336383881</v>
+        <v>0.2403616110275348</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3207710932588266</v>
+        <v>0.4691411841301418</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.6857176518055275</v>
+        <v>0.5178849391563829</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.039249756615742</v>
+        <v>0.3696125783083839</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2681096469267428</v>
+        <v>0.1105358390912996</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>195.01</v>
+        <v>88.61</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.005672687452697334</v>
+        <v>-0.06990654211594904</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.009577504709322282</v>
+        <v>-0.02893150016053081</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.0571939033339286</v>
+        <v>-0.0812856048310483</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.1719351061283665</v>
+        <v>-0.01005475929392941</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1945492101268345</v>
+        <v>0.1479809768467291</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2158779884097399</v>
+        <v>0.07044453306732956</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4729821544547015</v>
+        <v>0.3291830683655004</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5464698135162032</v>
+        <v>0.7570162029035277</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3663889805979699</v>
+        <v>1.563956580278602</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1096638812938833</v>
+        <v>0.3686851505255091</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>100.11</v>
+        <v>110.5</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01634518386143724</v>
+        <v>-0.004145629851010191</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.01438847029909018</v>
+        <v>-0.009235172514751921</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.005167411877761374</v>
+        <v>-0.06813966694457096</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.1311864475745939</v>
+        <v>-0.07290882006381572</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2887011248914635</v>
+        <v>0.174282697043711</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>-0.02149273756748038</v>
+        <v>0.4184852096991443</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.291287110823844</v>
+        <v>0.2873281409266621</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6301047697667759</v>
+        <v>0.2865793470142493</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>3.178370539305554</v>
+        <v>1.104333165472413</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.6106542278098561</v>
+        <v>0.2814593473991487</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>495.65</v>
+        <v>490.47</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.0006653838512311605</v>
+        <v>-0.01045090838206097</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.03888071170752405</v>
+        <v>0.0249728589847682</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.01006705085983262</v>
+        <v>-0.01956984039061715</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.08999943186103165</v>
+        <v>-0.06648272091786467</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.1412685644336509</v>
+        <v>-0.1189785038425308</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.4982736806758969</v>
+        <v>0.4799336228302693</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.447249079221482</v>
+        <v>0.4224203248913274</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.6884879275121565</v>
+        <v>0.6555330343392065</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.459147635156747</v>
+        <v>1.433447124297525</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3497754789224914</v>
+        <v>0.3450568420853157</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>69.31999999999999</v>
+        <v>152.43</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.01506106280136676</v>
+        <v>-0.01122217790108515</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.03008257295588379</v>
+        <v>-0.003985890205908893</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.0479329485069816</v>
+        <v>-0.00300874298975462</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.01701640676921634</v>
+        <v>0.007601757706001244</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1903768760148632</v>
+        <v>0.03102023780551622</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2593808750343316</v>
+        <v>0.3230506159981994</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2445445854999959</v>
+        <v>0.4024158331665069</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4634300375420353</v>
+        <v>0.5135015403709919</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6699879583609072</v>
+        <v>1.304841743683902</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1864181442742121</v>
+        <v>0.3209317235163318</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>110.96</v>
+        <v>202.64</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.007079313642552654</v>
+        <v>-0.0138693173747102</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.01444507104341985</v>
+        <v>-0.05224263737192281</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.01231638049998884</v>
+        <v>-0.05661081698951054</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.03864147595934253</v>
+        <v>0.01309866543957594</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1668945562915991</v>
+        <v>0.2214096586739513</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.4183816224346126</v>
+        <v>0.1773177624941711</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.3019325312667482</v>
+        <v>0.2018936940428218</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.292837676557081</v>
+        <v>0.4444062683606842</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.113093268002212</v>
+        <v>0.6109070958338347</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2832350760480551</v>
+        <v>0.1722587907111925</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>154.16</v>
+        <v>96.2</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.002458843280262579</v>
+        <v>-0.03905707360174637</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.0127447275380943</v>
+        <v>-0.05090769170321419</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.01447747335510896</v>
+        <v>-0.06728720653941345</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.01081902311129834</v>
+        <v>0.0655737510964931</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.01176874938723738</v>
+        <v>0.2972349182644201</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.3387599128794934</v>
+        <v>-0.08341894619310819</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.4316247128044373</v>
+        <v>0.2207843206735711</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.5482365510853715</v>
+        <v>0.5271292545942103</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.331000916546931</v>
+        <v>3.015175613616528</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3259103114923383</v>
+        <v>0.5894060006595374</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>429.35</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.001820003187266384</v>
+        <v>-0.01889782983786659</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.01656049450529096</v>
+        <v>-0.04251719970388967</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.06043766282749785</v>
+        <v>-0.06076510569466154</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.1057742027746411</v>
+        <v>-0.02995290908343018</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.02043970553420227</v>
+        <v>0.1664805453254974</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1324910625481566</v>
+        <v>0.2242619629034166</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4335014640238939</v>
+        <v>0.2074248538042787</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.7196261762205589</v>
+        <v>0.4466997097498302</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2805308076852924</v>
+        <v>0.6384286595211466</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.08591711274314218</v>
+        <v>0.1788969533906408</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>205.49</v>
+        <v>94.16</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.008874723009890118</v>
+        <v>-0.003386956852819978</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.03886808905508776</v>
+        <v>-0.01216949261884892</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.04525386994248193</v>
+        <v>-0.06578030750267183</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.03935055644682861</v>
+        <v>-0.06401585397308307</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.2135032424982086</v>
+        <v>0.1320236913646933</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.2007065868156697</v>
+        <v>0.4351604746013573</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2322190073472024</v>
+        <v>0.2439520853670276</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.4412549958877068</v>
+        <v>0.2622134404733962</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6335633084047101</v>
+        <v>1.028699586361434</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1777288759896727</v>
+        <v>0.2659189865113565</v>
       </c>
     </row>
     <row r="15">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>111.1</v>
+        <v>108.63</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.0008094609704913935</v>
+        <v>-0.02223223451509293</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.007618323250645043</v>
+        <v>-0.02002707488734345</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.02302025815033271</v>
+        <v>-0.01002466116707834</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.00981641396116828</v>
+        <v>-0.01308260602706224</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.04407475472798739</v>
+        <v>0.04241433842987052</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2077399831952609</v>
+        <v>0.1723504528398703</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.3847072194275327</v>
+        <v>0.3156628770448269</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.6073726931290087</v>
+        <v>0.5513096247466027</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.8308207180811742</v>
+        <v>0.7901174825217026</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2233440277384586</v>
+        <v>0.2142101099772191</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>99.47</v>
+        <v>420.22</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.0107712378736744</v>
+        <v>-0.02126471352747872</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.01884670714994563</v>
+        <v>-0.0223121760600351</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.02880293888871255</v>
+        <v>0.01270029849051446</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.1065747235076508</v>
+        <v>0.02158799280855273</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.2819951787022772</v>
+        <v>-0.006384214795483123</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>-0.02899259224834472</v>
+        <v>0.09930411365382574</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2227535497908577</v>
+        <v>0.3874460126329229</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4987647409439147</v>
+        <v>0.6438411063033291</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>2.635610277042516</v>
+        <v>0.2533008009700366</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.5376557176558776</v>
+        <v>0.07816469298469175</v>
       </c>
     </row>
     <row r="17">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>94.48</v>
+        <v>27.17</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.004999481012903706</v>
+        <v>-0.006944463809175905</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.0100492028245236</v>
+        <v>-0.04499123558242246</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.008755067934680838</v>
+        <v>-0.06051175641021156</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.03444042074337672</v>
+        <v>-0.03275187153066594</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1211910533472085</v>
+        <v>0.1880191989186075</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.429174368698803</v>
+        <v>0.3784881450196618</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.2557703893241372</v>
+        <v>0.1675977456729745</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2739769756510266</v>
+        <v>0.184394047243212</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.0355940555976</v>
+        <v>0.3470500730551402</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2673514264676664</v>
+        <v>0.1044038533599363</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>27.36</v>
+        <v>96.03</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.004774185468258585</v>
+        <v>-0.0345833155643942</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.002915449057909525</v>
+        <v>-0.05379839589514657</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.004366773430994009</v>
+        <v>-0.07387408122049122</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.002932548449136041</v>
+        <v>0.0612222460637879</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1793103323538441</v>
+        <v>0.3010432455720362</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.3762576340720791</v>
+        <v>-0.07100709850303122</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1757627878010344</v>
+        <v>0.1609150378037616</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1818574972438194</v>
+        <v>0.4120794364266935</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.3564700300873134</v>
+        <v>2.5098788195624</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.1069722508593762</v>
+        <v>0.5197216161985208</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>31.87</v>
+        <v>31.95</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.003463495263187344</v>
+        <v>0.002510195218055067</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.002503909915359093</v>
+        <v>0.006299236628014349</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.04150328241605972</v>
+        <v>0.03264383359560918</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.1233697531358471</v>
+        <v>0.07178803540208034</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1258346367742422</v>
+        <v>0.1015758563220654</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1068976191881539</v>
+        <v>0.1382396705322824</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.310963449206485</v>
+        <v>0.3068559099276724</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.420896104450504</v>
+        <v>0.3829385314401557</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2873343359338283</v>
+        <v>0.2905657964279276</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.08783689522549598</v>
+        <v>0.08874636232693822</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>56.19</v>
+        <v>56.69</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.003930630716593386</v>
+        <v>-0.000881266307342865</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.007169702538404321</v>
+        <v>-0.02258623057398301</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.01279738807373532</v>
+        <v>-0.009954588046326651</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.05326447273497714</v>
+        <v>-0.01064573505189548</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.09832069545112287</v>
+        <v>0.07384538055756495</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1162233612060712</v>
+        <v>0.2898748041550081</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.255623054054918</v>
+        <v>0.1910556435343769</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.2767199987241356</v>
+        <v>0.1912900419602483</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.7327945114753056</v>
+        <v>0.1838093987067981</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.2011088157434207</v>
+        <v>0.0578577235107518</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>56.74</v>
+        <v>55.75</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.003687429001920428</v>
+        <v>-0.007830550586627627</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01578490586862535</v>
+        <v>0.005954562287221465</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.01167040882644266</v>
+        <v>0.00795513678872295</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.005782337797828108</v>
+        <v>0.03191855777821995</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.0677202513620494</v>
+        <v>0.07650400901125209</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.2680255254692037</v>
+        <v>0.1166654734298767</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1975938542727964</v>
+        <v>0.2463164042026311</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1822654589382349</v>
+        <v>0.266722468395272</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1848534758530176</v>
+        <v>0.7192259786435005</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.0581686295648185</v>
+        <v>0.1979655292611215</v>
       </c>
     </row>
     <row r="22">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>119.19</v>
+        <v>114.77</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.006335927687967091</v>
+        <v>-0.03708369584531823</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.002260142684878841</v>
+        <v>-0.03049502191340292</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.009309243952415835</v>
+        <v>-0.06691059639783414</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.02980823087363027</v>
+        <v>-0.0235664816308081</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.02731738656827365</v>
+        <v>0.02151130456630468</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.06510889935618147</v>
+        <v>0.007007351630898384</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2012870038006798</v>
+        <v>0.1488847713817418</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.4350491766445133</v>
+        <v>0.3570868799465505</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>1.358681829292578</v>
+        <v>1.271213361193183</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.3311381196423833</v>
+        <v>0.3144759507739505</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>73.77</v>
+        <v>73.81</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.0002710973331445654</v>
+        <v>0.004901301910267497</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.00659851170304504</v>
+        <v>-0.01415794242156176</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.02831930423779105</v>
+        <v>-0.007262957990716079</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.003242879154661926</v>
+        <v>-0.02919901691893279</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>-0.0575358293431979</v>
+        <v>0.03631573659066856</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.03719879400141535</v>
+        <v>0.1537828261813023</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1567780583564404</v>
+        <v>0.1206553774331398</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.49503504275513</v>
+        <v>0.164552872343563</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.3256743448495794</v>
+        <v>0.851545443505985</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.0985309162360104</v>
+        <v>0.2279427667310989</v>
       </c>
     </row>
     <row r="24">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>73.45</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.01157314814434551</v>
+        <v>0.004285516822437607</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.01064117643129514</v>
+        <v>-0.01664016084101516</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.01515158025032348</v>
+        <v>-0.006723167155555987</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.03621574818773099</v>
+        <v>-0.02831002699195473</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.03705156734506931</v>
+        <v>0.04680510463111776</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1476235053518082</v>
+        <v>0.1583368194457322</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1537332871148362</v>
+        <v>0.1092999394643348</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1601236542907336</v>
+        <v>0.1450611721471402</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.8425147225765248</v>
+        <v>0.9313400093058311</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2259431243394578</v>
+        <v>0.2453351483011805</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>67.67</v>
+        <v>71.81</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01067256345977419</v>
+        <v>-0.0265690548144667</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.00994879766432244</v>
+        <v>-0.03558959922726512</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.01499270487701576</v>
+        <v>-0.0689744572056038</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.032871273569126</v>
+        <v>-0.0392025741091987</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.04522063883824279</v>
+        <v>-0.0577647505183041</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1516469995852865</v>
+        <v>0.001370300231929633</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1407876202441256</v>
+        <v>0.1087782538911222</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1418656713968034</v>
+        <v>0.4818549021929288</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.9230985381693011</v>
+        <v>0.2904525189776361</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2435612457101448</v>
+        <v>0.08871450704278416</v>
       </c>
     </row>
     <row r="26">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>142.94</v>
+        <v>143.28</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.0009086801996024407</v>
+        <v>0.002378594739635531</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.01277706285316715</v>
+        <v>-0.0310407553219505</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.02243194331770026</v>
+        <v>-0.009265636724747561</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.03471096249385985</v>
+        <v>-0.02264670658931944</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.08120252571396391</v>
+        <v>0.0656898635281129</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1006633436623521</v>
+        <v>0.1036986843180134</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1061516198681149</v>
+        <v>0.1046891417034121</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1146748151770767</v>
+        <v>0.1162245592279101</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6650712804711683</v>
+        <v>0.6690316619284109</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1852526728245578</v>
+        <v>0.1861916388340474</v>
       </c>
     </row>
     <row r="27">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>191.63</v>
+        <v>189.77</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.00858807212468049</v>
+        <v>-0.009706207602974359</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.004244825110070849</v>
+        <v>-0.04185596984913786</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.01708043555795502</v>
+        <v>-0.02856412417053034</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.01795487321547151</v>
+        <v>0.008181525686007163</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.06634962599072391</v>
+        <v>0.06391214591772409</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1447828537039761</v>
+        <v>0.1457721854146006</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.07421971361814128</v>
+        <v>0.05657573335562582</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1039782078242055</v>
+        <v>0.0944467031342402</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.113153398361779</v>
+        <v>1.092642868837109</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2832472478809802</v>
+        <v>0.2790819566334894</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2048,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>180.13</v>
+        <v>63.84</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.01011153665740194</v>
+        <v>-0.004677256624810111</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.02620638144764897</v>
+        <v>-0.01572618637319101</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.003871022181906381</v>
+        <v>-0.006999545131920692</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.03379278034905575</v>
+        <v>0.00330031558930588</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.03604781072208796</v>
+        <v>0.08767180677180497</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.07935306841196677</v>
+        <v>0.1922751944263843</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.1824116048415474</v>
+        <v>0.04648971117605272</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.2586232484826154</v>
+        <v>0.00205983256443143</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.8758398971839521</v>
+        <v>0.898050330914318</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2332901309756608</v>
+        <v>0.2381385378535033</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>23.84</v>
+        <v>129.7</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.008319498973491046</v>
+        <v>0.00247327294290578</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.0214224505883116</v>
+        <v>-0.04032554342855921</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.00334447840513763</v>
+        <v>-0.03049784622726492</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.006666660308837891</v>
+        <v>-0.0401124804973878</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.03992664775251586</v>
+        <v>0.07122435061422294</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.004409217916488739</v>
+        <v>0.07904158724885435</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.2055016825774747</v>
+        <v>0.07939305483234627</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2933201328519186</v>
+        <v>0.09656129467219476</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6286759474550803</v>
+        <v>0.6554669385002223</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1765531770377184</v>
+        <v>0.182969381246306</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>129.38</v>
+        <v>285.5</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.007898157736162537</v>
+        <v>-0.008439526057007596</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02984399902012391</v>
+        <v>-0.02699206961111045</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.0456590846572924</v>
+        <v>-0.02834968162862073</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.04762606499828259</v>
+        <v>-0.02599616281428041</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.08781828110674073</v>
+        <v>0.08621215940430571</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.06630341209501145</v>
+        <v>0.162601260271426</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.08373384649461557</v>
+        <v>0.04418106202550676</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.09150468778592047</v>
+        <v>0.008798240869420493</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6513827793633438</v>
+        <v>0.6741922362264217</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1819957558764698</v>
+        <v>0.1874129321887719</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>64.14</v>
+        <v>177.24</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.003598803673688922</v>
+        <v>-0.01604396442185518</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.0001559665781825093</v>
+        <v>-0.001689691361457246</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.009442846482151657</v>
+        <v>-0.02459964259283687</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.01039697309658894</v>
+        <v>-0.042825472561414</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.0683938124095953</v>
+        <v>-0.01947749591477133</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.1925332322599511</v>
+        <v>0.05398922219075586</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.05192463317120199</v>
+        <v>0.1484656393201633</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.002677437641250169</v>
+        <v>0.212634697013085</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.9069695013784032</v>
+        <v>0.8457436953197921</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.2400748960524943</v>
+        <v>0.2266588539005849</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>287.93</v>
+        <v>23.5</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.001112643303491589</v>
+        <v>-0.01426175127565943</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.001878903231917528</v>
+        <v>-0.004659068509440645</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.001110172850715574</v>
+        <v>-0.02812242748525628</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.005010754656730509</v>
+        <v>-0.008020284076586059</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.07589118126132632</v>
+        <v>-0.02546224577876255</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.1654725323579898</v>
+        <v>-0.003219997396559982</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.05322257492535254</v>
+        <v>0.1608910753487238</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01031616036404781</v>
+        <v>0.2593357520203565</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.6884418855149683</v>
+        <v>0.6054481761838268</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1907722514900265</v>
+        <v>0.1709331382981558</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>231.33</v>
+        <v>82.03</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.009081152901696199</v>
+        <v>0.003916285624889104</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.02433574071669065</v>
+        <v>-0.01877990099856552</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.03824885459166294</v>
+        <v>-0.05057873459959494</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.02148810013266322</v>
+        <v>-0.05615009408796123</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.0136702409088103</v>
+        <v>-0.01266030855019651</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.02497769251270276</v>
+        <v>0.08746653450725939</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1763476760014162</v>
+        <v>0.08975426842135459</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1436601925773946</v>
+        <v>0.1800293233857568</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3567378995894734</v>
+        <v>0.404731595426165</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1070451126704413</v>
+        <v>0.1199478067265105</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>92.26000000000001</v>
+        <v>227.71</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.01051046492912744</v>
+        <v>-0.01564861923889693</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.01809277314609004</v>
+        <v>-0.03565831531288888</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.04105599195333198</v>
+        <v>-0.04926720414012598</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.04492749903151705</v>
+        <v>-0.04287334198325132</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.01196487685156966</v>
+        <v>0.02368934321854987</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.04490677738877835</v>
+        <v>0.009293380476786073</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.1247422111804892</v>
+        <v>0.1370118336613095</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1118867037500824</v>
+        <v>0.1237382965600131</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.4357467087313305</v>
+        <v>0.3355070638261315</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1281303325742675</v>
+        <v>0.1012402165471438</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>54.19</v>
+        <v>92</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.01131185424279446</v>
+        <v>-0.002818145785933868</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.001658072118863374</v>
+        <v>-0.02407973611860059</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.03593667480278739</v>
+        <v>-0.03055849820074119</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.07667405188781373</v>
+        <v>-0.03229199226547752</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.05046302816536596</v>
+        <v>0.0002744847397184724</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.03994300716627119</v>
+        <v>0.04372548999242132</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1373793820836591</v>
+        <v>0.1252161342679727</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1885837223508744</v>
+        <v>0.1169175633747059</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.7631094936043517</v>
+        <v>0.431700565194451</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.2080727678277812</v>
+        <v>0.1270695902596226</v>
       </c>
     </row>
     <row r="36">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2510,37 +2510,37 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>81.70999999999999</v>
+        <v>27.84</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.01518623740740732</v>
+        <v>-0.006423993655785498</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.01932309909083663</v>
+        <v>-0.02040816052600403</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.06317360764863844</v>
+        <v>-0.05144804801553537</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.06328102785774081</v>
+        <v>-0.1145038269821274</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.04741399667899049</v>
+        <v>0.02165138174634462</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.07038078852172536</v>
+        <v>0.09822484156403788</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.09663880432204919</v>
+        <v>0.000999547169128201</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.1709248047755842</v>
+        <v>0.08203650783425354</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.399251817412406</v>
+        <v>0.5320976634221077</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1184896247645253</v>
+        <v>0.1528217193973689</v>
       </c>
     </row>
     <row r="37">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2566,37 +2566,37 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>58.77</v>
+        <v>101.86</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.01226889986951807</v>
+        <v>-0.002936599853207378</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.002387845592664917</v>
+        <v>-0.02320673376748983</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.02342970821305967</v>
+        <v>-0.04812635663087483</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.0386062582875123</v>
+        <v>-0.07693700028242934</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.03607784329044628</v>
+        <v>-0.08921004370306584</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.01092487908727402</v>
+        <v>0.09951491531236001</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1333791504976878</v>
+        <v>0.08871014170118063</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1699347735405643</v>
+        <v>0.2121483998607994</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.6333357894184433</v>
+        <v>0.3491434435903986</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1776741963169939</v>
+        <v>0.1049756534128909</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>73.34</v>
+        <v>53.36</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.01039001843367127</v>
+        <v>-0.01531644283800249</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.02912370334886383</v>
+        <v>-0.02431885261938715</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.03207074584710501</v>
+        <v>-0.0481626952693196</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.0149093439335295</v>
+        <v>-0.08473411134401343</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.01732824049399917</v>
+        <v>-0.03338924674176669</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.005809803486216847</v>
+        <v>0.02657137002764731</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1219731223288738</v>
+        <v>0.09802120747131471</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.07780694191080251</v>
+        <v>0.1597847649695354</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.2297604007561382</v>
+        <v>0.7361050355657546</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.07137169430080226</v>
+        <v>0.2018732399287761</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>46.86</v>
+        <v>73.44</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.01347367136101973</v>
+        <v>0.001363595698244735</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.05731049036590963</v>
+        <v>-0.02249427490741507</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.02476584069935117</v>
+        <v>-0.01673584093106195</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.04342019081640713</v>
+        <v>-0.01010917880198658</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.06210339403445997</v>
+        <v>0.001720712223966636</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>-0.08243585489778893</v>
+        <v>0.01171319555671069</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.02009028629301546</v>
+        <v>0.116474983976504</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1698105229797358</v>
+        <v>0.08486317165152202</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.184739084390594</v>
+        <v>0.2314371392117094</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.2975771607550288</v>
+        <v>0.07185840002760591</v>
       </c>
     </row>
     <row r="40">
@@ -2734,37 +2734,37 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>101.83</v>
+        <v>101.2</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.008084958128255271</v>
+        <v>-0.006186829730767673</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.0153741671440879</v>
+        <v>-0.05376344239432451</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.005469260298192391</v>
+        <v>-0.08266862556028365</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.008374725775688541</v>
+        <v>-0.03628230749910399</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.09574071054764777</v>
+        <v>0.1052518872084447</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.1612027662719449</v>
+        <v>0.1817742589168612</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>-0.07367803149549468</v>
+        <v>-0.0804962614988346</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>-0.07845547728873148</v>
+        <v>-0.09819160183626585</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.3998335981366683</v>
+        <v>0.3911730660135888</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.1186446184384962</v>
+        <v>0.1163328898454077</v>
       </c>
     </row>
     <row r="41">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2790,37 +2790,37 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>102.16</v>
+        <v>58.07</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.01551501429160551</v>
+        <v>-0.01191085175237527</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.01180106039583262</v>
+        <v>-0.01442631535194272</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.05258275129985546</v>
+        <v>-0.02974099957690957</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.0912648521076932</v>
+        <v>-0.04442982956394748</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.1145199561595223</v>
+        <v>-0.02946560078995897</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.09276240307063066</v>
+        <v>0.008785010869684085</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1217146431992859</v>
+        <v>0.1053657141707782</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.2127115617771393</v>
+        <v>0.1476928607326651</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.3531167333238614</v>
+        <v>0.613881882270721</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1060593250596711</v>
+        <v>0.1729799320685759</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>28.02</v>
+        <v>94.12</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.008843296637844333</v>
+        <v>-0.008637030479647367</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.01094244499743113</v>
+        <v>-0.02627768279842324</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.05846773379489123</v>
+        <v>-0.03614950050319621</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.1389059720525955</v>
+        <v>-0.03078980377898188</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.01890752865113521</v>
+        <v>-0.02795279551987495</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.08731082499155129</v>
+        <v>0.02504359126371658</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.02800232268043712</v>
+        <v>0.08601755904146269</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.09621660488833106</v>
+        <v>0.06765442069532179</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.5420034840206556</v>
+        <v>0.2992656011699659</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1553009177070834</v>
+        <v>0.09118732700071752</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>94.94</v>
+        <v>62.41</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.01032000271677391</v>
+        <v>-0.007158777578270437</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.008770060018754022</v>
+        <v>-0.0385149233346388</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.03721730195953432</v>
+        <v>-0.06655699554765615</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.03545664790154446</v>
+        <v>-0.06975699427539517</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.01938360212996848</v>
+        <v>-0.01629216550316248</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.0324301847194064</v>
+        <v>0.05843982217359445</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.09942461213931808</v>
+        <v>0.03497888562749307</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.07519483407803929</v>
+        <v>0.05044899798904368</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.3105851651878673</v>
+        <v>0.5864138668516015</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.09434707784703078</v>
+        <v>0.166287172761836</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>62.86</v>
+        <v>70.5</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.01427003043562503</v>
+        <v>-0.006622533642651529</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.03633301586102267</v>
+        <v>-0.0101095367644255</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.07721670469977182</v>
+        <v>-0.02678081689706513</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.06846476758669762</v>
+        <v>-0.03675368700198889</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.01401051175815882</v>
+        <v>0.08076305536530315</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.05554644530115005</v>
+        <v>-0.03002413031968165</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.04693482409217231</v>
+        <v>0.0129065185021493</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.05784614855244996</v>
+        <v>-0.0352626078045104</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5978525377723891</v>
+        <v>0.03120794239522628</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.169083592869425</v>
+        <v>0.01029627043343018</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>70.97</v>
+        <v>17.82</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.005604616932679884</v>
+        <v>-0.01054972413342459</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.003789958606999266</v>
+        <v>0.01077711532059733</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.01988678868358862</v>
+        <v>-0.0005608653350883674</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.03507820155002739</v>
+        <v>-0.01438054369352793</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.06977028214501457</v>
+        <v>-0.1003107712195344</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.01995050118837394</v>
+        <v>-0.02094084416654796</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.04456472464708439</v>
+        <v>0.07567774933705684</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>-0.03642535849006567</v>
+        <v>0.2367338661425411</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.03808267986649594</v>
+        <v>0.2067229109279012</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.01253640834101688</v>
+        <v>0.06463936327647835</v>
       </c>
     </row>
     <row r="46">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -3070,37 +3070,37 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>18.01</v>
+        <v>45</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.01638444816006479</v>
+        <v>-0.03969271417253628</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.03684509837229699</v>
+        <v>-0.01531730309088142</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.01866515373359179</v>
+        <v>-0.069671263309938</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.01584694099830419</v>
+        <v>0.01397023246874607</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.1246563026902113</v>
+        <v>0.06257382813126311</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.005475558209631748</v>
+        <v>-0.1397438574150647</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.09105733950731554</v>
+        <v>-0.01136175354291624</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.2646864142765684</v>
+        <v>0.1167256467439532</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.2195892409762938</v>
+        <v>1.098020860372309</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.06840979640671518</v>
+        <v>0.2801767456886555</v>
       </c>
     </row>
     <row r="47">
@@ -3126,37 +3126,37 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>13.06</v>
+        <v>12.98</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.006088274095571666</v>
+        <v>-0.00612564125650461</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.02098948499013864</v>
+        <v>-0.02771541787721388</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.02318619809991274</v>
+        <v>-0.0306199246134361</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.02609988305577449</v>
+        <v>-0.02552553756589093</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.05729115678485486</v>
+        <v>0.04914798307212642</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.0739256119407854</v>
+        <v>0.075698907088666</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>-0.05223023857155773</v>
+        <v>-0.06053954598929789</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.08233579209265307</v>
+        <v>-0.08508537994304888</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.1588381529675504</v>
+        <v>0.1517397210915405</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.05036666044826044</v>
+        <v>0.04821760223354543</v>
       </c>
     </row>
     <row r="48">
@@ -3182,37 +3182,37 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>219.45</v>
+        <v>218.32</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.01825259183704953</v>
+        <v>-0.005149189518056541</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.01754934975437838</v>
+        <v>-0.03389675435057471</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.07162199672076119</v>
+        <v>-0.06804400049685844</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.1248255356002306</v>
+        <v>-0.1306494521588698</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.0470642505716703</v>
+        <v>-0.02844634610968266</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.09191879630144695</v>
+        <v>-0.08803998601065821</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.08447199358028024</v>
+        <v>0.06933604442479013</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>0.1240189270113663</v>
+        <v>0.1032202438680987</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>1.000479050878361</v>
+        <v>0.9901784819468107</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.2600216362452403</v>
+        <v>0.25785527513207</v>
       </c>
     </row>
     <row r="49">
@@ -3241,28 +3241,28 @@
         <v>46.9</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.01013084701172262</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.03259071846691974</v>
+        <v>-0.02535323011400725</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.03398553526489279</v>
+        <v>-0.01923877404467833</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.01096576683140715</v>
+        <v>-0.002764134739361213</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.01031953389390161</v>
+        <v>-0.02225086254996678</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.03491845844472663</v>
+        <v>-0.02655753475363176</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.06042063871637438</v>
+        <v>0.05781288327749246</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.009185522033383631</v>
+        <v>0.01652502185049975</v>
       </c>
       <c r="O49" s="6" t="n">
         <v>0.1250061193585577</v>
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>42.94</v>
+        <v>83.63</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.01173767841830453</v>
+        <v>-0.00794787395118457</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0.006327641653384841</v>
+        <v>-0.03574317979393682</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.0131004301726696</v>
+        <v>-0.03418407679476254</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.01536349402122095</v>
+        <v>-0.07682966514881662</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.01741262459364967</v>
+        <v>-0.01387877193100828</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.07115650286653941</v>
+        <v>0.01702732317501443</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.02555173297538893</v>
+        <v>-0.04238113184668313</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.06112381738485961</v>
+        <v>-0.02473477829512705</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.4876075467868086</v>
+        <v>0.3990213213992599</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.14155311721772</v>
+        <v>0.1184282058563686</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>84.3</v>
+        <v>42.52</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.01633598537150349</v>
+        <v>-0.009781047563519718</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.02407958170637536</v>
+        <v>-0.01185215747155866</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.04454267432448122</v>
+        <v>-0.01528485045733075</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.07179031782619549</v>
+        <v>-0.01414330153593524</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.004103597518102742</v>
+        <v>-0.02746565331876349</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.02232959916565735</v>
+        <v>-0.07451282525194125</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>-0.0213533391335109</v>
+        <v>0.01599608490555715</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>-0.01998249881637293</v>
+        <v>0.03298847753985856</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.4102294689034649</v>
+        <v>0.4730570892792729</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1214069979053136</v>
+        <v>0.1378190294372297</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>44.57</v>
+        <v>111.5</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.008453861216139003</v>
+        <v>0.006045277974159324</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.002908301250478251</v>
+        <v>-0.01658138383277563</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.02387210153811836</v>
+        <v>0.0008077940484012558</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.03590741647954188</v>
+        <v>-0.002950923952887319</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.004733973886007048</v>
+        <v>0.007027022408470307</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.05950621926870503</v>
+        <v>-0.04458334480110049</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.003654932735081884</v>
+        <v>-0.03895219982496068</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.01873207378944985</v>
+        <v>-0.01498657197651099</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.2656355920911952</v>
+        <v>0.7224040799725726</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.08169019529033084</v>
+        <v>0.1987032473403454</v>
       </c>
     </row>
     <row r="53">
@@ -3462,37 +3462,37 @@
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>246.7</v>
+        <v>244.66</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.02594072418126114</v>
+        <v>-0.008269125704775782</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.01402825495160531</v>
+        <v>-0.03650608152266532</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.07481716634123359</v>
+        <v>-0.08039836539103451</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.1399086270706666</v>
+        <v>-0.1513406763662224</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.0973962395945942</v>
+        <v>-0.08254280035837624</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.1250421981505007</v>
+        <v>-0.1191967735233617</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.06848086298315725</v>
+        <v>0.04785902075146753</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.1487032787114699</v>
+        <v>0.123614624783051</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>1.125634057357708</v>
+        <v>1.10805678355788</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.2857686524181051</v>
+        <v>0.2822147495626377</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>110.83</v>
+        <v>25.81</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.006187184655502942</v>
+        <v>-0.009213043306992685</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.01414335851083337</v>
+        <v>-0.07540753646954323</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.01580675579121926</v>
+        <v>-0.07361546931551777</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.003775264439957904</v>
+        <v>-0.007574903055762139</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-0.003244272399765324</v>
+        <v>0.1079772985340697</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.05177848445236843</v>
+        <v>0.03584333266047279</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.03914597573575229</v>
+        <v>-0.1510871951167106</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.02811263895600613</v>
+        <v>-0.2231192845740998</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.7120538326575692</v>
+        <v>0.2243740858050716</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.1962973445959157</v>
+        <v>0.06980521268766715</v>
       </c>
     </row>
     <row r="55">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -3574,37 +3574,37 @@
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>26.05</v>
+        <v>34.76</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.02434462574177643</v>
+        <v>-0.01193865776006786</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.02813018927751876</v>
+        <v>-0.02932150269452261</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.05711600577396148</v>
+        <v>-0.03818486694580592</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.0009990420014671653</v>
+        <v>-0.07108498069408331</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>0.0959707950872668</v>
+        <v>-0.04035922846445894</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.03142548180998661</v>
+        <v>-0.04141721448837188</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.1342905195010418</v>
+        <v>-0.05677696248669595</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-0.2299300437807121</v>
+        <v>0.03550393359956217</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.2357591887278352</v>
+        <v>0.35551117742129</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.07311092459787383</v>
+        <v>0.1067113596083147</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>35.18</v>
+        <v>44.03</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.01207526812147208</v>
+        <v>-0.01211579356573456</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.0002841239534920881</v>
+        <v>-0.02566939328753393</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.01262982737719176</v>
+        <v>-0.0329453116673939</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.06461048300294259</v>
+        <v>-0.03358214547576999</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.06439146151823372</v>
+        <v>-0.01167228881411719</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.02472724334732646</v>
+        <v>-0.07109710206954567</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.04149750548095754</v>
+        <v>-0.02426356296218712</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.04522688585896639</v>
+        <v>-0.03163849515101924</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.3718895969819764</v>
+        <v>0.2503014125279721</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.1111509304988321</v>
+        <v>0.07730392120511165</v>
       </c>
     </row>
     <row r="57">
@@ -3686,37 +3686,37 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>17.92</v>
+        <v>17.68</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.0331354720821504</v>
+        <v>-0.01306101556624706</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.06711791526247368</v>
+        <v>-0.06887838759032161</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.1057202749613323</v>
+        <v>-0.1133286677797809</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.1035276547887095</v>
+        <v>-0.124219973312235</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>0.04041818122005858</v>
+        <v>0.0487543633709433</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.0538204190983933</v>
+        <v>0.04844348926846376</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.1386537969535606</v>
+        <v>-0.1580000377836681</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.1889542669780362</v>
+        <v>-0.1974036994996532</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.0269139604041253</v>
+        <v>0.01350142118209074</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.008892017796256368</v>
+        <v>0.004480370032510672</v>
       </c>
     </row>
     <row r="58">
@@ -3742,37 +3742,37 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>19.22</v>
+        <v>19.18</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.00445426729634435</v>
+        <v>-0.001873014108881854</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>0.002660437918090564</v>
+        <v>-0.01529540310667865</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.01803406274917996</v>
+        <v>-0.0184190641568841</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.008447072925265475</v>
+        <v>0.007615469718638135</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.01405489387285686</v>
+        <v>-0.03820128432154113</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.0457563410783659</v>
+        <v>0.05227068322980077</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.06489590880477003</v>
+        <v>-0.07738042823419256</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.1961523824140317</v>
+        <v>-0.1928471653979353</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1711495298418055</v>
+        <v>0.1689559502488014</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.05407322752452748</v>
+        <v>0.0534147182118494</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>99.23</v>
+        <v>50.9</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.01508681531579559</v>
+        <v>-0.01126647283439786</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.01917559402118496</v>
+        <v>-0.05583376609261281</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.06386789285911709</v>
+        <v>-0.06810687438212837</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.1044223770410868</v>
+        <v>-0.08205589133375779</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.0714520594966328</v>
+        <v>0.02528108126258877</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.05252786354941374</v>
+        <v>-0.095613459618616</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.04636953902114538</v>
+        <v>-0.1804241520132236</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1385811262121519</v>
+        <v>-0.1606001119147007</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.2491305923727236</v>
+        <v>0.01990589562236633</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.07696754283207663</v>
+        <v>0.006591751874848617</v>
       </c>
     </row>
     <row r="60">
@@ -3840,51 +3840,51 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>51.48</v>
+        <v>96.91</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.005025166752916421</v>
+        <v>-0.02338002233537273</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.05402423237100895</v>
+        <v>-0.05241021958438108</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.07059035729368202</v>
+        <v>-0.07280896694768368</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.05332845658179419</v>
+        <v>-0.1046747452445449</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>0.01212896705219313</v>
+        <v>-0.06213911958302354</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.1001435084338044</v>
+        <v>-0.0670530800894652</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.1634324036941409</v>
+        <v>-0.0962860839010039</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1725039494877623</v>
+        <v>-0.1564682428474852</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.03152749415487976</v>
+        <v>0.2199257740608358</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.01040061686571514</v>
+        <v>0.06850805959388073</v>
       </c>
     </row>
     <row r="61">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>47.74</v>
+        <v>47.04</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.02829227273415491</v>
+        <v>-0.0146627720638558</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>0.009942907047844729</v>
+        <v>-0.01424979647487445</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.021320154302084</v>
+        <v>-0.05428228129932544</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.09497627149825982</v>
+        <v>-0.09294253062276514</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.2278829004580598</v>
+        <v>-0.2048681366319332</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.1175600180228585</v>
+        <v>-0.1431694060453986</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.005687812319792318</v>
+        <v>-0.03567031380304209</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.1374791586834032</v>
+        <v>0.1224051798328032</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>-0.1358550196654661</v>
+        <v>-0.1485258393366055</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>-0.0475060982024027</v>
+        <v>-0.05218446121678322</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>90.31</v>
+        <v>88.22</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.00812746258496444</v>
+        <v>-0.0231424692103952</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.02704160896878816</v>
+        <v>-0.05767999751608699</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.07193505472842143</v>
+        <v>-0.07748610525501187</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.1070793147756646</v>
+        <v>-0.1033641450557351</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.06036821120074631</v>
+        <v>-0.05582942962755499</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.07377224339911492</v>
+        <v>-0.08586525049433535</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.08310014718128966</v>
+        <v>-0.1320217796764305</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>-0.1986346927845513</v>
+        <v>-0.2128775483586737</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>0.09752792911874364</v>
+        <v>0.07212842281156417</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>0.03150624162540905</v>
+        <v>0.02348685647299242</v>
       </c>
     </row>
   </sheetData>
@@ -4181,17 +4181,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4602,21 +4602,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1719351061283665</v>
+        <v>0.1536231779896946</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1399086270706666</v>
+        <v>-0.1513406763662224</v>
       </c>
     </row>
     <row r="18">
@@ -4647,21 +4647,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1700581477953975</v>
+        <v>0.1110669548024814</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1389059720525955</v>
+        <v>-0.1306494521588698</v>
       </c>
     </row>
     <row r="19">
@@ -4692,21 +4692,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1311864475745939</v>
+        <v>0.07430524308851139</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1248255356002306</v>
+        <v>-0.124219973312235</v>
       </c>
     </row>
     <row r="20">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.1233697531358471</v>
+        <v>0.07178803540208034</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1070793147756646</v>
+        <v>-0.1145038269821274</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.1098332325732603</v>
+        <v>0.0655737510964931</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.1044223770410868</v>
+        <v>-0.1046747452445449</v>
       </c>
     </row>
     <row r="22">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.1065747235076508</v>
+        <v>0.0612222460637879</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.1035276547887095</v>
+        <v>-0.1033641450557351</v>
       </c>
     </row>
     <row r="23">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.1057742027746411</v>
+        <v>0.03191855777821995</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.09497627149825982</v>
+        <v>-0.09294253062276514</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.08224466618386739</v>
+        <v>0.02158799280855273</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.0912648521076932</v>
+        <v>-0.08473411134401343</v>
       </c>
     </row>
     <row r="25">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.05326447273497714</v>
+        <v>0.01397023246874607</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.08999943186103165</v>
+        <v>-0.08205589133375779</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.04342019081640713</v>
+        <v>0.01309866543957594</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.07667405188781373</v>
+        <v>-0.07693700028242934</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3274916531260985</v>
+        <v>0.327739054342352</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2278829004580598</v>
+        <v>-0.2048681366319332</v>
       </c>
     </row>
     <row r="32">
@@ -5158,21 +5158,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.3015360170104044</v>
+        <v>0.3010432455720362</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1412685644336509</v>
+        <v>-0.1189785038425308</v>
       </c>
     </row>
     <row r="33">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2887011248914635</v>
+        <v>0.2972349182644201</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1246563026902113</v>
+        <v>-0.1003107712195344</v>
       </c>
     </row>
     <row r="34">
@@ -5248,21 +5248,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2819951787022772</v>
+        <v>0.2736000061035155</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1145199561595223</v>
+        <v>-0.08921004370306584</v>
       </c>
     </row>
     <row r="35">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2143131175831314</v>
+        <v>0.2214096586739513</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.0973962395945942</v>
+        <v>-0.08254280035837624</v>
       </c>
     </row>
     <row r="36">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2135032424982086</v>
+        <v>0.2182688237468962</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.0714520594966328</v>
+        <v>-0.06213911958302354</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1945492101268345</v>
+        <v>0.1880191989186075</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.06439146151823372</v>
+        <v>-0.0577647505183041</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1928344319429605</v>
+        <v>0.174282697043711</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.06036821120074631</v>
+        <v>-0.05582942962755499</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1903768760148632</v>
+        <v>0.1692841787504875</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.0575358293431979</v>
+        <v>-0.04035922846445894</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1793103323538441</v>
+        <v>0.1664805453254974</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.05046302816536596</v>
+        <v>-0.03820128432154113</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5692007819013811</v>
+        <v>0.5562073107203438</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5646,21 +5646,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1250421981505007</v>
+        <v>-0.1431694060453986</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4982736806758969</v>
+        <v>0.4799336228302693</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1175600180228585</v>
+        <v>-0.1397438574150647</v>
       </c>
     </row>
     <row r="47">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4562212773228167</v>
+        <v>0.4351604746013573</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5736,21 +5736,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1001435084338044</v>
+        <v>-0.1191967735233617</v>
       </c>
     </row>
     <row r="48">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.429174368698803</v>
+        <v>0.4184852096991443</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.09191879630144695</v>
+        <v>-0.095613459618616</v>
       </c>
     </row>
     <row r="49">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4183816224346126</v>
+        <v>0.4101126223328033</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.08243585489778893</v>
+        <v>-0.08803998601065821</v>
       </c>
     </row>
     <row r="50">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3762576340720791</v>
+        <v>0.3784881450196618</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.07377224339911492</v>
+        <v>-0.08586525049433535</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3387599128794934</v>
+        <v>0.3230506159981994</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.07115650286653941</v>
+        <v>-0.08341894619310819</v>
       </c>
     </row>
     <row r="52">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2818372654801797</v>
+        <v>0.2898748041550081</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.05950621926870503</v>
+        <v>-0.07451282525194125</v>
       </c>
     </row>
     <row r="53">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2680255254692037</v>
+        <v>0.2743626030966451</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.05252786354941374</v>
+        <v>-0.07109710206954567</v>
       </c>
     </row>
     <row r="54">
@@ -6029,21 +6029,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2593808750343316</v>
+        <v>0.2403616110275348</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.05177848445236843</v>
+        <v>-0.07100709850303122</v>
       </c>
     </row>
     <row r="55"/>
@@ -6135,21 +6135,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9343774756852821</v>
+        <v>0.9367396057334156</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2299300437807121</v>
+        <v>-0.2231192845740998</v>
       </c>
     </row>
     <row r="60">
@@ -6180,21 +6180,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.9189510992431646</v>
+        <v>0.868242648151998</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.1986346927845513</v>
+        <v>-0.2128775483586737</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.9022979877554096</v>
+        <v>0.7570162029035277</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1961523824140317</v>
+        <v>-0.1974036994996532</v>
       </c>
     </row>
     <row r="62">
@@ -6270,21 +6270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.7196261762205589</v>
+        <v>0.6998458500628668</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1889542669780362</v>
+        <v>-0.1928471653979353</v>
       </c>
     </row>
     <row r="63">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.7138820653594284</v>
+        <v>0.6777183233486406</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1725039494877623</v>
+        <v>-0.1606001119147007</v>
       </c>
     </row>
     <row r="64">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.6884879275121565</v>
+        <v>0.6555330343392065</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1385811262121519</v>
+        <v>-0.1564682428474852</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.6857176518055275</v>
+        <v>0.6438411063033291</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6427,21 +6427,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.08233579209265307</v>
+        <v>-0.09819160183626585</v>
       </c>
     </row>
     <row r="66">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.6301047697667759</v>
+        <v>0.5513096247466027</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6472,21 +6472,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.07845547728873148</v>
+        <v>-0.08508537994304888</v>
       </c>
     </row>
     <row r="67">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.6073726931290087</v>
+        <v>0.5271292545942103</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.03642535849006567</v>
+        <v>-0.0352626078045104</v>
       </c>
     </row>
     <row r="68">
@@ -6540,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.5482365510853715</v>
+        <v>0.5178849391563829</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.02811263895600613</v>
+        <v>-0.03163849515101924</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.178370539305554</v>
+        <v>3.015175613616528</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1358550196654661</v>
+        <v>-0.1485258393366055</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.870979646142213</v>
+        <v>2.776546510641252</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.0269139604041253</v>
+        <v>0.01350142118209074</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.635610277042516</v>
+        <v>2.5098788195624</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.03152749415487976</v>
+        <v>0.01990589562236633</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>2.037735811710868</v>
+        <v>2.003773491201815</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.03808267986649594</v>
+        <v>0.03120794239522628</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.756665535645811</v>
+        <v>1.563956580278602</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.09752792911874364</v>
+        <v>0.07212842281156417</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.459147635156747</v>
+        <v>1.433447124297525</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.358681829292578</v>
+        <v>1.304841743683902</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1588381529675504</v>
+        <v>0.1517397210915405</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.331000916546931</v>
+        <v>1.271213361193183</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1711495298418055</v>
+        <v>0.1689559502488014</v>
       </c>
     </row>
     <row r="81">
@@ -7006,21 +7006,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.184739084390594</v>
+        <v>1.10805678355788</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1848534758530176</v>
+        <v>0.1838093987067981</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.125634057357708</v>
+        <v>1.104333165472413</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2195892409762938</v>
+        <v>0.2067229109279012</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -489,15 +489,15 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>15.92</v>
+        <v>16.01</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.01118014291372016</v>
+        <v>0.005653275889232479</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.01363068907521714</v>
+        <v>-0.03321251538634928</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.07422404886107348</v>
+        <v>0.03157214926968943</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.1536231779896946</v>
+        <v>0.1609862417092056</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.2736000061035155</v>
+        <v>0.2787539651369588</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5562073107203438</v>
+        <v>0.4962617303057115</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7663376121530259</v>
+        <v>0.8110859674810009</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9367396057334156</v>
+        <v>0.9728897942625354</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.003773491201815</v>
+        <v>2.139215789855056</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4428540187319319</v>
+        <v>0.4642224344406485</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>37.88</v>
+        <v>38.06</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.01865278327636655</v>
+        <v>0.004751855863259102</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.05981632644945711</v>
+        <v>-0.04299721058059081</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.06699501251803286</v>
+        <v>-0.03130566336409102</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.07430524308851139</v>
+        <v>0.08125001557848632</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.327739054342352</v>
+        <v>0.294731843948052</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2743626030966451</v>
+        <v>0.2757170985225788</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.434165304416291</v>
+        <v>0.4404402862400516</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.6998458500628668</v>
+        <v>0.6578417767545091</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.7663501204825063</v>
+        <v>0.759676615450062</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2088124679584211</v>
+        <v>0.2072881954314076</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>560.28</v>
+        <v>568.53</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.02439525199202008</v>
+        <v>0.01472477969695496</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.01389803483576735</v>
+        <v>0.00268076313481358</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-0.02219890175065442</v>
+        <v>0.02787880232448048</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.01603404274294096</v>
+        <v>-0.007679757448823543</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.01861929962285869</v>
+        <v>-0.06714247615152347</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.4101126223328033</v>
+        <v>0.417674565562264</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5023346047505155</v>
+        <v>0.5376501005932421</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.868242648151998</v>
+        <v>0.8764159167469507</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.776546510641252</v>
+        <v>2.829354236076945</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5572736885715217</v>
+        <v>0.5644986075059293</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>156.82</v>
+        <v>195.72</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.01606222537435631</v>
+        <v>0.001278968631701849</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.045990980253245</v>
+        <v>0.02627022353553121</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.06782374542646741</v>
+        <v>0.05259760487729781</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-0.007656720017874541</v>
+        <v>0.09726975712544483</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.2182688237468962</v>
+        <v>0.2035938802693626</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2318445414978014</v>
+        <v>0.199039064124213</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.2903995190644055</v>
+        <v>0.4954616298678527</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6777183233486406</v>
+        <v>0.524453679351564</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.006494671561847</v>
+        <v>0.3988498348758804</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2612833718871301</v>
+        <v>0.1183825064809605</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>195.47</v>
+        <v>156.2</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.002358887886902972</v>
+        <v>-0.003953643330054879</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.01632610284279346</v>
+        <v>-0.04645626471992048</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.0539170751829583</v>
+        <v>-0.03805892196536353</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.1110669548024814</v>
+        <v>-0.01183026690282218</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1692841787504875</v>
+        <v>0.1778915159829142</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.2403616110275348</v>
+        <v>0.2371683366735888</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.4691411841301418</v>
+        <v>0.2751634061424379</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.5178849391563829</v>
+        <v>0.6396541144386847</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.3696125783083839</v>
+        <v>0.9939985583684026</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1105358390912996</v>
+        <v>0.2586595634891469</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>88.61</v>
+        <v>505.57</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.06990654211594904</v>
+        <v>0.03078680870580075</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.02893150016053081</v>
+        <v>0.02873129467181545</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.0812856048310483</v>
+        <v>0.04924873644089822</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.01005475929392941</v>
+        <v>-0.04629223879091648</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1479809768467291</v>
+        <v>-0.1536469492904977</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.07044453306732956</v>
+        <v>0.5016396420469882</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3291830683655004</v>
+        <v>0.4688065685855629</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.7570162029035277</v>
+        <v>0.6906695938305043</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.563956580278602</v>
+        <v>1.521774551636385</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3686851505255091</v>
+        <v>0.3611377718609963</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>110.5</v>
+        <v>156.05</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.004145629851010191</v>
+        <v>0.02374867512902346</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.009235172514751921</v>
+        <v>0.008922253178700768</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.06813966694457096</v>
+        <v>0.02725297406257043</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.07290882006381572</v>
+        <v>0.02718539318450786</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.174282697043711</v>
+        <v>0.009714568762854148</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.4184852096991443</v>
+        <v>0.3545882870133334</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.2873281409266621</v>
+        <v>0.4407048384423573</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.2865793470142493</v>
+        <v>0.5332567421574004</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.104333165472413</v>
+        <v>1.347462518421874</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2814593473991487</v>
+        <v>0.3290241996207364</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>490.47</v>
+        <v>88.53</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.01045090838206097</v>
+        <v>-0.0009028532953800905</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.0249728589847682</v>
+        <v>-0.02349442749584529</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.01956984039061715</v>
+        <v>-0.06238084626002094</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.06648272091786467</v>
+        <v>-0.0006772498145830586</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.1189785038425308</v>
+        <v>0.06819191288473481</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.4799336228302693</v>
+        <v>0.07948528408971445</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.4224203248913274</v>
+        <v>0.3147318967797927</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.6555330343392065</v>
+        <v>0.7153530236638159</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.433447124297525</v>
+        <v>1.490994625401555</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3450568420853157</v>
+        <v>0.3555772244930473</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>152.43</v>
+        <v>109.9</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.01122217790108515</v>
+        <v>-0.005429850444534812</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.003985890205908893</v>
+        <v>-0.007674929788903828</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.00300874298975462</v>
+        <v>-0.04881425778914361</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.007601757706001244</v>
+        <v>-0.07491583583547068</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.03102023780551622</v>
+        <v>0.1374456468825411</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.3230506159981994</v>
+        <v>0.4010708580481357</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.4024158331665069</v>
+        <v>0.2893440085182841</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5135015403709919</v>
+        <v>0.268231605252528</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.304841743683902</v>
+        <v>1.071682735180211</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3209317235163318</v>
+        <v>0.2747971452599531</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>202.64</v>
+        <v>202.93</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.0138693173747102</v>
+        <v>0.001431076228811001</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.05224263737192281</v>
+        <v>-0.04242169484164071</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.05661081698951054</v>
+        <v>-0.02881074113608206</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.01309866543957594</v>
+        <v>0.01597069738103296</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.2214096586739513</v>
+        <v>0.190442388965939</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1773177624941711</v>
+        <v>0.1886627456966992</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2018936940428218</v>
+        <v>0.1940712054748053</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4444062683606842</v>
+        <v>0.4147876103718737</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6109070958338347</v>
+        <v>0.6027254196795855</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1722587907111925</v>
+        <v>0.1702708165268314</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>96.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.03905707360174637</v>
+        <v>0.002548830229773147</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.05090769170321419</v>
+        <v>-0.002008614223147132</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.06728720653941345</v>
+        <v>-0.04220775300082302</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.0655737510964931</v>
+        <v>-0.05524416277243283</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.2972349182644201</v>
+        <v>0.1054308552081957</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>-0.08341894619310819</v>
+        <v>0.4392559445570168</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2207843206735711</v>
+        <v>0.2527195061611902</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.5271292545942103</v>
+        <v>0.2555536027513163</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>3.015175613616528</v>
+        <v>1.015014411284552</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.5894060006595374</v>
+        <v>0.2630660217963274</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>68.01000000000001</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.01889782983786659</v>
+        <v>-0.007351859789659354</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.04251719970388967</v>
+        <v>-0.04821652550727196</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.06076510569466154</v>
+        <v>-0.04633421015505912</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.02995290908343018</v>
+        <v>-0.03197585024156646</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1664805453254974</v>
+        <v>0.1305892557957151</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2242619629034166</v>
+        <v>0.2192033947720422</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2074248538042787</v>
+        <v>0.2019481820044593</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4466997097498302</v>
+        <v>0.4270148847911552</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.6384286595211466</v>
+        <v>0.6181045364750855</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1788969533906408</v>
+        <v>0.1740020587217068</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>94.16</v>
+        <v>420.67</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.003386956852819978</v>
+        <v>0.001070896686792722</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.01216949261884892</v>
+        <v>-0.01604562339753801</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.06578030750267183</v>
+        <v>0.005641786911416258</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.06401585397308307</v>
+        <v>0.01293047385650925</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.1320236913646933</v>
+        <v>-0.01223347279831022</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.4351604746013573</v>
+        <v>0.09259265864452715</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2439520853670276</v>
+        <v>0.386546993274935</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.2622134404733962</v>
+        <v>0.6449688614398215</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.028699586361434</v>
+        <v>0.2525498259317014</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2659189865113565</v>
+        <v>0.07794930533438671</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>108.63</v>
+        <v>27.13</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.02223223451509293</v>
+        <v>-0.001472245690652185</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.02002707488734345</v>
+        <v>-0.02374961255909758</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.01002466116707834</v>
+        <v>-0.05929268317524072</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.01308260602706224</v>
+        <v>-0.02968526290714324</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.04241433842987052</v>
+        <v>0.1925274356380924</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1723504528398703</v>
+        <v>0.3688193531027808</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.3156628770448269</v>
+        <v>0.1693964770943057</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.5513096247466027</v>
+        <v>0.1594016924377457</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.7901174825217026</v>
+        <v>0.3338249241514784</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2142101099772191</v>
+        <v>0.1007776661041582</v>
       </c>
     </row>
     <row r="16">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>420.22</v>
+        <v>31.83</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.02126471352747872</v>
+        <v>-0.003755894721999331</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.0223121760600351</v>
+        <v>0.01272668198047722</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.01270029849051446</v>
+        <v>0.03411303488099371</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.02158799280855273</v>
+        <v>0.05888225180339934</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.006384214795483123</v>
+        <v>0.1267962610653408</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.09930411365382574</v>
+        <v>0.1047487398197882</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.3874460126329229</v>
+        <v>0.32648223561963</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.6438411063033291</v>
+        <v>0.3835897067697212</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2533008009700366</v>
+        <v>0.3131474425233451</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.07816469298469175</v>
+        <v>0.0950597862933702</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>27.17</v>
+        <v>96.36</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.006944463809175905</v>
+        <v>0.001663239783629811</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.04499123558242246</v>
+        <v>-0.02950952037626153</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.06051175641021156</v>
+        <v>-0.02804114178345607</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.03275187153066594</v>
+        <v>0.06123345123044155</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1880191989186075</v>
+        <v>0.2200391665274855</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.3784881450196618</v>
+        <v>-0.05952343898111812</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1675977456729745</v>
+        <v>0.1698656795287599</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.184394047243212</v>
+        <v>0.4913104975282576</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.3470500730551402</v>
+        <v>2.961589504096277</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1044038533599363</v>
+        <v>0.5823036289701311</v>
       </c>
     </row>
     <row r="18">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>96.03</v>
+        <v>108.97</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.0345833155643942</v>
+        <v>0.003129927054052795</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.05379839589514657</v>
+        <v>-0.01819980792815024</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.07387408122049122</v>
+        <v>0.002576122670048031</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.0612222460637879</v>
+        <v>-0.003383895459847186</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.3010432455720362</v>
+        <v>-0.0006419634467762503</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>-0.07100709850303122</v>
+        <v>0.171972438013223</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1609150378037616</v>
+        <v>0.2900934368063663</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.4120794364266935</v>
+        <v>0.5331027851477392</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.5098788195624</v>
+        <v>0.7848523589262606</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.5197216161985208</v>
+        <v>0.2130185225862815</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>31.95</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.002510195218055067</v>
+        <v>0.01114234831225369</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.006299236628014349</v>
+        <v>-0.02176106805987021</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.03264383359560918</v>
+        <v>-0.02558959370507974</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.07178803540208034</v>
+        <v>0.07745223607201668</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1015758563220654</v>
+        <v>0.2493566256951565</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1382396705322824</v>
+        <v>-0.0420284343979711</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.3068559099276724</v>
+        <v>0.1338419237704112</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.3829385314401557</v>
+        <v>0.4020242454713518</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2905657964279276</v>
+        <v>2.495943346180588</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.08874636232693822</v>
+        <v>0.5177076691519817</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>56.69</v>
+        <v>55.91</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.000881266307342865</v>
+        <v>0.002869952419948252</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.02258623057398301</v>
+        <v>0.003409881955249938</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.009954588046326651</v>
+        <v>0.01212885859137258</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.01064573505189548</v>
+        <v>0.02927106200070351</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.07384538055756495</v>
+        <v>0.08908715642210097</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.2898748041550081</v>
+        <v>0.1081181943667278</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1910556435343769</v>
+        <v>0.2517418218561138</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1912900419602483</v>
+        <v>0.2663705272791432</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1838093987067981</v>
+        <v>0.7287745368752885</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.0578577235107518</v>
+        <v>0.2001792641623203</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>55.75</v>
+        <v>56.63</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.007830550586627627</v>
+        <v>-0.001058344682433709</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.005954562287221465</v>
+        <v>-0.01375822232710089</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.00795513678872295</v>
+        <v>-0.003869787368701583</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.03191855777821995</v>
+        <v>0.005147336079906362</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.07650400901125209</v>
+        <v>0.06926873953660606</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1166654734298767</v>
+        <v>0.2879260309982692</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2463164042026311</v>
+        <v>0.1638561000777878</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.266722468395272</v>
+        <v>0.1657973899395615</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.7192259786435005</v>
+        <v>0.1778379413674496</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1979655292611215</v>
+        <v>0.05607601675507845</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>114.77</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.03708369584531823</v>
+        <v>0.001219400762257239</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.03049502191340292</v>
+        <v>-0.01820107849458363</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.06691059639783414</v>
+        <v>-0.005383600396358879</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.0235664816308081</v>
+        <v>-0.03788564152075358</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.02151130456630468</v>
+        <v>0.02739723557322593</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.007007351630898384</v>
+        <v>0.1685508707351158</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1488847713817418</v>
+        <v>0.1161952829322239</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.3570868799465505</v>
+        <v>0.1607876518308502</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>1.271213361193183</v>
+        <v>0.8572300848686465</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.3144759507739505</v>
+        <v>0.229198165320424</v>
       </c>
     </row>
     <row r="23">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>73.81</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.004901301910267497</v>
+        <v>0.001177189996062866</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.01415794242156176</v>
+        <v>-0.01874813226162375</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.007262957990716079</v>
+        <v>-0.006134942660853349</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.02919901691893279</v>
+        <v>-0.03503050837994448</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.03631573659066856</v>
+        <v>0.03660249354923195</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.1537828261813023</v>
+        <v>0.1729462416786627</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1206553774331398</v>
+        <v>0.103000155713787</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.164552872343563</v>
+        <v>0.1391000470743193</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.851545443505985</v>
+        <v>0.9361499483296136</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2279427667310989</v>
+        <v>0.2463681133834443</v>
       </c>
     </row>
     <row r="24">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>67.95999999999999</v>
+        <v>144.02</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.004285516822437607</v>
+        <v>0.005164750833812848</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.01664016084101516</v>
+        <v>-0.01057978367657575</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.006723167155555987</v>
+        <v>-0.007306296837713777</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.02831002699195473</v>
+        <v>-0.01234400604407904</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.04680510463111776</v>
+        <v>0.07262572689367386</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1583368194457322</v>
+        <v>0.1224747426696895</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1092999394643348</v>
+        <v>0.08369403862906011</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1450611721471402</v>
+        <v>0.103247724101075</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.9313400093058311</v>
+        <v>0.6679537641593243</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2453351483011805</v>
+        <v>0.1859362275283625</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>71.81</v>
+        <v>64.62</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.0265690548144667</v>
+        <v>0.01221808571631899</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.03558959922726512</v>
+        <v>0.006385355364512346</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.0689744572056038</v>
+        <v>0.006855756299688931</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.0392025741091987</v>
+        <v>0.02230665531611664</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.0577647505183041</v>
+        <v>0.08233823065714696</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.001370300231929633</v>
+        <v>0.2050422169467045</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1087782538911222</v>
+        <v>0.06415967660117139</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.4818549021929288</v>
+        <v>0.01081317797924197</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.2904525189776361</v>
+        <v>0.9059838551520563</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.08871450704278416</v>
+        <v>0.2398612087010661</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>143.28</v>
+        <v>288.92</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.002378594739635531</v>
+        <v>0.01197903127052324</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.0310407553219505</v>
+        <v>-0.006703963015049053</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.009265636724747561</v>
+        <v>-0.0186474310182605</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.02264670658931944</v>
+        <v>-0.004787930634661763</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.0656898635281129</v>
+        <v>0.0899762532331454</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1036986843180134</v>
+        <v>0.1771512815915495</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1046891417034121</v>
+        <v>0.05707597572617695</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1162245592279101</v>
+        <v>0.01936993576481938</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6690316619284109</v>
+        <v>0.6751899540953485</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1861916388340474</v>
+        <v>0.187648760909678</v>
       </c>
     </row>
     <row r="27">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>189.77</v>
+        <v>190.51</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.009706207602974359</v>
+        <v>0.003899405689597568</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.04185596984913786</v>
+        <v>-0.03028612442071787</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.02856412417053034</v>
+        <v>-0.02372658038994602</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.008181525686007163</v>
+        <v>0.01345887241621124</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.06391214591772409</v>
+        <v>0.05554742529210821</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1457721854146006</v>
+        <v>0.1590671771344119</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.05657573335562582</v>
+        <v>0.0552821825125549</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0944467031342402</v>
+        <v>0.07873222904929711</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.092642868837109</v>
+        <v>1.109072834117779</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2790819566334894</v>
+        <v>0.2824207189924648</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2048,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>63.84</v>
+        <v>180.78</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.004677256624810111</v>
+        <v>0.01997287957807781</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.01572618637319101</v>
+        <v>0.01000052087378234</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.006999545131920692</v>
+        <v>0.008873242458995678</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.00330031558930588</v>
+        <v>-0.03542844656130539</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.08767180677180497</v>
+        <v>-0.04145903170323251</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1922751944263843</v>
+        <v>0.07408685693916017</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.04648971117605272</v>
+        <v>0.1698228005884068</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.00205983256443143</v>
+        <v>0.2293477511968078</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.898050330914318</v>
+        <v>0.8714655400845333</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2381385378535033</v>
+        <v>0.2323307295558952</v>
       </c>
     </row>
     <row r="29">
@@ -2118,37 +2118,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>129.7</v>
+        <v>129.84</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.00247327294290578</v>
+        <v>0.001079409351908422</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.04032554342855921</v>
+        <v>-0.02383278174470105</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.03049784622726492</v>
+        <v>-0.03807971219693673</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.0401124804973878</v>
+        <v>-0.03299328065545404</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.07122435061422294</v>
+        <v>0.07538805154718253</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.07904158724885435</v>
+        <v>0.09105407345348637</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.07939305483234627</v>
+        <v>0.05526425216036523</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.09656129467219476</v>
+        <v>0.07721795468331316</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6554669385002223</v>
+        <v>0.6407962568561796</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.182969381246306</v>
+        <v>0.1794645317434582</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>285.5</v>
+        <v>23.65</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.008439526057007596</v>
+        <v>0.006382962490649957</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02699206961111045</v>
+        <v>-0.0008449707519732064</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.02834968162862073</v>
+        <v>-0.007553516817124128</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.02599616281428041</v>
+        <v>-0.01128764451933495</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.08621215940430571</v>
+        <v>-0.04910457823445757</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.162601260271426</v>
+        <v>0.0001833487696918379</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.04418106202550676</v>
+        <v>0.1625937385727547</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.008798240869420493</v>
+        <v>0.2741264215405002</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6741922362264217</v>
+        <v>0.6062040505856543</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1874129321887719</v>
+        <v>0.1711168750538763</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>177.24</v>
+        <v>113.63</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.01604396442185518</v>
+        <v>-0.009932904269343346</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.001689691361457246</v>
+        <v>-0.04206715037618602</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.02459964259283687</v>
+        <v>-0.04303520887893453</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.042825472561414</v>
+        <v>-0.03564461098505889</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.01947749591477133</v>
+        <v>-0.03922488573237393</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.05398922219075586</v>
+        <v>-0.009763269389775231</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1484656393201633</v>
+        <v>0.08617397819704453</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.212634697013085</v>
+        <v>0.3254923902854314</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.8457436953197921</v>
+        <v>1.243417984565997</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.2266588539005849</v>
+        <v>0.3090916890920434</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>23.5</v>
+        <v>92.08</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.01426175127565943</v>
+        <v>0.000869585120159666</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.004659068509440645</v>
+        <v>-0.01254689725410518</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.02812242748525628</v>
+        <v>-0.02704984758139972</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.008020284076586059</v>
+        <v>-0.01021172697740169</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.02546224577876255</v>
+        <v>0.006586496884897874</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>-0.003219997396559982</v>
+        <v>0.06042644763277272</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1608910753487238</v>
+        <v>0.1319147435592631</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.2593357520203565</v>
+        <v>0.1043791174783675</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.6054481761838268</v>
+        <v>0.4271784375394292</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1709331382981558</v>
+        <v>0.1258816956502766</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>82.03</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.003916285624889104</v>
+        <v>-0.004456199773062441</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01877990099856552</v>
+        <v>-0.03626317646723654</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.05057873459959494</v>
+        <v>-0.06020772774324479</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.05615009408796123</v>
+        <v>-0.03535289063560032</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.01266030855019651</v>
+        <v>-0.110759086443635</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.08746653450725939</v>
+        <v>-0.01634044356096731</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.08975426842135459</v>
+        <v>0.1053626326077799</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1800293233857568</v>
+        <v>0.4289851200266206</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.404731595426165</v>
+        <v>0.2650088851190491</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1199478067265105</v>
+        <v>0.0815116250091521</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>227.71</v>
+        <v>82.14</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.01564861923889693</v>
+        <v>0.001340980275368775</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.03565831531288888</v>
+        <v>-0.02411784274038209</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.04926720414012598</v>
+        <v>-0.04919550908700721</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.04287334198325132</v>
+        <v>-0.05564501932040145</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.02368934321854987</v>
+        <v>-0.04451372922214725</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.009293380476786073</v>
+        <v>0.08978686494664712</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.1370118336613095</v>
+        <v>0.08236605307228473</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1237382965600131</v>
+        <v>0.1686341901993567</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.3355070638261315</v>
+        <v>0.396907426834872</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1012402165471438</v>
+        <v>0.1178646139980373</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>92</v>
+        <v>101.52</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.002818145785933868</v>
+        <v>0.003162052415751404</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.02407973611860059</v>
+        <v>-0.02916709439283638</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.03055849820074119</v>
+        <v>-0.07287674298569491</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.03229199226547752</v>
+        <v>-0.02309470331184149</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.0002744847397184724</v>
+        <v>0.1167953522131071</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.04372548999242132</v>
+        <v>0.1842668115342765</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1252161342679727</v>
+        <v>-0.07506804870465389</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1169175633747059</v>
+        <v>-0.09662783386879226</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.431700565194451</v>
+        <v>0.3843462597586971</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1270695902596226</v>
+        <v>0.1145038606567232</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>27.84</v>
+        <v>73.66</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.006423993655785498</v>
+        <v>0.002995659223713254</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.02040816052600403</v>
+        <v>-0.01087683020432884</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.05144804801553537</v>
+        <v>-0.0199574231893791</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.1145038269821274</v>
+        <v>-0.005937851836331443</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.02165138174634462</v>
+        <v>0.009651268071421581</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.09822484156403788</v>
+        <v>0.0259349519026113</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.000999547169128201</v>
+        <v>0.115996545701089</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.08203650783425354</v>
+        <v>0.07865250385330236</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.5320976634221077</v>
+        <v>0.2226966153398038</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1528217193973689</v>
+        <v>0.06931642230627344</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>101.86</v>
+        <v>228.45</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.002936599853207378</v>
+        <v>0.003249704503785145</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.02320673376748983</v>
+        <v>-0.02977155171045087</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.04812635663087483</v>
+        <v>-0.04221871182224113</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.07693700028242934</v>
+        <v>-0.04073062018409479</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.08921004370306584</v>
+        <v>-0.007530510333272122</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.09951491531236001</v>
+        <v>0.01534357952157595</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.08871014170118063</v>
+        <v>0.1140801744584024</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.2121483998607994</v>
+        <v>0.1033562395637071</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.3491434435903986</v>
+        <v>0.3371587930318443</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1049756534128909</v>
+        <v>0.1016940270164164</v>
       </c>
     </row>
     <row r="38">
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>53.36</v>
+        <v>54.08</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.01531644283800249</v>
+        <v>0.01349327609571738</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.02431885261938715</v>
+        <v>-0.01957936945875627</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.0481626952693196</v>
+        <v>-0.02223828442771092</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.08473411134401343</v>
+        <v>-0.07870526187116555</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.03338924674176669</v>
+        <v>-0.05255622895037848</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.02657137002764731</v>
+        <v>0.04222463225585615</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.09802120747131471</v>
+        <v>0.09628435200068308</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1597847649695354</v>
+        <v>0.1569822799917506</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.7361050355657546</v>
+        <v>0.757291395254919</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.2018732399287761</v>
+        <v>0.2067424606356267</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>73.44</v>
+        <v>102.41</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.001363595698244735</v>
+        <v>0.005399597962518765</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.02249427490741507</v>
+        <v>-0.02947302008999242</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.01673584093106195</v>
+        <v>-0.03903533869407416</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.01010917880198658</v>
+        <v>-0.06670919047558455</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.001720712223966636</v>
+        <v>-0.1180030078254978</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.01171319555671069</v>
+        <v>0.1217404609828885</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.116474983976504</v>
+        <v>0.08937979431034515</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.08486317165152202</v>
+        <v>0.1967922281656775</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.2314371392117094</v>
+        <v>0.342912576368108</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.07185840002760591</v>
+        <v>0.1032719593580986</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>101.2</v>
+        <v>58.38</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.006186829730767673</v>
+        <v>0.005338408385055393</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.05376344239432451</v>
+        <v>-0.01484976844992936</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.08266862556028365</v>
+        <v>-0.01385134601784599</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.03628230749910399</v>
+        <v>-0.0462342437295562</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.1052518872084447</v>
+        <v>-0.04419376752286575</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.1817742589168612</v>
+        <v>0.01504517206160405</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>-0.0804962614988346</v>
+        <v>0.09827060042247338</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>-0.09819160183626585</v>
+        <v>0.135081687267262</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.3911730660135888</v>
+        <v>0.6190952724939833</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.1163328898454077</v>
+        <v>0.1742416165486453</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>58.07</v>
+        <v>94.8</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.01191085175237527</v>
+        <v>0.007224822411094456</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.01442631535194272</v>
+        <v>-0.01270562001625197</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.02974099957690957</v>
+        <v>-0.02509250170315802</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.04442982956394748</v>
+        <v>-0.01639338292888493</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.02946560078995897</v>
+        <v>-0.020227787731394</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.008785010869684085</v>
+        <v>0.04325858436816432</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1053657141707782</v>
+        <v>0.08910040281099096</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1476928607326651</v>
+        <v>0.0561074613611634</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.613881882270721</v>
+        <v>0.3084921548658555</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1729799320685759</v>
+        <v>0.09376420840933886</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>94.12</v>
+        <v>28.17</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.008637030479647367</v>
+        <v>0.01185344547045131</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.02627768279842324</v>
+        <v>-0.02187497143944028</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.03614950050319621</v>
+        <v>-0.03461275593964563</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.03078980377898188</v>
+        <v>-0.111356485857642</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.02795279551987495</v>
+        <v>-0.02761474822306142</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.02504359126371658</v>
+        <v>0.1169706916438087</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.08601755904146269</v>
+        <v>0.005335580906402182</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.06765442069532179</v>
+        <v>0.07905515485945114</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.2992656011699659</v>
+        <v>0.5418421082027245</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.09118732700071752</v>
+        <v>0.1552606142670814</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>62.41</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.007158777578270437</v>
+        <v>0.00368797356355266</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.0385149233346388</v>
+        <v>-0.01352294960696332</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.06655699554765615</v>
+        <v>-0.01912943256298372</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.06975699427539517</v>
+        <v>-0.02507577361406865</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.01629216550316248</v>
+        <v>0.06121632386483378</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.05843982217359445</v>
+        <v>-0.02016931047673942</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.03497888562749307</v>
+        <v>0.01224109674918283</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.05044899798904368</v>
+        <v>-0.04194317060326458</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.5864138668516015</v>
+        <v>0.01850161912091308</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.166287172761836</v>
+        <v>0.006129558125297141</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>70.5</v>
+        <v>63.09</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.006622533642651529</v>
+        <v>0.01089569470979534</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.0101095367644255</v>
+        <v>-0.02623862847533986</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.02678081689706513</v>
+        <v>-0.05695069187430724</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.03675368700198889</v>
+        <v>-0.06408549584384204</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.08076305536530315</v>
+        <v>-0.02851172312111394</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.03002413031968165</v>
+        <v>0.07305513009443065</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0129065185021493</v>
+        <v>0.03093972692229063</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>-0.0352626078045104</v>
+        <v>0.02517071647985225</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.03120794239522628</v>
+        <v>0.5972745823644527</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.01029627043343018</v>
+        <v>0.168942620397267</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>17.82</v>
+        <v>13.05</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.01054972413342459</v>
+        <v>0.005392962324132222</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.01077711532059733</v>
+        <v>-0.02100523140088251</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.0005608653350883674</v>
+        <v>-0.02320355343627922</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.01438054369352793</v>
+        <v>-0.02320355343627922</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.1003107712195344</v>
+        <v>0.05397016192681447</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.02094084416654796</v>
+        <v>0.08831268835224759</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.07567774933705684</v>
+        <v>-0.04339626585328293</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.2367338661425411</v>
+        <v>-0.08476202464388838</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.2067229109279012</v>
+        <v>0.1520803241605271</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.06463936327647835</v>
+        <v>0.0483209215678182</v>
       </c>
     </row>
     <row r="46">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -3070,37 +3070,37 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>45</v>
+        <v>17.92</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.03969271417253628</v>
+        <v>0.005611693781272686</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.01531730309088142</v>
+        <v>0.008441171337434605</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.069671263309938</v>
+        <v>0.02517165592564563</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.01397023246874607</v>
+        <v>-0.01538465246746978</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.06257382813126311</v>
+        <v>-0.1336500677847258</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.1397438574150647</v>
+        <v>-0.02927615615203571</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>-0.01136175354291624</v>
+        <v>0.06266978103682463</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.1167256467439532</v>
+        <v>0.2326681076071317</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>1.098020860372309</v>
+        <v>0.2072435840889764</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.2801767456886555</v>
+        <v>0.06479246371901115</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>12.98</v>
+        <v>47.03</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.00612564125650461</v>
+        <v>0.002771796357964762</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.02771541787721388</v>
+        <v>-0.01754752812472682</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.0306199246134361</v>
+        <v>-0.02407138162417766</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.02552553756589093</v>
+        <v>-0.003812758073850175</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.04914798307212642</v>
+        <v>-0.02258809337388656</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.075698907088666</v>
+        <v>-0.02727045710342968</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>-0.06053954598929789</v>
+        <v>0.04971492351939921</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.08508537994304888</v>
+        <v>0.007916002585064197</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.1517397210915405</v>
+        <v>0.1201507219640956</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.04821760223354543</v>
+        <v>0.0385454029776926</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>218.32</v>
+        <v>112.6</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.005149189518056541</v>
+        <v>0.009865457167005376</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.03389675435057471</v>
+        <v>0.005087920209185581</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.06804400049685844</v>
+        <v>-0.00345162755130457</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.1306494521588698</v>
+        <v>0.01195292415907123</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.02844634610968266</v>
+        <v>0.006893732908681782</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.08803998601065821</v>
+        <v>-0.03202405303031541</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.06933604442479013</v>
+        <v>-0.0273107742810037</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>0.1032202438680987</v>
+        <v>-0.02031198627838682</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.9901784819468107</v>
+        <v>0.7135500273890152</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.25785527513207</v>
+        <v>0.196645731738943</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>46.9</v>
+        <v>219.01</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0</v>
+        <v>0.003160439535862203</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.02535323011400725</v>
+        <v>-0.02925404940233312</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.01923877404467833</v>
+        <v>-0.05931626313434213</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.002764134739361213</v>
+        <v>-0.1305676863301721</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.02225086254996678</v>
+        <v>-0.07149747584884358</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.02655753475363176</v>
+        <v>-0.08117145999428976</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.05781288327749246</v>
+        <v>0.05298882432169405</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.01652502185049975</v>
+        <v>0.1002348561550128</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.1250061193585577</v>
+        <v>1.025734935569158</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.04004379726753204</v>
+        <v>0.2653020334319214</v>
       </c>
     </row>
     <row r="50">
@@ -3294,37 +3294,37 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>83.63</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.00794787395118457</v>
+        <v>0.01387066483566057</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.03574317979393682</v>
+        <v>-0.03196706860863319</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.03418407679476254</v>
+        <v>-0.02416847150273171</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.07682966514881662</v>
+        <v>-0.05399973765709398</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.01387877193100828</v>
+        <v>-0.03076360628032948</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.01702732317501443</v>
+        <v>0.04236132989293417</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.04238113184668313</v>
+        <v>-0.03817728906179751</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.02473477829512705</v>
+        <v>-0.03049845134933904</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.3990213213992599</v>
+        <v>0.4179689005147693</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1184282058563686</v>
+        <v>0.1234547081353394</v>
       </c>
     </row>
     <row r="51">
@@ -3350,37 +3350,37 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>42.52</v>
+        <v>42.39</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.009781047563519718</v>
+        <v>-0.003057409847499137</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.01185215747155866</v>
+        <v>-0.01601676908260607</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.01528485045733075</v>
+        <v>-0.007956942575012671</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.01414330153593524</v>
+        <v>-0.02842084914302212</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.02746565331876349</v>
+        <v>-0.03153960960156177</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.07451282525194125</v>
+        <v>-0.06954862539203222</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.01599608490555715</v>
+        <v>0.005594244224111922</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.03298847753985856</v>
+        <v>0.02438257683341316</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.4730570892792729</v>
+        <v>0.4625350143281861</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1378190294372297</v>
+        <v>0.1351033988428869</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>111.5</v>
+        <v>26.15</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0.006045277974159324</v>
+        <v>0.01313447148077729</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.01658138383277563</v>
+        <v>-0.047395284478435</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>0.0008077940484012558</v>
+        <v>-0.03544818962998986</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.002950923952887319</v>
+        <v>0.003607747517555326</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.007027022408470307</v>
+        <v>0.08915744067198883</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.04458334480110049</v>
+        <v>0.05558072887051391</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.03895219982496068</v>
+        <v>-0.1433214336373765</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.01498657197651099</v>
+        <v>-0.221175952359825</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.7224040799725726</v>
+        <v>0.2375640430670189</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.1987032473403454</v>
+        <v>0.07363310474777607</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>244.66</v>
+        <v>35.28</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.008269125704775782</v>
+        <v>0.01495973771211445</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.03650608152266532</v>
+        <v>-0.01863705060983689</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.08039836539103451</v>
+        <v>-0.0131468872923951</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.1513406763662224</v>
+        <v>-0.05869799332468684</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.08254280035837624</v>
+        <v>-0.05266658902343979</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.1191967735233617</v>
+        <v>-0.02761318888272413</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.04785902075146753</v>
+        <v>-0.04007436578692203</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.123614624783051</v>
+        <v>0.03624836777358165</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>1.10805678355788</v>
+        <v>0.3710196569930722</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.2822147495626377</v>
+        <v>0.1109160138742367</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>25.81</v>
+        <v>44.08</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.009213043306992685</v>
+        <v>0.001135658713243615</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.07540753646954323</v>
+        <v>-0.02628669349847346</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.07361546931551777</v>
+        <v>-0.0260715098152603</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.007574903055762139</v>
+        <v>-0.03163441591010319</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.1079772985340697</v>
+        <v>-0.0286469635624127</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0.03584333266047279</v>
+        <v>-0.05791833792363399</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1510871951167106</v>
+        <v>-0.02459993836277452</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.2231192845740998</v>
+        <v>-0.04100855160215766</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.2243740858050716</v>
+        <v>0.2507910460685834</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.06980521268766715</v>
+        <v>0.07744453137758778</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>34.76</v>
+        <v>43.53</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.01193865776006786</v>
+        <v>-0.03266669379340281</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.02932150269452261</v>
+        <v>-0.05492840900046569</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.03818486694580592</v>
+        <v>-0.04476631400458497</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.07108498069408331</v>
+        <v>-0.03630727155477165</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.04035922846445894</v>
+        <v>-0.02899850543519877</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.04141721448837188</v>
+        <v>-0.1524533048676903</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.05677696248669595</v>
+        <v>-0.06922480289459598</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.03550393359956217</v>
+        <v>0.06935481452604431</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.35551117742129</v>
+        <v>0.996081524785567</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.1067113596083147</v>
+        <v>0.2590976837028309</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>44.03</v>
+        <v>245.96</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.01211579356573456</v>
+        <v>0.005313508674483547</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.02566939328753393</v>
+        <v>-0.02751854936527798</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.0329453116673939</v>
+        <v>-0.06046831931837593</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.03358214547576999</v>
+        <v>-0.1586220435409746</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.01167228881411719</v>
+        <v>-0.1349427274854403</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.07109710206954567</v>
+        <v>-0.112920800650086</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.02426356296218712</v>
+        <v>0.02908109231033729</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.03163849515101924</v>
+        <v>0.1178685340857899</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.2503014125279721</v>
+        <v>1.129187868468857</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.07730392120511165</v>
+        <v>0.2864848049752502</v>
       </c>
     </row>
     <row r="57">
@@ -3686,37 +3686,37 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>17.68</v>
+        <v>17.78</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.01306101556624706</v>
+        <v>0.005429288298530954</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.06887838759032161</v>
+        <v>-0.06332980470478</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.1133286677797809</v>
+        <v>-0.109095467506875</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.124219973312235</v>
+        <v>-0.120336433286208</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>0.0487543633709433</v>
+        <v>0.02995192676912639</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.04844348926846376</v>
+        <v>0.05815125577236602</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.1580000377836681</v>
+        <v>-0.1570412636650359</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.1974036994996532</v>
+        <v>-0.2112338512372971</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.01350142118209074</v>
+        <v>0.01379029202075621</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.004480370032510672</v>
+        <v>0.004575794178724113</v>
       </c>
     </row>
     <row r="58">
@@ -3742,37 +3742,37 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>19.18</v>
+        <v>19.36</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.001873014108881854</v>
+        <v>0.009069574731333185</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.01529540310667865</v>
+        <v>-0.0005163007460216029</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.0184190641568841</v>
+        <v>-0.01445809712379043</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.007615469718638135</v>
+        <v>0.007179573181018029</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.03820128432154113</v>
+        <v>-0.04352769410877111</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.05227068322980077</v>
+        <v>0.04869990316537232</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.07738042823419256</v>
+        <v>-0.07509643666181476</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.1928471653979353</v>
+        <v>-0.1874883973413171</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1689559502488014</v>
+        <v>0.1792173290506884</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.0534147182118494</v>
+        <v>0.05648811927434849</v>
       </c>
     </row>
     <row r="59">
@@ -3798,37 +3798,37 @@
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>50.9</v>
+        <v>50.88</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.01126647283439786</v>
+        <v>-0.0003929362900608746</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.05583376609261281</v>
+        <v>-0.05127726916334086</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.06810687438212837</v>
+        <v>-0.07809381528971349</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.08205589133375779</v>
+        <v>-0.0911039391894457</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>0.02528108126258877</v>
+        <v>0.02590994514204303</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.095613459618616</v>
+        <v>-0.0938806192207905</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.1804241520132236</v>
+        <v>-0.179956549256452</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1606001119147007</v>
+        <v>-0.1728816617914352</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.01990589562236633</v>
+        <v>0.007174042629089383</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.006591751874848617</v>
+        <v>0.00238565168322924</v>
       </c>
     </row>
     <row r="60">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>96.91</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.02338002233537273</v>
+        <v>0.01599417360221711</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.05241021958438108</v>
+        <v>-0.04639226068307356</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.07280896694768368</v>
+        <v>-0.05869980381660833</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.1046747452445449</v>
+        <v>-0.1073436413390604</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.06213911958302354</v>
+        <v>-0.08557840614780787</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.0670530800894652</v>
+        <v>-0.04026573174245107</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.0962860839010039</v>
+        <v>-0.09126456709979425</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1564682428474852</v>
+        <v>-0.1646962207555305</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2199257740608358</v>
+        <v>0.2257096885622867</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.06850805959388073</v>
+        <v>0.07019406866913447</v>
       </c>
     </row>
     <row r="61">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>47.04</v>
+        <v>47.15</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.0146627720638558</v>
+        <v>0.002338448303797813</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.01424979647487445</v>
+        <v>-0.01852621508507868</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.05428228129932544</v>
+        <v>-0.03083247590859972</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.09294253062276514</v>
+        <v>-0.1053130769774772</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.2048681366319332</v>
+        <v>-0.2431781363838176</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.1431694060453986</v>
+        <v>-0.1539565420210504</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.03567031380304209</v>
+        <v>-0.0424451681832877</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.1224051798328032</v>
+        <v>0.1263736464021736</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>-0.1485258393366055</v>
+        <v>-0.1489849378315992</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>-0.05218446121678322</v>
+        <v>-0.05235483981327127</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>88.22</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.0231424692103952</v>
+        <v>0.01496258984991305</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.05767999751608699</v>
+        <v>-0.04653394288328871</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.07748610525501187</v>
+        <v>-0.07125819402164435</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.1033641450557351</v>
+        <v>-0.1090547172584344</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.05582942962755499</v>
+        <v>-0.08239114299513051</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.08586525049433535</v>
+        <v>-0.057690335931736</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.1320217796764305</v>
+        <v>-0.1246038272611897</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>-0.2128775483586737</v>
+        <v>-0.2225355760819557</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>0.07212842281156417</v>
+        <v>0.08025257773189054</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>0.02348685647299242</v>
+        <v>0.02606554359512803</v>
       </c>
     </row>
   </sheetData>
@@ -4015,7 +4015,7 @@
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1536231779896946</v>
+        <v>0.1609862417092056</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1513406763662224</v>
+        <v>-0.1586220435409746</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1110669548024814</v>
+        <v>0.09726975712544483</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1306494521588698</v>
+        <v>-0.1305676863301721</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.07430524308851139</v>
+        <v>0.08125001557848632</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.124219973312235</v>
+        <v>-0.120336433286208</v>
       </c>
     </row>
     <row r="20">
@@ -4737,21 +4737,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.07178803540208034</v>
+        <v>0.07745223607201668</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1145038269821274</v>
+        <v>-0.111356485857642</v>
       </c>
     </row>
     <row r="21">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.0655737510964931</v>
+        <v>0.06123345123044155</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.1046747452445449</v>
+        <v>-0.1090547172584344</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.0612222460637879</v>
+        <v>0.05888225180339934</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.1033641450557351</v>
+        <v>-0.1073436413390604</v>
       </c>
     </row>
     <row r="23">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.03191855777821995</v>
+        <v>0.02927106200070351</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.09294253062276514</v>
+        <v>-0.1053130769774772</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02158799280855273</v>
+        <v>0.02718539318450786</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.08473411134401343</v>
+        <v>-0.0911039391894457</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01397023246874607</v>
+        <v>0.02230665531611664</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.08205589133375779</v>
+        <v>-0.07870526187116555</v>
       </c>
     </row>
     <row r="26">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.01309866543957594</v>
+        <v>0.01597069738103296</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.07693700028242934</v>
+        <v>-0.07491583583547068</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.327739054342352</v>
+        <v>0.294731843948052</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2048681366319332</v>
+        <v>-0.2431781363838176</v>
       </c>
     </row>
     <row r="32">
@@ -5158,21 +5158,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.3010432455720362</v>
+        <v>0.2787539651369588</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1189785038425308</v>
+        <v>-0.1536469492904977</v>
       </c>
     </row>
     <row r="33">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2972349182644201</v>
+        <v>0.2493566256951565</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5225,21 +5225,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1003107712195344</v>
+        <v>-0.1349427274854403</v>
       </c>
     </row>
     <row r="34">
@@ -5248,21 +5248,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2736000061035155</v>
+        <v>0.2200391665274855</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.08921004370306584</v>
+        <v>-0.1336500677847258</v>
       </c>
     </row>
     <row r="35">
@@ -5293,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2214096586739513</v>
+        <v>0.2035938802693626</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.08254280035837624</v>
+        <v>-0.1180030078254978</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2182688237468962</v>
+        <v>0.1925274356380924</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.06213911958302354</v>
+        <v>-0.110759086443635</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1880191989186075</v>
+        <v>0.190442388965939</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.0577647505183041</v>
+        <v>-0.08557840614780787</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.174282697043711</v>
+        <v>0.1778915159829142</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.05582942962755499</v>
+        <v>-0.08239114299513051</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1692841787504875</v>
+        <v>0.1374456468825411</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.04035922846445894</v>
+        <v>-0.07149747584884358</v>
       </c>
     </row>
     <row r="40">
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1664805453254974</v>
+        <v>0.1305892557957151</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.03820128432154113</v>
+        <v>-0.06714247615152347</v>
       </c>
     </row>
     <row r="41"/>
@@ -5624,21 +5624,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5562073107203438</v>
+        <v>0.5016396420469882</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1431694060453986</v>
+        <v>-0.1539565420210504</v>
       </c>
     </row>
     <row r="46">
@@ -5669,21 +5669,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4799336228302693</v>
+        <v>0.4962617303057115</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1397438574150647</v>
+        <v>-0.1524533048676903</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4351604746013573</v>
+        <v>0.4392559445570168</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1191967735233617</v>
+        <v>-0.112920800650086</v>
       </c>
     </row>
     <row r="48">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4184852096991443</v>
+        <v>0.417674565562264</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.095613459618616</v>
+        <v>-0.0938806192207905</v>
       </c>
     </row>
     <row r="49">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4101126223328033</v>
+        <v>0.4010708580481357</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.08803998601065821</v>
+        <v>-0.08117145999428976</v>
       </c>
     </row>
     <row r="50">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3784881450196618</v>
+        <v>0.3688193531027808</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.08586525049433535</v>
+        <v>-0.06954862539203222</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3230506159981994</v>
+        <v>0.3545882870133334</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.08341894619310819</v>
+        <v>-0.05952343898111812</v>
       </c>
     </row>
     <row r="52">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2898748041550081</v>
+        <v>0.2879260309982692</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.07451282525194125</v>
+        <v>-0.05791833792363399</v>
       </c>
     </row>
     <row r="53">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2743626030966451</v>
+        <v>0.2757170985225788</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.07109710206954567</v>
+        <v>-0.057690335931736</v>
       </c>
     </row>
     <row r="54">
@@ -6029,21 +6029,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2403616110275348</v>
+        <v>0.2371683366735888</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.07100709850303122</v>
+        <v>-0.0420284343979711</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9367396057334156</v>
+        <v>0.9728897942625354</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6157,21 +6157,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2231192845740998</v>
+        <v>-0.2225355760819557</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.868242648151998</v>
+        <v>0.8764159167469507</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6202,21 +6202,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2128775483586737</v>
+        <v>-0.221175952359825</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7570162029035277</v>
+        <v>0.7153530236638159</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1974036994996532</v>
+        <v>-0.2112338512372971</v>
       </c>
     </row>
     <row r="62">
@@ -6270,21 +6270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6998458500628668</v>
+        <v>0.6906695938305043</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1928471653979353</v>
+        <v>-0.1874883973413171</v>
       </c>
     </row>
     <row r="63">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6777183233486406</v>
+        <v>0.6578417767545091</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1606001119147007</v>
+        <v>-0.1728816617914352</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.6555330343392065</v>
+        <v>0.6449688614398215</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1564682428474852</v>
+        <v>-0.1646962207555305</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.6438411063033291</v>
+        <v>0.6396541144386847</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.09819160183626585</v>
+        <v>-0.09662783386879226</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.5513096247466027</v>
+        <v>0.5332567421574004</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.08508537994304888</v>
+        <v>-0.08476202464388838</v>
       </c>
     </row>
     <row r="67">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5271292545942103</v>
+        <v>0.5331027851477392</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.0352626078045104</v>
+        <v>-0.04194317060326458</v>
       </c>
     </row>
     <row r="68">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.5178849391563829</v>
+        <v>0.524453679351564</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.03163849515101924</v>
+        <v>-0.04100855160215766</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.015175613616528</v>
+        <v>2.961589504096277</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1485258393366055</v>
+        <v>-0.1489849378315992</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.776546510641252</v>
+        <v>2.829354236076945</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6713,21 +6713,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.01350142118209074</v>
+        <v>0.007174042629089383</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.5098788195624</v>
+        <v>2.495943346180588</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6758,21 +6758,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.01990589562236633</v>
+        <v>0.01379029202075621</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>2.003773491201815</v>
+        <v>2.139215789855056</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.03120794239522628</v>
+        <v>0.01850161912091308</v>
       </c>
     </row>
     <row r="77">
@@ -6826,21 +6826,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.563956580278602</v>
+        <v>1.521774551636385</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.07212842281156417</v>
+        <v>0.08025257773189054</v>
       </c>
     </row>
     <row r="78">
@@ -6871,21 +6871,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.433447124297525</v>
+        <v>1.490994625401555</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1250061193585577</v>
+        <v>0.1201507219640956</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.304841743683902</v>
+        <v>1.347462518421874</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1517397210915405</v>
+        <v>0.1520803241605271</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.271213361193183</v>
+        <v>1.243417984565997</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6983,21 +6983,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1689559502488014</v>
+        <v>0.1778379413674496</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.10805678355788</v>
+        <v>1.129187868468857</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,21 +7028,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1838093987067981</v>
+        <v>0.1792173290506884</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.104333165472413</v>
+        <v>1.109072834117779</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2067229109279012</v>
+        <v>0.2072435840889764</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -489,15 +489,15 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>16.01</v>
+        <v>15.3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.005653275889232479</v>
+        <v>-0.04434728469685723</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.03321251538634928</v>
+        <v>-0.07608691520786937</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.03157214926968943</v>
+        <v>-0.01098901573106414</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.1609862417092056</v>
+        <v>0.07090365432759693</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.2787539651369588</v>
+        <v>0.2418831631272345</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4962617303057115</v>
+        <v>0.4585319851826828</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.8110859674810009</v>
+        <v>0.7626727710610395</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9728897942625354</v>
+        <v>0.888888823479131</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2.139215789855056</v>
+        <v>1.802197817553022</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4642224344406485</v>
+        <v>0.4098284279864777</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>38.06</v>
+        <v>38.74</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.004751855863259102</v>
+        <v>0.01786653391066295</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.04299721058059081</v>
+        <v>-0.02589888779082994</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.03130566336409102</v>
+        <v>-0.01324494817365285</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.08125001557848632</v>
+        <v>0.09963105824121343</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.294731843948052</v>
+        <v>0.3067971354448489</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.2757170985225788</v>
+        <v>0.3517494381109427</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4404402862400516</v>
+        <v>0.4817205098055408</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.6578417767545091</v>
+        <v>0.7280740205045306</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.759676615450062</v>
+        <v>0.8370839749118675</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2072881954314076</v>
+        <v>0.2247374641966762</v>
       </c>
     </row>
     <row r="4">
@@ -704,12 +704,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>568.53</v>
+        <v>118.56</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.01472477969695496</v>
+        <v>0.07879887090516213</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.00268076313481358</v>
+        <v>0.07051916531461622</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.02787880232448048</v>
+        <v>0.0135931975831185</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>-0.007679757448823543</v>
+        <v>0.003215410834631172</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>-0.06714247615152347</v>
+        <v>0.2343570410373244</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.417674565562264</v>
+        <v>0.5217557692947976</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5376501005932421</v>
+        <v>0.4226309694370316</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.8764159167469507</v>
+        <v>0.3883387165321246</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>2.829354236076945</v>
+        <v>1.256969292594426</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5644986075059293</v>
+        <v>0.3117222443549044</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>195.72</v>
+        <v>157.6</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.001278968631701849</v>
+        <v>0.008962926905417001</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.02627022353553121</v>
+        <v>-0.03790972191948694</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.05259760487729781</v>
+        <v>-0.03015380859375005</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.09726975712544483</v>
+        <v>0.001207054424660958</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.2035938802693626</v>
+        <v>0.1791219597733285</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.199039064124213</v>
+        <v>0.2948757343675816</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4954616298678527</v>
+        <v>0.2854431488825322</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.524453679351564</v>
+        <v>0.6821220278900557</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3988498348758804</v>
+        <v>1.027819193111072</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1183825064809605</v>
+        <v>0.2657358367080496</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>156.2</v>
+        <v>100.05</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.003953643330054879</v>
+        <v>0.05985171011178436</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.04645626471992048</v>
+        <v>0.05772287689242717</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.03805892196536353</v>
+        <v>-0.0009984869954819953</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-0.01183026690282218</v>
+        <v>0.004518118318582509</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1778915159829142</v>
+        <v>0.1735150737858984</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.2371683366735888</v>
+        <v>0.5396800871272862</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.2751634061424379</v>
+        <v>0.3575608416372569</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.6396541144386847</v>
+        <v>0.3422426866155608</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.9939985583684026</v>
+        <v>1.15285384895101</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2586595634891469</v>
+        <v>0.2912336912757496</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>505.57</v>
+        <v>193.47</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.03078680870580075</v>
+        <v>-0.01149601464319838</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.02873129467181545</v>
+        <v>0.01447220601788834</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.04924873644089822</v>
+        <v>0.02386745526351097</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.04629223879091648</v>
+        <v>0.07191531570999188</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.1536469492904977</v>
+        <v>0.1758694715100022</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.5016396420469882</v>
+        <v>0.1626638130201292</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4688065685855629</v>
+        <v>0.4926340392253996</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.6906695938305043</v>
+        <v>0.5212879832317272</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.521774551636385</v>
+        <v>0.3592367584230762</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3611377718609963</v>
+        <v>0.1077243528853913</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>156.05</v>
+        <v>541.5</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.02374867512902346</v>
+        <v>-0.04754371432289017</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.008922253178700768</v>
+        <v>-0.04499040462472548</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.02725297406257043</v>
+        <v>-0.02718143964588793</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.02718539318450786</v>
+        <v>-0.07879964401870121</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.009714568762854148</v>
+        <v>-0.1265565829922446</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.3545882870133334</v>
+        <v>0.3980327337732998</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.4407048384423573</v>
+        <v>0.5339007124079667</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5332567421574004</v>
+        <v>0.7849135491648447</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.347462518421874</v>
+        <v>2.625610142954565</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.3290241996207364</v>
+        <v>0.5362445943281311</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>88.53</v>
+        <v>28.35</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.0009028532953800905</v>
+        <v>0.04496871575534001</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.02349442749584529</v>
+        <v>0.02015111361977273</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.06238084626002094</v>
+        <v>-0.01630809570892877</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.0006772498145830586</v>
+        <v>-0.002463043442515911</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.06819191288473481</v>
+        <v>0.2488986532438622</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.07948528408971445</v>
+        <v>0.4427481390246546</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.3147318967797927</v>
+        <v>0.2336815033161141</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.7153530236638159</v>
+        <v>0.2262110446536534</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.490994625401555</v>
+        <v>0.4282115786725564</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3555772244930473</v>
+        <v>0.1261533071256091</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>109.9</v>
+        <v>204.6</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.005429850444534812</v>
+        <v>0.008229505189026209</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.007674929788903828</v>
+        <v>-0.03454129921044113</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.04881425778914361</v>
+        <v>-0.02128675859019447</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.07491583583547068</v>
+        <v>0.0319782698090465</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1374456468825411</v>
+        <v>0.1990436027610614</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.4010708580481357</v>
+        <v>0.2372560559144048</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2893440085182841</v>
+        <v>0.2100090791293818</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.268231605252528</v>
+        <v>0.4549633727257831</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.071682735180211</v>
+        <v>0.6171815558556932</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2747971452599531</v>
+        <v>0.173778796005736</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>202.93</v>
+        <v>152.38</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.001431076228811001</v>
+        <v>-0.02351809097836455</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.04242169484164071</v>
+        <v>-0.01480567216165263</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.02881074113608206</v>
+        <v>-0.0009179083774371044</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.01597069738103296</v>
+        <v>-0.02151153237419734</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.190442388965939</v>
+        <v>-0.01852390216115141</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1886627456966992</v>
+        <v>0.3510651819759862</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1940712054748053</v>
+        <v>0.4370822773457173</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4147876103718737</v>
+        <v>0.5038898470023632</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6027254196795855</v>
+        <v>1.276023171896981</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1702708165268314</v>
+        <v>0.315403197097172</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>94.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.002548830229773147</v>
+        <v>0.005776912713784998</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.002008614223147132</v>
+        <v>-0.04271815545270452</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.04220775300082302</v>
+        <v>-0.03851601692035866</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.05524416277243283</v>
+        <v>-0.04339252867552623</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1054308552081957</v>
+        <v>0.1276870394073244</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.4392559445570168</v>
+        <v>0.2778295622109559</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2527195061611902</v>
+        <v>0.2121154217287873</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2555536027513163</v>
+        <v>0.4695195836702781</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.015014411284552</v>
+        <v>0.6399738924708118</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2630660217963274</v>
+        <v>0.1792674502529907</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>67.51000000000001</v>
+        <v>85.62</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.007351859789659354</v>
+        <v>-0.03287016912729657</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.04821652550727196</v>
+        <v>-0.05559233081780446</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.04633421015505912</v>
+        <v>-0.0779668082724787</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.03197585024156646</v>
+        <v>-0.0009334212894834826</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1305892557957151</v>
+        <v>-0.0006867260362933836</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2192033947720422</v>
+        <v>0.1246362244304857</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2019481820044593</v>
+        <v>0.2903634360663638</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4270148847911552</v>
+        <v>0.6465422588355743</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.6181045364750855</v>
+        <v>1.381954101094161</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1740020587217068</v>
+        <v>0.3355017543948644</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>420.67</v>
+        <v>474.62</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.001070896686792722</v>
+        <v>-0.06121805439139349</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.01604562339753801</v>
+        <v>-0.03424563367953248</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.005641786911416258</v>
+        <v>-0.02168450182134218</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.01293047385650925</v>
+        <v>-0.1280015905541002</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>-0.01223347279831022</v>
+        <v>-0.2161884508517007</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.09259265864452715</v>
+        <v>0.4510046386886166</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.386546993274935</v>
+        <v>0.4486885386541639</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6449688614398215</v>
+        <v>0.5919514080808357</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.2525498259317014</v>
+        <v>1.341664938914357</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.07794930533438671</v>
+        <v>0.327929190961749</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>27.13</v>
+        <v>31.7</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.001472245690652185</v>
+        <v>-0.004084170941822118</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.02374961255909758</v>
+        <v>0.008590533093924657</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.05929268317524072</v>
+        <v>0.01602564063376311</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.02968526290714324</v>
+        <v>0.05878424173305485</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1925274356380924</v>
+        <v>0.1073822864995273</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.3688193531027808</v>
+        <v>0.07801732449891596</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1693964770943057</v>
+        <v>0.3300620498167155</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.1594016924377457</v>
+        <v>0.390326183440677</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.3338249241514784</v>
+        <v>0.2780838381926742</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1007776661041582</v>
+        <v>0.08522497778800298</v>
       </c>
     </row>
     <row r="16">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>31.83</v>
+        <v>402.06</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.003755894721999331</v>
+        <v>-0.04423898845915142</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.01272668198047722</v>
+        <v>-0.05957476970838593</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.03411303488099371</v>
+        <v>-0.0631902595181667</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.05888225180339934</v>
+        <v>-0.04573609671232537</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1267962610653408</v>
+        <v>-0.06098048684006552</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1047487398197882</v>
+        <v>0.08334004868603295</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.32648223561963</v>
+        <v>0.3652366918017522</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.3835897067697212</v>
+        <v>0.5877593100086718</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3131474425233451</v>
+        <v>0.1769708364597096</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.0950597862933702</v>
+        <v>0.05581679787284921</v>
       </c>
     </row>
     <row r="17">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>96.36</v>
+        <v>106.11</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.001663239783629811</v>
+        <v>-0.02624576101966858</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.02950952037626153</v>
+        <v>-0.0439679011383326</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.02804114178345607</v>
+        <v>-0.01759097757893269</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.06123345123044155</v>
+        <v>-0.01713596229908798</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.2200391665274855</v>
+        <v>-0.04276046846203729</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>-0.05952343898111812</v>
+        <v>0.2019710248935358</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1698656795287599</v>
+        <v>0.2656748184762379</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.4913104975282576</v>
+        <v>0.5068486175136178</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.961589504096277</v>
+        <v>0.6989339374454235</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.5823036289701311</v>
+        <v>0.1932336637331848</v>
       </c>
     </row>
     <row r="18">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>108.97</v>
+        <v>93.27</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.003129927054052795</v>
+        <v>-0.03206728878904974</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.01819980792815024</v>
+        <v>-0.06063051885337944</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.002576122670048031</v>
+        <v>-0.04777948393044607</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.003383895459847186</v>
+        <v>0.04154096554478648</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-0.0006419634467762503</v>
+        <v>0.1434700224932319</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.171972438013223</v>
+        <v>-0.009558564334131825</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.2900934368063663</v>
+        <v>0.1445699265102274</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.5331027851477392</v>
+        <v>0.4336237969810497</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7848523589262606</v>
+        <v>2.779410701995538</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2130185225862815</v>
+        <v>0.5576672759140806</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>97.09999999999999</v>
+        <v>57.62</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.01114234831225369</v>
+        <v>0.01748186200065138</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.02176106805987021</v>
+        <v>0.003483120329453859</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.02558959370507974</v>
+        <v>0.01604655020460521</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.07745223607201668</v>
+        <v>0.008223926394700598</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.2493566256951565</v>
+        <v>0.07840016460792532</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>-0.0420284343979711</v>
+        <v>0.3242387248161223</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1338419237704112</v>
+        <v>0.1822753604437199</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.4020242454713518</v>
+        <v>0.1910280631756571</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>2.495943346180588</v>
+        <v>0.2001216430471782</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.5177076691519817</v>
+        <v>0.06269447492118885</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>55.91</v>
+        <v>94.14</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.002869952419948252</v>
+        <v>-0.03048402812551587</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.003409881955249938</v>
+        <v>-0.05158173117460774</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.01212885859137258</v>
+        <v>-0.04436100550011879</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.02927106200070351</v>
+        <v>0.04634876194695159</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.08908715642210097</v>
+        <v>0.1763088944842233</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.1081181943667278</v>
+        <v>0.009435955750167091</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2517418218561138</v>
+        <v>0.1069776605091044</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.2663705272791432</v>
+        <v>0.3594797381723696</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.7287745368752885</v>
+        <v>2.349785648617388</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.2001792641623203</v>
+        <v>0.4962551992944091</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>56.63</v>
+        <v>55.48</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.001058344682433709</v>
+        <v>-0.007690937334096315</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01375822232710089</v>
+        <v>-0.004307280567280802</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.003869787368701583</v>
+        <v>-0.001978784134729739</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.005147336079906362</v>
+        <v>0.009461434978636829</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.06926873953660606</v>
+        <v>0.08444266186354077</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.2879260309982692</v>
+        <v>0.1038079298553778</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1638561000777878</v>
+        <v>0.2400189075452923</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1657973899395615</v>
+        <v>0.2574203693511292</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.1778379413674496</v>
+        <v>0.6867506028231061</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.05607601675507845</v>
+        <v>0.1903745267532047</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>73.90000000000001</v>
+        <v>292.71</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.001219400762257239</v>
+        <v>0.01311774142046995</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.01820107849458363</v>
+        <v>0.006325837552097147</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.005383600396358879</v>
+        <v>0.0007521666656928883</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.03788564152075358</v>
+        <v>0.004564440078173915</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.02739723557322593</v>
+        <v>0.107198233011762</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1685508707351158</v>
+        <v>0.2191169679890823</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1161952829322239</v>
+        <v>0.08567934185892256</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1607876518308502</v>
+        <v>0.04651404605022691</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.8572300848686465</v>
+        <v>0.7239531364006744</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.229198165320424</v>
+        <v>0.199062493777816</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>68.04000000000001</v>
+        <v>65.59</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.001177189996062866</v>
+        <v>0.01501073274652409</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.01874813226162375</v>
+        <v>0.02149193697390483</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.006134942660853349</v>
+        <v>0.02117379588787172</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.03503050837994448</v>
+        <v>0.01344244593291499</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.03660249354923195</v>
+        <v>0.09382198196144143</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.1729462416786627</v>
+        <v>0.2566380309414342</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.103000155713787</v>
+        <v>0.09418693795642907</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1391000470743193</v>
+        <v>0.02678916298824974</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.9361499483296136</v>
+        <v>0.9460410671361728</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2463681133834443</v>
+        <v>0.2484869302239172</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>144.02</v>
+        <v>106.64</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.005164750833812848</v>
+        <v>0.05043344085779888</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.01057978367657575</v>
+        <v>0.01979534953490747</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.007306296837713777</v>
+        <v>-0.03036919317455711</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.01234400604407904</v>
+        <v>0.02459644036852726</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.07262572689367386</v>
+        <v>0.1759647336391776</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1224747426696895</v>
+        <v>0.2668962409915885</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.08369403862906011</v>
+        <v>-0.01213306117643054</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.103247724101075</v>
+        <v>-0.04486435963866775</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.6679537641593243</v>
+        <v>0.4867991762648547</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1859362275283625</v>
+        <v>0.1413463052593551</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>64.62</v>
+        <v>74.11</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.01221808571631899</v>
+        <v>0.002841665495759482</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.006385355364512346</v>
+        <v>-0.01541113437556796</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.006855756299688931</v>
+        <v>0.007476931348722626</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.02230665531611664</v>
+        <v>-0.04901834569312213</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.08233823065714696</v>
+        <v>0.01543949535707045</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2050422169467045</v>
+        <v>0.1880262074622692</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.06415967660117139</v>
+        <v>0.1247070347552128</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.01081317797924197</v>
+        <v>0.1680268049561271</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.9059838551520563</v>
+        <v>0.8336970367858985</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2398612087010661</v>
+        <v>0.2239843391531435</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>288.92</v>
+        <v>145.66</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.01197903127052324</v>
+        <v>0.01138730274265121</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.006703963015049053</v>
+        <v>0.0006870438663986178</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.0186474310182605</v>
+        <v>0.01194943164881002</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.004787930634661763</v>
+        <v>-0.0006174705858704721</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.0899762532331454</v>
+        <v>0.07755809274181491</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1771512815915495</v>
+        <v>0.1327425794538732</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.05707597572617695</v>
+        <v>0.08700220350271648</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.01936993576481938</v>
+        <v>0.1194003300047128</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6751899540953485</v>
+        <v>0.6477657273288973</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.187648760909678</v>
+        <v>0.1811321431794555</v>
       </c>
     </row>
     <row r="27">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>190.51</v>
+        <v>68.14</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.003899405689597568</v>
+        <v>0.001469701245966126</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.03028612442071787</v>
+        <v>-0.01730598516900195</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.02372658038994602</v>
+        <v>0.004866566036513031</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.01345887241621124</v>
+        <v>-0.04925350731802347</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.05554742529210821</v>
+        <v>0.02339301299986141</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1590671771344119</v>
+        <v>0.1917355794259346</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0552821825125549</v>
+        <v>0.1101018286220767</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.07873222904929711</v>
+        <v>0.1441407955152862</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.109072834117779</v>
+        <v>0.9104296080839471</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2824207189924648</v>
+        <v>0.24082446212689</v>
       </c>
     </row>
     <row r="28">
@@ -2048,51 +2048,51 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>180.78</v>
+        <v>132.07</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.01997287957807781</v>
+        <v>0.01717506969520266</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.01000052087378234</v>
+        <v>-0.00706704173699424</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.008873242458995678</v>
+        <v>-0.004672508145150411</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.03542844656130539</v>
+        <v>-0.009969914790983192</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.04145903170323251</v>
+        <v>0.0880247187494303</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.07408685693916017</v>
+        <v>0.1049326955826386</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.1698228005884068</v>
+        <v>0.06294336306367176</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.2293477511968078</v>
+        <v>0.0987564228866733</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.8714655400845333</v>
+        <v>0.627690755794295</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2323307295558952</v>
+        <v>0.1763158955045154</v>
       </c>
     </row>
     <row r="29">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2118,37 +2118,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>129.84</v>
+        <v>188.87</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.001079409351908422</v>
+        <v>-0.008608469040660149</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.02383278174470105</v>
+        <v>-0.03863387629694071</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.03807971219693673</v>
+        <v>-0.02879624655918112</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.03299328065545404</v>
+        <v>-0.01203119251863571</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.07538805154718253</v>
+        <v>0.02760663846469003</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.09105407345348637</v>
+        <v>0.1739168535975517</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.05526425216036523</v>
+        <v>0.05622558054381122</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.07721795468331316</v>
+        <v>0.07728304787474394</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6407962568561796</v>
+        <v>1.021865208920734</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1794645317434582</v>
+        <v>0.2644958249388645</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>23.65</v>
+        <v>82.64</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.006382962490649957</v>
+        <v>0.006087168294561796</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.0008449707519732064</v>
+        <v>-0.01817748381348272</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.007553516817124128</v>
+        <v>-0.02936340166692508</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.01128764451933495</v>
+        <v>-0.05489481836387533</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.04910457823445757</v>
+        <v>-0.04303121146363409</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.0001833487696918379</v>
+        <v>0.1341353615540133</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1625937385727547</v>
+        <v>0.089952619549452</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2741264215405002</v>
+        <v>0.1804017257825243</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6062040505856543</v>
+        <v>0.4046028347540647</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1711168750538763</v>
+        <v>0.1199135867519006</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>113.63</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.009932904269343346</v>
+        <v>0.00380102592486109</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.04206715037618602</v>
+        <v>-0.008793562410983613</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.04303520887893453</v>
+        <v>-0.01429024619667307</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.03564461098505889</v>
+        <v>-0.0312336572953833</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.03922488573237393</v>
+        <v>0.001484414188344552</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.009763269389775231</v>
+        <v>0.06604441508186776</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.08617397819704453</v>
+        <v>0.1310196647360422</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.3254923902854314</v>
+        <v>0.1128858005057642</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.243417984565997</v>
+        <v>0.4121024850819901</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.3090916890920434</v>
+        <v>0.1219032491144711</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>92.08</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.000869585120159666</v>
+        <v>0.01004612852266518</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01254689725410518</v>
+        <v>-0.0009399717158156129</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.02704984758139972</v>
+        <v>-0.003482482232483819</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.01021172697740169</v>
+        <v>-0.005879139945774603</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.006586496884897874</v>
+        <v>0.01275477617374787</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.06042644763277272</v>
+        <v>0.03296645444707802</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1319147435592631</v>
+        <v>0.1175866357511945</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1043791174783675</v>
+        <v>0.09432418523446984</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4271784375394292</v>
+        <v>0.2272688773746363</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1258816956502766</v>
+        <v>0.07064766372891396</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>71.48999999999999</v>
+        <v>102.81</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.004456199773062441</v>
+        <v>0.003905808829029134</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.03626317646723654</v>
+        <v>-0.02568232724304897</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.06020772774324479</v>
+        <v>-0.02669695889566981</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.03535289063560032</v>
+        <v>-0.07768909632433885</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.110759086443635</v>
+        <v>-0.1202335526322232</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>-0.01634044356096731</v>
+        <v>0.1755187351811756</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1053626326077799</v>
+        <v>0.09944818365006847</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.4289851200266206</v>
+        <v>0.2145627708608666</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.2650088851190491</v>
+        <v>0.3471252389994284</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.0815116250091521</v>
+        <v>0.1044243950399026</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>82.14</v>
+        <v>69.97</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.001340980275368775</v>
+        <v>-0.02126166860380796</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.02411784274038209</v>
+        <v>-0.05675382943047669</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.04919550908700721</v>
+        <v>-0.08380255723069674</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.05564501932040145</v>
+        <v>-0.06991894060238235</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.04451372922214725</v>
+        <v>-0.1468886733061159</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.08978686494664712</v>
+        <v>-0.001835551758804677</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.08236605307228473</v>
+        <v>0.1032033298521069</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1686341901993567</v>
+        <v>0.4089501463203076</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.396907426834872</v>
+        <v>0.2355588601601897</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1178646139980373</v>
+        <v>0.07305293422942771</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>101.52</v>
+        <v>110.17</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.003162052415751404</v>
+        <v>-0.03044969786240648</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.02916709439283638</v>
+        <v>-0.07123591621970515</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.07287674298569491</v>
+        <v>-0.06738338499573904</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.02309470331184149</v>
+        <v>-0.0595014619858284</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.1167953522131071</v>
+        <v>-0.08464488553435234</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.1842668115342765</v>
+        <v>0.01177368592826067</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>-0.07506804870465389</v>
+        <v>0.08135073494876677</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>-0.09662783386879226</v>
+        <v>0.2921902954465874</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3843462597586971</v>
+        <v>1.079870220218303</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1145038606567232</v>
+        <v>0.2764743105013847</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>73.66</v>
+        <v>172.99</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.002995659223713254</v>
+        <v>-0.04309101304753926</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.01087683020432884</v>
+        <v>-0.03352142474921116</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.0199574231893791</v>
+        <v>-0.0302707209762888</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.005937851836331443</v>
+        <v>-0.07920365151839048</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.009651268071421581</v>
+        <v>-0.08106499479986806</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.0259349519026113</v>
+        <v>0.05175048486711775</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.115996545701089</v>
+        <v>0.1396148353836619</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.07865250385330236</v>
+        <v>0.1761358113256679</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.2226966153398038</v>
+        <v>0.8071385738154846</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.06931642230627344</v>
+        <v>0.2180463612231445</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>228.45</v>
+        <v>22.91</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.003249704503785145</v>
+        <v>-0.03128963141878272</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.02977155171045087</v>
+        <v>-0.03210816334736699</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.04221871182224113</v>
+        <v>-0.03046971387751563</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.04073062018409479</v>
+        <v>-0.05797696813755249</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.007530510333272122</v>
+        <v>-0.07663808892348201</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.01534357952157595</v>
+        <v>-0.01954328104312675</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1140801744584024</v>
+        <v>0.127044670289292</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1033562395637071</v>
+        <v>0.245540208866915</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.3371587930318443</v>
+        <v>0.5221647736824</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1016940270164164</v>
+        <v>0.1503249928816097</v>
       </c>
     </row>
     <row r="38">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>54.08</v>
+        <v>28.18</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.01349327609571738</v>
+        <v>0.0003549956994941539</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.01957936945875627</v>
+        <v>-0.02152774126073365</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.02223828442771092</v>
+        <v>-0.01122805946751648</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.07870526187116555</v>
+        <v>-0.1070975671090898</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.05255622895037848</v>
+        <v>-0.04571623264743929</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.04222463225585615</v>
+        <v>0.1717256215855087</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.09628435200068308</v>
+        <v>0.004625602033399012</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1569822799917506</v>
+        <v>0.09314401255324989</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.757291395254919</v>
+        <v>0.5783785400696435</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.2067424606356267</v>
+        <v>0.1643147228407791</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>102.41</v>
+        <v>225.51</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.005399597962518765</v>
+        <v>-0.0128693476939391</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.02947302008999242</v>
+        <v>-0.04225775895404005</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.03903533869407416</v>
+        <v>-0.04598532088771834</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.06670919047558455</v>
+        <v>-0.04233905810087946</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.1180030078254978</v>
+        <v>-0.03755277122048262</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.1217404609828885</v>
+        <v>0.02147845350103084</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.08937979431034515</v>
+        <v>0.1012297481042395</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1967922281656775</v>
+        <v>0.0995691457464396</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.342912576368108</v>
+        <v>0.3091528857700998</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.1032719593580986</v>
+        <v>0.09394827834681418</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>58.38</v>
+        <v>63.66</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.005338408385055393</v>
+        <v>0.009034707456738511</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.01484976844992936</v>
+        <v>-0.01744097935094213</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.01385134601784599</v>
+        <v>-0.02615883168613342</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.0462342437295562</v>
+        <v>-0.07672222385739991</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.04419376752286575</v>
+        <v>-0.02229052326283765</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.01504517206160405</v>
+        <v>0.1125435093378033</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.09827060042247338</v>
+        <v>0.04160935546075906</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.135081687267262</v>
+        <v>0.03393158925200002</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.6190952724939833</v>
+        <v>0.6100928017610587</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.1742416165486453</v>
+        <v>0.1720612365354999</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>94.8</v>
+        <v>53.02</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.007224822411094456</v>
+        <v>-0.0196006164460284</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.01270562001625197</v>
+        <v>-0.03879621819376855</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.02509250170315802</v>
+        <v>-0.03071298504101705</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.01639338292888493</v>
+        <v>-0.09506741219180892</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.020227787731394</v>
+        <v>-0.08045395642229525</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.04325858436816432</v>
+        <v>0.05866015636990629</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.08910040281099096</v>
+        <v>0.08969068390367574</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.0561074613611634</v>
+        <v>0.149422269320189</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.3084921548658555</v>
+        <v>0.7288983625260925</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.09376420840933886</v>
+        <v>0.2002079182613639</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>28.17</v>
+        <v>94.33</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.01185344547045131</v>
+        <v>-0.004957818624188426</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.02187497143944028</v>
+        <v>-0.01760044648089198</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.03461275593964563</v>
+        <v>-0.02187889420298939</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.111356485857642</v>
+        <v>-0.04553273213221776</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.02761474822306142</v>
+        <v>-0.03399225507559445</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.1169706916438087</v>
+        <v>0.04360565619078871</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.005335580906402182</v>
+        <v>0.08503360974260854</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.07905515485945114</v>
+        <v>0.05574023576505804</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.5418421082027245</v>
+        <v>0.2936019132384289</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1552606142670814</v>
+        <v>0.08959946938070962</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>70.76000000000001</v>
+        <v>13.08</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.00368797356355266</v>
+        <v>0.002298830079136005</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.01352294960696332</v>
+        <v>-0.01875468877951003</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.01912943256298372</v>
+        <v>-0.03182829740124815</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.02507577361406865</v>
+        <v>-0.02169034886576593</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.06121632386483378</v>
+        <v>0.04891264031070519</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>-0.02016931047673942</v>
+        <v>0.1100436421808966</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.01224109674918283</v>
+        <v>-0.039905117351686</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-0.04194317060326458</v>
+        <v>-0.07629164950685829</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.01850161912091308</v>
+        <v>0.1460139937736749</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.006129558125297141</v>
+        <v>0.04647768902458882</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>63.09</v>
+        <v>57.41</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.01089569470979534</v>
+        <v>-0.01661529981082688</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.02623862847533986</v>
+        <v>-0.03121833490583925</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.05695069187430724</v>
+        <v>-0.02264218238083993</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.06408549584384204</v>
+        <v>-0.07163648600007955</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.02851172312111394</v>
+        <v>-0.07204164887015174</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.07305513009443065</v>
+        <v>0.005815471995910926</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.03093972692229063</v>
+        <v>0.08871284409828695</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.02517071647985225</v>
+        <v>0.1233044467659057</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5972745823644527</v>
+        <v>0.5643178231893269</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.168942620397267</v>
+        <v>0.1608470386866356</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>13.05</v>
+        <v>115.07</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.005392962324132222</v>
+        <v>0.02193606797668668</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.02100523140088251</v>
+        <v>0.02713559714944069</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.02320355343627922</v>
+        <v>0.03238830647769553</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.02320355343627922</v>
+        <v>0.01876939180045745</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.05397016192681447</v>
+        <v>0.03331260421792859</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.08831268835224759</v>
+        <v>0.01124959444294826</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>-0.04339626585328293</v>
+        <v>-0.003756376440586129</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>-0.08476202464388838</v>
+        <v>-0.007097047246258592</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.1520803241605271</v>
+        <v>0.7396214101927068</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.0483209215678182</v>
+        <v>0.2026841329637781</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>17.92</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.005611693781272686</v>
+        <v>-0.007066138848291437</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.008441171337434605</v>
+        <v>-0.02049353341569349</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.02517165592564563</v>
+        <v>-0.02008361050630447</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.01538465246746978</v>
+        <v>-0.02902153754018455</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.1336500677847258</v>
+        <v>0.04164501549496213</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.02927615615203571</v>
+        <v>0.006174745460417519</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.06266978103682463</v>
+        <v>0.01087624681175803</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.2326681076071317</v>
+        <v>-0.03854679097082969</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.2072435840889764</v>
+        <v>-0.005640748227042303</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.06479246371901115</v>
+        <v>-0.00188379586755083</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>47.03</v>
+        <v>85.52</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.002771796357964762</v>
+        <v>0.008609455356255014</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.01754752812472682</v>
+        <v>-0.02363283230243451</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.02407138162417766</v>
+        <v>-0.006736374463804595</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.003812758073850175</v>
+        <v>-0.03856099407368851</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-0.02258809337388656</v>
+        <v>-0.02308764479999414</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.02727045710342968</v>
+        <v>0.07393365210429836</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.04971492351939921</v>
+        <v>-0.02029364069254758</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.007916002585064197</v>
+        <v>-0.001539029559824878</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.1201507219640956</v>
+        <v>0.4065825281143287</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.0385454029776926</v>
+        <v>0.1204394874171355</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>112.6</v>
+        <v>47.36</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.009865457167005376</v>
+        <v>0.007016836904532475</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0.005087920209185581</v>
+        <v>-0.01065381936312326</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.00345162755130457</v>
+        <v>-0.007127885684481083</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0.01195292415907123</v>
+        <v>-0.01415487702365958</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.006893732908681782</v>
+        <v>-0.02181058101432565</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.03202405303031541</v>
+        <v>-0.02565209744562058</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>-0.0273107742810037</v>
+        <v>0.05034163425224003</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.02031198627838682</v>
+        <v>0.01520301500856269</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.7135500273890152</v>
+        <v>0.1236556672742395</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.196645731738943</v>
+        <v>0.03962747606965311</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>219.01</v>
+        <v>26.59</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.003160439535862203</v>
+        <v>0.01701784741167267</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.02925404940233312</v>
+        <v>-0.03118400278604916</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.05931626313434213</v>
+        <v>-0.01536528207523824</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.1305676863301721</v>
+        <v>-0.006203302122238963</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.07149747584884358</v>
+        <v>0.0999176733069187</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.08117145999428976</v>
+        <v>0.1017371964248279</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.05298882432169405</v>
+        <v>-0.1207942599994262</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1002348561550128</v>
+        <v>-0.2056912231848654</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>1.025734935569158</v>
+        <v>0.257452387555267</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.2653020334319214</v>
+        <v>0.07935386235280117</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>84.79000000000001</v>
+        <v>216.77</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.01387066483566057</v>
+        <v>-0.0102277991441394</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.03196706860863319</v>
+        <v>-0.0391826440050328</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.02416847150273171</v>
+        <v>-0.05071163355172081</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.05399973765709398</v>
+        <v>-0.1439459630855655</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.03076360628032948</v>
+        <v>-0.07214945313842491</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.04236132989293417</v>
+        <v>-0.05353203629562964</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.03817728906179751</v>
+        <v>0.03654530500886799</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.03049845134933904</v>
+        <v>0.09253137475679751</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.4179689005147693</v>
+        <v>1.012299809212937</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1234547081353394</v>
+        <v>0.2624985713463819</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>42.39</v>
+        <v>17.56</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.003057409847499137</v>
+        <v>-0.02008931968855299</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.01601676908260607</v>
+        <v>-0.01181772574066198</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.007956942575012671</v>
+        <v>0.01502891562705133</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.02842084914302212</v>
+        <v>-0.03569465410267469</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.03153960960156177</v>
+        <v>-0.1583589342287438</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.06954862539203222</v>
+        <v>-0.0420494290793787</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.005594244224111922</v>
+        <v>0.06892275447196838</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.02438257683341316</v>
+        <v>0.2128584777537588</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.4625350143281861</v>
+        <v>0.1576463626548306</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1351033988428869</v>
+        <v>0.05000645881282662</v>
       </c>
     </row>
     <row r="52">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -3406,37 +3406,37 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>26.15</v>
+        <v>34.76</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0.01313447148077729</v>
+        <v>-0.01473924251008818</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.047395284478435</v>
+        <v>-0.03310159711131389</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.03544818962998986</v>
+        <v>-0.03148512363700828</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.003607747517555326</v>
+        <v>-0.07896139969262073</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.08915744067198883</v>
+        <v>-0.06310929319701442</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0.05558072887051391</v>
+        <v>-0.001510753117058283</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.1433214336373765</v>
+        <v>-0.0399245563004561</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.221175952359825</v>
+        <v>0.02607364657427635</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.2375640430670189</v>
+        <v>0.3597158662578424</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.07363310474777607</v>
+        <v>0.1078544889264763</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>35.28</v>
+        <v>43.99</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.01495973771211445</v>
+        <v>-0.002041745663551309</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.01863705060983689</v>
+        <v>-0.02827476841956511</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.0131468872923951</v>
+        <v>-0.01676352194597641</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.05869799332468684</v>
+        <v>-0.03297427884488391</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.05266658902343979</v>
+        <v>-0.03720720068589412</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.02761318888272413</v>
+        <v>-0.02784526677421439</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.04007436578692203</v>
+        <v>-0.02905260573459134</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.03624836777358165</v>
+        <v>-0.04177250542049249</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.3710196569930722</v>
+        <v>0.2408585033404582</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.1109160138742367</v>
+        <v>0.07458494980406338</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>44.08</v>
+        <v>17.86</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.001135658713243615</v>
+        <v>0.004612483574357285</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.02628669349847346</v>
+        <v>-0.05900942881439086</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.0260715098152603</v>
+        <v>-0.0945959260711432</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.03163441591010319</v>
+        <v>-0.1245097576311478</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-0.0286469635624127</v>
+        <v>0.02969162971373285</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.05791833792363399</v>
+        <v>0.1093167818124716</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.02459993836277452</v>
+        <v>-0.1545561841253699</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.04100855160215766</v>
+        <v>-0.2021442739451919</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.2507910460685834</v>
+        <v>0.01788769082980957</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.07744453137758778</v>
+        <v>0.005927360589861985</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>43.53</v>
+        <v>41.82</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.03266669379340281</v>
+        <v>-0.01344656058106508</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.05492840900046569</v>
+        <v>-0.02924795920788892</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.04476631400458497</v>
+        <v>-0.009708734356060011</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.03630727155477165</v>
+        <v>-0.05619502598272785</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.02899850543519877</v>
+        <v>-0.05486091503684953</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.1524533048676903</v>
+        <v>-0.09750233941896469</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.06922480289459598</v>
+        <v>-0.003063324963433978</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.06935481452604431</v>
+        <v>0.005525645308310345</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.996081524785567</v>
+        <v>0.4034895775856706</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.2590976837028309</v>
+        <v>0.1196176356295529</v>
       </c>
     </row>
     <row r="56">
@@ -3630,37 +3630,37 @@
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>245.96</v>
+        <v>242.83</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0.005313508674483547</v>
+        <v>-0.01272566595126878</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.02751854936527798</v>
+        <v>-0.0398940234498607</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.06046831931837593</v>
+        <v>-0.05336811074745351</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.1586220435409746</v>
+        <v>-0.1816466388961139</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.1349427274854403</v>
+        <v>-0.1324678458134141</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.112920800650086</v>
+        <v>-0.0837898329105039</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.02908109231033729</v>
+        <v>0.02710283757678944</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.1178685340857899</v>
+        <v>0.1009500940339547</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>1.129187868468857</v>
+        <v>1.110723928079363</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.2864848049752502</v>
+        <v>0.2827552806656319</v>
       </c>
     </row>
     <row r="57">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3686,37 +3686,37 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>17.78</v>
+        <v>19.36</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.005429288298530954</v>
+        <v>0.0001033529001031042</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.06332980470478</v>
+        <v>-0.0004130012070979738</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.109095467506875</v>
+        <v>0.0007236232426997002</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.120336433286208</v>
+        <v>-0.01062906538456143</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>0.02995192676912639</v>
+        <v>-0.03863150505425128</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.05815125577236602</v>
+        <v>0.06937313176223858</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.1570412636650359</v>
+        <v>-0.07866384591953168</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.2112338512372971</v>
+        <v>-0.1732998073155272</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.01379029202075621</v>
+        <v>0.183098335461201</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.004575794178724113</v>
+        <v>0.05764587792062925</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>19.36</v>
+        <v>51.86</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.009069574731333185</v>
+        <v>0.01926099688803773</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.0005163007460216029</v>
+        <v>-0.03300392359708515</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.01445809712379043</v>
+        <v>-0.05657632420026681</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.007179573181018029</v>
+        <v>-0.06994257224852807</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.04352769410877111</v>
+        <v>0.04566999340283084</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.04869990316537232</v>
+        <v>-0.0490552449110897</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.07509643666181476</v>
+        <v>-0.1633552372132593</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.1874883973413171</v>
+        <v>-0.1499332316697235</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1792173290506884</v>
+        <v>0.03322483353382544</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.05648811927434849</v>
+        <v>0.01095450514380425</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>50.88</v>
+        <v>42.19</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.0003929362900608746</v>
+        <v>-0.03078337216092919</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.05127726916334086</v>
+        <v>-0.08402089950492586</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.07809381528971349</v>
+        <v>-0.07295099576510755</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.0911039391894457</v>
+        <v>-0.06098378944705141</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>0.02590994514204303</v>
+        <v>-0.07315469678310904</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.0938806192207905</v>
+        <v>-0.1440454890838055</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.179956549256452</v>
+        <v>-0.04008654609845175</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1728816617914352</v>
+        <v>0.05122508297753425</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.007174042629089383</v>
+        <v>0.8219951635772791</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.00238565168322924</v>
+        <v>0.2213751321238757</v>
       </c>
     </row>
     <row r="60">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>98.45999999999999</v>
+        <v>98.27</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0.01599417360221711</v>
+        <v>-0.001929742465701656</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.04639226068307356</v>
+        <v>-0.04823247803325514</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.05869980381660833</v>
+        <v>-0.04415913844312558</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.1073436413390604</v>
+        <v>-0.09860576344719318</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.08557840614780787</v>
+        <v>-0.08530714580524135</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.04026573174245107</v>
+        <v>-0.01810639211999665</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.09126456709979425</v>
+        <v>-0.08343388171695931</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1646962207555305</v>
+        <v>-0.147575916727927</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2257096885622867</v>
+        <v>0.2460943595571989</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.07019406866913447</v>
+        <v>0.07609424819162958</v>
       </c>
     </row>
     <row r="61">
@@ -3896,51 +3896,51 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>47.15</v>
+        <v>90.05</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.002338448303797813</v>
+        <v>0.005695802222646984</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.01852621508507868</v>
+        <v>-0.04110318879594499</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.03083247590859972</v>
+        <v>-0.04900199883846923</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.1053130769774772</v>
+        <v>-0.08837817205327569</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.2431781363838176</v>
+        <v>-0.0696448769921626</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.1539565420210504</v>
+        <v>-0.02910976045822133</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.0424451681832877</v>
+        <v>-0.1171276444393115</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.1263736464021736</v>
+        <v>-0.2027692998101592</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>-0.1489849378315992</v>
+        <v>0.1052128102063952</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>-0.05235483981327127</v>
+        <v>0.03390817680882896</v>
       </c>
     </row>
     <row r="62">
@@ -3952,51 +3952,51 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>46.22</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.01496258984991305</v>
+        <v>-0.01972429003348686</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.04653394288328871</v>
+        <v>-0.03788508867900464</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.07125819402164435</v>
+        <v>-0.02837919871309103</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.1090547172584344</v>
+        <v>-0.1106407516825185</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.08239114299513051</v>
+        <v>-0.2666983640195665</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.057690335931736</v>
+        <v>-0.1654026664995125</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.1246038272611897</v>
+        <v>-0.03386285381935006</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>-0.2225355760819557</v>
+        <v>0.1062710045747151</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>0.08025257773189054</v>
+        <v>-0.1857862558352184</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>0.02606554359512803</v>
+        <v>-0.06621661313286287</v>
       </c>
     </row>
   </sheetData>
@@ -4015,7 +4015,7 @@
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -4113,17 +4113,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -4158,17 +4158,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4602,21 +4602,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1609862417092056</v>
+        <v>0.09963105824121343</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1586220435409746</v>
+        <v>-0.1816466388961139</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.09726975712544483</v>
+        <v>0.07191531570999188</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1305676863301721</v>
+        <v>-0.1439459630855655</v>
       </c>
     </row>
     <row r="19">
@@ -4692,21 +4692,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.08125001557848632</v>
+        <v>0.07090365432759693</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.120336433286208</v>
+        <v>-0.1280015905541002</v>
       </c>
     </row>
     <row r="20">
@@ -4737,21 +4737,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.07745223607201668</v>
+        <v>0.05878424173305485</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.111356485857642</v>
+        <v>-0.1245097576311478</v>
       </c>
     </row>
     <row r="21">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.06123345123044155</v>
+        <v>0.04634876194695159</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.1090547172584344</v>
+        <v>-0.1106407516825185</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.05888225180339934</v>
+        <v>0.04154096554478648</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.1073436413390604</v>
+        <v>-0.1070975671090898</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.02927106200070351</v>
+        <v>0.0319782698090465</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.1053130769774772</v>
+        <v>-0.09860576344719318</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02718539318450786</v>
+        <v>0.02459644036852726</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.0911039391894457</v>
+        <v>-0.09506741219180892</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.02230665531611664</v>
+        <v>0.01876939180045745</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.07870526187116555</v>
+        <v>-0.08837817205327569</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.01597069738103296</v>
+        <v>0.01344244593291499</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.07491583583547068</v>
+        <v>-0.07920365151839048</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.294731843948052</v>
+        <v>0.3067971354448489</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2431781363838176</v>
+        <v>-0.2666983640195665</v>
       </c>
     </row>
     <row r="32">
@@ -5158,21 +5158,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2787539651369588</v>
+        <v>0.2488986532438622</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1536469492904977</v>
+        <v>-0.2161884508517007</v>
       </c>
     </row>
     <row r="33">
@@ -5203,21 +5203,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2493566256951565</v>
+        <v>0.2418831631272345</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5225,21 +5225,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1349427274854403</v>
+        <v>-0.1583589342287438</v>
       </c>
     </row>
     <row r="34">
@@ -5248,21 +5248,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2200391665274855</v>
+        <v>0.2343570410373244</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1336500677847258</v>
+        <v>-0.1468886733061159</v>
       </c>
     </row>
     <row r="35">
@@ -5293,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2035938802693626</v>
+        <v>0.1990436027610614</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1180030078254978</v>
+        <v>-0.1324678458134141</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1925274356380924</v>
+        <v>0.1791219597733285</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.110759086443635</v>
+        <v>-0.1265565829922446</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.190442388965939</v>
+        <v>0.1763088944842233</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.08557840614780787</v>
+        <v>-0.1202335526322232</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1778915159829142</v>
+        <v>0.1759647336391776</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.08239114299513051</v>
+        <v>-0.08530714580524135</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1374456468825411</v>
+        <v>0.1758694715100022</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.07149747584884358</v>
+        <v>-0.08464488553435234</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1305892557957151</v>
+        <v>0.1735150737858984</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.06714247615152347</v>
+        <v>-0.08106499479986806</v>
       </c>
     </row>
     <row r="41"/>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5016396420469882</v>
+        <v>0.5396800871272862</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1539565420210504</v>
+        <v>-0.1654026664995125</v>
       </c>
     </row>
     <row r="46">
@@ -5669,21 +5669,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.4962617303057115</v>
+        <v>0.5217557692947976</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1524533048676903</v>
+        <v>-0.1440454890838055</v>
       </c>
     </row>
     <row r="47">
@@ -5714,21 +5714,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4392559445570168</v>
+        <v>0.4585319851826828</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5736,21 +5736,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.112920800650086</v>
+        <v>-0.09750233941896469</v>
       </c>
     </row>
     <row r="48">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.417674565562264</v>
+        <v>0.4510046386886166</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.0938806192207905</v>
+        <v>-0.0837898329105039</v>
       </c>
     </row>
     <row r="49">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4010708580481357</v>
+        <v>0.4427481390246546</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.08117145999428976</v>
+        <v>-0.05353203629562964</v>
       </c>
     </row>
     <row r="50">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3688193531027808</v>
+        <v>0.3980327337732998</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.06954862539203222</v>
+        <v>-0.0490552449110897</v>
       </c>
     </row>
     <row r="51">
@@ -5894,21 +5894,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3545882870133334</v>
+        <v>0.3517494381109427</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.05952343898111812</v>
+        <v>-0.0420494290793787</v>
       </c>
     </row>
     <row r="52">
@@ -5939,21 +5939,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.2879260309982692</v>
+        <v>0.3510651819759862</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.05791833792363399</v>
+        <v>-0.02910976045822133</v>
       </c>
     </row>
     <row r="53">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2757170985225788</v>
+        <v>0.3242387248161223</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.057690335931736</v>
+        <v>-0.02784526677421439</v>
       </c>
     </row>
     <row r="54">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2371683366735888</v>
+        <v>0.2948757343675816</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.0420284343979711</v>
+        <v>-0.02565209744562058</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9728897942625354</v>
+        <v>0.888888823479131</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6157,21 +6157,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2225355760819557</v>
+        <v>-0.2056912231848654</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8764159167469507</v>
+        <v>0.7849135491648447</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6202,21 +6202,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.221175952359825</v>
+        <v>-0.2027692998101592</v>
       </c>
     </row>
     <row r="61">
@@ -6225,21 +6225,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7153530236638159</v>
+        <v>0.7280740205045306</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.2112338512372971</v>
+        <v>-0.2021442739451919</v>
       </c>
     </row>
     <row r="62">
@@ -6270,21 +6270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6906695938305043</v>
+        <v>0.6821220278900557</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1874883973413171</v>
+        <v>-0.1732998073155272</v>
       </c>
     </row>
     <row r="63">
@@ -6315,21 +6315,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6578417767545091</v>
+        <v>0.6465422588355743</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1728816617914352</v>
+        <v>-0.1499332316697235</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.6449688614398215</v>
+        <v>0.5919514080808357</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1646962207555305</v>
+        <v>-0.147575916727927</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.6396541144386847</v>
+        <v>0.5877593100086718</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6427,21 +6427,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.09662783386879226</v>
+        <v>-0.07629164950685829</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.5332567421574004</v>
+        <v>0.5212879832317272</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6472,21 +6472,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.08476202464388838</v>
+        <v>-0.04486435963866775</v>
       </c>
     </row>
     <row r="67">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5331027851477392</v>
+        <v>0.5068486175136178</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.04194317060326458</v>
+        <v>-0.04177250542049249</v>
       </c>
     </row>
     <row r="68">
@@ -6540,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.524453679351564</v>
+        <v>0.5038898470023632</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.04100855160215766</v>
+        <v>-0.03854679097082969</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.961589504096277</v>
+        <v>2.779410701995538</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1489849378315992</v>
+        <v>-0.1857862558352184</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.829354236076945</v>
+        <v>2.625610142954565</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6713,21 +6713,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.007174042629089383</v>
+        <v>-0.005640748227042303</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.495943346180588</v>
+        <v>2.349785648617388</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.01379029202075621</v>
+        <v>0.01788769082980957</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>2.139215789855056</v>
+        <v>1.802197817553022</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6803,21 +6803,21 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.01850161912091308</v>
+        <v>0.03322483353382544</v>
       </c>
     </row>
     <row r="77">
@@ -6826,21 +6826,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.521774551636385</v>
+        <v>1.381954101094161</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.08025257773189054</v>
+        <v>0.1052128102063952</v>
       </c>
     </row>
     <row r="78">
@@ -6871,21 +6871,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.490994625401555</v>
+        <v>1.341664938914357</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1201507219640956</v>
+        <v>0.1236556672742395</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.347462518421874</v>
+        <v>1.276023171896981</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1520803241605271</v>
+        <v>0.1460139937736749</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.243417984565997</v>
+        <v>1.256969292594426</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6983,21 +6983,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1778379413674496</v>
+        <v>0.1576463626548306</v>
       </c>
     </row>
     <row r="81">
@@ -7006,21 +7006,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.129187868468857</v>
+        <v>1.15285384895101</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,21 +7028,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1792173290506884</v>
+        <v>0.1769708364597096</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.109072834117779</v>
+        <v>1.110723928079363</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,21 +7073,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2072435840889764</v>
+        <v>0.183098335461201</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -489,16 +489,16 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>15.3</v>
+        <v>15.33</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.04434728469685723</v>
+        <v>0.001960766836418548</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.07608691520786937</v>
+        <v>-0.05950916311388843</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.01098901573106414</v>
+        <v>-0.0294397056246799</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.07090365432759693</v>
+        <v>0.07300344669800185</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.2418831631272345</v>
+        <v>0.278565489269931</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4585319851826828</v>
+        <v>0.4613918263290848</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7626727710610395</v>
+        <v>0.7186098422182208</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.888888823479131</v>
+        <v>0.8672350612030073</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1.802197817553022</v>
+        <v>1.797445231815515</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4098284279864777</v>
+        <v>0.409030944195129</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>38.74</v>
+        <v>38.59</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.01786653391066295</v>
+        <v>-0.003910704577705482</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.02589888779082994</v>
+        <v>-0.0163522450461201</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.01324494817365285</v>
+        <v>-0.02726234540715045</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.09963105824121343</v>
+        <v>0.09533072602796233</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3067971354448489</v>
+        <v>0.2880007395114283</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3517494381109427</v>
+        <v>0.3464631453954115</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4817205098055408</v>
+        <v>0.4709133554707809</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7280740205045306</v>
+        <v>0.7285678266870388</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.8370839749118675</v>
+        <v>0.8383249012552301</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2247374641966762</v>
+        <v>0.2250131668733817</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>118.56</v>
+        <v>120.59</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.07879887090516213</v>
+        <v>0.01712212231021359</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.07051916531461622</v>
+        <v>0.0944817208557025</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.0135931975831185</v>
+        <v>0.07814034852930041</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.003215410834631172</v>
+        <v>0.02039258780243292</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2343570410373244</v>
+        <v>0.2383446266081919</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5217557692947976</v>
+        <v>0.5478114577029365</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4226309694370316</v>
+        <v>0.4745715259416736</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.3883387165321246</v>
+        <v>0.4016135344001139</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.256969292594426</v>
+        <v>1.327840184342412</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3117222443549044</v>
+        <v>0.3253107488723539</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>157.6</v>
+        <v>199.7</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.008962926905417001</v>
+        <v>0.03220135260366352</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.03790972191948694</v>
+        <v>0.0298591778494417</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-0.03015380859375005</v>
+        <v>0.03621832546350778</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.001207054424660958</v>
+        <v>0.1064324387524365</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1791219597733285</v>
+        <v>0.2672315379802321</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2948757343675816</v>
+        <v>0.2001031604227101</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.2854431488825322</v>
+        <v>0.5626442979055615</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6821220278900557</v>
+        <v>0.5798669716741409</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.027819193111072</v>
+        <v>0.4272958127873328</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2657358367080496</v>
+        <v>0.1259125600507398</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>100.05</v>
+        <v>101</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.05985171011178436</v>
+        <v>0.009495221581859781</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.05772287689242717</v>
+        <v>0.07435376773675939</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.0009984869954819953</v>
+        <v>0.04989608320196015</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.004518118318582509</v>
+        <v>0.01405624043501041</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1735150737858984</v>
+        <v>0.1717497800027015</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.5396800871272862</v>
+        <v>0.5542996907197371</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3575608416372569</v>
+        <v>0.3963408562754096</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3422426866155608</v>
+        <v>0.3412066904150675</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.15285384895101</v>
+        <v>1.210385912126526</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2912336912757496</v>
+        <v>0.3026348753094534</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>193.47</v>
+        <v>154.03</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.01149601464319838</v>
+        <v>-0.02265232986015164</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.01447220601788834</v>
+        <v>-0.04878647720500962</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.02386745526351097</v>
+        <v>-0.05734391350787615</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.07191531570999188</v>
+        <v>-0.02147261803047729</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1758694715100022</v>
+        <v>0.1303607117486181</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1626638130201292</v>
+        <v>0.265543782104781</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.4926340392253996</v>
+        <v>0.2592908395087217</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5212879832317272</v>
+        <v>0.6561593743991105</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3592367584230762</v>
+        <v>1.010156612641044</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1077243528853913</v>
+        <v>0.262050204795343</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>541.5</v>
+        <v>542.11</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.04754371432289017</v>
+        <v>0.001126473410087758</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.04499040462472548</v>
+        <v>-0.05511302562810694</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.02718143964588793</v>
+        <v>-0.005704092877507394</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.07879964401870121</v>
+        <v>-0.07776193631232486</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-0.1265565829922446</v>
+        <v>-0.1622469389514478</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.3980327337732998</v>
+        <v>0.3996075804743275</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.5339007124079667</v>
+        <v>0.5409373924625152</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7849135491648447</v>
+        <v>0.7703446987156328</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>2.625610142954565</v>
+        <v>2.742928881789077</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.5362445943281311</v>
+        <v>0.5526391226230247</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>28.35</v>
+        <v>28.19</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.04496871575534001</v>
+        <v>-0.005643733518842842</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.02015111361977273</v>
+        <v>0.03525527021519914</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.01630809570892877</v>
+        <v>0.009670503475138537</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.002463043442515911</v>
+        <v>-0.008092876200523902</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2488986532438622</v>
+        <v>0.2261853333931783</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.4427481390246546</v>
+        <v>0.434605652993193</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2336815033161141</v>
+        <v>0.2573595199878991</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2262110446536534</v>
+        <v>0.2031583511260275</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4282115786725564</v>
+        <v>0.4434203555012552</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1261533071256091</v>
+        <v>0.1301366048602857</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>204.6</v>
+        <v>32.53</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.008229505189026209</v>
+        <v>0.02618290209405205</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.03454129921044113</v>
+        <v>0.02424428667713996</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.02128675859019447</v>
+        <v>0.02102944620558556</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.0319782698090465</v>
+        <v>0.08650628587307674</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1990436027610614</v>
+        <v>0.1828014961408135</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.2372560559144048</v>
+        <v>0.1062429465619632</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.2100090791293818</v>
+        <v>0.3850179913355412</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4549633727257831</v>
+        <v>0.4396713295007013</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6171815558556932</v>
+        <v>0.3344007440996397</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.173778796005736</v>
+        <v>0.1009360473471599</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>152.38</v>
+        <v>153.12</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.02351809097836455</v>
+        <v>0.004884454580921016</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.01480567216165263</v>
+        <v>-0.009160704360899663</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.0009179083774371044</v>
+        <v>0.008923329940815794</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.02151153237419734</v>
+        <v>-0.01673214989612404</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-0.01852390216115141</v>
+        <v>-0.03774918653418013</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3510651819759862</v>
+        <v>0.3576643984932117</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4370822773457173</v>
+        <v>0.4443726787031128</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5038898470023632</v>
+        <v>0.5043649900737419</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.276023171896981</v>
+        <v>1.303779747802547</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.315403197097172</v>
+        <v>0.3207288116002232</v>
       </c>
     </row>
     <row r="12">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>67.90000000000001</v>
+        <v>202</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.005776912713784998</v>
+        <v>-0.01270775183750572</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.04271815545270452</v>
+        <v>-0.02570781741176997</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.03851601692035866</v>
+        <v>-0.04183667117824597</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.04339252867552623</v>
+        <v>0.01886414605461462</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1276870394073244</v>
+        <v>0.1732590006871197</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2778295622109559</v>
+        <v>0.2215333129963934</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2121154217287873</v>
+        <v>0.194914559677887</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4695195836702781</v>
+        <v>0.4391281310829853</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6399738924708118</v>
+        <v>0.608863222577485</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1792674502529907</v>
+        <v>0.171762804647045</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>85.62</v>
+        <v>411.51</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.03287016912729657</v>
+        <v>0.02350398513757646</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.05559233081780446</v>
+        <v>-0.03980679297907019</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.0779668082724787</v>
+        <v>-0.03600542293239262</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.0009334212894834826</v>
+        <v>-0.023307092112126</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-0.0006867260362933836</v>
+        <v>-0.009173643194173131</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1246362244304857</v>
+        <v>0.1088028570892909</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2903634360663638</v>
+        <v>0.4109824534931819</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6465422588355743</v>
+        <v>0.6415816979483882</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.381954101094161</v>
+        <v>0.2140504490939386</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3355017543948644</v>
+        <v>0.06678993937215227</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>474.62</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.06121805439139349</v>
+        <v>-0.01634757857742475</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.03424563367953248</v>
+        <v>-0.05100875927806714</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.02168450182134218</v>
+        <v>-0.04721822582943003</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.1280015905541002</v>
+        <v>-0.05903074448075463</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>-0.2161884508517007</v>
+        <v>0.1085163602828634</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.4510046386886166</v>
+        <v>0.2569401430341562</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4486885386541639</v>
+        <v>0.193998568587276</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.5919514080808357</v>
+        <v>0.4612084034473258</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.341664938914357</v>
+        <v>0.6302691192992578</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.327929190961749</v>
+        <v>0.176936687036169</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>31.7</v>
+        <v>480.49</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.004084170941822118</v>
+        <v>0.01236777880741857</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.008590533093924657</v>
+        <v>-0.03123113917665543</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.01602564063376311</v>
+        <v>0.01598544747779718</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.05878424173305485</v>
+        <v>-0.1172169071056525</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1073822864995273</v>
+        <v>-0.2395969346447389</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.07801732449891596</v>
+        <v>0.4689503431084561</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.3300620498167155</v>
+        <v>0.482828989080065</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.390326183440677</v>
+        <v>0.5881436758635528</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.2780838381926742</v>
+        <v>1.426218458647355</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.08522497778800298</v>
+        <v>0.3437236702349282</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>402.06</v>
+        <v>106.58</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.04423898845915142</v>
+        <v>0.004429377231171872</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.05957476970838593</v>
+        <v>-0.04146056757918404</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.0631902595181667</v>
+        <v>-0.01624510399046786</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.04573609671232537</v>
+        <v>-0.01278248670915794</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.06098048684006552</v>
+        <v>-0.04051134250829602</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.08334004868603295</v>
+        <v>0.2072950079837277</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.3652366918017522</v>
+        <v>0.272925203540952</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.5877593100086718</v>
+        <v>0.4916270348880665</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1769708364597096</v>
+        <v>0.7307783752160275</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.05581679787284921</v>
+        <v>0.200642798025219</v>
       </c>
     </row>
     <row r="17">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>106.11</v>
+        <v>84.59</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.02624576101966858</v>
+        <v>-0.01202997402067385</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.0439679011383326</v>
+        <v>-0.1037296164487099</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.01759097757893269</v>
+        <v>-0.0521066969653835</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.01713596229908798</v>
+        <v>-0.01295216627629447</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.04276046846203729</v>
+        <v>-0.05492200667438984</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.2019710248935358</v>
+        <v>0.1111068798678783</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.2656748184762379</v>
+        <v>0.2633453153509255</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5068486175136178</v>
+        <v>0.601541656711843</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6989339374454235</v>
+        <v>1.343468110364328</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1932336637331848</v>
+        <v>0.3282699555765642</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>93.27</v>
+        <v>57.06</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.03206728878904974</v>
+        <v>-0.009718805431700006</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.06063051885337944</v>
+        <v>0.001931529567654522</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.04777948393044607</v>
+        <v>-0.006442607172534198</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.04154096554478648</v>
+        <v>-0.00157480577751401</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1434700224932319</v>
+        <v>0.06574524463152964</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>-0.009558564334131825</v>
+        <v>0.3113687063045119</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1445699265102274</v>
+        <v>0.1700709789728958</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.4336237969810497</v>
+        <v>0.1931134617553598</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.779410701995538</v>
+        <v>0.1904279733129086</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.5576672759140806</v>
+        <v>0.05982552406346553</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>57.62</v>
+        <v>55.3</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.01748186200065138</v>
+        <v>-0.003244417928279675</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.003483120329453859</v>
+        <v>-0.01197073376862368</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.01604655020460521</v>
+        <v>-0.01002508713161809</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.008223926394700598</v>
+        <v>0.006186320201085005</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.07840016460792532</v>
+        <v>0.09969906617206403</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.3242387248161223</v>
+        <v>0.1002267156183776</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1822753604437199</v>
+        <v>0.2328751733450765</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1910280631756571</v>
+        <v>0.2575536603921549</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2001216430471782</v>
+        <v>0.6889548553003115</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.06269447492118885</v>
+        <v>0.190892829786232</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>94.14</v>
+        <v>94.13</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.03048402812551587</v>
+        <v>-0.0001062474643649391</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.05158173117460774</v>
+        <v>-0.043491578593847</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.04436100550011879</v>
+        <v>-0.005704034287226656</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.04634876194695159</v>
+        <v>0.0462375900441534</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.1763088944842233</v>
+        <v>0.1039052534203659</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.009435955750167091</v>
+        <v>0.00932870573943001</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1069776605091044</v>
+        <v>0.1174265385618265</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3594797381723696</v>
+        <v>0.3452558653876978</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>2.349785648617388</v>
+        <v>2.280683146875289</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.4962551992944091</v>
+        <v>0.4858949129584329</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>55.48</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.007690937334096315</v>
+        <v>-0.006004048233611448</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.004307280567280802</v>
+        <v>-0.05878173518301877</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.001978784134729739</v>
+        <v>-0.01675683334089884</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.009461434978636829</v>
+        <v>0.03528750335037323</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.08444266186354077</v>
+        <v>0.06771549529769483</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.1038079298553778</v>
+        <v>-0.01550522248643715</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2400189075452923</v>
+        <v>0.1410180714078737</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2574203693511292</v>
+        <v>0.3926585098373956</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6867506028231061</v>
+        <v>2.661377939505551</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1903745267532047</v>
+        <v>0.5412799191764606</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>292.71</v>
+        <v>74.05</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01311774142046995</v>
+        <v>-0.0008095743907654551</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.006325837552097147</v>
+        <v>-0.003498782335861761</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.0007521666656928883</v>
+        <v>0.01969154848652344</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.004564440078173915</v>
+        <v>-0.04978823608653671</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.107198233011762</v>
+        <v>0.03119284730616978</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.2191169679890823</v>
+        <v>0.1870644844602858</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.08567934185892256</v>
+        <v>0.1207889359950836</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.04651404605022691</v>
+        <v>0.1785052168553065</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.7239531364006744</v>
+        <v>0.8426922391261136</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.199062493777816</v>
+        <v>0.2259824941207174</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>65.59</v>
+        <v>67.95</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.01501073274652409</v>
+        <v>-0.00278841272539132</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.02149193697390483</v>
+        <v>-0.006579014146168682</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.02117379588787172</v>
+        <v>0.01493652047173488</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.01344244593291499</v>
+        <v>-0.05190458093683903</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.09382198196144143</v>
+        <v>0.03366489188600741</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2566380309414342</v>
+        <v>0.1884125287709617</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.09418693795642907</v>
+        <v>0.1038264721531239</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.02678916298824974</v>
+        <v>0.1507618433085884</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.9460410671361728</v>
+        <v>0.9120210000799687</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2484869302239172</v>
+        <v>0.2411689029915927</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>106.64</v>
+        <v>144.96</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.05043344085779888</v>
+        <v>-0.004805690859832623</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.01979534953490747</v>
+        <v>0.01321031168584064</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.03036919317455711</v>
+        <v>0.007926570237745123</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.02459644036852726</v>
+        <v>-0.005420194072952356</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.1759647336391776</v>
+        <v>0.07361873890440718</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.2668962409915885</v>
+        <v>0.1272989687932484</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>-0.01213306117643054</v>
+        <v>0.06991808004187727</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>-0.04486435963866775</v>
+        <v>0.1283713305449787</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.4867991762648547</v>
+        <v>0.6480999730495092</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1413463052593551</v>
+        <v>0.1812120011485034</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>74.11</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.002841665495759482</v>
+        <v>-0.005070831586602376</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.01541113437556796</v>
+        <v>0.02108278310906253</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.007476931348722626</v>
+        <v>0.02140242817514282</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.04901834569312213</v>
+        <v>0.008303449966874821</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.01543949535707045</v>
+        <v>0.05690486702344888</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1880262074622692</v>
+        <v>0.2502658311212105</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1247070347552128</v>
+        <v>0.09760980293586319</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1680268049561271</v>
+        <v>0.01066743801176351</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8336970367858985</v>
+        <v>0.9699775627457745</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2239843391531435</v>
+        <v>0.2535849222231465</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>145.66</v>
+        <v>105.55</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.01138730274265121</v>
+        <v>-0.01022127104397219</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.0006870438663986178</v>
+        <v>0.02815117169838066</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.01194943164881002</v>
+        <v>-0.005933294891761864</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.0006174705858704721</v>
+        <v>0.01412376244083147</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.07755809274181491</v>
+        <v>0.1388649407013791</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1327425794538732</v>
+        <v>0.2539469511278241</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.08700220350271648</v>
+        <v>0.001705948024808279</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1194003300047128</v>
+        <v>-0.06418050984005097</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6477657273288973</v>
+        <v>0.4999116943272848</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1811321431794555</v>
+        <v>0.1446917788322306</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>68.14</v>
+        <v>289.9</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.001469701245966126</v>
+        <v>-0.0095999372779354</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.01730598516900195</v>
+        <v>0.007962201111072931</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.004866566036513031</v>
+        <v>0.009611963179099403</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.04925350731802347</v>
+        <v>-0.00507931553822083</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.02339301299986141</v>
+        <v>0.06887394953066361</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1917355794259346</v>
+        <v>0.2074135215619204</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1101018286220767</v>
+        <v>0.08434631486126687</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1441407955152862</v>
+        <v>0.02091844844398061</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.9104296080839471</v>
+        <v>0.7349931189791068</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.24082446212689</v>
+        <v>0.2016165987372647</v>
       </c>
     </row>
     <row r="28">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>132.07</v>
+        <v>131.54</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.01717506969520266</v>
+        <v>-0.004032770520857598</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.00706704173699424</v>
+        <v>0.008645008804722298</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.004672508145150411</v>
+        <v>-0.00853696308573737</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.009969914790983192</v>
+        <v>-0.01396247893337632</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.0880247187494303</v>
+        <v>0.08899749258979028</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1049326955826386</v>
+        <v>0.1004768258232878</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.06294336306367176</v>
+        <v>0.04640448314354151</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.0987564228866733</v>
+        <v>0.1125566591222267</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.627690755794295</v>
+        <v>0.6331321543610906</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1763158955045154</v>
+        <v>0.1776252523662063</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>188.87</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.008608469040660149</v>
+        <v>-0.009628901727901429</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.03863387629694071</v>
+        <v>-0.01823248592010918</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02879624655918112</v>
+        <v>-0.02957702598717471</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.01203119251863571</v>
+        <v>-0.04056181320658458</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.02760663846469003</v>
+        <v>0.002409124194462597</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.1739168535975517</v>
+        <v>0.05577957817146628</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.05622558054381122</v>
+        <v>0.1094447501492641</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.07728304787474394</v>
+        <v>0.1101463728045884</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.021865208920734</v>
+        <v>0.3992988071300927</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2644958249388645</v>
+        <v>0.1185021450087327</v>
       </c>
     </row>
     <row r="30">
@@ -2174,37 +2174,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>82.64</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.006087168294561796</v>
+        <v>-0.009922552043568067</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01817748381348272</v>
+        <v>-0.01386044966806577</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.02936340166692508</v>
+        <v>-0.01338478965714274</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.05489481836387533</v>
+        <v>-0.06427267371530565</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.04303121146363409</v>
+        <v>-0.05421341261812396</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.1341353615540133</v>
+        <v>0.1228818444045428</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.089952619549452</v>
+        <v>0.08854350322605131</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.1804017257825243</v>
+        <v>0.1614648111493924</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4046028347540647</v>
+        <v>0.3972054226518291</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1199135867519006</v>
+        <v>0.1179440979799928</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>92.43000000000001</v>
+        <v>185.23</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.00380102592486109</v>
+        <v>-0.01927251275349451</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.008793562410983613</v>
+        <v>-0.04169899031794311</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.01429024619667307</v>
+        <v>-0.03218560887065114</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.0312336572953833</v>
+        <v>-0.03107183396087498</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.001484414188344552</v>
+        <v>-0.006383448412695447</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.06604441508186776</v>
+        <v>0.1512925260650508</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1310196647360422</v>
+        <v>0.04530963011439715</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1128858005057642</v>
+        <v>0.06130703060665388</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.4121024850819901</v>
+        <v>0.9966613843905656</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1219032491144711</v>
+        <v>0.2592195940874382</v>
       </c>
     </row>
     <row r="32">
@@ -2286,37 +2286,37 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.01004612852266518</v>
+        <v>-0.01008064495454508</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.0009399717158156129</v>
+        <v>-0.006206977205292397</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.003482482232483819</v>
+        <v>-0.01904635415957467</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.005879139945774603</v>
+        <v>-0.01590051937788828</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.01275477617374787</v>
+        <v>0.006697619453828851</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.03296645444707802</v>
+        <v>0.02255348636984178</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.1175866357511945</v>
+        <v>0.09663698248019181</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.09432418523446984</v>
+        <v>0.1015866759570048</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2272688773746363</v>
+        <v>0.2228430241174928</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07064766372891396</v>
+        <v>0.06935910148494262</v>
       </c>
     </row>
     <row r="33">
@@ -2342,37 +2342,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>102.81</v>
+        <v>102.22</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.003905808829029134</v>
+        <v>-0.005738705883679973</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.02568232724304897</v>
+        <v>-0.01493683600756723</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.02669695889566981</v>
+        <v>-0.004770692903682483</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.07768909632433885</v>
+        <v>-0.08298196733384455</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.1202335526322232</v>
+        <v>-0.1235594495153345</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.1755187351811756</v>
+        <v>0.1687727788992155</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.09944818365006847</v>
+        <v>0.09839361067822971</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2145627708608666</v>
+        <v>0.208442532601038</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3471252389994284</v>
+        <v>0.3479977853613512</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1044243950399026</v>
+        <v>0.104662792450219</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>69.97</v>
+        <v>22.86</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.02126166860380796</v>
+        <v>-0.001964211112774339</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.05675382943047669</v>
+        <v>-0.04887691762317081</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.08380255723069674</v>
+        <v>-0.02244547380204798</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.06991894060238235</v>
+        <v>-0.05982730024522609</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.1468886733061159</v>
+        <v>-0.07919140776463374</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.001835551758804677</v>
+        <v>-0.02146910502609611</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.1032033298521069</v>
+        <v>0.119343881209822</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.4089501463203076</v>
+        <v>0.2311790365745421</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2355588601601897</v>
+        <v>0.5348566312316507</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.07305293422942771</v>
+        <v>0.1535132964453805</v>
       </c>
     </row>
     <row r="35">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2454,37 +2454,37 @@
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>110.17</v>
+        <v>226.25</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.03044969786240648</v>
+        <v>0.003281475372221898</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.07123591621970515</v>
+        <v>-0.03084170932689489</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.06738338499573904</v>
+        <v>-0.02980273172895753</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.0595014619858284</v>
+        <v>-0.03919651730509877</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.08464488553435234</v>
+        <v>-0.04314387618392035</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.01177368592826067</v>
+        <v>0.02483048072243066</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.08135073494876677</v>
+        <v>0.1057513759697264</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.2921902954465874</v>
+        <v>0.1081815413788563</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>1.079870220218303</v>
+        <v>0.3273887168127532</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.2764743105013847</v>
+        <v>0.09900425504782651</v>
       </c>
     </row>
     <row r="36">
@@ -2510,37 +2510,37 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>172.99</v>
+        <v>172.77</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.04309101304753926</v>
+        <v>-0.001271756828239545</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.03352142474921116</v>
+        <v>-0.05055776714033167</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.0302707209762888</v>
+        <v>-0.01538722818407101</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.07920365151839048</v>
+        <v>-0.08037468056198993</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.08106499479986806</v>
+        <v>-0.09863859472814485</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.05175048486711775</v>
+        <v>0.05041291400638381</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.1396148353836619</v>
+        <v>0.1289121792627179</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.1761358113256679</v>
+        <v>0.166851684025527</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.8071385738154846</v>
+        <v>0.8153154088387855</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.2180463612231445</v>
+        <v>0.21988071234443</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>22.91</v>
+        <v>13.07</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.03128963141878272</v>
+        <v>-0.0007645434969545395</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.03210816334736699</v>
+        <v>-0.005327294267089333</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.03046971387751563</v>
+        <v>-0.02097383360633898</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.05797696813755249</v>
+        <v>-0.02243830914754852</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.07663808892348201</v>
+        <v>0.06231956213318002</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-0.01954328104312675</v>
+        <v>0.1091949655329314</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.127044670289292</v>
+        <v>-0.034130532775274</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.245540208866915</v>
+        <v>-0.05797912635149827</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.5221647736824</v>
+        <v>0.1401183170468256</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1503249928816097</v>
+        <v>0.04468006568450034</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>28.18</v>
+        <v>109.44</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.0003549956994941539</v>
+        <v>-0.006626084593553516</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.02152774126073365</v>
+        <v>-0.08761979803443387</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.01122805946751648</v>
+        <v>-0.05467732905941369</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.1070975671090898</v>
+        <v>-0.06573328485882368</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.04571623264743929</v>
+        <v>-0.09214225837882006</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.1717256215855087</v>
+        <v>0.005069587895768501</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.004625602033399012</v>
+        <v>0.08792577375195121</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.09314401255324989</v>
+        <v>0.2329112100605484</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.5783785400696435</v>
+        <v>1.088171079413132</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1643147228407791</v>
+        <v>0.2781702125550627</v>
       </c>
     </row>
     <row r="39">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2678,37 +2678,37 @@
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>225.51</v>
+        <v>70.02</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.0128693476939391</v>
+        <v>0.0007145265326720107</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.04225775895404005</v>
+        <v>-0.0510909909972318</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.04598532088771834</v>
+        <v>-0.062776100908573</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.04233905810087946</v>
+        <v>-0.06925437300790716</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.03755277122048262</v>
+        <v>-0.1636419026692182</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.02147845350103084</v>
+        <v>-0.001122336776566479</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1012297481042395</v>
+        <v>0.1085039999956519</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.0995691457464396</v>
+        <v>0.359659524412701</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.3091528857700998</v>
+        <v>0.2426357605680916</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.09394827834681418</v>
+        <v>0.07509774069095365</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>63.66</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.009034707456738511</v>
+        <v>-0.002438284241163546</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.01744097935094213</v>
+        <v>-0.01907642890892347</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.02615883168613342</v>
+        <v>-0.02284532199292133</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.07672222385739991</v>
+        <v>-0.04785999463016621</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.02229052326283765</v>
+        <v>-0.02955023517161492</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.1125435093378033</v>
+        <v>0.0410610489653096</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.04160935546075906</v>
+        <v>0.07901026443630466</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.03393158925200002</v>
+        <v>0.05487086039813516</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.6100928017610587</v>
+        <v>0.2953373997439757</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.1720612365354999</v>
+        <v>0.09008651776402665</v>
       </c>
     </row>
     <row r="41">
@@ -2790,37 +2790,37 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>53.02</v>
+        <v>52.84</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.0196006164460284</v>
+        <v>-0.003394951030209259</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.03879621819376855</v>
+        <v>-0.03594236765816083</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.03071298504101705</v>
+        <v>-0.02002963748206199</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.09506741219180892</v>
+        <v>-0.09813961401305826</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.08045395642229525</v>
+        <v>-0.09003501591291996</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.05866015636990629</v>
+        <v>0.05506605698139677</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.08969068390367574</v>
+        <v>0.08687727858399596</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.149422269320189</v>
+        <v>0.1401282121561862</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.7288983625260925</v>
+        <v>0.7441907743306824</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.2002079182613639</v>
+        <v>0.2037362195748551</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>94.33</v>
+        <v>27.88</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.004957818624188426</v>
+        <v>-0.01064588861463134</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.01760044648089198</v>
+        <v>-0.01379558863395658</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.02187889420298939</v>
+        <v>-0.0003585596665716118</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.04553273213221776</v>
+        <v>-0.1166033069533797</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.03399225507559445</v>
+        <v>-0.08470124757886943</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.04360565619078871</v>
+        <v>0.1592515611311998</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.08503360974260854</v>
+        <v>-0.01408787094253772</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.05574023576505804</v>
+        <v>0.09201065299061217</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.2936019132384289</v>
+        <v>0.5615752979403377</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.08959946938070962</v>
+        <v>0.1601682519374872</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>13.08</v>
+        <v>70.69</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.002298830079136005</v>
+        <v>0.006081689247364519</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.01875468877951003</v>
+        <v>-0.009565659024337592</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.03182829740124815</v>
+        <v>-0.007897520901864019</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.02169034886576593</v>
+        <v>-0.02311634826562015</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.04891264031070519</v>
+        <v>0.03298701330556142</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.1100436421808966</v>
+        <v>0.01229398759085387</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>-0.039905117351686</v>
+        <v>0.01007257051960408</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-0.07629164950685829</v>
+        <v>-0.03373224578847522</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.1460139937736749</v>
+        <v>-0.004663461579780148</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.04647768902458882</v>
+        <v>-0.001556909903741577</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>57.41</v>
+        <v>62.41</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.01661529981082688</v>
+        <v>-0.01963556398046107</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.03121833490583925</v>
+        <v>-0.02132665203997175</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.02264218238083993</v>
+        <v>-0.03464813032634095</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.07163648600007955</v>
+        <v>-0.09485130370258577</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.07204164887015174</v>
+        <v>-0.04354212905031707</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.005815471995910926</v>
+        <v>0.0906980900791543</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.08871284409828695</v>
+        <v>0.0228226314008364</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.1233044467659057</v>
+        <v>0.009066197228183803</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5643178231893269</v>
+        <v>0.5832296985599839</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1608470386866356</v>
+        <v>0.1655063462479855</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>115.07</v>
+        <v>56.74</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.02193606797668668</v>
+        <v>-0.01167040882644266</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.02713559714944069</v>
+        <v>-0.04638652641232277</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.03238830647769553</v>
+        <v>-0.02825822449784365</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0.01876939180045745</v>
+        <v>-0.0824708677480116</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.03331260421792859</v>
+        <v>-0.08690051117189412</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.01124959444294826</v>
+        <v>-0.005922805766242822</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>-0.003756376440586129</v>
+        <v>0.07500128285648411</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>-0.007097047246258592</v>
+        <v>0.1084260359544928</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.7396214101927068</v>
+        <v>0.5625562424821804</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.2026841329637781</v>
+        <v>0.1604111311415997</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>70.26000000000001</v>
+        <v>114.03</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.007066138848291437</v>
+        <v>-0.009037984863869974</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.02049353341569349</v>
+        <v>0.02250719343423269</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.02008361050630447</v>
+        <v>0.02840910537434027</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.02902153754018455</v>
+        <v>0.009561769457590907</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.04164501549496213</v>
+        <v>0.01904490219142363</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.006174745460417519</v>
+        <v>0.002110003104326186</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.01087624681175803</v>
+        <v>-0.01292973328813429</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-0.03854679097082969</v>
+        <v>-0.02971374811199745</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>-0.005640748227042303</v>
+        <v>0.747135535814774</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>-0.00188379586755083</v>
+        <v>0.2044132714775819</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>85.52</v>
+        <v>47.07</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.008609455356255014</v>
+        <v>-0.006123330063132593</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.02363283230243451</v>
+        <v>-0.006542873919427428</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.006736374463804595</v>
+        <v>-0.02161714617196597</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.03856099407368851</v>
+        <v>-0.02019153210277325</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-0.02308764479999414</v>
+        <v>-0.0178902408322773</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.07393365210429836</v>
+        <v>-0.03161835124928203</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>-0.02029364069254758</v>
+        <v>0.03934067735321145</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.001539029559824878</v>
+        <v>0.02459290072438258</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.4065825281143287</v>
+        <v>0.1280478896957253</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.1204394874171355</v>
+        <v>0.04098030400835095</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>47.36</v>
+        <v>83.22</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.007016836904532475</v>
+        <v>-0.02689424126105544</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.01065381936312326</v>
+        <v>-0.0289381075361862</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.007127885684481083</v>
+        <v>-0.03142454615668355</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.01415487702365958</v>
+        <v>-0.06441816665686007</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.02181058101432565</v>
+        <v>-0.04620811349164844</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.02565209744562058</v>
+        <v>0.04505092124244392</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.05034163425224003</v>
+        <v>-0.04468562626455663</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>0.01520301500856269</v>
+        <v>-0.04192956673179227</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1236556672742395</v>
+        <v>0.3865696441013016</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.03962747606965311</v>
+        <v>0.115100205919388</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>26.59</v>
+        <v>17.44</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.01701784741167267</v>
+        <v>-0.006833652365280773</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.03118400278604916</v>
+        <v>-0.04751496216605644</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.01536528207523824</v>
+        <v>0.01160097248229142</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.006203302122238963</v>
+        <v>-0.04228438161051873</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.0999176733069187</v>
+        <v>-0.1707085133319856</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.1017371964248279</v>
+        <v>-0.04859573026417241</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>-0.1207942599994262</v>
+        <v>0.06289871417566317</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.2056912231848654</v>
+        <v>0.1899298763061976</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.257452387555267</v>
+        <v>0.1658979197323516</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.07935386235280117</v>
+        <v>0.05249532584849415</v>
       </c>
     </row>
     <row r="50">
@@ -3294,37 +3294,37 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>216.77</v>
+        <v>214</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.0102277991441394</v>
+        <v>-0.01277854047084526</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.0391826440050328</v>
+        <v>-0.04263409310312016</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.05071163355172081</v>
+        <v>-0.05082944368227205</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.1439459630855655</v>
+        <v>-0.154885084241507</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.07214945313842491</v>
+        <v>-0.09856779485296741</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.05353203629562964</v>
+        <v>-0.0656264532230405</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.03654530500886799</v>
+        <v>0.02217708270698604</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.09253137475679751</v>
+        <v>0.06574432432625499</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>1.012299809212937</v>
+        <v>0.9918316844690234</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.2624985713463819</v>
+        <v>0.2582034707002412</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>17.56</v>
+        <v>34.63</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.02008931968855299</v>
+        <v>-0.003739852120114628</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.01181772574066198</v>
+        <v>-0.02752034612297782</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.01502891562705133</v>
+        <v>-0.01479375349047496</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.03569465410267469</v>
+        <v>-0.08240594785468769</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.1583589342287438</v>
+        <v>-0.09418772468079217</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.0420494290793787</v>
+        <v>-0.005244955243925209</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.06892275447196838</v>
+        <v>-0.03716320773387916</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.2128584777537588</v>
+        <v>0.01124449488387347</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.1576463626548306</v>
+        <v>0.3743480282946485</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.05000645881282662</v>
+        <v>0.1118142633057211</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>34.76</v>
+        <v>43.59</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.01473924251008818</v>
+        <v>-0.009093010016289815</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.03310159711131389</v>
+        <v>-0.03025585288694499</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.03148512363700828</v>
+        <v>-0.01912687894662157</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.07896139969262073</v>
+        <v>-0.0417674534133573</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.06310929319701442</v>
+        <v>-0.04617069092179693</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.001510753117058283</v>
+        <v>-0.03668507950082012</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.0399245563004561</v>
+        <v>-0.03869165196685798</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.02607364657427635</v>
+        <v>-0.05539628262744811</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.3597158662578424</v>
+        <v>0.2402671942562549</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.1078544889264763</v>
+        <v>0.07441423122522051</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>43.99</v>
+        <v>25.68</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.002041745663551309</v>
+        <v>-0.03436863812194224</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.02827476841956511</v>
+        <v>-0.03820226324410703</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.01676352194597641</v>
+        <v>-0.02171427408854165</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.03297427884488391</v>
+        <v>-0.0403587411983809</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.03720720068589412</v>
+        <v>0.03769356487706221</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.02784526677421439</v>
+        <v>0.06387198941541983</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.02905260573459134</v>
+        <v>-0.1268568707028944</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>-0.04177250542049249</v>
+        <v>-0.2433099749630583</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.2408585033404582</v>
+        <v>0.219917291414796</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.07458494980406338</v>
+        <v>0.06850558299602505</v>
       </c>
     </row>
     <row r="54">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -3518,37 +3518,37 @@
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>17.86</v>
+        <v>19.33</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.004612483574357285</v>
+        <v>-0.001652785905264076</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.05900942881439086</v>
+        <v>0.001139548732774331</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.0945959260711432</v>
+        <v>0.01517854745791714</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.1245097576311478</v>
+        <v>-0.01226428372037169</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.02969162971373285</v>
+        <v>-0.03451548296409979</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0.1093167818124716</v>
+        <v>0.06760568692259383</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1545561841253699</v>
+        <v>-0.07343879260971942</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.2021442739451919</v>
+        <v>-0.1751713963306958</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.01788769082980957</v>
+        <v>0.1890677412042223</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.005927360589861985</v>
+        <v>0.05942170342945396</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>41.82</v>
+        <v>241.53</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.01344656058106508</v>
+        <v>-0.005353552040337495</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.02924795920788892</v>
+        <v>-0.04635371459359428</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.009708734356060011</v>
+        <v>-0.04169970951754587</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.05619502598272785</v>
+        <v>-0.1860277362021686</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.05486091503684953</v>
+        <v>-0.1457170329308554</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.09750233941896469</v>
+        <v>-0.0886948117199039</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.003063324963433978</v>
+        <v>0.03184904371384323</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.005525645308310345</v>
+        <v>0.08418105166228451</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.4034895775856706</v>
+        <v>1.105548028889097</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.1196176356295529</v>
+        <v>0.2817059019237216</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>242.83</v>
+        <v>51.78</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.01272566595126878</v>
+        <v>-0.001542650021464143</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.0398940234498607</v>
+        <v>0.0007730401919705532</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.05336811074745351</v>
+        <v>-0.04623323068525842</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.1816466388961139</v>
+        <v>-0.07137732535941177</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.1324678458134141</v>
+        <v>0.04290024547749027</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.0837898329105039</v>
+        <v>-0.0505222198579387</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.02710283757678944</v>
+        <v>-0.1711762276393455</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.1009500940339547</v>
+        <v>-0.1381630255243458</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>1.110723928079363</v>
+        <v>0.04062103240604054</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.2827552806656319</v>
+        <v>0.01336103190392546</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>19.36</v>
+        <v>41.32</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.0001033529001031042</v>
+        <v>-0.01195600200020763</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.0004130012070979738</v>
+        <v>-0.04902188793359041</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.0007236232426997002</v>
+        <v>-0.02913537684340806</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.01062906538456143</v>
+        <v>-0.06747916013988431</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.03863150505425128</v>
+        <v>-0.07054432474877315</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.06937313176223858</v>
+        <v>-0.1082926766622366</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.07866384591953168</v>
+        <v>-0.02387101582374329</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.1732998073155272</v>
+        <v>-0.008815055322405785</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.183098335461201</v>
+        <v>0.3926885775079263</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.05764587792062925</v>
+        <v>0.1167381117399204</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>51.86</v>
+        <v>17.66</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.01926099688803773</v>
+        <v>-0.0111925905168252</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.03300392359708515</v>
+        <v>-0.0469454785494311</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.05657632420026681</v>
+        <v>-0.07538740396974164</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.06994257224852807</v>
+        <v>-0.1343087614154584</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.04566999340283084</v>
+        <v>-0.010361355201985</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.0490552449110897</v>
+        <v>0.09690065332020215</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.1633552372132593</v>
+        <v>-0.1610403051322993</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.1499332316697235</v>
+        <v>-0.2247541525649442</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.03322483353382544</v>
+        <v>0.006494890714234591</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.01095450514380425</v>
+        <v>0.002160293343480779</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>42.19</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.03078337216092919</v>
+        <v>-0.00518972752882374</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.08402089950492586</v>
+        <v>-0.02967739815155868</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.07295099576510755</v>
+        <v>-0.02784402834468835</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.06098378944705141</v>
+        <v>-0.1032837539309543</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.07315469678310904</v>
+        <v>-0.09627000466196522</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.1440454890838055</v>
+        <v>-0.02320215240718759</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.04008654609845175</v>
+        <v>-0.08573288394373546</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.05122508297753425</v>
+        <v>-0.1468586283728652</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.8219951635772791</v>
+        <v>0.2672795372455261</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.2213751321238757</v>
+        <v>0.08215833161585073</v>
       </c>
     </row>
     <row r="60">
@@ -3840,51 +3840,51 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>98.27</v>
+        <v>41.77</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.001929742465701656</v>
+        <v>-0.009954922555494572</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.04823247803325514</v>
+        <v>-0.1206315693102384</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.04415913844312558</v>
+        <v>-0.0493854855886654</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.09860576344719318</v>
+        <v>-0.07033162310146013</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.08530714580524135</v>
+        <v>-0.1308780843902132</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.01810639211999665</v>
+        <v>-0.1525664499510025</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.08343388171695931</v>
+        <v>-0.01940475730978464</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.147575916727927</v>
+        <v>-0.04819558618860043</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2460943595571989</v>
+        <v>0.7869670557500501</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.07609424819162958</v>
+        <v>0.2134973958105137</v>
       </c>
     </row>
     <row r="61">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>90.05</v>
+        <v>89.12</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.005695802222646984</v>
+        <v>-0.01032759881908329</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.04110318879594499</v>
+        <v>-0.02119714706740494</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.04900199883846923</v>
+        <v>-0.03508009790340338</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.08837817205327569</v>
+        <v>-0.09779303656702887</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.0696448769921626</v>
+        <v>-0.08208872069138395</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.02910976045822133</v>
+        <v>-0.03913672534957258</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.1171276444393115</v>
+        <v>-0.1241955079201608</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.2027692998101592</v>
+        <v>-0.2003103014310793</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1052128102063952</v>
+        <v>0.1253721772454361</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.03390817680882896</v>
+        <v>0.04015658923157406</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>46.22</v>
+        <v>45.09</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.01972429003348686</v>
+        <v>-0.02444831324688668</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.03788508867900464</v>
+        <v>-0.08223083304895862</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.02837919871309103</v>
+        <v>-0.03777209634463108</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.1106407516825185</v>
+        <v>-0.1323840851744</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2666983640195665</v>
+        <v>-0.2808612503360676</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1654026664995125</v>
+        <v>-0.1858071635439488</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.03386285381935006</v>
+        <v>-0.05213368842014432</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.1062710045747151</v>
+        <v>0.06469897939054547</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1857862558352184</v>
+        <v>-0.1889312581629585</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.06621661313286287</v>
+        <v>-0.06742044945984382</v>
       </c>
     </row>
   </sheetData>
@@ -4203,17 +4203,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,12 +4473,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4602,21 +4602,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.09963105824121343</v>
+        <v>0.1064324387524365</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1816466388961139</v>
+        <v>-0.1860277362021686</v>
       </c>
     </row>
     <row r="18">
@@ -4647,21 +4647,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.07191531570999188</v>
+        <v>0.09533072602796233</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1439459630855655</v>
+        <v>-0.154885084241507</v>
       </c>
     </row>
     <row r="19">
@@ -4692,21 +4692,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.07090365432759693</v>
+        <v>0.08650628587307674</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1280015905541002</v>
+        <v>-0.1343087614154584</v>
       </c>
     </row>
     <row r="20">
@@ -4737,21 +4737,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.05878424173305485</v>
+        <v>0.07300344669800185</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1245097576311478</v>
+        <v>-0.1323840851744</v>
       </c>
     </row>
     <row r="21">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.04634876194695159</v>
+        <v>0.0462375900441534</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.1106407516825185</v>
+        <v>-0.1172169071056525</v>
       </c>
     </row>
     <row r="22">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.04154096554478648</v>
+        <v>0.03528750335037323</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.1070975671090898</v>
+        <v>-0.1166033069533797</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.0319782698090465</v>
+        <v>0.02039258780243292</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.09860576344719318</v>
+        <v>-0.1032837539309543</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02459644036852726</v>
+        <v>0.01886414605461462</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.09506741219180892</v>
+        <v>-0.09813961401305826</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01876939180045745</v>
+        <v>0.01412376244083147</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.08837817205327569</v>
+        <v>-0.09779303656702887</v>
       </c>
     </row>
     <row r="26">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.01344244593291499</v>
+        <v>0.01405624043501041</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.07920365151839048</v>
+        <v>-0.09485130370258577</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3067971354448489</v>
+        <v>0.2880007395114283</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2666983640195665</v>
+        <v>-0.2808612503360676</v>
       </c>
     </row>
     <row r="32">
@@ -5158,21 +5158,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2488986532438622</v>
+        <v>0.278565489269931</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.2161884508517007</v>
+        <v>-0.2395969346447389</v>
       </c>
     </row>
     <row r="33">
@@ -5203,21 +5203,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2418831631272345</v>
+        <v>0.2672315379802321</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1583589342287438</v>
+        <v>-0.1707085133319856</v>
       </c>
     </row>
     <row r="34">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2343570410373244</v>
+        <v>0.2383446266081919</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1468886733061159</v>
+        <v>-0.1636419026692182</v>
       </c>
     </row>
     <row r="35">
@@ -5293,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.1990436027610614</v>
+        <v>0.2261853333931783</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1324678458134141</v>
+        <v>-0.1622469389514478</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1791219597733285</v>
+        <v>0.1828014961408135</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.1265565829922446</v>
+        <v>-0.1457170329308554</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1763088944842233</v>
+        <v>0.1732590006871197</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.1202335526322232</v>
+        <v>-0.1308780843902132</v>
       </c>
     </row>
     <row r="38">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1759647336391776</v>
+        <v>0.1717497800027015</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.08530714580524135</v>
+        <v>-0.1235594495153345</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1758694715100022</v>
+        <v>0.1388649407013791</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.08464488553435234</v>
+        <v>-0.09863859472814485</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1735150737858984</v>
+        <v>0.1303607117486181</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.08106499479986806</v>
+        <v>-0.09856779485296741</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5396800871272862</v>
+        <v>0.5542996907197371</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1654026664995125</v>
+        <v>-0.1858071635439488</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5217557692947976</v>
+        <v>0.5478114577029365</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1440454890838055</v>
+        <v>-0.1525664499510025</v>
       </c>
     </row>
     <row r="47">
@@ -5714,21 +5714,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4585319851826828</v>
+        <v>0.4689503431084561</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.09750233941896469</v>
+        <v>-0.1082926766622366</v>
       </c>
     </row>
     <row r="48">
@@ -5759,21 +5759,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4510046386886166</v>
+        <v>0.4613918263290848</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.0837898329105039</v>
+        <v>-0.0886948117199039</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4427481390246546</v>
+        <v>0.434605652993193</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.05353203629562964</v>
+        <v>-0.0656264532230405</v>
       </c>
     </row>
     <row r="50">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3980327337732998</v>
+        <v>0.3996075804743275</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.0490552449110897</v>
+        <v>-0.0505222198579387</v>
       </c>
     </row>
     <row r="51">
@@ -5894,21 +5894,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3517494381109427</v>
+        <v>0.3576643984932117</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.0420494290793787</v>
+        <v>-0.04859573026417241</v>
       </c>
     </row>
     <row r="52">
@@ -5939,21 +5939,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3510651819759862</v>
+        <v>0.3464631453954115</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.02910976045822133</v>
+        <v>-0.03913672534957258</v>
       </c>
     </row>
     <row r="53">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.3242387248161223</v>
+        <v>0.3113687063045119</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.02784526677421439</v>
+        <v>-0.03668507950082012</v>
       </c>
     </row>
     <row r="54">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2948757343675816</v>
+        <v>0.265543782104781</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.02565209744562058</v>
+        <v>-0.03161835124928203</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.888888823479131</v>
+        <v>0.8672350612030073</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2056912231848654</v>
+        <v>-0.2433099749630583</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7849135491648447</v>
+        <v>0.7703446987156328</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2027692998101592</v>
+        <v>-0.2247541525649442</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7280740205045306</v>
+        <v>0.7285678266870388</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.2021442739451919</v>
+        <v>-0.2003103014310793</v>
       </c>
     </row>
     <row r="62">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6821220278900557</v>
+        <v>0.6561593743991105</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1732998073155272</v>
+        <v>-0.1751713963306958</v>
       </c>
     </row>
     <row r="63">
@@ -6315,21 +6315,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6465422588355743</v>
+        <v>0.6415816979483882</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6337,21 +6337,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1499332316697235</v>
+        <v>-0.1468586283728652</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5919514080808357</v>
+        <v>0.601541656711843</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6382,21 +6382,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.147575916727927</v>
+        <v>-0.1381630255243458</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.5877593100086718</v>
+        <v>0.5881436758635528</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6427,21 +6427,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.07629164950685829</v>
+        <v>-0.06418050984005097</v>
       </c>
     </row>
     <row r="66">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.5212879832317272</v>
+        <v>0.5798669716741409</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6472,21 +6472,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.04486435963866775</v>
+        <v>-0.05797912635149827</v>
       </c>
     </row>
     <row r="67">
@@ -6495,21 +6495,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5068486175136178</v>
+        <v>0.5043649900737419</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.04177250542049249</v>
+        <v>-0.05539628262744811</v>
       </c>
     </row>
     <row r="68">
@@ -6540,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.5038898470023632</v>
+        <v>0.4916270348880665</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.03854679097082969</v>
+        <v>-0.04819558618860043</v>
       </c>
     </row>
     <row r="69"/>
@@ -6646,21 +6646,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.779410701995538</v>
+        <v>2.742928881789077</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1857862558352184</v>
+        <v>-0.1889312581629585</v>
       </c>
     </row>
     <row r="74">
@@ -6691,21 +6691,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.625610142954565</v>
+        <v>2.661377939505551</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>-0.005640748227042303</v>
+        <v>-0.004663461579780148</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.349785648617388</v>
+        <v>2.280683146875289</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.01788769082980957</v>
+        <v>0.006494890714234591</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.802197817553022</v>
+        <v>1.797445231815515</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.03322483353382544</v>
+        <v>0.04062103240604054</v>
       </c>
     </row>
     <row r="77">
@@ -6826,21 +6826,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.381954101094161</v>
+        <v>1.426218458647355</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1052128102063952</v>
+        <v>0.1253721772454361</v>
       </c>
     </row>
     <row r="78">
@@ -6871,21 +6871,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.341664938914357</v>
+        <v>1.343468110364328</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1236556672742395</v>
+        <v>0.1280478896957253</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.276023171896981</v>
+        <v>1.327840184342412</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1460139937736749</v>
+        <v>0.1401183170468256</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.256969292594426</v>
+        <v>1.303779747802547</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1576463626548306</v>
+        <v>0.1658979197323516</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.15285384895101</v>
+        <v>1.210385912126526</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,21 +7028,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1769708364597096</v>
+        <v>0.1890677412042223</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.110723928079363</v>
+        <v>1.105548028889097</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,21 +7073,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.183098335461201</v>
+        <v>0.1904279733129086</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -489,15 +489,15 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>15.33</v>
+        <v>15.3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.001960766836418548</v>
+        <v>-0.001956929753456849</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.05950916311388843</v>
+        <v>-0.04968945166334415</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.0294397056246799</v>
+        <v>-0.07720143177691152</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.07300344669800185</v>
+        <v>0.07090365432759693</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.278565489269931</v>
+        <v>0.2613355355635998</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4613918263290848</v>
+        <v>0.4339269054671904</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7186098422182208</v>
+        <v>0.7445837391251773</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.8672350612030073</v>
+        <v>0.9029851073791024</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1.797445231815515</v>
+        <v>1.791970828007709</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.409030944195129</v>
+        <v>0.4081112191287783</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>38.59</v>
+        <v>38.7</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.003910704577705482</v>
+        <v>0.002876468916430897</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-0.0163522450461201</v>
+        <v>0.002590732973354992</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.02726234540715045</v>
+        <v>-0.03731343212766447</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.09533072602796233</v>
+        <v>0.09849563626996449</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2880007395114283</v>
+        <v>0.2956143178981134</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3464631453954115</v>
+        <v>0.3191847091716611</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4709133554707809</v>
+        <v>0.4884404938759936</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7285678266870388</v>
+        <v>0.718548883613614</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.8383249012552301</v>
+        <v>0.8436366606808134</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2250131668733817</v>
+        <v>0.2261919062908933</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>120.59</v>
+        <v>119.46</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.01712212231021359</v>
+        <v>-0.009370572085032114</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.0944817208557025</v>
+        <v>0.076604182319153</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.07814034852930041</v>
+        <v>0.09215580621839603</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.02039258780243292</v>
+        <v>0.01083092550339759</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2383446266081919</v>
+        <v>0.2455426391738014</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5478114577029365</v>
+        <v>0.5540522286475964</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4745715259416736</v>
+        <v>0.4620044017386222</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4016135344001139</v>
+        <v>0.3928473832063351</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.327840184342412</v>
+        <v>1.306026820281405</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3253107488723539</v>
+        <v>0.3211580784724306</v>
       </c>
     </row>
     <row r="5">
@@ -760,51 +760,51 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>199.7</v>
+        <v>100.3</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.03220135260366352</v>
+        <v>-0.006930662853882996</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.0298591778494417</v>
+        <v>0.061600333277265</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.03621832546350778</v>
+        <v>0.07226857034494993</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.1064324387524365</v>
+        <v>0.007028158517679017</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.2672315379802321</v>
+        <v>0.1799041915630237</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2001031604227101</v>
+        <v>0.559082504636681</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5626442979055615</v>
+        <v>0.3878113702905515</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5798669716741409</v>
+        <v>0.3366779797503259</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.4272958127873328</v>
+        <v>1.195066655847051</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1259125600507398</v>
+        <v>0.2996185578816568</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>101</v>
+        <v>191.8</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.009495221581859781</v>
+        <v>-0.03955930904962346</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.07435376773675939</v>
+        <v>-0.01646065096917682</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.04989608320196015</v>
+        <v>-0.007040798222030409</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.01405624043501041</v>
+        <v>0.06266273596530025</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1717497800027015</v>
+        <v>0.2263159784328941</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.5542996907197371</v>
+        <v>0.1562090215505252</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.3963408562754096</v>
+        <v>0.5599186521448438</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3412066904150675</v>
+        <v>0.4709670828269126</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.210385912126526</v>
+        <v>0.3708325281248597</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3026348753094534</v>
+        <v>0.1108654690324271</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>154.03</v>
+        <v>545.5599999999999</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.02265232986015164</v>
+        <v>0.006364044751534959</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.04878647720500962</v>
+        <v>-0.05002695775300836</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.05734391350787615</v>
+        <v>-0.008937623682457541</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.02147261803047729</v>
+        <v>-0.07189277200344768</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1303607117486181</v>
+        <v>-0.1143506533139712</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.265543782104781</v>
+        <v>0.3849512057317142</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2592908395087217</v>
+        <v>0.5549740501471869</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.6561593743991105</v>
+        <v>0.7813793946667562</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.010156612641044</v>
+        <v>2.766749048694595</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.262050204795343</v>
+        <v>0.5559258484485829</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>542.11</v>
+        <v>154.18</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.001126473410087758</v>
+        <v>0.0009737966478808868</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.05511302562810694</v>
+        <v>-0.03262650299737835</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.005704092877507394</v>
+        <v>-0.06766646170290191</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.07776193631232486</v>
+        <v>-0.02051973134605567</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-0.1622469389514478</v>
+        <v>0.1403231980700927</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.3996075804743275</v>
+        <v>0.2455115359097158</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.5409373924625152</v>
+        <v>0.2690919440241772</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7703446987156328</v>
+        <v>0.6522900142346602</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>2.742928881789077</v>
+        <v>1.012114296751981</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.5526391226230247</v>
+        <v>0.2624597738780301</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>28.19</v>
+        <v>28.02</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.005643733518842842</v>
+        <v>-0.006030509864253464</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.03525527021519914</v>
+        <v>0.02412280090236552</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.009670503475138537</v>
+        <v>0.02113702304729115</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.008092876200523902</v>
+        <v>-0.01407458189501998</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2261853333931783</v>
+        <v>0.2376325624184912</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.434605652993193</v>
+        <v>0.4317833875681802</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2573595199878991</v>
+        <v>0.2393843198696577</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2031583511260275</v>
+        <v>0.2005141505818231</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4434203555012552</v>
+        <v>0.4347157948091407</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1301366048602857</v>
+        <v>0.1278602562140609</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>32.53</v>
+        <v>152.76</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.02618290209405205</v>
+        <v>-0.002347812707526264</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.02424428667713996</v>
+        <v>-0.009078266619024222</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.02102944620558556</v>
+        <v>0.003550760884492465</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.08650628587307674</v>
+        <v>-0.01906824479632951</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1828014961408135</v>
+        <v>-0.0132872388929528</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.1062429465619632</v>
+        <v>0.3292459177681686</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.3850179913355412</v>
+        <v>0.4504629318736142</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4396713295007013</v>
+        <v>0.4973146093328655</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3344007440996397</v>
+        <v>1.298306581237188</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1009360473471599</v>
+        <v>0.3196820823817219</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>153.12</v>
+        <v>202.4</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.004884454580921016</v>
+        <v>0.001980167804378041</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.009160704360899663</v>
+        <v>-0.01498432862138721</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.008923329940815794</v>
+        <v>-0.05327002427548266</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.01673214989612404</v>
+        <v>0.02093659187769403</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-0.03774918653418013</v>
+        <v>0.1806513781000754</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3576643984932117</v>
+        <v>0.2120810003030091</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4443726787031128</v>
+        <v>0.2050871639298211</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5043649900737419</v>
+        <v>0.4389548693071346</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.303779747802547</v>
+        <v>0.6121355425246851</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3207288116002232</v>
+        <v>0.172556695648862</v>
       </c>
     </row>
     <row r="12">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>202</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.01270775183750572</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.02570781741176997</v>
+        <v>-0.03649738589779272</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.04183667117824597</v>
+        <v>-0.06548202357970712</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.01886414605461462</v>
+        <v>-0.05903074448075463</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1732590006871197</v>
+        <v>0.1101730493201691</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2215333129963934</v>
+        <v>0.2445531689244806</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.194914559677887</v>
+        <v>0.2029936396322982</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4391281310829853</v>
+        <v>0.4615261457997</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.608863222577485</v>
+        <v>0.6302694228961416</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.171762804647045</v>
+        <v>0.1769367600945135</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>411.51</v>
+        <v>479.8</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.02350398513757646</v>
+        <v>-0.001436039158838054</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.03980679297907019</v>
+        <v>-0.03197822313869714</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.03600542293239262</v>
+        <v>0.005659152494052355</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.023307092112126</v>
+        <v>-0.1184846181958088</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-0.009173643194173131</v>
+        <v>-0.1945229293301994</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1088028570892909</v>
+        <v>0.4393636805908152</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4109824534931819</v>
+        <v>0.4884505127467167</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6415816979483882</v>
+        <v>0.5709400658967883</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2140504490939386</v>
+        <v>1.422734313932842</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.06678993937215227</v>
+        <v>0.3430801488262034</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>66.79000000000001</v>
+        <v>399.85</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.01634757857742475</v>
+        <v>-0.02833467810114831</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.05100875927806714</v>
+        <v>-0.06870851189154892</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.04721822582943003</v>
+        <v>-0.08413115946319316</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.05903074448075463</v>
+        <v>-0.05098137126080349</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.1085163602828634</v>
+        <v>-0.01560844998592792</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.2569401430341562</v>
+        <v>0.07322113493574167</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.193998568587276</v>
+        <v>0.433571250070572</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.4612084034473258</v>
+        <v>0.563315060253794</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6302691192992578</v>
+        <v>0.1796508266289532</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.176936687036169</v>
+        <v>0.05661756358758807</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>480.49</v>
+        <v>30.7</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.01236777880741857</v>
+        <v>-0.05625570504238975</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.03123113917665543</v>
+        <v>-0.03671164246891456</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.01598544747779718</v>
+        <v>-0.03912362973868666</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.1172169071056525</v>
+        <v>0.02538410872829866</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>-0.2395969346447389</v>
+        <v>0.1239829041302822</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.4689503431084561</v>
+        <v>0.04330810177613942</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.482828989080065</v>
+        <v>0.3538869768585826</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.5881436758635528</v>
+        <v>0.3188039355571002</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1.426218458647355</v>
+        <v>0.2593330894312251</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.3437236702349282</v>
+        <v>0.07989170422778313</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>106.58</v>
+        <v>106.19</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.004429377231171872</v>
+        <v>-0.003677972267602359</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.04146056757918404</v>
+        <v>-0.04421237625152807</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.01624510399046786</v>
+        <v>-0.03693087717484622</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.01278248670915794</v>
+        <v>-0.01641344534513289</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.04051134250829602</v>
+        <v>-0.03841344519979961</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.2072950079837277</v>
+        <v>0.1847373289525529</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.272925203540952</v>
+        <v>0.2721324571104753</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4916270348880665</v>
+        <v>0.4806329512110303</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.7307783752160275</v>
+        <v>0.7244125135270734</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.200642798025219</v>
+        <v>0.1991689879651266</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>84.59</v>
+        <v>84.19</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.01202997402067385</v>
+        <v>-0.004728619385283128</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.1037296164487099</v>
+        <v>-0.1163009823876858</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.0521066969653835</v>
+        <v>-0.06351500542331978</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.01295216627629447</v>
+        <v>-0.01761953979704212</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.05492200667438984</v>
+        <v>-0.05918145275804265</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1111068798678783</v>
+        <v>0.07393973415228849</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.2633453153509255</v>
+        <v>0.2652840325620285</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.601541656711843</v>
+        <v>0.6090983643848624</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.343468110364328</v>
+        <v>1.332386988119676</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3282699555765642</v>
+        <v>0.3261730659210462</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>57.06</v>
+        <v>56.67</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.009718805431700006</v>
+        <v>-0.006834966613377236</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.001931529567654522</v>
+        <v>0.001059502989795735</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.006442607172534198</v>
+        <v>-0.0147420931224147</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.00157480577751401</v>
+        <v>-0.006122212774156477</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.06574524463152964</v>
+        <v>0.06506872542051201</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.3113687063045119</v>
+        <v>0.2988556095590569</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1700709789728958</v>
+        <v>0.186205151999977</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1931134617553598</v>
+        <v>0.1996158826019399</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1904279733129086</v>
+        <v>0.1850063044469983</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.05982552406346553</v>
+        <v>0.05821412364898126</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>55.3</v>
+        <v>54.73</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.003244417928279675</v>
+        <v>-0.01030740872853797</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.01197073376862368</v>
+        <v>-0.02598325538628277</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.01002508713161809</v>
+        <v>-0.01899984505997743</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.006186320201085005</v>
+        <v>-0.004184853458291005</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.09969906617206403</v>
+        <v>0.09391479183647333</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.1002267156183776</v>
+        <v>0.08680458579002015</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2328751733450765</v>
+        <v>0.2392000548638837</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2575536603921549</v>
+        <v>0.2417220569195919</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.6889548553003115</v>
+        <v>0.6715466915246646</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.190892829786232</v>
+        <v>0.1867871557646061</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>94.13</v>
+        <v>92.8</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.0001062474643649391</v>
+        <v>-0.01412933432983676</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.043491578593847</v>
+        <v>-0.06705537435498754</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.005704034287226656</v>
+        <v>-0.04947244020834041</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.0462375900441534</v>
+        <v>0.03145494934597681</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.1039052534203659</v>
+        <v>0.06373229394927948</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.00932870573943001</v>
+        <v>-0.01674077397372398</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1174265385618265</v>
+        <v>0.1018977200779767</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3452558653876978</v>
+        <v>0.3543029118084566</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>2.280683146875289</v>
+        <v>2.234329277862827</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.4858949129584329</v>
+        <v>0.4788634563006329</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>92.70999999999999</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.006004048233611448</v>
+        <v>-0.01919964186036749</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.05878173518301877</v>
+        <v>-0.09169913344528091</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.01675683334089884</v>
+        <v>-0.07863007340422046</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.03528750335037323</v>
+        <v>0.01541035406353219</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.06771549529769483</v>
+        <v>0.02045721681367141</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>-0.01550522248643715</v>
+        <v>-0.04323412599978393</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1410180714078737</v>
+        <v>0.1252680782836268</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.3926585098373956</v>
+        <v>0.4085658374378764</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>2.661377939505551</v>
+        <v>2.591080794351594</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.5412799191764606</v>
+        <v>0.5313521011213993</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>74.05</v>
+        <v>64.86</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.0008095743907654551</v>
+        <v>-0.006083407306659017</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.003498782335861761</v>
+        <v>0.01127221047137383</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01969154848652344</v>
+        <v>0.01142993513765211</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.04978823608653671</v>
+        <v>0.002209482988289491</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.03119284730616978</v>
+        <v>0.07275400584532443</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.1870644844602858</v>
+        <v>0.2278900732497411</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1207889359950836</v>
+        <v>0.08877869551046658</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1785052168553065</v>
+        <v>0.005026121836966713</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.8426922391261136</v>
+        <v>0.9580714463714617</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2259824941207174</v>
+        <v>0.2510543523154907</v>
       </c>
     </row>
     <row r="23">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>67.95</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.00278841272539132</v>
+        <v>-0.01769081882512069</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.006579014146168682</v>
+        <v>-0.009666427691929935</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.01493652047173488</v>
+        <v>-0.02020474196069488</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.05190458093683903</v>
+        <v>-0.0665982602474281</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.03366489188600741</v>
+        <v>0.009317220268754589</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.1884125287709617</v>
+        <v>0.1596331812888743</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1038264721531239</v>
+        <v>0.1052337072634091</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1507618433085884</v>
+        <v>0.1698347979514161</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.9120210000799687</v>
+        <v>0.8100931609213951</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2411689029915927</v>
+        <v>0.2187098160723118</v>
       </c>
     </row>
     <row r="24">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>144.96</v>
+        <v>143.86</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.004805690859832623</v>
+        <v>-0.007588341974120505</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.01321031168584064</v>
+        <v>0.009958602234911629</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.007926570237745123</v>
+        <v>-0.002945685655555752</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.005420194072952356</v>
+        <v>-0.009512994561466703</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.07361873890440718</v>
+        <v>0.0628247415172789</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1272989687932484</v>
+        <v>0.1162668746700368</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.06991808004187727</v>
+        <v>0.07425893238954817</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1283713305449787</v>
+        <v>0.1360688812798909</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.6480999730495092</v>
+        <v>0.6413180356185519</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1812120011485034</v>
+        <v>0.1795895430639114</v>
       </c>
     </row>
     <row r="25">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>65.26000000000001</v>
+        <v>104.96</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.005070831586602376</v>
+        <v>-0.005589805307687601</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.02108278310906253</v>
+        <v>0.03073747615767419</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.02140242817514282</v>
+        <v>0.01489074591755091</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.008303449966874821</v>
+        <v>0.008455008050887614</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.05690486702344888</v>
+        <v>0.1487358643906684</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2502658311212105</v>
+        <v>0.2357819853062377</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.09760980293586319</v>
+        <v>-0.01251359135298524</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.01066743801176351</v>
+        <v>-0.06866855776457437</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.9699775627457745</v>
+        <v>0.4915274799772715</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2535849222231465</v>
+        <v>0.1425549242786122</v>
       </c>
     </row>
     <row r="26">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>105.55</v>
+        <v>288.66</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.01022127104397219</v>
+        <v>-0.004277303416631906</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.02815117169838066</v>
+        <v>0.002535376671058076</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.005933294891761864</v>
+        <v>0.004419043630397024</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.01412376244083147</v>
+        <v>-0.009334893181146886</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.1388649407013791</v>
+        <v>0.06678002723224985</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.2539469511278241</v>
+        <v>0.1870220098532702</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.001705948024808279</v>
+        <v>0.07733074954059616</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.06418050984005097</v>
+        <v>0.01985583291238324</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.4999116943272848</v>
+        <v>0.7275720269834645</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1446917788322306</v>
+        <v>0.1999009239922773</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>289.9</v>
+        <v>66.78</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.0095999372779354</v>
+        <v>-0.01721851687258358</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.007962201111072931</v>
+        <v>-0.01315205281115062</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.009611963179099403</v>
+        <v>-0.02297000336318455</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.00507931553822083</v>
+        <v>-0.06822937790679728</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.06887394953066361</v>
+        <v>0.01005906193737283</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.2074135215619204</v>
+        <v>0.1611219799246204</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.08434631486126687</v>
+        <v>0.08916568587077167</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.02091844844398061</v>
+        <v>0.1422815921780292</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.7349931189791068</v>
+        <v>0.8790990359326392</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2016165987372647</v>
+        <v>0.234003969091638</v>
       </c>
     </row>
     <row r="28">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>131.54</v>
+        <v>130.48</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.004032770520857598</v>
+        <v>-0.008090267446426269</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.008645008804722298</v>
+        <v>0.008469582906005524</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.00853696308573737</v>
+        <v>-0.02162718233806615</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.01396247893337632</v>
+        <v>-0.02192049827383513</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.08899749258979028</v>
+        <v>0.07330626907711557</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1004768258232878</v>
+        <v>0.08398166544282049</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.04640448314354151</v>
+        <v>0.04441134421732307</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1125566591222267</v>
+        <v>0.1162527244264213</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6331321543610906</v>
+        <v>0.6199519311148418</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1776252523662063</v>
+        <v>0.1744486759812547</v>
       </c>
     </row>
     <row r="29">
@@ -2118,37 +2118,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>91.54000000000001</v>
+        <v>90.94</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.009628901727901429</v>
+        <v>-0.006554494954339907</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.01823248592010918</v>
+        <v>-0.008568867465726715</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02957702598717471</v>
+        <v>-0.02650658378906456</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.04056181320658458</v>
+        <v>-0.04130136772556303</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.002409124194462597</v>
+        <v>0.002514763089131566</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.05577957817146628</v>
+        <v>0.04942849551155071</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1094447501492641</v>
+        <v>0.1150813745384149</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1101463728045884</v>
+        <v>0.1194005265452311</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.3992988071300927</v>
+        <v>0.3982199443465744</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1185021450087327</v>
+        <v>0.1182146151426251</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>81.81999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.009922552043568067</v>
+        <v>-0.006381550725942264</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01386044966806577</v>
+        <v>0.00371396757153386</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.01338478965714274</v>
+        <v>-0.02551797349249307</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.06427267371530565</v>
+        <v>-0.01640331216427393</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.05421341261812396</v>
+        <v>0.00371396757153386</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.1228818444045428</v>
+        <v>0.02076858316005437</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.08854350322605131</v>
+        <v>0.1024784316790532</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.1614648111493924</v>
+        <v>0.0959169822961834</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.3972054226518291</v>
+        <v>0.222218477413163</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1179440979799928</v>
+        <v>0.06917701803352849</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>185.23</v>
+        <v>23.03</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.01927251275349451</v>
+        <v>0.006996057784905307</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.04169899031794311</v>
+        <v>-0.03397648744790194</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.03218560887065114</v>
+        <v>-0.0132818964831074</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.03107183396087498</v>
+        <v>-0.05304272304136781</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.006383448412695447</v>
+        <v>-0.06579868588936899</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.1512925260650508</v>
+        <v>-0.03336931873902971</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.04530963011439715</v>
+        <v>0.1368490260801021</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.06130703060665388</v>
+        <v>0.2500481928459248</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.9966613843905656</v>
+        <v>0.5459328296843202</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.2592195940874382</v>
+        <v>0.1562814010456171</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>73.65000000000001</v>
+        <v>174.24</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.01008064495454508</v>
+        <v>0.008508428456046824</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.006206977205292397</v>
+        <v>-0.03269860228716648</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.01904635415957467</v>
+        <v>-0.007349132883859855</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.01590051937788828</v>
+        <v>-0.07255011432518255</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.006697619453828851</v>
+        <v>-0.0894079313821925</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.02255348636984178</v>
+        <v>0.04418422680072043</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.09663698248019181</v>
+        <v>0.141784893153706</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1015866759570048</v>
+        <v>0.1812893948720071</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.2228430241174928</v>
+        <v>0.830761183638574</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.06935910148494262</v>
+        <v>0.2233307674023457</v>
       </c>
     </row>
     <row r="33">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2342,37 +2342,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>102.22</v>
+        <v>80.16</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.005738705883679973</v>
+        <v>-0.02028838962241952</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01493683600756723</v>
+        <v>-0.01675646194740155</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.004770692903682483</v>
+        <v>-0.03575577081439918</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.08298196733384455</v>
+        <v>-0.08118911695098474</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.1235594495153345</v>
+        <v>-0.06688932112090884</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.1687727788992155</v>
+        <v>0.09008308269705489</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.09839361067822971</v>
+        <v>0.07242640443010062</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.208442532601038</v>
+        <v>0.1404030793296642</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3479977853613512</v>
+        <v>0.3719462416306141</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.104662792450219</v>
+        <v>0.1111662232473485</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>22.86</v>
+        <v>13.1</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.001964211112774339</v>
+        <v>0.002295385412854234</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.04887691762317081</v>
+        <v>0.003062784116985684</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.02244547380204798</v>
+        <v>-0.01799098713440461</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.05982730024522609</v>
+        <v>-0.02019442830220075</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.07919140776463374</v>
+        <v>0.05800837712642881</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-0.02146910502609611</v>
+        <v>0.1064216104408258</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.119343881209822</v>
+        <v>-0.02861840430406815</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2311790365745421</v>
+        <v>-0.04846433659906335</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.5348566312316507</v>
+        <v>0.1427352329358347</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1535132964453805</v>
+        <v>0.04547874035489552</v>
       </c>
     </row>
     <row r="35">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2454,37 +2454,37 @@
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>226.25</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.003281475372221898</v>
+        <v>-0.002427851715159246</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.03084170932689489</v>
+        <v>-0.05313810962893339</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.02980273172895753</v>
+        <v>-0.05938598889371416</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.03919651730509877</v>
+        <v>-0.07151408537477688</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.04314387618392035</v>
+        <v>-0.1608820025301728</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.02483048072243066</v>
+        <v>-0.02052134137339157</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1057513759697264</v>
+        <v>0.1166970894565411</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1081815413788563</v>
+        <v>0.3566200503106649</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3273887168127532</v>
+        <v>0.2396187412846089</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.09900425504782651</v>
+        <v>0.07422695207545926</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>172.77</v>
+        <v>108.77</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.001271756828239545</v>
+        <v>-0.006122128868724763</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.05055776714033167</v>
+        <v>-0.08742348842103864</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.01538722818407101</v>
+        <v>-0.08948604154807605</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.08037468056198993</v>
+        <v>-0.07145298608667805</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.09863859472814485</v>
+        <v>-0.08787054796540705</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.05041291400638381</v>
+        <v>-0.01419391392861813</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.1289121792627179</v>
+        <v>0.08062247949582524</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.166851684025527</v>
+        <v>0.2371669333063049</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.8153154088387855</v>
+        <v>1.075387329084841</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.21988071234443</v>
+        <v>0.2755565590850768</v>
       </c>
     </row>
     <row r="37">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2566,37 +2566,37 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>13.07</v>
+        <v>181.16</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.0007645434969545395</v>
+        <v>-0.02197264028130941</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.005327294267089333</v>
+        <v>-0.05205674707928132</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.02097383360633898</v>
+        <v>-0.04803293448679624</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.02243830914754852</v>
+        <v>-0.04977581195832825</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.06231956213318002</v>
+        <v>-0.03246673552334967</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.1091949655329314</v>
+        <v>0.1182305503266297</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-0.034130532775274</v>
+        <v>0.02515424586048431</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>-0.05797912635149827</v>
+        <v>0.04344959412036786</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.1401183170468256</v>
+        <v>0.9581184550551072</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.04468006568450034</v>
+        <v>0.2510643638581838</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>109.44</v>
+        <v>100.16</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.006626084593553516</v>
+        <v>-0.02015258788880281</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.08761979803443387</v>
+        <v>-0.01957713320581833</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.05467732905941369</v>
+        <v>-0.03114716267031181</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.06573328485882368</v>
+        <v>-0.1014622538327663</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.09214225837882006</v>
+        <v>-0.1317800194302017</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.005069587895768501</v>
+        <v>0.1324454748190746</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.08792577375195121</v>
+        <v>0.07648820822984459</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.2329112100605484</v>
+        <v>0.1764999191659793</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.088171079413132</v>
+        <v>0.3208321415179451</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.2781702125550627</v>
+        <v>0.09719177394578637</v>
       </c>
     </row>
     <row r="39">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2678,37 +2678,37 @@
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>70.02</v>
+        <v>224.7</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.0007145265326720107</v>
+        <v>-0.006850842217714037</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.0510909909972318</v>
+        <v>-0.02866037621723849</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.062776100908573</v>
+        <v>-0.05229864544946372</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.06925437300790716</v>
+        <v>-0.04577883036727171</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.1636419026692182</v>
+        <v>-0.0521757342723822</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>-0.001122336776566479</v>
+        <v>0.01103464507257246</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1085039999956519</v>
+        <v>0.1004629047707797</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.359659524412701</v>
+        <v>0.1070538930591733</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.2426357605680916</v>
+        <v>0.3182951041686624</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.07509774069095365</v>
+        <v>0.09648883308210565</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>94.09999999999999</v>
+        <v>52.75</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.002438284241163546</v>
+        <v>-0.001703257992581308</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.01907642890892347</v>
+        <v>-0.02657314381254183</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.02284532199292133</v>
+        <v>-0.02818715574253916</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.04785999463016621</v>
+        <v>-0.09967571492368299</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.02955023517161492</v>
+        <v>-0.0967093679955533</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.0410610489653096</v>
+        <v>0.04266976499602149</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.07901026443630466</v>
+        <v>0.09103421166974024</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.05487086039813516</v>
+        <v>0.1445530314718446</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.2953373997439757</v>
+        <v>0.741219967453717</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.09008651776402665</v>
+        <v>0.2030524067455757</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>52.84</v>
+        <v>93.48</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.003394951030209259</v>
+        <v>-0.006588683605111889</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.03594236765816083</v>
+        <v>-0.01537812351936396</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.02002963748206199</v>
+        <v>-0.02401331647187732</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.09813961401305826</v>
+        <v>-0.05413334387331759</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.09003501591291996</v>
+        <v>-0.03830369689899016</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.05506605698139677</v>
+        <v>0.02563267423062343</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.08687727858399596</v>
+        <v>0.07984372835264542</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1401282121561862</v>
+        <v>0.05349179173750063</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.7441907743306824</v>
+        <v>0.286802966598773</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.2037362195748551</v>
+        <v>0.08768720017938869</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>27.88</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.01064588861463134</v>
+        <v>0.000212185445330304</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.01379558863395658</v>
+        <v>-0.003733963436527765</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.0003585596665716118</v>
+        <v>-0.007509770476662569</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.1166033069533797</v>
+        <v>-0.02287173528658204</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.08470124757886943</v>
+        <v>0.03749083269213949</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.1592515611311998</v>
+        <v>0.001464248139378288</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>-0.01408787094253772</v>
+        <v>0.00811336100915705</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.09201065299061217</v>
+        <v>-0.04142079281349476</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.5615752979403377</v>
+        <v>-0.00441412101904326</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1601682519374872</v>
+        <v>-0.001473543938234734</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>70.69</v>
+        <v>62.33</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.006081689247364519</v>
+        <v>-0.001281814077119248</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.009565659024337592</v>
+        <v>-0.008431415433514888</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.007897520901864019</v>
+        <v>-0.04445809254386079</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.02311634826562015</v>
+        <v>-0.09601153604338586</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.03298701330556142</v>
+        <v>-0.04956829483060154</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.01229398759085387</v>
+        <v>0.07507054324781737</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.01007257051960408</v>
+        <v>0.02267935467080795</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-0.03373224578847522</v>
+        <v>0.0244096275258463</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>-0.004663461579780148</v>
+        <v>0.5812001394291186</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-0.001556909903741577</v>
+        <v>0.1650081082599528</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>62.41</v>
+        <v>56.66</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.01963556398046107</v>
+        <v>-0.001409972306804619</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.02132665203997175</v>
+        <v>-0.03153351317646647</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.03464813032634095</v>
+        <v>-0.02922099206119677</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.09485130370258577</v>
+        <v>-0.07961233500049048</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.04354212905031707</v>
+        <v>-0.08670130292406519</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.0906980900791543</v>
+        <v>-0.009712275375462931</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0228226314008364</v>
+        <v>0.08282909595077448</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.009066197228183803</v>
+        <v>0.1211072431913458</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5832296985599839</v>
+        <v>0.5674244850600536</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1655063462479855</v>
+        <v>0.1616149931386119</v>
       </c>
     </row>
     <row r="45">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -3014,37 +3014,37 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>56.74</v>
+        <v>27.8</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.01167040882644266</v>
+        <v>-0.00286943780897353</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.04638652641232277</v>
+        <v>-0.007851578055280473</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.02825822449784365</v>
+        <v>-0.01870810759169872</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.0824708677480116</v>
+        <v>-0.11913815882473</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.08690051117189412</v>
+        <v>-0.09239307872169156</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.005922805766242822</v>
+        <v>0.1310007861411333</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.07500128285648411</v>
+        <v>-0.02512349989027363</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.1084260359544928</v>
+        <v>0.09057193497873817</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.5625562424821804</v>
+        <v>0.5570944547388685</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1604111311415997</v>
+        <v>0.1590575119770317</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>114.03</v>
+        <v>46.93</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.009037984863869974</v>
+        <v>-0.002974280657661255</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.02250719343423269</v>
+        <v>0.0006396328000186635</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.02840910537434027</v>
+        <v>-0.03197193175940871</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.009561769457590907</v>
+        <v>-0.02310575747705268</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.01904490219142363</v>
+        <v>-0.016720302157611</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.002110003104326186</v>
+        <v>-0.0339059836033454</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>-0.01292973328813429</v>
+        <v>0.0412630696208236</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-0.02971374811199745</v>
+        <v>0.01522086368907272</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.747135535814774</v>
+        <v>0.1246924502167717</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.2044132714775819</v>
+        <v>0.03994712817282342</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>47.07</v>
+        <v>113</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.006123330063132593</v>
+        <v>-0.00903270008176027</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.006542873919427428</v>
+        <v>0.01957951938188351</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.02161714617196597</v>
+        <v>0.005159240708962232</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.02019153210277325</v>
+        <v>0.0004427007800693605</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-0.0178902408322773</v>
+        <v>0.00867138882988594</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.03161835124928203</v>
+        <v>-0.01451912521294174</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.03934067735321145</v>
+        <v>-0.02251649632633645</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.02459290072438258</v>
+        <v>-0.03458388477113894</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.1280478896957253</v>
+        <v>0.7313541845175737</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.04098030400835095</v>
+        <v>0.2007759297706435</v>
       </c>
     </row>
     <row r="48">
@@ -3182,37 +3182,37 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>83.22</v>
+        <v>82.73</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.02689424126105544</v>
+        <v>-0.005887981934415421</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.0289381075361862</v>
+        <v>-0.01862395774600722</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.03142454615668355</v>
+        <v>-0.04225508234014153</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.06441816665686007</v>
+        <v>-0.06992685558975176</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.04620811349164844</v>
+        <v>-0.04790416795736585</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.04505092124244392</v>
+        <v>0.03695383687054465</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>-0.04468562626455663</v>
+        <v>-0.04606886934270205</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.04192956673179227</v>
+        <v>-0.0466996917568383</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.3865696441013016</v>
+        <v>0.3784056346955014</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.115100205919388</v>
+        <v>0.1129073566953396</v>
       </c>
     </row>
     <row r="49">
@@ -3238,37 +3238,37 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>17.44</v>
+        <v>17.32</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.006833652365280773</v>
+        <v>-0.006880781855428064</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.04751496216605644</v>
+        <v>-0.03831207802824421</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.01160097248229142</v>
+        <v>-0.002878591939744934</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.04228438161051873</v>
+        <v>-0.04887421386019308</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.1707085133319856</v>
+        <v>-0.168107591320959</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.04859573026417241</v>
+        <v>-0.06228470535703778</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.06289871417566317</v>
+        <v>0.0660826341104912</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1899298763061976</v>
+        <v>0.1753930157796555</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.1658979197323516</v>
+        <v>0.1578756304809759</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.05249532584849415</v>
+        <v>0.05007577094350646</v>
       </c>
     </row>
     <row r="50">
@@ -3294,37 +3294,37 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>214</v>
+        <v>215.27</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.01277854047084526</v>
+        <v>0.005934599404022967</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.04263409310312016</v>
+        <v>-0.01791047726860906</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.05082944368227205</v>
+        <v>-0.0351454736227883</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.154885084241507</v>
+        <v>-0.1488841782764053</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.09856779485296741</v>
+        <v>-0.1002023214733994</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.0656264532230405</v>
+        <v>-0.0730173679945485</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.02217708270698604</v>
+        <v>0.03780151314629432</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.06574432432625499</v>
+        <v>0.068952448293506</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.9918316844690234</v>
+        <v>1.005975297298554</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.2582034707002412</v>
+        <v>0.2611745362045061</v>
       </c>
     </row>
     <row r="51">
@@ -3350,37 +3350,37 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>34.63</v>
+        <v>34.72</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.003739852120114628</v>
+        <v>0.002598907011607254</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.02752034612297782</v>
+        <v>-0.01307558500518202</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.01479375349047496</v>
+        <v>-0.01335599387176833</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.08240594785468769</v>
+        <v>-0.08002120623875819</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.09418772468079217</v>
+        <v>-0.08296299102513516</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.005244955243925209</v>
+        <v>-0.01844124418086368</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>-0.03716320773387916</v>
+        <v>-0.02522049876798294</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.01124449488387347</v>
+        <v>0.01240157559141397</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.3743480282946485</v>
+        <v>0.377919831021772</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1118142633057211</v>
+        <v>0.112776597409125</v>
       </c>
     </row>
     <row r="52">
@@ -3406,37 +3406,37 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>43.59</v>
+        <v>43.4</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.009093010016289815</v>
+        <v>-0.004358766369439993</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.03025585288694499</v>
+        <v>-0.02625080047019124</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.01912687894662157</v>
+        <v>-0.02908275648483594</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.0417674534133573</v>
+        <v>-0.045944165211522</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.04617069092179693</v>
+        <v>-0.05032821003639321</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.03668507950082012</v>
+        <v>-0.05652170595915418</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.03869165196685798</v>
+        <v>-0.04126704888850841</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.05539628262744811</v>
+        <v>-0.05775926082669358</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.2402671942562549</v>
+        <v>0.234861159320811</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.07441423122522051</v>
+        <v>0.072850917441174</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>25.68</v>
+        <v>242.29</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.03436863812194224</v>
+        <v>0.003146584319450918</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.03820226324410703</v>
+        <v>-0.01787597777325711</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.02171427408854165</v>
+        <v>-0.03165346395114987</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.0403587411983809</v>
+        <v>-0.1834665038404344</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.03769356487706221</v>
+        <v>-0.1400487915517806</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.06387198941541983</v>
+        <v>-0.1047973995082077</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.1268568707028944</v>
+        <v>0.04171937735574383</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>-0.2433099749630583</v>
+        <v>0.08289361095022119</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.219917291414796</v>
+        <v>1.112173453780401</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.06850558299602505</v>
+        <v>0.2830488547082526</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>19.33</v>
+        <v>51.9</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.001652785905264076</v>
+        <v>0.002317550201063501</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.001139548732774331</v>
+        <v>0.00973564458317977</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>0.01517854745791714</v>
+        <v>-0.04481453206262409</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.01226428372037169</v>
+        <v>-0.06776917785612335</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-0.03451548296409979</v>
+        <v>0.04149849668977801</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0.06760568692259383</v>
+        <v>-0.0626105656302699</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.07343879260971942</v>
+        <v>-0.1618386444052701</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.1751713963306958</v>
+        <v>-0.1358322406272239</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.1890677412042223</v>
+        <v>0.04466443681435428</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.05942170342945396</v>
+        <v>0.01467183023683294</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>241.53</v>
+        <v>41.32</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.005353552040337495</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.04635371459359428</v>
+        <v>-0.03772703734734439</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.04169970951754587</v>
+        <v>-0.03163811886693746</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.1860277362021686</v>
+        <v>-0.06747916013988431</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.1457170329308554</v>
+        <v>-0.07714500001320579</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.0886948117199039</v>
+        <v>-0.1139530639601356</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.03184904371384323</v>
+        <v>-0.01978876002050589</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.08418105166228451</v>
+        <v>0.00956203898576935</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1.105548028889097</v>
+        <v>0.3926883984441496</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.2817059019237216</v>
+        <v>0.1167380638786935</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>51.78</v>
+        <v>19.13</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.001542650021464143</v>
+        <v>-0.01029024874079365</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.0007730401919705532</v>
+        <v>-0.004729224180190394</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.04623323068525842</v>
+        <v>-0.002081368069431822</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.07137732535941177</v>
+        <v>-0.02242832993105515</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>0.04290024547749027</v>
+        <v>-0.03772127475751585</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.0505222198579387</v>
+        <v>0.05691159376046206</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.1711762276393455</v>
+        <v>-0.08297333790733552</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.1381630255243458</v>
+        <v>-0.1848236497390703</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.04062103240604054</v>
+        <v>0.1768319383775772</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.01336103190392546</v>
+        <v>0.05577526280303058</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>41.32</v>
+        <v>17.67</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.01195600200020763</v>
+        <v>0.0006511554363863858</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.04902188793359041</v>
+        <v>-0.01364708131803372</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.02913537684340806</v>
+        <v>-0.07984903293302348</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.06747916013988431</v>
+        <v>-0.1337500204525746</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.07054432474877315</v>
+        <v>-0.009778180684884119</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.1082926766622366</v>
+        <v>0.0864740187796158</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.02387101582374329</v>
+        <v>-0.1580991212474915</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.008815055322405785</v>
+        <v>-0.2228208911792133</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.3926885775079263</v>
+        <v>0.007144510231344325</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.1167381117399204</v>
+        <v>0.002375854256684073</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>17.66</v>
+        <v>25.15</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.0111925905168252</v>
+        <v>-0.02063865577675583</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.0469454785494311</v>
+        <v>-0.03454893070591236</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.07538740396974164</v>
+        <v>-0.06170725202333793</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.1343087614154584</v>
+        <v>-0.06016444680796018</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.010361355201985</v>
+        <v>0.008951046468235191</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.09690065332020215</v>
+        <v>0.02746767190242982</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.1610403051322993</v>
+        <v>-0.1548604881485495</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.2247541525649442</v>
+        <v>-0.2621641130839568</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.006494890714234591</v>
+        <v>0.1947398383611736</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.002160293343480779</v>
+        <v>0.06110358493415502</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>97.76000000000001</v>
+        <v>41.37</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.00518972752882374</v>
+        <v>-0.009576287323323718</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.02967739815155868</v>
+        <v>-0.1171575246897038</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.02784402834468835</v>
+        <v>-0.06656138951381718</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.1032837539309543</v>
+        <v>-0.07923439459404846</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.09627000466196522</v>
+        <v>-0.1357844191567454</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.02320215240718759</v>
+        <v>-0.1717718058058698</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.08573288394373546</v>
+        <v>-0.02089738112615291</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1468586283728652</v>
+        <v>-0.02288392444536991</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.2672795372455261</v>
+        <v>0.7698546902043528</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.08215833161585073</v>
+        <v>0.2096113976937766</v>
       </c>
     </row>
     <row r="60">
@@ -3840,51 +3840,51 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>41.77</v>
+        <v>96.8</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.009954922555494572</v>
+        <v>-0.009819957687141612</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.1206315693102384</v>
+        <v>-0.0244885641738315</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.0493854855886654</v>
+        <v>-0.04319457543025729</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.07033162310146013</v>
+        <v>-0.1120894695247249</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.1308780843902132</v>
+        <v>-0.1174463799655584</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.1525664499510025</v>
+        <v>-0.0436392718019224</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.01940475730978464</v>
+        <v>-0.0868174659113965</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.04819558618860043</v>
+        <v>-0.1520047651138274</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.7869670557500501</v>
+        <v>0.2548350299166084</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.2134973958105137</v>
+        <v>0.07860445891097867</v>
       </c>
     </row>
     <row r="61">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>89.12</v>
+        <v>88.12</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.01032759881908329</v>
+        <v>-0.01122082550696901</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.02119714706740494</v>
+        <v>-0.01601065190162754</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.03508009790340338</v>
+        <v>-0.04261936210625872</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.09779303656702887</v>
+        <v>-0.1003838963548384</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.08208872069138395</v>
+        <v>-0.09562310669175622</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.03913672534957258</v>
+        <v>-0.05409087424769932</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.1241955079201608</v>
+        <v>-0.1173760923364604</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.2003103014310793</v>
+        <v>-0.1995629430359527</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1253721772454361</v>
+        <v>0.1221404645751965</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.04015658923157406</v>
+        <v>0.03915996780300834</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>45.09</v>
+        <v>44.62</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.02444831324688668</v>
+        <v>-0.01042362428726118</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.08223083304895862</v>
+        <v>-0.06535405607221234</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.03777209634463108</v>
+        <v>-0.05606095832909319</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.1323840851744</v>
+        <v>-0.1414277874961904</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2808612503360676</v>
+        <v>-0.2634533248064126</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1858071635439488</v>
+        <v>-0.2137445122134843</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.05213368842014432</v>
+        <v>-0.0663319088284976</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.06469897939054547</v>
+        <v>0.04569957456334373</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1889312581629585</v>
+        <v>-0.1973855339990094</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.06742044945984382</v>
+        <v>-0.07067205990652825</v>
       </c>
     </row>
   </sheetData>
@@ -4203,17 +4203,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4602,21 +4602,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1064324387524365</v>
+        <v>0.09849563626996449</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1860277362021686</v>
+        <v>-0.1834665038404344</v>
       </c>
     </row>
     <row r="18">
@@ -4647,21 +4647,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.09533072602796233</v>
+        <v>0.07090365432759693</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.154885084241507</v>
+        <v>-0.1488841782764053</v>
       </c>
     </row>
     <row r="19">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.08650628587307674</v>
+        <v>0.06266273596530025</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1343087614154584</v>
+        <v>-0.1414277874961904</v>
       </c>
     </row>
     <row r="20">
@@ -4737,21 +4737,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.07300344669800185</v>
+        <v>0.03145494934597681</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1323840851744</v>
+        <v>-0.1337500204525746</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.0462375900441534</v>
+        <v>0.02538410872829866</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.1172169071056525</v>
+        <v>-0.11913815882473</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.03528750335037323</v>
+        <v>0.02093659187769403</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.1166033069533797</v>
+        <v>-0.1184846181958088</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.02039258780243292</v>
+        <v>0.01541035406353219</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.1032837539309543</v>
+        <v>-0.1120894695247249</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01886414605461462</v>
+        <v>0.01083092550339759</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.09813961401305826</v>
+        <v>-0.1014622538327663</v>
       </c>
     </row>
     <row r="25">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.01412376244083147</v>
+        <v>0.008455008050887614</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.09779303656702887</v>
+        <v>-0.1003838963548384</v>
       </c>
     </row>
     <row r="26">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.01405624043501041</v>
+        <v>0.007028158517679017</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.09485130370258577</v>
+        <v>-0.09967571492368299</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2880007395114283</v>
+        <v>0.2956143178981134</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2808612503360676</v>
+        <v>-0.2634533248064126</v>
       </c>
     </row>
     <row r="32">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.278565489269931</v>
+        <v>0.2613355355635998</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.2395969346447389</v>
+        <v>-0.1945229293301994</v>
       </c>
     </row>
     <row r="33">
@@ -5203,21 +5203,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2672315379802321</v>
+        <v>0.2455426391738014</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1707085133319856</v>
+        <v>-0.168107591320959</v>
       </c>
     </row>
     <row r="34">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2383446266081919</v>
+        <v>0.2376325624184912</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1636419026692182</v>
+        <v>-0.1608820025301728</v>
       </c>
     </row>
     <row r="35">
@@ -5293,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2261853333931783</v>
+        <v>0.2263159784328941</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1622469389514478</v>
+        <v>-0.1400487915517806</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1828014961408135</v>
+        <v>0.1806513781000754</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.1457170329308554</v>
+        <v>-0.1357844191567454</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1732590006871197</v>
+        <v>0.1799041915630237</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.1308780843902132</v>
+        <v>-0.1317800194302017</v>
       </c>
     </row>
     <row r="38">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1717497800027015</v>
+        <v>0.1487358643906684</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.1235594495153345</v>
+        <v>-0.1174463799655584</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1388649407013791</v>
+        <v>0.1403231980700927</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.09863859472814485</v>
+        <v>-0.1143506533139712</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1303607117486181</v>
+        <v>0.1239829041302822</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.09856779485296741</v>
+        <v>-0.1002023214733994</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5542996907197371</v>
+        <v>0.559082504636681</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1858071635439488</v>
+        <v>-0.2137445122134843</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5478114577029365</v>
+        <v>0.5540522286475964</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1525664499510025</v>
+        <v>-0.1717718058058698</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4689503431084561</v>
+        <v>0.4393636805908152</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1082926766622366</v>
+        <v>-0.1139530639601356</v>
       </c>
     </row>
     <row r="48">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4613918263290848</v>
+        <v>0.4339269054671904</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.0886948117199039</v>
+        <v>-0.1047973995082077</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.434605652993193</v>
+        <v>0.4317833875681802</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.0656264532230405</v>
+        <v>-0.0730173679945485</v>
       </c>
     </row>
     <row r="50">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3996075804743275</v>
+        <v>0.3849512057317142</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.0505222198579387</v>
+        <v>-0.0626105656302699</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3576643984932117</v>
+        <v>0.3292459177681686</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.04859573026417241</v>
+        <v>-0.06228470535703778</v>
       </c>
     </row>
     <row r="52">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3464631453954115</v>
+        <v>0.3191847091716611</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.03913672534957258</v>
+        <v>-0.05652170595915418</v>
       </c>
     </row>
     <row r="53">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.3113687063045119</v>
+        <v>0.2988556095590569</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.03668507950082012</v>
+        <v>-0.05409087424769932</v>
       </c>
     </row>
     <row r="54">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.265543782104781</v>
+        <v>0.2455115359097158</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.03161835124928203</v>
+        <v>-0.0436392718019224</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.8672350612030073</v>
+        <v>0.9029851073791024</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2433099749630583</v>
+        <v>-0.2621641130839568</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7703446987156328</v>
+        <v>0.7813793946667562</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2247541525649442</v>
+        <v>-0.2228208911792133</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7285678266870388</v>
+        <v>0.718548883613614</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.2003103014310793</v>
+        <v>-0.1995629430359527</v>
       </c>
     </row>
     <row r="62">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6561593743991105</v>
+        <v>0.6522900142346602</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1751713963306958</v>
+        <v>-0.1848236497390703</v>
       </c>
     </row>
     <row r="63">
@@ -6315,21 +6315,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6415816979483882</v>
+        <v>0.6090983643848624</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1468586283728652</v>
+        <v>-0.1520047651138274</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.601541656711843</v>
+        <v>0.5709400658967883</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1381630255243458</v>
+        <v>-0.1358322406272239</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.5881436758635528</v>
+        <v>0.563315060253794</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06418050984005097</v>
+        <v>-0.06866855776457437</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.5798669716741409</v>
+        <v>0.4973146093328655</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6472,21 +6472,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.05797912635149827</v>
+        <v>-0.05775926082669358</v>
       </c>
     </row>
     <row r="67">
@@ -6495,21 +6495,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5043649900737419</v>
+        <v>0.4806329512110303</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.05539628262744811</v>
+        <v>-0.04846433659906335</v>
       </c>
     </row>
     <row r="68">
@@ -6540,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.4916270348880665</v>
+        <v>0.4709670828269126</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.04819558618860043</v>
+        <v>-0.0466996917568383</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.742928881789077</v>
+        <v>2.766749048694595</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1889312581629585</v>
+        <v>-0.1973855339990094</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.661377939505551</v>
+        <v>2.591080794351594</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>-0.004663461579780148</v>
+        <v>-0.00441412101904326</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.280683146875289</v>
+        <v>2.234329277862827</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.006494890714234591</v>
+        <v>0.007144510231344325</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.797445231815515</v>
+        <v>1.791970828007709</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.04062103240604054</v>
+        <v>0.04466443681435428</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.426218458647355</v>
+        <v>1.422734313932842</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1253721772454361</v>
+        <v>0.1221404645751965</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.343468110364328</v>
+        <v>1.332386988119676</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1280478896957253</v>
+        <v>0.1246924502167717</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.327840184342412</v>
+        <v>1.306026820281405</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1401183170468256</v>
+        <v>0.1427352329358347</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.303779747802547</v>
+        <v>1.298306581237188</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1658979197323516</v>
+        <v>0.1578756304809759</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.210385912126526</v>
+        <v>1.195066655847051</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1890677412042223</v>
+        <v>0.1768319383775772</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.105548028889097</v>
+        <v>1.112173453780401</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,21 +7073,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1904279733129086</v>
+        <v>0.1796508266289532</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -494,10 +494,10 @@
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -745,10 +745,10 @@
         <v>0.3928473832063351</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.306026820281405</v>
+        <v>1.306027159903814</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3211580784724306</v>
+        <v>0.3211581433307205</v>
       </c>
     </row>
     <row r="5">
@@ -792,19 +792,19 @@
         <v>0.1799041915630237</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.559082504636681</v>
+        <v>0.5590823197407846</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>0.3878113702905515</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3366779797503259</v>
+        <v>0.3366781156576177</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.195066655847051</v>
+        <v>1.195066839101528</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2996185578816568</v>
+        <v>0.2996185940477434</v>
       </c>
     </row>
     <row r="6">
@@ -857,10 +857,10 @@
         <v>0.4709670828269126</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.3708325281248597</v>
+        <v>0.3708326776245554</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1108654690324271</v>
+        <v>0.1108655094151969</v>
       </c>
     </row>
     <row r="7">
@@ -969,10 +969,10 @@
         <v>0.6522900142346602</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.012114296751981</v>
+        <v>1.012113896072358</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2624597738780301</v>
+        <v>0.2624596900786256</v>
       </c>
     </row>
     <row r="9">
@@ -1057,34 +1057,34 @@
         <v>152.76</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.002347812707526264</v>
+        <v>-0.002351101239756681</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.009078266619024222</v>
+        <v>-0.00908153296585279</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.003550760884492465</v>
+        <v>0.003547452908963411</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.01906824479632951</v>
+        <v>-0.01907147821348021</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.0132872388929528</v>
+        <v>-0.01329049136586713</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.3292459177681686</v>
+        <v>0.329241624457683</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.4504629318736142</v>
+        <v>0.450458150754341</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4973146093328655</v>
+        <v>0.4973096737777547</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.298306581237188</v>
+        <v>1.298298741583929</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3196820823817219</v>
+        <v>0.3196805818767001</v>
       </c>
     </row>
     <row r="11">
@@ -1137,10 +1137,10 @@
         <v>0.4389548693071346</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6121355425246851</v>
+        <v>0.6121357384600061</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.172556695648862</v>
+        <v>0.1725567431521597</v>
       </c>
     </row>
     <row r="12">
@@ -1184,7 +1184,7 @@
         <v>0.1101730493201691</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2445531689244806</v>
+        <v>0.2445530804586606</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>0.2029936396322982</v>
@@ -1193,10 +1193,10 @@
         <v>0.4615261457997</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6302694228961416</v>
+        <v>0.6302692710976856</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1769367600945135</v>
+        <v>0.176936723565339</v>
       </c>
     </row>
     <row r="13">
@@ -1243,10 +1243,10 @@
         <v>0.4393636805908152</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4884505127467167</v>
+        <v>0.4884506536621869</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.5709400658967883</v>
+        <v>0.5709399089295486</v>
       </c>
       <c r="O13" s="6" t="n">
         <v>1.422734313932842</v>
@@ -1305,10 +1305,10 @@
         <v>0.563315060253794</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.1796508266289532</v>
+        <v>0.1796507204203073</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.05661756358758807</v>
+        <v>0.05661753187709606</v>
       </c>
     </row>
     <row r="15">
@@ -1361,10 +1361,10 @@
         <v>0.3188039355571002</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.2593330894312251</v>
+        <v>0.25933289236924</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.07989170422778313</v>
+        <v>0.07989164790018766</v>
       </c>
     </row>
     <row r="16">
@@ -1393,34 +1393,34 @@
         <v>106.19</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.003677972267602359</v>
+        <v>-0.003659217329219477</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.04421237625152807</v>
+        <v>-0.04419438433978506</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.03693087717484622</v>
+        <v>-0.03691274819490364</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.01641344534513289</v>
+        <v>-0.01639493014150073</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.03841344519979961</v>
+        <v>-0.0383953441279743</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1847373289525529</v>
+        <v>0.1847596306531938</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2721324571104753</v>
+        <v>0.2721564039521429</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4806329512110303</v>
+        <v>0.4806608229021048</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.7244125135270734</v>
+        <v>0.7244450809923986</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1991689879651266</v>
+        <v>0.1991765371349206</v>
       </c>
     </row>
     <row r="17">
@@ -1473,10 +1473,10 @@
         <v>0.6090983643848624</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.332386988119676</v>
+        <v>1.332386741628867</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3261730659210462</v>
+        <v>0.326173019203601</v>
       </c>
     </row>
     <row r="18">
@@ -1529,10 +1529,10 @@
         <v>0.1996158826019399</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1850063044469983</v>
+        <v>0.1850061153963689</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.05821412364898126</v>
+        <v>0.05821406737472179</v>
       </c>
     </row>
     <row r="19">
@@ -1585,10 +1585,10 @@
         <v>0.2417220569195919</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.6715466915246646</v>
+        <v>0.6715461072826825</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1867871557646061</v>
+        <v>0.1867870174952686</v>
       </c>
     </row>
     <row r="20">
@@ -1729,34 +1729,34 @@
         <v>64.86</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.006083407306659017</v>
+        <v>-0.006129352019387024</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01127221047137383</v>
+        <v>0.01122546347917996</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01142993513765211</v>
+        <v>0.01138318085448975</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.002209482988289491</v>
+        <v>0.002163154929046174</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.07275400584532443</v>
+        <v>0.07270441680033946</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.2278900732497411</v>
+        <v>0.2278333128967176</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.08877869551046658</v>
+        <v>0.08872836570939735</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.005026121836966713</v>
+        <v>0.004979663575990445</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.9580714463714617</v>
+        <v>0.9579809327098869</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2510543523154907</v>
+        <v>0.2510350749707086</v>
       </c>
     </row>
     <row r="23">
@@ -1803,16 +1803,16 @@
         <v>0.1596331812888743</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1052337072634091</v>
+        <v>0.1052335791410337</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1698347979514161</v>
+        <v>0.1698347261825905</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8100931609213951</v>
+        <v>0.8100933327473201</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2187098160723118</v>
+        <v>0.2187098546349557</v>
       </c>
     </row>
     <row r="24">
@@ -1856,19 +1856,19 @@
         <v>0.0628247415172789</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1162668746700368</v>
+        <v>0.1162667425051664</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.07425893238954817</v>
+        <v>0.0742588099849002</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>0.1360688812798909</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.6413180356185519</v>
+        <v>0.6413178927503886</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1795895430639114</v>
+        <v>0.1795895088382071</v>
       </c>
     </row>
     <row r="25">
@@ -2027,7 +2027,7 @@
         <v>0.1611219799246204</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.08916568587077167</v>
+        <v>0.08916575363517198</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>0.1422815921780292</v>
@@ -2065,34 +2065,34 @@
         <v>130.48</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.008090267446426269</v>
+        <v>-0.008058367133165212</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.008469582906005524</v>
+        <v>0.008502015792339002</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.02162718233806615</v>
+        <v>-0.02159571737876065</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.02192049827383513</v>
+        <v>-0.02188904274771686</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.07330626907711557</v>
+        <v>0.07334078714371461</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.08398166544282049</v>
+        <v>0.08401652683550775</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.04441134421732307</v>
+        <v>0.04444493300868246</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1162527244264213</v>
+        <v>0.1162886236725111</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6199519311148418</v>
+        <v>0.6200035692174319</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1744486759812547</v>
+        <v>0.1744611548817434</v>
       </c>
     </row>
     <row r="29">
@@ -2142,13 +2142,13 @@
         <v>0.1150813745384149</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1194005265452311</v>
+        <v>0.1194006316702694</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.3982199443465744</v>
+        <v>0.3982201083625487</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1182146151426251</v>
+        <v>0.1182146588660877</v>
       </c>
     </row>
     <row r="30">
@@ -2201,10 +2201,10 @@
         <v>0.0959169822961834</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.222218477413163</v>
+        <v>0.222218321674909</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.06917701803352849</v>
+        <v>0.06917697262108868</v>
       </c>
     </row>
     <row r="31">
@@ -2254,13 +2254,13 @@
         <v>0.1368490260801021</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2500481928459248</v>
+        <v>0.2500480634294397</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.5459328296843202</v>
+        <v>0.5459327307180171</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1562814010456171</v>
+        <v>0.1562813763716475</v>
       </c>
     </row>
     <row r="32">
@@ -2310,13 +2310,13 @@
         <v>0.141784893153706</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1812893948720071</v>
+        <v>0.1812895170758457</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.830761183638574</v>
+        <v>0.8307610368793001</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.2233307674023457</v>
+        <v>0.2233307347137312</v>
       </c>
     </row>
     <row r="33">
@@ -2366,13 +2366,13 @@
         <v>0.07242640443010062</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1404030793296642</v>
+        <v>0.140403203109287</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3719462416306141</v>
+        <v>0.3719460624848774</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1111662232473485</v>
+        <v>0.1111661748827955</v>
       </c>
     </row>
     <row r="34">
@@ -2416,7 +2416,7 @@
         <v>0.05800837712642881</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.1064216104408258</v>
+        <v>0.1064216995597864</v>
       </c>
       <c r="M34" s="6" t="n">
         <v>-0.02861840430406815</v>
@@ -2481,10 +2481,10 @@
         <v>0.3566200503106649</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.2396187412846089</v>
+        <v>0.2396188252054781</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.07422695207545926</v>
+        <v>0.07422697631679909</v>
       </c>
     </row>
     <row r="36">
@@ -2590,13 +2590,13 @@
         <v>0.02515424586048431</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.04344959412036786</v>
+        <v>0.04344968582699815</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.9581184550551072</v>
+        <v>0.958118293579979</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2510643638581838</v>
+        <v>0.2510643294687449</v>
       </c>
     </row>
     <row r="38">
@@ -2649,10 +2649,10 @@
         <v>0.1764999191659793</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.3208321415179451</v>
+        <v>0.3208320086283569</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.09719177394578637</v>
+        <v>0.09719173714944596</v>
       </c>
     </row>
     <row r="39">
@@ -2702,7 +2702,7 @@
         <v>0.1004629047707797</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1070538930591733</v>
+        <v>0.1070539762843188</v>
       </c>
       <c r="O39" s="6" t="n">
         <v>0.3182951041686624</v>
@@ -2761,10 +2761,10 @@
         <v>0.1445530314718446</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.741219967453717</v>
+        <v>0.7412198578273888</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2030524067455757</v>
+        <v>0.2030523814977183</v>
       </c>
     </row>
     <row r="41">
@@ -2808,7 +2808,7 @@
         <v>-0.03830369689899016</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.02563267423062343</v>
+        <v>0.02563258837771465</v>
       </c>
       <c r="M41" s="6" t="n">
         <v>0.07984372835264542</v>
@@ -2817,10 +2817,10 @@
         <v>0.05349179173750063</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.286802966598773</v>
+        <v>0.286802831455194</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.08768720017938869</v>
+        <v>0.08768716210208916</v>
       </c>
     </row>
     <row r="42">
@@ -2849,34 +2849,34 @@
         <v>70.70999999999999</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.000212185445330304</v>
+        <v>0.0002828779512771273</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.003733963436527765</v>
+        <v>-0.003663549834554858</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.007509770476662569</v>
+        <v>-0.007439623739326606</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.02287173528658204</v>
+        <v>-0.02280267429465532</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.03749083269213949</v>
+        <v>0.03756415996002049</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.001464248139378288</v>
+        <v>0.001535029137997634</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.00811336100915705</v>
+        <v>0.008184611950512455</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.04142079281349476</v>
+        <v>-0.04135304282275221</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>-0.00441412101904326</v>
+        <v>-0.004343862450550739</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-0.001473543938234734</v>
+        <v>-0.001450055795668481</v>
       </c>
     </row>
     <row r="43">
@@ -2926,13 +2926,13 @@
         <v>0.02267935467080795</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.0244096275258463</v>
+        <v>0.02440969175175645</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.5812001394291186</v>
+        <v>0.5812007514930475</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1650081082599528</v>
+        <v>0.1650082585802337</v>
       </c>
     </row>
     <row r="44">
@@ -2976,7 +2976,7 @@
         <v>-0.08670130292406519</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.009712275375462931</v>
+        <v>-0.009712341400137769</v>
       </c>
       <c r="M44" s="6" t="n">
         <v>0.08282909595077448</v>
@@ -2985,10 +2985,10 @@
         <v>0.1211072431913458</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5674244850600536</v>
+        <v>0.5674241542439316</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1616149931386119</v>
+        <v>0.1616149114162284</v>
       </c>
     </row>
     <row r="45">
@@ -3088,19 +3088,19 @@
         <v>-0.016720302157611</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.0339059836033454</v>
+        <v>-0.03390605946953495</v>
       </c>
       <c r="M46" s="6" t="n">
         <v>0.0412630696208236</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.01522086368907272</v>
+        <v>0.0152207799109636</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.1246924502167717</v>
+        <v>0.1246926558565635</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.03994712817282342</v>
+        <v>0.03994719155444626</v>
       </c>
     </row>
     <row r="47">
@@ -3153,10 +3153,10 @@
         <v>-0.03458388477113894</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.7313541845175737</v>
+        <v>0.7313543869049979</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.2007759297706435</v>
+        <v>0.2007759765590553</v>
       </c>
     </row>
     <row r="48">
@@ -3203,16 +3203,16 @@
         <v>0.03695383687054465</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>-0.04606886934270205</v>
+        <v>-0.04606895326184446</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>-0.0466996917568383</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.3784056346955014</v>
+        <v>0.3784055470860244</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.1129073566953396</v>
+        <v>0.1129073331170762</v>
       </c>
     </row>
     <row r="49">
@@ -3265,10 +3265,10 @@
         <v>0.1753930157796555</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.1578756304809759</v>
+        <v>0.1578755566606418</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.05007577094350646</v>
+        <v>0.05007574862765396</v>
       </c>
     </row>
     <row r="50">
@@ -3318,13 +3318,13 @@
         <v>0.03780151314629432</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.068952448293506</v>
+        <v>0.06895252928760054</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>1.005975297298554</v>
+        <v>1.005975012073514</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.2611745362045061</v>
+        <v>0.2611744764299957</v>
       </c>
     </row>
     <row r="51">
@@ -3377,10 +3377,10 @@
         <v>0.01240157559141397</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.377919831021772</v>
+        <v>0.377920039628501</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.112776597409125</v>
+        <v>0.1127766535644663</v>
       </c>
     </row>
     <row r="52">
@@ -3480,10 +3480,10 @@
         <v>-0.1400487915517806</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.1047973995082077</v>
+        <v>-0.1047972985696008</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.04171937735574383</v>
+        <v>0.04171930901400134</v>
       </c>
       <c r="N53" s="6" t="n">
         <v>0.08289361095022119</v>
@@ -3539,16 +3539,16 @@
         <v>-0.0626105656302699</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1618386444052701</v>
+        <v>-0.1618386960407179</v>
       </c>
       <c r="N54" s="6" t="n">
         <v>-0.1358322406272239</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.04466443681435428</v>
+        <v>0.04466435660107071</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.01467183023683294</v>
+        <v>0.01467180426671955</v>
       </c>
     </row>
     <row r="55">
@@ -3601,10 +3601,10 @@
         <v>0.00956203898576935</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.3926883984441496</v>
+        <v>0.3926884879760322</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.1167380638786935</v>
+        <v>0.1167380878093061</v>
       </c>
     </row>
     <row r="56">
@@ -3633,34 +3633,34 @@
         <v>19.13</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.01029024874079365</v>
+        <v>-0.01029547867897285</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.004729224180190394</v>
+        <v>-0.004734483504575615</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.002081368069431822</v>
+        <v>-0.002086641385923071</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.02242832993105515</v>
+        <v>-0.02243349572778863</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.03772127475751585</v>
+        <v>-0.03772635974151006</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>0.05691159376046206</v>
+        <v>0.05690600870657203</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.08297333790733552</v>
+        <v>-0.08297818376516941</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.1848236497390703</v>
+        <v>-0.1848279573877638</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.1768319383775772</v>
+        <v>0.1768257196267999</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.05577526280303058</v>
+        <v>0.05577340311670187</v>
       </c>
     </row>
     <row r="57">
@@ -3689,34 +3689,34 @@
         <v>17.67</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.0006511554363863858</v>
+        <v>0.0006795604587399584</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.01364708131803372</v>
+        <v>-0.01361908217312546</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.07984903293302348</v>
+        <v>-0.07982291303235067</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.1337500204525746</v>
+        <v>-0.1337254306143486</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.009778180684884119</v>
+        <v>-0.009750071715279862</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.0864740187796158</v>
+        <v>0.08650486001596702</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.1580991212474915</v>
+        <v>-0.1580752225959479</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.2228208911792133</v>
+        <v>-0.2227988297546711</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.007144510231344325</v>
+        <v>0.007173099577562514</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.002375854256684073</v>
+        <v>0.002385338827134209</v>
       </c>
     </row>
     <row r="58">
@@ -3769,10 +3769,10 @@
         <v>-0.2621641130839568</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1947398383611736</v>
+        <v>0.1947397301084701</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.06110358493415502</v>
+        <v>0.06110355288608016</v>
       </c>
     </row>
     <row r="59">
@@ -3872,19 +3872,19 @@
         <v>-0.1174463799655584</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.0436392718019224</v>
+        <v>-0.04363934388911928</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.0868174659113965</v>
+        <v>-0.08681740018649764</v>
       </c>
       <c r="N60" s="6" t="n">
         <v>-0.1520047651138274</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2548350299166084</v>
+        <v>0.2548346576028406</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.07860445891097867</v>
+        <v>0.07860435223577955</v>
       </c>
     </row>
     <row r="61">
@@ -3937,10 +3937,10 @@
         <v>-0.1995629430359527</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1221404645751965</v>
+        <v>0.1221403555542429</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.03915996780300834</v>
+        <v>0.03915993414999797</v>
       </c>
     </row>
     <row r="62">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1337500204525746</v>
+        <v>-0.1337254306143486</v>
       </c>
     </row>
     <row r="21">
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.559082504636681</v>
+        <v>0.5590823197407846</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1047973995082077</v>
+        <v>-0.1047972985696008</v>
       </c>
     </row>
     <row r="49">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3292459177681686</v>
+        <v>0.329241624457683</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.0436392718019224</v>
+        <v>-0.04363934388911928</v>
       </c>
     </row>
     <row r="55"/>
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2228208911792133</v>
+        <v>-0.2227988297546711</v>
       </c>
     </row>
     <row r="61">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1848236497390703</v>
+        <v>-0.1848279573877638</v>
       </c>
     </row>
     <row r="63">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5709400658967883</v>
+        <v>0.5709399089295486</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.4973146093328655</v>
+        <v>0.4973096737777547</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.4806329512110303</v>
+        <v>0.4806608229021048</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>-0.00441412101904326</v>
+        <v>-0.004343862450550739</v>
       </c>
     </row>
     <row r="75">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.007144510231344325</v>
+        <v>0.007173099577562514</v>
       </c>
     </row>
     <row r="76">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.04466443681435428</v>
+        <v>0.04466435660107071</v>
       </c>
     </row>
     <row r="77">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1221404645751965</v>
+        <v>0.1221403555542429</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.332386988119676</v>
+        <v>1.332386741628867</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1246924502167717</v>
+        <v>0.1246926558565635</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.306026820281405</v>
+        <v>1.306027159903814</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.298306581237188</v>
+        <v>1.298298741583929</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1578756304809759</v>
+        <v>0.1578755566606418</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.195066655847051</v>
+        <v>1.195066839101528</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1768319383775772</v>
+        <v>0.1768257196267999</v>
       </c>
     </row>
     <row r="82">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1796508266289532</v>
+        <v>0.1796507204203073</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -490,15 +490,15 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>15.3</v>
+        <v>15.79</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.001956929753456849</v>
+        <v>0.03202612843200425</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.04968945166334415</v>
+        <v>-0.008165836295095152</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.07720143177691152</v>
+        <v>-0.02168521939473467</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.07090365432759693</v>
+        <v>0.1278571401323592</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.2613355355635998</v>
+        <v>0.3291245631099993</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4339269054671904</v>
+        <v>0.5139021572240416</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.7445837391251773</v>
+        <v>0.8752968905913574</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9029851073791024</v>
+        <v>0.9398033533015231</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1.791970828007709</v>
+        <v>1.881386844323893</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4081112191287783</v>
+        <v>0.4229856581713587</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>38.7</v>
+        <v>40</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.002876468916430897</v>
+        <v>0.03359171088971857</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.002590732973354992</v>
+        <v>0.05596617930587211</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.03731343212766447</v>
+        <v>-0.007197838395073819</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.09849563626996449</v>
+        <v>0.1154489492243165</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.2956143178981134</v>
+        <v>0.3162224680275894</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3191847091716611</v>
+        <v>0.357966981324807</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.4884404938759936</v>
+        <v>0.5545147411724121</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.718548883613614</v>
+        <v>0.7783887913828087</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.8436366606808134</v>
+        <v>0.9055675703720893</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2261919062908933</v>
+        <v>0.2397709363499672</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>119.46</v>
+        <v>120.48</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.009370572085032114</v>
+        <v>0.008538458733284182</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.076604182319153</v>
+        <v>0.0903167724609375</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.09215580621839603</v>
+        <v>0.08024750897153332</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.01083092550339759</v>
+        <v>0.04257533664142898</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2455426391738014</v>
+        <v>0.2631579663063595</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5540522286475964</v>
+        <v>0.5535783187077863</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4620044017386222</v>
+        <v>0.5063574616779951</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.3928473832063351</v>
+        <v>0.4114826527182891</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.306027159903814</v>
+        <v>1.325716906385342</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3211581433307205</v>
+        <v>0.3249076772289528</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>100.3</v>
+        <v>101.66</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.006930662853882996</v>
+        <v>0.01355932770659796</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.061600333277265</v>
+        <v>0.07965165365661564</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.07226857034494993</v>
+        <v>0.06651284082651343</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.007028158517679017</v>
+        <v>0.03957462634574482</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.1799041915630237</v>
+        <v>0.20797130991308</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.5590823197407846</v>
+        <v>0.5687909408215208</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.3878113702905515</v>
+        <v>0.4287126555687368</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3366781156576177</v>
+        <v>0.3584039545142776</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.195066839101528</v>
+        <v>1.224829726753839</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2996185940477434</v>
+        <v>0.3054660826441722</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>191.8</v>
+        <v>560.61</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.03955930904962346</v>
+        <v>0.02758631105711218</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.01646065096917682</v>
+        <v>0.0005889127533271754</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.007040798222030409</v>
+        <v>0.01449513231905541</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.06266273596530025</v>
+        <v>-0.05632336519287562</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2263159784328941</v>
+        <v>-0.1015433247214843</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.1562090215505252</v>
+        <v>0.412542779818537</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.5599186521448438</v>
+        <v>0.6576889501227876</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4709670828269126</v>
+        <v>0.842274784746984</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.3708326776245554</v>
+        <v>2.870659759625966</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1108655094151969</v>
+        <v>0.5701036835829725</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>545.5599999999999</v>
+        <v>192.59</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.006364044751534959</v>
+        <v>0.004118838756846266</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.05002695775300836</v>
+        <v>-0.01473374361706126</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.008937623682457541</v>
+        <v>0.00135181461218048</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-0.07189277200344768</v>
+        <v>0.05039536365850084</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-0.1143506533139712</v>
+        <v>0.2425935375296568</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3849512057317142</v>
+        <v>0.1424727024347467</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5549740501471869</v>
+        <v>0.5303387184942865</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.7813793946667562</v>
+        <v>0.4780227231049305</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>2.766749048694595</v>
+        <v>0.3764790665018007</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5559258484485829</v>
+        <v>0.1123886193088206</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>154.18</v>
+        <v>158.25</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.0009737966478808868</v>
+        <v>0.02639776571255514</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.03262650299737835</v>
+        <v>0.009118687724741559</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.06766646170290191</v>
+        <v>-0.03729166991558752</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.02051973134605567</v>
+        <v>-0.008023561644150079</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1403231980700927</v>
+        <v>0.1364183445641207</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2455115359097158</v>
+        <v>0.2755079997262306</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.2690919440241772</v>
+        <v>0.3141176896929845</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6522900142346602</v>
+        <v>0.695364238410596</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.012113896072358</v>
+        <v>1.065229618544522</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2624596900786256</v>
+        <v>0.2734721400896583</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>28.02</v>
+        <v>28.34</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.006030509864253464</v>
+        <v>0.01142040291207613</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.02412280090236552</v>
+        <v>0.04306220364403979</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.02113702304729115</v>
+        <v>-0.003866453687229932</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.01407458189501998</v>
+        <v>0.01649931871119326</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2376325624184912</v>
+        <v>0.289353991938458</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.4317833875681802</v>
+        <v>0.4269888862851456</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2393843198696577</v>
+        <v>0.2534276597769287</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2005141505818231</v>
+        <v>0.2044198608405612</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4347157948091407</v>
+        <v>0.4511008272501806</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1278602562140609</v>
+        <v>0.1321375540002143</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>152.76</v>
+        <v>499.27</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.002351101239756681</v>
+        <v>0.04057941166331247</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.00908153296585279</v>
+        <v>0.01794194909182401</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.003547452908963411</v>
+        <v>0.04336286984117432</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.01907147821348021</v>
+        <v>-0.09114580295269525</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.01329049136586713</v>
+        <v>-0.1581072592931696</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.329241624457683</v>
+        <v>0.5032690891051099</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.450458150754341</v>
+        <v>0.5936724689637194</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4973096737777547</v>
+        <v>0.6221786646658571</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.298298741583929</v>
+        <v>1.521047447008756</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3196805818767001</v>
+        <v>0.3610069400879758</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>202.4</v>
+        <v>155.64</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.001980167804378041</v>
+        <v>0.01885313554841495</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.01498432862138721</v>
+        <v>0.02105889174117381</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.05327002427548266</v>
+        <v>0.01698906310492632</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.02093659187769403</v>
+        <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1806513781000754</v>
+        <v>0.01280701512246551</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.2120810003030091</v>
+        <v>0.348120463279231</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2050871639298211</v>
+        <v>0.4955933613986172</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4389548693071346</v>
+        <v>0.5242149768876483</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6121357384600061</v>
+        <v>1.341628879289763</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1725567431521597</v>
+        <v>0.3279223746045616</v>
       </c>
     </row>
     <row r="12">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>66.79000000000001</v>
+        <v>207.07</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0</v>
+        <v>0.02307318956799387</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.03649738589779272</v>
+        <v>0.02191641086513707</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.06548202357970712</v>
+        <v>-0.03147122231532828</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.05903074448075463</v>
+        <v>0.02550953591456739</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1101730493201691</v>
+        <v>0.1939641136999246</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2445530804586606</v>
+        <v>0.2389200041922581</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2029936396322982</v>
+        <v>0.2371608643517575</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4615261457997</v>
+        <v>0.4715299029653022</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6302692710976856</v>
+        <v>0.6493326515066578</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.176936723565339</v>
+        <v>0.1815064193165576</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>479.8</v>
+        <v>67.75</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.001436039158838054</v>
+        <v>0.01437339528841775</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.03197822313869714</v>
+        <v>-0.003822998501156638</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.005659152494052355</v>
+        <v>-0.04617765501430493</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.1184846181958088</v>
+        <v>-0.03791533993709706</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>-0.1945229293301994</v>
+        <v>0.1194378889218468</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.4393636805908152</v>
+        <v>0.2501216669005919</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.4884506536621869</v>
+        <v>0.2291033640267945</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.5709399089295486</v>
+        <v>0.4764337224239865</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.422734313932842</v>
+        <v>0.6537014677971886</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3430801488262034</v>
+        <v>0.1825487062488025</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>399.85</v>
+        <v>86.61</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.02833467810114831</v>
+        <v>0.02874448389082263</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.06870851189154892</v>
+        <v>-0.0225708157795268</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.08413115946319316</v>
+        <v>-0.05084930837970891</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.05098137126080349</v>
+        <v>-0.008358092032829334</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>-0.01560844998592792</v>
+        <v>0.001663417537743239</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.07322113493574167</v>
+        <v>0.115445010358904</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.433571250070572</v>
+        <v>0.293702024551532</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.563315060253794</v>
+        <v>0.6772018864437233</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.1796507204203073</v>
+        <v>1.399430248326846</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.05661753187709606</v>
+        <v>0.3387599444062275</v>
       </c>
     </row>
     <row r="15">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>30.7</v>
+        <v>400.6</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.05625570504238975</v>
+        <v>0.001875703360139092</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.03671164246891456</v>
+        <v>-0.0466898173818312</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.03912362973868666</v>
+        <v>-0.06796024201623208</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.02538410872829866</v>
+        <v>-0.06094702210034908</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.1239829041302822</v>
+        <v>0.008763122051563377</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.04330810177613942</v>
+        <v>0.03881959658520939</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.3538869768585826</v>
+        <v>0.4209372179839495</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.3188039355571002</v>
+        <v>0.5894590877955688</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.25933289236924</v>
+        <v>0.1818633952403903</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.07989164790018766</v>
+        <v>0.05727775294101511</v>
       </c>
     </row>
     <row r="16">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>106.19</v>
+        <v>108.37</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.003659217329219477</v>
+        <v>0.02052924244331433</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.04419438433978506</v>
+        <v>-0.002393395134029253</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.03691274819490364</v>
+        <v>-0.02237253731778843</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.01639493014150073</v>
+        <v>0.0006463498878275242</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>-0.0383953441279743</v>
+        <v>0.006875457698114484</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1847596306531938</v>
+        <v>0.1985180816316543</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2721564039521429</v>
+        <v>0.2935434897373175</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4806608229021048</v>
+        <v>0.5244503004839425</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.7244450809923986</v>
+        <v>0.7598466321402726</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1991765371349206</v>
+        <v>0.2073270761611745</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>84.19</v>
+        <v>30.71</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.004728619385283128</v>
+        <v>0.0003256782177436524</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.1163009823876858</v>
+        <v>-0.03881069323494801</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.06351500542331978</v>
+        <v>-0.03275593434731794</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.01761953979704212</v>
+        <v>0.01086240726866849</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>-0.05918145275804265</v>
+        <v>0.1321797968755944</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.07393973415228849</v>
+        <v>0.031504386407748</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.2652840325620285</v>
+        <v>0.3175224050386491</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.6090983643848624</v>
+        <v>0.3236735135469313</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1.332386741628867</v>
+        <v>0.2597432267873367</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.326173019203601</v>
+        <v>0.08000892390526837</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>56.67</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.006834966613377236</v>
+        <v>0.04486969995998624</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.001059502989795735</v>
+        <v>-0.01237000883328476</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.0147420931224147</v>
+        <v>-0.06264797194044802</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.006122212774156477</v>
+        <v>0.04728836924385238</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.06506872542051201</v>
+        <v>0.1069346530700153</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.2988556095590569</v>
+        <v>0.00988250455933759</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.186205151999977</v>
+        <v>0.1642287776699645</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1996158826019399</v>
+        <v>0.4939457720935561</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1850061153963689</v>
+        <v>2.752211229485098</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.05821406737472179</v>
+        <v>0.5539215620477853</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>54.73</v>
+        <v>56.55</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.01030740872853797</v>
+        <v>-0.002117503719111236</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.02598325538628277</v>
+        <v>-0.0001791338836260037</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.01899984505997743</v>
+        <v>-0.02276129879117472</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.004184853458291005</v>
+        <v>0.007641678595850188</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.09391479183647333</v>
+        <v>0.08105749083843583</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.08680458579002015</v>
+        <v>0.2952471047018517</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.2392000548638837</v>
+        <v>0.1891345017099544</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.2417220569195919</v>
+        <v>0.1925809711314701</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.6715461072826825</v>
+        <v>0.1824969548649971</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.1867870174952686</v>
+        <v>0.05746664359163756</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>92.8</v>
+        <v>95.92</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.01412933432983676</v>
+        <v>0.03362063593303288</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.06705537435498754</v>
+        <v>-0.00114548174268303</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.04947244020834041</v>
+        <v>-0.0548822525575462</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.03145494934597681</v>
+        <v>0.04385677229366558</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.06373229394927948</v>
+        <v>0.1370317386789499</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.01674077397372398</v>
+        <v>0.02085993085962645</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1018977200779767</v>
+        <v>0.1256744461398429</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.3543029118084566</v>
+        <v>0.4071749837568128</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>2.234329277862827</v>
+        <v>2.343069485001402</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.4788634563006329</v>
+        <v>0.4952545563415325</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>90.93000000000001</v>
+        <v>55.01</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.01919964186036749</v>
+        <v>0.005116001857094821</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.09169913344528091</v>
+        <v>-0.01327357270792462</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.07863007340422046</v>
+        <v>-0.007398048736166341</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.01541035406353219</v>
+        <v>0.005851155656601881</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.02045721681367141</v>
+        <v>0.107549548694331</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>-0.04323412599978393</v>
+        <v>0.08510443776015753</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1252680782836268</v>
+        <v>0.2383951824971344</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.4085658374378764</v>
+        <v>0.2472903374520337</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>2.591080794351594</v>
+        <v>0.6800977402717603</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.5313521011213993</v>
+        <v>0.1888074440955161</v>
       </c>
     </row>
     <row r="22">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>64.86</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.006129352019387024</v>
+        <v>0.01387606409820585</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01122546347917996</v>
+        <v>0.03007521897013565</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01138318085448975</v>
+        <v>0.01387606409820585</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.002163154929046174</v>
+        <v>0.03559058482252708</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.07270441680033946</v>
+        <v>0.1029100525038362</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.2278333128967176</v>
+        <v>0.2486525545797789</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.08872836570939735</v>
+        <v>0.1207656834047381</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.004979663575990445</v>
+        <v>0.01876705865221462</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.9579809327098869</v>
+        <v>0.9851500016352341</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2510350749707086</v>
+        <v>0.2567949958431981</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>72.73999999999999</v>
+        <v>105.78</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.01769081882512069</v>
+        <v>0.00781249716060195</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.009666427691929935</v>
+        <v>0.04525693645422812</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.02020474196069488</v>
+        <v>-0.0109396746360968</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.0665982602474281</v>
+        <v>0.03716051568693768</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.009317220268754589</v>
+        <v>0.1864063978751334</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.1596331812888743</v>
+        <v>0.2369908623706305</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.1052335791410337</v>
+        <v>0.01050466577239506</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1698347261825905</v>
+        <v>-0.06553761190629759</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.8100933327473201</v>
+        <v>0.5031800341795536</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2187098546349557</v>
+        <v>0.1455226116612289</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>143.86</v>
+        <v>291.6</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.007588341974120505</v>
+        <v>0.01018500105351516</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.009958602234911629</v>
+        <v>0.0213660458967273</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.002945685655555752</v>
+        <v>-0.006202737512541856</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.009512994561466703</v>
+        <v>0.01624034161309029</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.0628247415172789</v>
+        <v>0.1097579360101835</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1162667425051664</v>
+        <v>0.1914684953770682</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0742588099849002</v>
+        <v>0.1009590811403984</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1360688812798909</v>
+        <v>0.02546075792978431</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.6413178927503886</v>
+        <v>0.7451673498983142</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1795895088382071</v>
+        <v>0.2039608356875504</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>104.96</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.005589805307687601</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.03073747615767419</v>
+        <v>-0.01449667701146862</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.01489074591755091</v>
+        <v>-0.02844937631459798</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.008455008050887614</v>
+        <v>-0.06008530252683897</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.1487358643906684</v>
+        <v>0.0283260050017522</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.2357819853062377</v>
+        <v>0.1598158634902365</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>-0.01251359135298524</v>
+        <v>0.1004704903016347</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.06866855776457437</v>
+        <v>0.1560400120160939</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4915274799772715</v>
+        <v>0.8100933327473201</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.1425549242786122</v>
+        <v>0.2187098546349557</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>288.66</v>
+        <v>143.58</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.004277303416631906</v>
+        <v>-0.001946328222639626</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.002535376671058076</v>
+        <v>0.005600897699644669</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.004419043630397024</v>
+        <v>-0.02561362160751623</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.009334893181146886</v>
+        <v>0.001337861403220009</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.06678002723224985</v>
+        <v>0.06696170001619217</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1870220098532702</v>
+        <v>0.1105322994268809</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.07733074954059616</v>
+        <v>0.0717765493854603</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.01985583291238324</v>
+        <v>0.1286496752555701</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.7275720269834645</v>
+        <v>0.6381233494134053</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1999009239922773</v>
+        <v>0.1788237223484332</v>
       </c>
     </row>
     <row r="27">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>66.78</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.01721851687258358</v>
+        <v>-0.001497431505675495</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.01315205281115062</v>
+        <v>-0.01883459088493911</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.02297000336318455</v>
+        <v>-0.03516134110425406</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.06822937790679728</v>
+        <v>-0.06163801581623141</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.01005906193737283</v>
+        <v>0.02567460440870062</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1611219799246204</v>
+        <v>0.1581884308122072</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.08916575363517198</v>
+        <v>0.08440717264462538</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1422815921780292</v>
+        <v>0.128134601456501</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8790990359326392</v>
+        <v>0.8762850124327042</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.234003969091638</v>
+        <v>0.2333876717856278</v>
       </c>
     </row>
     <row r="28">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>130.48</v>
+        <v>129.78</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.008058367133165212</v>
+        <v>-0.005364783653916461</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.008502015792339002</v>
+        <v>0.0006168221506328564</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.02159571737876065</v>
+        <v>-0.03973359496634943</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.02188904274771686</v>
+        <v>-0.01397961104809642</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.07334078714371461</v>
+        <v>0.07241442919742114</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.08401652683550775</v>
+        <v>0.08121746039312905</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.04444493300868246</v>
+        <v>0.03590730200194936</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1162886236725111</v>
+        <v>0.1041903609682484</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6200035692174319</v>
+        <v>0.611312753180729</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1744611548817434</v>
+        <v>0.1723571815456508</v>
       </c>
     </row>
     <row r="29">
@@ -2118,37 +2118,37 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>90.94</v>
+        <v>91.13</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.006554494954339907</v>
+        <v>0.002089232536959029</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.008568867465726715</v>
+        <v>-0.003689768815581362</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02650658378906456</v>
+        <v>-0.02768066914141065</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.04130136772556303</v>
+        <v>-0.03097002532301163</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.002514763089131566</v>
+        <v>0.02943101412553539</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.04942849551155071</v>
+        <v>0.04601145546553354</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1150813745384149</v>
+        <v>0.1086740074011281</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1194006316702694</v>
+        <v>0.1229558941032785</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.3982201083625487</v>
+        <v>0.4011411509481282</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1182146588660877</v>
+        <v>0.1189928102362225</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>73.18000000000001</v>
+        <v>23.45</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.006381550725942264</v>
+        <v>0.01823708483593278</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.00371396757153386</v>
+        <v>-0.002127627108959418</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.02551797349249307</v>
+        <v>-0.006776782857936814</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.01640331216427393</v>
+        <v>-0.03656529926331209</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.00371396757153386</v>
+        <v>-0.04334805933060104</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.02076858316005437</v>
+        <v>-0.02309520093900685</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1024784316790532</v>
+        <v>0.1749195134213741</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.0959169822961834</v>
+        <v>0.26537418508027</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.222218321674909</v>
+        <v>0.5741260370787669</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.06917697262108868</v>
+        <v>0.1632681413914472</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>23.03</v>
+        <v>176.84</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.006996057784905307</v>
+        <v>0.01492189372565522</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.03397648744790194</v>
+        <v>-0.002256878486098124</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.0132818964831074</v>
+        <v>-0.003942756419473503</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.05304272304136781</v>
+        <v>-0.06532769983993592</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.06579868588936899</v>
+        <v>-0.07064424205138209</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>-0.03336931873902971</v>
+        <v>0.05454430307989666</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.1368490260801021</v>
+        <v>0.185975157057934</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2500480634294397</v>
+        <v>0.2062151158730394</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.5459327307180171</v>
+        <v>0.8580796074578834</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1562813763716475</v>
+        <v>0.2293855541352223</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>174.24</v>
+        <v>80.8</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.008508428456046824</v>
+        <v>0.007984023957211539</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.03269860228716648</v>
+        <v>-0.0127725239025146</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.007349132883859855</v>
+        <v>-0.03131248310155099</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.07255011432518255</v>
+        <v>-0.07258048485184965</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.0894079313821925</v>
+        <v>-0.02805722178797854</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.04418422680072043</v>
+        <v>0.08024893848019987</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.141784893153706</v>
+        <v>0.0912756009754343</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1812895170758457</v>
+        <v>0.1651042272883392</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.8307610368793001</v>
+        <v>0.3828997127157585</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.2233307347137312</v>
+        <v>0.1141155319615381</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>80.16</v>
+        <v>111.32</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.02028838962241952</v>
+        <v>0.02344399310892475</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.01675646194740155</v>
+        <v>-0.03006009452951053</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.03575577081439918</v>
+        <v>-0.05963843320151718</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.08118911695098474</v>
+        <v>-0.05740896585009314</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.06688932112090884</v>
+        <v>-0.05907459241807167</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.09008308269705489</v>
+        <v>0.006275959600919645</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.07242640443010062</v>
+        <v>0.1046429582123465</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.140403203109287</v>
+        <v>0.2732412725732782</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3719460624848774</v>
+        <v>1.124042695326255</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1111661748827955</v>
+        <v>0.2854477075166471</v>
       </c>
     </row>
     <row r="34">
@@ -2398,37 +2398,37 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>13.1</v>
+        <v>13.31</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.002295385412854234</v>
+        <v>0.01603053679632116</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.003062784116985684</v>
+        <v>0.02542379730496624</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.01799098713440461</v>
+        <v>-0.002996251738580424</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.02019442830220075</v>
+        <v>0.009863437893083082</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.05800837712642881</v>
+        <v>0.09936028340895153</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.1064216995597864</v>
+        <v>0.08856709283640796</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.02861840430406815</v>
+        <v>-0.007642404061993568</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.04846433659906335</v>
+        <v>-0.03383768500078643</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.1427352329358347</v>
+        <v>0.1610539887246742</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.04547874035489552</v>
+        <v>0.05103570933578716</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>69.84999999999999</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.002427851715159246</v>
+        <v>-0.00191308266007939</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.05313810962893339</v>
+        <v>0.0004295990506393288</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.05938598889371416</v>
+        <v>-0.02207434871176528</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.07151408537477688</v>
+        <v>-0.002287438793894814</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.1608820025301728</v>
+        <v>0.01944707169960957</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>-0.02052134137339157</v>
+        <v>0.02211357115212653</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1166970894565411</v>
+        <v>0.09565936417759446</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.3566200503106649</v>
+        <v>0.08574389256946668</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.2396188252054781</v>
+        <v>0.2198802724371951</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.07422697631679909</v>
+        <v>0.06849477478122967</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>108.77</v>
+        <v>100.96</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.006122128868724763</v>
+        <v>0.007987174452010581</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.08742348842103864</v>
+        <v>-0.008835671711035165</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.08948604154807605</v>
+        <v>-0.03183735839747015</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.07145298608667805</v>
+        <v>-0.08740846433173488</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.08787054796540705</v>
+        <v>-0.09434591256477487</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>-0.01419391392861813</v>
+        <v>0.1225205650779724</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.08062247949582524</v>
+        <v>0.09822890333291356</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.2371669333063049</v>
+        <v>0.195650472910214</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.075387329084841</v>
+        <v>0.3313818582540715</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.2755565590850768</v>
+        <v>0.1001051850529071</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>181.16</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.02197264028130941</v>
+        <v>0.01503225590114843</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.05205674707928132</v>
+        <v>-0.01267227494294687</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.04803293448679624</v>
+        <v>-0.0478108729836948</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.04977581195832825</v>
+        <v>-0.07004192664633158</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.03246673552334967</v>
+        <v>-0.1428340438869102</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.1182305503266297</v>
+        <v>-0.006075099312221055</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.02515424586048431</v>
+        <v>0.1222592262840143</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.04344968582699815</v>
+        <v>0.3581534909918798</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.958118293579979</v>
+        <v>0.2582530926058477</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2510643294687449</v>
+        <v>0.07958291296377307</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>100.16</v>
+        <v>226.3</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.02015258788880281</v>
+        <v>0.007120632511108393</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.01957713320581833</v>
+        <v>-0.00619210232548606</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.03114716267031181</v>
+        <v>-0.04162961770120299</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.1014622538327663</v>
+        <v>-0.03472103440061547</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.1317800194302017</v>
+        <v>-0.03199916089345789</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.1324454748190746</v>
+        <v>0.01510494922968419</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.07648820822984459</v>
+        <v>0.1056056037400412</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1764999191659793</v>
+        <v>0.1130997975813333</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.3208320086283569</v>
+        <v>0.3276820802899223</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.09719173714944596</v>
+        <v>0.09908521198153131</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>224.7</v>
+        <v>93.81</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.006850842217714037</v>
+        <v>0.003530104726249705</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.02866037621723849</v>
+        <v>-0.003293722683189615</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.05229864544946372</v>
+        <v>-0.02948485408171808</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.04577883036727171</v>
+        <v>-0.04255976378311432</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.0521757342723822</v>
+        <v>-0.01017846608809447</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.01103464507257246</v>
+        <v>0.02473227364821318</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.1004629047707797</v>
+        <v>0.07965559869874417</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.1070539762843188</v>
+        <v>0.05858874853039131</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.3182951041686624</v>
+        <v>0.2913457870743006</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.09648883308210565</v>
+        <v>0.08896565657156175</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>52.75</v>
+        <v>182.51</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.001703257992581308</v>
+        <v>0.007451925466089637</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.02657314381254183</v>
+        <v>-0.03563241271955209</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.02818715574253916</v>
+        <v>-0.07599699213641742</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.09967571492368299</v>
+        <v>-0.04184274508581898</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.0967093679955533</v>
+        <v>-0.02442538567739938</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.04266976499602149</v>
+        <v>0.1122023009180686</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.09103421166974024</v>
+        <v>0.03540520127510671</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.1445530314718446</v>
+        <v>0.04362330084753463</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.7412198578273888</v>
+        <v>0.9727105331928909</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2030523814977183</v>
+        <v>0.2541643581715025</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>93.48</v>
+        <v>52.91</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.006588683605111889</v>
+        <v>0.00303317246278878</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.01537812351936396</v>
+        <v>-0.008433297559823361</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.02401331647187732</v>
+        <v>-0.03254706205875779</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.05413334387331759</v>
+        <v>-0.09909756070470765</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.03830369689899016</v>
+        <v>-0.08584371345980291</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.02563258837771465</v>
+        <v>0.04192618030109996</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.07984372835264542</v>
+        <v>0.1144567127186955</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.05349179173750063</v>
+        <v>0.1539831901646631</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.286802831455194</v>
+        <v>0.7465012779518119</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.08768716210208916</v>
+        <v>0.2042675088792101</v>
       </c>
     </row>
     <row r="42">
@@ -2846,37 +2846,37 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>70.70999999999999</v>
+        <v>71.59</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.0002828779512771273</v>
+        <v>0.01244516001713825</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.003663549834554858</v>
+        <v>0.01546094096298756</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.007439623739326606</v>
+        <v>0.005195101247484235</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.02280267429465532</v>
+        <v>0.006325512399535826</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.03756415996002049</v>
+        <v>0.0667560078497158</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.001535029137997634</v>
+        <v>0.0093253028558693</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.008184611950512455</v>
+        <v>0.01613832428601869</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.04135304282275221</v>
+        <v>-0.02568313948809819</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>-0.004343862450550739</v>
+        <v>0.008047345796089234</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-0.001450055795668481</v>
+        <v>0.002675285066039423</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>62.33</v>
+        <v>28.17</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.001281814077119248</v>
+        <v>0.01330938307149832</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.008431415433514888</v>
+        <v>0.01185344547045131</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.04445809254386079</v>
+        <v>-0.008796622073500071</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.09601153604338586</v>
+        <v>-0.08687196992015411</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.04956829483060154</v>
+        <v>-0.06876032805639853</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.07507054324781737</v>
+        <v>0.1236537861669671</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.02267935467080795</v>
+        <v>0.003204929218225017</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.02440969175175645</v>
+        <v>0.09867430300667879</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.5812007514930475</v>
+        <v>0.5778184213154938</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1650082585802337</v>
+        <v>0.164176979865114</v>
       </c>
     </row>
     <row r="44">
@@ -2958,37 +2958,37 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>56.66</v>
+        <v>56.96</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.001409972306804619</v>
+        <v>0.005294727106750052</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.03153351317646647</v>
+        <v>-0.01466963300709656</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.02922099206119677</v>
+        <v>-0.0288843349922342</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.07961233500049048</v>
+        <v>-0.07876132675152436</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.08670130292406519</v>
+        <v>-0.0706816059931572</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.009712341400137769</v>
+        <v>-0.006451134677616932</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.08282909595077448</v>
+        <v>0.09434720885696057</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.1211072431913458</v>
+        <v>0.1268241900423019</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5674241542439316</v>
+        <v>0.575723569968885</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1616149114162284</v>
+        <v>0.1636615302227107</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>27.8</v>
+        <v>46.95</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.00286943780897353</v>
+        <v>0.0004261763825614828</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.007851578055280473</v>
+        <v>0.001066081778972938</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.01870810759169872</v>
+        <v>-0.02431417695169691</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.11913815882473</v>
+        <v>-0.01737124398414724</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.09239307872169156</v>
+        <v>0.006619515314238766</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.1310007861411333</v>
+        <v>-0.03605789451012487</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>-0.02512349989027363</v>
+        <v>0.03828174654125727</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.09057193497873817</v>
+        <v>0.01608728090014533</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.5570944547388685</v>
+        <v>0.1251720761678736</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1590575119770317</v>
+        <v>0.04009493591191959</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>46.93</v>
+        <v>62.13</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.002974280657661255</v>
+        <v>-0.003208739885513845</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.0006396328000186635</v>
+        <v>-0.004486440954677984</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.03197193175940871</v>
+        <v>-0.04282856935990198</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.02310575747705268</v>
+        <v>-0.08940351734862506</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.016720302157611</v>
+        <v>-0.03945374093299447</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.03390605946953495</v>
+        <v>0.05960070889839764</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0412630696208236</v>
+        <v>0.02779072480954614</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.0152207799109636</v>
+        <v>0.01564435862713021</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.1246926558565635</v>
+        <v>0.5761267845246809</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.03994719155444626</v>
+        <v>0.163760778859914</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>113</v>
+        <v>17.73</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.00903270008176027</v>
+        <v>0.02367204703442516</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0.01957951938188351</v>
+        <v>-0.005050513699729753</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.005159240708962232</v>
+        <v>0.005672171652297386</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0.0004427007800693605</v>
+        <v>-0.0209829406575518</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.00867138882988594</v>
+        <v>-0.1342773467513326</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.01451912521294174</v>
+        <v>-0.05236746908423273</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>-0.02251649632633645</v>
+        <v>0.1110992113101446</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.03458388477113894</v>
+        <v>0.1896348636420877</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.7313543869049979</v>
+        <v>0.1852849168657362</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.2007759765590553</v>
+        <v>0.05829705105396021</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>82.73</v>
+        <v>112.35</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.005887981934415421</v>
+        <v>-0.00575222589273372</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.01862395774600722</v>
+        <v>0.007623304700637545</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.04225508234014153</v>
+        <v>-0.009084484073453525</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.06992685558975176</v>
+        <v>0.01380616119391975</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.04790416795736585</v>
+        <v>0.03152272536073508</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.03695383687054465</v>
+        <v>-0.02052756841203618</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>-0.04606895326184446</v>
+        <v>-0.02108999415018076</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.0466996917568383</v>
+        <v>-0.04264131972239216</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.3784055470860244</v>
+        <v>0.7213952453711447</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.1129073331170762</v>
+        <v>0.1984691695759544</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>17.32</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.006880781855428064</v>
+        <v>0.001087831913922921</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.03831207802824421</v>
+        <v>-0.009685490675544028</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.002878591939744934</v>
+        <v>-0.04508248023487238</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.04887421386019308</v>
+        <v>-0.0539182221994462</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.168107591320959</v>
+        <v>-0.01834779339061654</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.06228470535703778</v>
+        <v>0.03562747652199438</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.0660826341104912</v>
+        <v>-0.04415546564408268</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1753930157796555</v>
+        <v>-0.04762237730334773</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.1578755566606418</v>
+        <v>0.3799049329257027</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.05007574862765396</v>
+        <v>0.1133107153244461</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>215.27</v>
+        <v>35.12</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.005934599404022967</v>
+        <v>0.01137674089504759</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.01791047726860906</v>
+        <v>0.01021298544521732</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.0351454736227883</v>
+        <v>-0.01940797732955646</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.1488841782764053</v>
+        <v>-0.07152295182930979</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.1002023214733994</v>
+        <v>-0.06537481516017551</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.0730173679945485</v>
+        <v>-0.006993728923317177</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.03780151314629432</v>
+        <v>0.008121758921532107</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.06895252928760054</v>
+        <v>0.02660062801477658</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>1.005975012073514</v>
+        <v>0.3935960679134545</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.2611744764299957</v>
+        <v>0.1169806184753519</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>34.72</v>
+        <v>43.78</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.002598907011607254</v>
+        <v>0.008755696775526234</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.01307558500518202</v>
+        <v>-0.005677947011834883</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.01335599387176833</v>
+        <v>-0.03120159084445617</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.08002120623875819</v>
+        <v>-0.03269994690945877</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.08296299102513516</v>
+        <v>-0.0247271246478904</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.01844124418086368</v>
+        <v>-0.05666884457578569</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>-0.02522049876798294</v>
+        <v>-0.02959841091981918</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.01240157559141397</v>
+        <v>-0.04812836087416839</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.377920039628501</v>
+        <v>0.2456732291916985</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.1127766535644663</v>
+        <v>0.0759730088376469</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>43.4</v>
+        <v>213.88</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.004358766369439993</v>
+        <v>-0.006457004515543874</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.02625080047019124</v>
+        <v>-0.01920146539984979</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.02908275648483594</v>
+        <v>-0.05244736973571451</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.045944165211522</v>
+        <v>-0.1475798367764296</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.05032821003639321</v>
+        <v>-0.1180528407963702</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.05652170595915418</v>
+        <v>-0.07995593820163427</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.04126704888850841</v>
+        <v>0.04695955128640361</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.05775926082669358</v>
+        <v>0.06930645030986748</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.234861159320811</v>
+        <v>0.9930222806708473</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.072850917441174</v>
+        <v>0.2584541133474854</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>242.29</v>
+        <v>41.69</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.003146584319450918</v>
+        <v>0.008954475668379924</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.01787597777325711</v>
+        <v>-0.01952026862932776</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.03165346395114987</v>
+        <v>-0.03114106880320455</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.1834665038404344</v>
+        <v>-0.05636038164932033</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.1400487915517806</v>
+        <v>-0.05631556660356318</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.1047972985696008</v>
+        <v>-0.1035531138716037</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.04171930901400134</v>
+        <v>-0.004535197789366618</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.08289361095022119</v>
+        <v>0.01606613848896643</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>1.112173453780401</v>
+        <v>0.4051592831552464</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.2830488547082526</v>
+        <v>0.1200614557995627</v>
       </c>
     </row>
     <row r="54">
@@ -3518,37 +3518,37 @@
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.002317550201063501</v>
+        <v>-0.003853579134091678</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.00973564458317977</v>
+        <v>0.01730595866026041</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.04481453206262409</v>
+        <v>-0.03949402237119337</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.06776917785612335</v>
+        <v>-0.05989696413930301</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.04149849668977801</v>
+        <v>0.06985280100107727</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.0626105656302699</v>
+        <v>-0.07311562072795141</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1618386960407179</v>
+        <v>-0.1668111889444607</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.1358322406272239</v>
+        <v>-0.1391623794730976</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.04466435660107071</v>
+        <v>0.04063873973851906</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.01467180426671955</v>
+        <v>0.01336677969566913</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>41.32</v>
+        <v>241.32</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>-0.004003409091553167</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.03772703734734439</v>
+        <v>-0.01365158296369262</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.03163811886693746</v>
+        <v>-0.0496592986857719</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.06747916013988431</v>
+        <v>-0.181605414859816</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.07714500001320579</v>
+        <v>-0.1548280642980912</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.1139530639601356</v>
+        <v>-0.1179241052604807</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.01978876002050589</v>
+        <v>0.05531507482957965</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.00956203898576935</v>
+        <v>0.08639742855604116</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.3926884879760322</v>
+        <v>1.103717419455247</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.1167380878093061</v>
+        <v>0.2813343465238016</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>19.13</v>
+        <v>42.68</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.01029547867897285</v>
+        <v>0.0316654920742907</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.004734483504575615</v>
+        <v>-0.05155554877387147</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.002086641385923071</v>
+        <v>-0.06608315989816682</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.02243349572778863</v>
+        <v>-0.05679557336628105</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.03772635974151006</v>
+        <v>-0.09384285163775241</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>0.05690600870657203</v>
+        <v>-0.1551860665389815</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.08297818376516941</v>
+        <v>0.0470008942498128</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.1848279573877638</v>
+        <v>0.003757798468028373</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.1768257196267999</v>
+        <v>0.8258980098696651</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.05577340311670187</v>
+        <v>0.2222466016548086</v>
       </c>
     </row>
     <row r="57">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3686,37 +3686,37 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>17.67</v>
+        <v>18.88</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.0006795604587399584</v>
+        <v>-0.01332980512040871</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.01361908217312546</v>
+        <v>-0.01615842974052206</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.07982291303235067</v>
+        <v>-0.03120668315074848</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.1337254306143486</v>
+        <v>-0.03031082188352563</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.009750071715279862</v>
+        <v>-0.03600612494653244</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.08650486001596702</v>
+        <v>0.03765802341016089</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.1580752225959479</v>
+        <v>-0.08800966406356991</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.2227988297546711</v>
+        <v>-0.1877820487345413</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.007173099577562514</v>
+        <v>0.1611388621234899</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.002385338827134209</v>
+        <v>0.05106131905484301</v>
       </c>
     </row>
     <row r="58">
@@ -3742,37 +3742,37 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>25.15</v>
+        <v>25.4</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.02063865577675583</v>
+        <v>0.009741584212704435</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.03454893070591236</v>
+        <v>-0.01607900103703308</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.06170725202333793</v>
+        <v>-0.09027405964948243</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.06016444680796018</v>
+        <v>-0.03569389251519728</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.008951046468235191</v>
+        <v>0.0290830503623547</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.02746767190242982</v>
+        <v>0.01959643435533742</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.1548604881485495</v>
+        <v>-0.1342095177105972</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.2621641130839568</v>
+        <v>-0.2575708370182598</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1947397301084701</v>
+        <v>0.2063783878015857</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.06110355288608016</v>
+        <v>0.06453803435473926</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>41.37</v>
+        <v>17.68</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.009576287323323718</v>
+        <v>0.0004526606929269317</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.1171575246897038</v>
+        <v>-0.0001130472490038503</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.06656138951381718</v>
+        <v>-0.06898364832709247</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.07923439459404846</v>
+        <v>-0.1200039493158475</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.1357844191567454</v>
+        <v>-0.01449276594993665</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.1717718058058698</v>
+        <v>0.06969992955919557</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.02089738112615291</v>
+        <v>-0.1524448807349381</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.02288392444536991</v>
+        <v>-0.2296296419420548</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.7698546902043528</v>
+        <v>0.007629007250714803</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.2096113976937766</v>
+        <v>0.002536562825726785</v>
       </c>
     </row>
     <row r="60">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>96.8</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.009819957687141612</v>
+        <v>0.002789221431346967</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.0244885641738315</v>
+        <v>0.001650975406756627</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.04319457543025729</v>
+        <v>-0.05084577216122099</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.1120894695247249</v>
+        <v>-0.1027821655943156</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.1174463799655584</v>
+        <v>-0.09428797780018872</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.04363934388911928</v>
+        <v>-0.04482380248617479</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.08681740018649764</v>
+        <v>-0.07516597630265098</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1520047651138274</v>
+        <v>-0.1409007175074048</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2548346576028406</v>
+        <v>0.2583349182240877</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.07860435223577955</v>
+        <v>0.07960631462145917</v>
       </c>
     </row>
     <row r="61">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>88.12</v>
+        <v>88.55</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.01122082550696901</v>
+        <v>0.004879712798153024</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.01601065190162754</v>
+        <v>0.01221609104621946</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.04261936210625872</v>
+        <v>-0.04616856293219673</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.1003838963548384</v>
+        <v>-0.08730877319960062</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.09562310669175622</v>
+        <v>-0.06777634103836716</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.05409087424769932</v>
+        <v>-0.0507864582639026</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.1173760923364604</v>
+        <v>-0.1026786062882092</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.1995629430359527</v>
+        <v>-0.1869878276104799</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1221403555542429</v>
+        <v>0.1276161877615094</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.03915993414999797</v>
+        <v>0.04084749329042903</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>44.62</v>
+        <v>46.36</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.01042362428726118</v>
+        <v>0.03899600448496243</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.06535405607221234</v>
+        <v>-0.0144557885191563</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.05606095832909319</v>
+        <v>-0.02849959294974891</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.1414277874961904</v>
+        <v>-0.0895521940802968</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2634533248064126</v>
+        <v>-0.2068434558559257</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.2137445122134843</v>
+        <v>-0.1970904180343871</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.0663319088284976</v>
+        <v>-0.01883596591848546</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.04569957456334373</v>
+        <v>0.08166122142225718</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1973855339990094</v>
+        <v>-0.1660867766831391</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.07067205990652825</v>
+        <v>-0.05874574278360223</v>
       </c>
     </row>
   </sheetData>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4602,21 +4602,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.09849563626996449</v>
+        <v>0.1278571401323592</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1834665038404344</v>
+        <v>-0.181605414859816</v>
       </c>
     </row>
     <row r="18">
@@ -4647,21 +4647,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.07090365432759693</v>
+        <v>0.1154489492243165</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1488841782764053</v>
+        <v>-0.1475798367764296</v>
       </c>
     </row>
     <row r="19">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.06266273596530025</v>
+        <v>0.05039536365850084</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1414277874961904</v>
+        <v>-0.1200039493158475</v>
       </c>
     </row>
     <row r="20">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.03145494934597681</v>
+        <v>0.04728836924385238</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1337254306143486</v>
+        <v>-0.1027821655943156</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.02538410872829866</v>
+        <v>0.04385677229366558</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.11913815882473</v>
+        <v>-0.09909756070470765</v>
       </c>
     </row>
     <row r="22">
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.02093659187769403</v>
+        <v>0.04257533664142898</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.1184846181958088</v>
+        <v>-0.09114580295269525</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.01541035406353219</v>
+        <v>0.03957462634574482</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.1120894695247249</v>
+        <v>-0.0895521940802968</v>
       </c>
     </row>
     <row r="24">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.01083092550339759</v>
+        <v>0.03716051568693768</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.1014622538327663</v>
+        <v>-0.08940351734862506</v>
       </c>
     </row>
     <row r="25">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.008455008050887614</v>
+        <v>0.03559058482252708</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.1003838963548384</v>
+        <v>-0.08740846433173488</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.007028158517679017</v>
+        <v>0.02550953591456739</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.09967571492368299</v>
+        <v>-0.08730877319960062</v>
       </c>
     </row>
     <row r="27"/>
@@ -5113,21 +5113,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.2956143178981134</v>
+        <v>0.3291245631099993</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2634533248064126</v>
+        <v>-0.2068434558559257</v>
       </c>
     </row>
     <row r="32">
@@ -5158,21 +5158,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2613355355635998</v>
+        <v>0.3162224680275894</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1945229293301994</v>
+        <v>-0.1581072592931696</v>
       </c>
     </row>
     <row r="33">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2455426391738014</v>
+        <v>0.289353991938458</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5225,21 +5225,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.168107591320959</v>
+        <v>-0.1548280642980912</v>
       </c>
     </row>
     <row r="34">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2376325624184912</v>
+        <v>0.2631579663063595</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1608820025301728</v>
+        <v>-0.1428340438869102</v>
       </c>
     </row>
     <row r="35">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2263159784328941</v>
+        <v>0.2425935375296568</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1400487915517806</v>
+        <v>-0.1342773467513326</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1806513781000754</v>
+        <v>0.20797130991308</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.1357844191567454</v>
+        <v>-0.1180528407963702</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1799041915630237</v>
+        <v>0.1939641136999246</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.1317800194302017</v>
+        <v>-0.1015433247214843</v>
       </c>
     </row>
     <row r="38">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1487358643906684</v>
+        <v>0.1864063978751334</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.1174463799655584</v>
+        <v>-0.09434591256477487</v>
       </c>
     </row>
     <row r="39">
@@ -5473,21 +5473,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1403231980700927</v>
+        <v>0.1370317386789499</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.1143506533139712</v>
+        <v>-0.09428797780018872</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1239829041302822</v>
+        <v>0.1364183445641207</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.1002023214733994</v>
+        <v>-0.09384285163775241</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5590823197407846</v>
+        <v>0.5687909408215208</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.2137445122134843</v>
+        <v>-0.1970904180343871</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5540522286475964</v>
+        <v>0.5535783187077863</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1717718058058698</v>
+        <v>-0.1551860665389815</v>
       </c>
     </row>
     <row r="47">
@@ -5714,21 +5714,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.4393636805908152</v>
+        <v>0.5139021572240416</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5736,21 +5736,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1139530639601356</v>
+        <v>-0.1179241052604807</v>
       </c>
     </row>
     <row r="48">
@@ -5759,21 +5759,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4339269054671904</v>
+        <v>0.5032690891051099</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1047972985696008</v>
+        <v>-0.1035531138716037</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4317833875681802</v>
+        <v>0.4269888862851456</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.0730173679945485</v>
+        <v>-0.07995593820163427</v>
       </c>
     </row>
     <row r="50">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3849512057317142</v>
+        <v>0.412542779818537</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.0626105656302699</v>
+        <v>-0.07311562072795141</v>
       </c>
     </row>
     <row r="51">
@@ -5894,21 +5894,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.329241624457683</v>
+        <v>0.357966981324807</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.06228470535703778</v>
+        <v>-0.05666884457578569</v>
       </c>
     </row>
     <row r="52">
@@ -5939,21 +5939,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3191847091716611</v>
+        <v>0.348120463279231</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.05652170595915418</v>
+        <v>-0.05236746908423273</v>
       </c>
     </row>
     <row r="53">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2988556095590569</v>
+        <v>0.2952471047018517</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.05409087424769932</v>
+        <v>-0.0507864582639026</v>
       </c>
     </row>
     <row r="54">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2455115359097158</v>
+        <v>0.2755079997262306</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.04363934388911928</v>
+        <v>-0.04482380248617479</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9029851073791024</v>
+        <v>0.9398033533015231</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2621641130839568</v>
+        <v>-0.2575708370182598</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.7813793946667562</v>
+        <v>0.842274784746984</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2227988297546711</v>
+        <v>-0.2296296419420548</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.718548883613614</v>
+        <v>0.7783887913828087</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1995629430359527</v>
+        <v>-0.1877820487345413</v>
       </c>
     </row>
     <row r="62">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6522900142346602</v>
+        <v>0.695364238410596</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1848279573877638</v>
+        <v>-0.1869878276104799</v>
       </c>
     </row>
     <row r="63">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6090983643848624</v>
+        <v>0.6772018864437233</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1520047651138274</v>
+        <v>-0.1409007175074048</v>
       </c>
     </row>
     <row r="64">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5709399089295486</v>
+        <v>0.6221786646658571</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1358322406272239</v>
+        <v>-0.1391623794730976</v>
       </c>
     </row>
     <row r="65">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.563315060253794</v>
+        <v>0.5894590877955688</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06866855776457437</v>
+        <v>-0.06553761190629759</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.4973096737777547</v>
+        <v>0.5244503004839425</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.05775926082669358</v>
+        <v>-0.04812836087416839</v>
       </c>
     </row>
     <row r="67">
@@ -6495,21 +6495,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.4806608229021048</v>
+        <v>0.5242149768876483</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.04846433659906335</v>
+        <v>-0.04762237730334773</v>
       </c>
     </row>
     <row r="68">
@@ -6540,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.4709670828269126</v>
+        <v>0.4939457720935561</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.0466996917568383</v>
+        <v>-0.04264131972239216</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.766749048694595</v>
+        <v>2.870659759625966</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1973855339990094</v>
+        <v>-0.1660867766831391</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.591080794351594</v>
+        <v>2.752211229485098</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6713,21 +6713,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>-0.004343862450550739</v>
+        <v>0.007629007250714803</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.234329277862827</v>
+        <v>2.343069485001402</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6758,21 +6758,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.007173099577562514</v>
+        <v>0.008047345796089234</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.791970828007709</v>
+        <v>1.881386844323893</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.04466435660107071</v>
+        <v>0.04063873973851906</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.422734313932842</v>
+        <v>1.521047447008756</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6848,21 +6848,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1221403555542429</v>
+        <v>0.1251720761678736</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.332386741628867</v>
+        <v>1.399430248326846</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6893,21 +6893,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1246926558565635</v>
+        <v>0.1276161877615094</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.306027159903814</v>
+        <v>1.341628879289763</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1427352329358347</v>
+        <v>0.1610539887246742</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.298298741583929</v>
+        <v>1.325716906385342</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6983,21 +6983,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1578755566606418</v>
+        <v>0.1611388621234899</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.195066839101528</v>
+        <v>1.224829726753839</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,21 +7028,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1768257196267999</v>
+        <v>0.1818633952403903</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.112173453780401</v>
+        <v>1.124042695326255</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,21 +7073,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1796507204203073</v>
+        <v>0.1824969548649971</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -489,16 +489,16 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -609,34 +609,34 @@
         <v>15.79</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.03202612843200425</v>
+        <v>0</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.008165836295095152</v>
+        <v>-0.01374142810016521</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.02168521939473467</v>
+        <v>-0.04649755609430739</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.1278571401323592</v>
+        <v>0.1425470557547552</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3291245631099993</v>
+        <v>0.3647364199081704</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5139021572240416</v>
+        <v>0.4757009573196866</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.8752968905913574</v>
+        <v>0.8241681736762536</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9398033533015231</v>
+        <v>0.9256097962358474</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1.881386844323893</v>
+        <v>1.784832407299326</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4229856581713587</v>
+        <v>0.4069101238323851</v>
       </c>
     </row>
     <row r="3">
@@ -665,34 +665,34 @@
         <v>40</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.03359171088971857</v>
+        <v>0</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.05596617930587211</v>
+        <v>0.05097211131659063</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-0.007197838395073819</v>
+        <v>0.005783242131983224</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1154489492243165</v>
+        <v>0.1117287523321022</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3162224680275894</v>
+        <v>0.3089005464341723</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.357966981324807</v>
+        <v>0.39960488220479</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5545147411724121</v>
+        <v>0.5557188888417419</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7783887913828087</v>
+        <v>0.7415945089520355</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.9055675703720893</v>
+        <v>0.9214913723777369</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2397709363499672</v>
+        <v>0.2432147274793039</v>
       </c>
     </row>
     <row r="4">
@@ -721,34 +721,34 @@
         <v>120.48</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.008538458733284182</v>
+        <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.0903167724609375</v>
+        <v>0.09626935108425227</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.08024750897153332</v>
+        <v>0.08785556078495338</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.04257533664142898</v>
+        <v>0.04510760437803363</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2631579663063595</v>
+        <v>0.2550000349680583</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5535783187077863</v>
+        <v>0.5420454062752822</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5063574616779951</v>
+        <v>0.486485608772169</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4114826527182891</v>
+        <v>0.3802959818374783</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.325716906385342</v>
+        <v>1.32705916904759</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3249076772289528</v>
+        <v>0.3251625136462939</v>
       </c>
     </row>
     <row r="5">
@@ -777,34 +777,34 @@
         <v>101.66</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.01355932770659796</v>
+        <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.07965165365661564</v>
+        <v>0.07690680104745762</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.06651284082651343</v>
+        <v>0.07474371072986985</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.03957462634574482</v>
+        <v>0.043308714234082</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.20797130991308</v>
+        <v>0.2035418405019245</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.5687909408215208</v>
+        <v>0.569032567412993</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4287126555687368</v>
+        <v>0.4085732096474639</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3584039545142776</v>
+        <v>0.3280445887493779</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.224829726753839</v>
+        <v>1.226754161863887</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3054660826441722</v>
+        <v>0.3058423752240338</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>560.61</v>
+        <v>573</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.02758631105711218</v>
+        <v>0.02210095248422594</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.0005889127533271754</v>
+        <v>0.007862329996276785</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.01449513231905541</v>
+        <v>0.01056417017549838</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-0.05632336519287562</v>
+        <v>0.005668919665880789</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.1015433247214843</v>
+        <v>-0.1316603082983875</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.412542779818537</v>
+        <v>0.4555337730979732</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.6576889501227876</v>
+        <v>0.6552424530510803</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.842274784746984</v>
+        <v>0.8133669684588607</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.870659759625966</v>
+        <v>2.943044454230621</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5701036835829725</v>
+        <v>0.5798307320443696</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>192.59</v>
+        <v>190.61</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.004118838756846266</v>
+        <v>-0.01028088563886387</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.01473374361706126</v>
+        <v>-0.02610872970815736</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.00135181461218048</v>
+        <v>-0.000524388338288273</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.05039536365850084</v>
+        <v>0.02837871234759115</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2425935375296568</v>
+        <v>0.2489843604710456</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1424727024347467</v>
+        <v>0.1093335642258662</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5303387184942865</v>
+        <v>0.5486293090944254</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4780227231049305</v>
+        <v>0.4673395869634622</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3764790665018007</v>
+        <v>0.3619447311853279</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1123886193088206</v>
+        <v>0.1084594952344937</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>158.25</v>
+        <v>156.72</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.02639776571255514</v>
+        <v>-0.009668238731733836</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.009118687724741559</v>
+        <v>0.003329092718441284</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.03729166991558752</v>
+        <v>-0.0432818292140843</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.008023561644150079</v>
+        <v>-0.02117293970848477</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1364183445641207</v>
+        <v>0.1147942155055659</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2755079997262306</v>
+        <v>0.2953004632260816</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.3141176896929845</v>
+        <v>0.311497603096476</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.695364238410596</v>
+        <v>0.6284369803271792</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.065229618544522</v>
+        <v>1.076500010058209</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2734721400896583</v>
+        <v>0.2757844738021193</v>
       </c>
     </row>
     <row r="9">
@@ -1001,34 +1001,34 @@
         <v>28.34</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.01142040291207613</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.04306220364403979</v>
+        <v>0.04460011165688149</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.003866453687229932</v>
+        <v>0.01979126372584039</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.01649931871119326</v>
+        <v>0.0212612667599239</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.289353991938458</v>
+        <v>0.3029885127626617</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.4269888862851456</v>
+        <v>0.4191287494755269</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2534276597769287</v>
+        <v>0.2440737181014161</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2044198608405612</v>
+        <v>0.1887583880535972</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4511008272501806</v>
+        <v>0.4653567698548187</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1321375540002143</v>
+        <v>0.1358329372950091</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>499.27</v>
+        <v>506.66</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.04057941166331247</v>
+        <v>0.0148016400165305</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.01794194909182401</v>
+        <v>0.002155975081788553</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.04336286984117432</v>
+        <v>0.03094921370898374</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.09114580295269525</v>
+        <v>-0.02140067752396302</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.1581072592931696</v>
+        <v>-0.2034487083308625</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.5032690891051099</v>
+        <v>0.5425026300310289</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.5936724689637194</v>
+        <v>0.5903971146799756</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.6221786646658571</v>
+        <v>0.5824622543010014</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.521047447008756</v>
+        <v>1.563749630738493</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3610069400879758</v>
+        <v>0.3686483250990342</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>155.64</v>
+        <v>154.72</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.01885313554841495</v>
+        <v>-0.005911065102500279</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.02105889174117381</v>
+        <v>-0.008522920891027241</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.01698906310492632</v>
+        <v>0.0003232886296615778</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0</v>
+        <v>0.02165873432659216</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.01280701512246551</v>
+        <v>-0.01775964965440491</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.348120463279231</v>
+        <v>0.3614908963984587</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4955933613986172</v>
+        <v>0.4749161573658169</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5242149768876483</v>
+        <v>0.4975880657662486</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.341628879289763</v>
+        <v>1.325133922337083</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3279223746045616</v>
+        <v>0.3247969637557717</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>207.07</v>
+        <v>204.56</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.02307318956799387</v>
+        <v>-0.01212155153737438</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.02191641086513707</v>
+        <v>0.0080865480743888</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.03147122231532828</v>
+        <v>-0.03467816926732414</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.02550953591456739</v>
+        <v>0.004966569566194901</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1939641136999246</v>
+        <v>0.1781329194268173</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2389200041922581</v>
+        <v>0.2492353281025774</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2371608643517575</v>
+        <v>0.2320188197011717</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4715299029653022</v>
+        <v>0.4270741021177493</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6493326515066578</v>
+        <v>0.6470320839715777</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1815064193165576</v>
+        <v>0.1809568232757424</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>67.75</v>
+        <v>87.28</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.01437339528841775</v>
+        <v>0.007735806075785057</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.003822998501156638</v>
+        <v>-0.01411950770626602</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.04617765501430493</v>
+        <v>-0.03728220545202943</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.03791533993709706</v>
+        <v>0.01998362849796864</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.1194378889218468</v>
+        <v>0.02452729648426621</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2501216669005919</v>
+        <v>0.1687788358006665</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2291033640267945</v>
+        <v>0.2961685296315368</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4764337224239865</v>
+        <v>0.7014056421108741</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.6537014677971886</v>
+        <v>1.442222835389073</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1825487062488025</v>
+        <v>0.3466717897526526</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>86.61</v>
+        <v>398.71</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.02874448389082263</v>
+        <v>-0.004717959609688904</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.0225708157795268</v>
+        <v>-0.05220248953263862</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.05084930837970891</v>
+        <v>-0.06741049144272204</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.008358092032829334</v>
+        <v>-0.05179671165812294</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.001663417537743239</v>
+        <v>0.03429401944435817</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.115445010358904</v>
+        <v>0.03998640089994132</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.293702024551532</v>
+        <v>0.4355040932141105</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6772018864437233</v>
+        <v>0.5699594055439274</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1.399430248326846</v>
+        <v>0.1705157267459414</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3387599444062275</v>
+        <v>0.05388304531168964</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>400.6</v>
+        <v>66.94</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.001875703360139092</v>
+        <v>-0.01195568352167897</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.0466898173818312</v>
+        <v>-0.00844318881332573</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.06796024201623208</v>
+        <v>-0.05625261309181728</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.06094702210034908</v>
+        <v>-0.07605237734892167</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.008763122051563377</v>
+        <v>0.0977190198077631</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.03881959658520939</v>
+        <v>0.2640358829930212</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.4209372179839495</v>
+        <v>0.216386494915179</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.5894590877955688</v>
+        <v>0.4299840034682241</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.1818633952403903</v>
+        <v>0.6479488821731838</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.05727775294101511</v>
+        <v>0.1811759038620564</v>
       </c>
     </row>
     <row r="16">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>108.37</v>
+        <v>95.2</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.02052924244331433</v>
+        <v>0.001999734846224843</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.002393395134029253</v>
+        <v>-0.01203822804858679</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.02237253731778843</v>
+        <v>-0.04119250608895453</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.0006463498878275242</v>
+        <v>0.08762707958313687</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.006875457698114484</v>
+        <v>0.1385559472182418</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.1985180816316543</v>
+        <v>0.0849127956641933</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2935434897373175</v>
+        <v>0.1756661710448375</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.5244503004839425</v>
+        <v>0.5032387317818325</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.7598466321402726</v>
+        <v>2.776882209033695</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2073270761611745</v>
+        <v>0.5573198293850297</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>30.71</v>
+        <v>106.09</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.0003256782177436524</v>
+        <v>-0.0210390915466071</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.03881069323494801</v>
+        <v>-0.02642933697852734</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.03275593434731794</v>
+        <v>-0.04414813605000001</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.01086240726866849</v>
+        <v>-0.005623826879609939</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1321797968755944</v>
+        <v>0.007024184855126681</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.031504386407748</v>
+        <v>0.1979448877886265</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.3175224050386491</v>
+        <v>0.2699098706814005</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3236735135469313</v>
+        <v>0.4892834865875435</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2597432267873367</v>
+        <v>0.7272260516548286</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.08000892390526837</v>
+        <v>0.199820818536804</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>95.01000000000001</v>
+        <v>30.44</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.04486969995998624</v>
+        <v>-0.008791877514302993</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.01237000883328476</v>
+        <v>-0.04366947511718988</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.06264797194044802</v>
+        <v>-0.03149856065878354</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.04728836924385238</v>
+        <v>-0.009759246561296675</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1069346530700153</v>
+        <v>0.1389256751862518</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.00988250455933759</v>
+        <v>0.01434236350084639</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.1642287776699645</v>
+        <v>0.344181034119718</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.4939457720935561</v>
+        <v>0.320368057361325</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.752211229485098</v>
+        <v>0.2505625809941889</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.5539215620477853</v>
+        <v>0.07737892664560908</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>56.55</v>
+        <v>95.48</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.002117503719111236</v>
+        <v>-0.004587101964250939</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.0001791338836260037</v>
+        <v>-0.01668378107770263</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.02276129879117472</v>
+        <v>-0.038081792242045</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.007641678595850188</v>
+        <v>0.0734121037968225</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.08105749083843583</v>
+        <v>0.1571930782317597</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2952471047018517</v>
+        <v>0.08364547378877418</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1891345017099544</v>
+        <v>0.122603633862407</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.1925809711314701</v>
+        <v>0.39807311255597</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.1824969548649971</v>
+        <v>2.324378718831347</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.05746664359163756</v>
+        <v>0.4924627408571669</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>95.92</v>
+        <v>56.16</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.03362063593303288</v>
+        <v>-0.006896541024050906</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.00114548174268303</v>
+        <v>-0.006022466636243728</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.0548822525575462</v>
+        <v>-0.01969779245663072</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.04385677229366558</v>
+        <v>-0.003382621484263271</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.1370317386789499</v>
+        <v>0.07647636301204996</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.02085993085962645</v>
+        <v>0.3029733834933299</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1256744461398429</v>
+        <v>0.1863871128861871</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.4071749837568128</v>
+        <v>0.1794358306538608</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>2.343069485001402</v>
+        <v>0.174579048206865</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.4952545563415325</v>
+        <v>0.0551011180773513</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>55.01</v>
+        <v>54.98</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.005116001857094821</v>
+        <v>-0.0005453332160006985</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01327357270792462</v>
+        <v>-0.01663388137567356</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.007398048736166341</v>
+        <v>-0.01328071899237226</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.005851155656601881</v>
+        <v>-0.005966404318587526</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.107549548694331</v>
+        <v>0.1056348751735336</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.08510443776015753</v>
+        <v>0.08761073212791692</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2383951824971344</v>
+        <v>0.2443286720972402</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2472903374520337</v>
+        <v>0.2447849871403307</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6800977402717603</v>
+        <v>0.6675597233591444</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1888074440955161</v>
+        <v>0.185842830841928</v>
       </c>
     </row>
     <row r="22">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>65.76000000000001</v>
+        <v>65.08</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01387606409820585</v>
+        <v>-0.01034063690823905</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.03007521897013565</v>
+        <v>0.00711852468153884</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01387606409820585</v>
+        <v>0.01354933435581396</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.03559058482252708</v>
+        <v>0.03432936625823779</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1029100525038362</v>
+        <v>0.07652104699667506</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.2486525545797789</v>
+        <v>0.2449591083405676</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1207656834047381</v>
+        <v>0.1025997581307718</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.01876705865221462</v>
+        <v>0.002950238880931488</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.9851500016352341</v>
+        <v>0.9652138574139533</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2567949958431981</v>
+        <v>0.2525736536570797</v>
       </c>
     </row>
     <row r="23">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>105.78</v>
+        <v>104.35</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.00781249716060195</v>
+        <v>-0.01351862659933833</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.04525693645422812</v>
+        <v>0.02787629949402648</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.0109396746360968</v>
+        <v>-0.002103865557475104</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.03716051568693768</v>
+        <v>0.0234405591517155</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.1864063978751334</v>
+        <v>0.1712874931361994</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2369908623706305</v>
+        <v>0.2374859534550429</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.01050466577239506</v>
+        <v>-0.01705063222729253</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>-0.06553761190629759</v>
+        <v>-0.09534919837644729</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.5031800341795536</v>
+        <v>0.4834493550035341</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1455226116612289</v>
+        <v>0.1404884935842077</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>291.6</v>
+        <v>72.75</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.01018500105351516</v>
+        <v>0.0001375053137779858</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.0213660458967273</v>
+        <v>-0.01556159001534241</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.006202737512541856</v>
+        <v>-0.03347943078855631</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.01624034161309029</v>
+        <v>-0.05335066435299607</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.1097579360101835</v>
+        <v>0.02029365619543344</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1914684953770682</v>
+        <v>0.1753504099864789</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1009590811403984</v>
+        <v>0.09752283300401654</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.02546075792978431</v>
+        <v>0.1261450573029101</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.7451673498983142</v>
+        <v>0.8454760474887231</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2039608356875504</v>
+        <v>0.2265995592012631</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>72.73999999999999</v>
+        <v>288.14</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0</v>
+        <v>-0.01186553972104465</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.01449667701146862</v>
+        <v>-0.002699704911553247</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.02844937631459798</v>
+        <v>-0.009385569204723665</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.06008530252683897</v>
+        <v>0.01543559603916789</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.0283260050017522</v>
+        <v>0.08453787485633146</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1598158634902365</v>
+        <v>0.186005426087009</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1004704903016347</v>
+        <v>0.07526966949976654</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1560400120160939</v>
+        <v>0.007693964426967792</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8100933327473201</v>
+        <v>0.7309864413482183</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2187098546349557</v>
+        <v>0.2006909079964159</v>
       </c>
     </row>
     <row r="26">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>143.58</v>
+        <v>142.7</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.001946328222639626</v>
+        <v>-0.006129021253586386</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.005600897699644669</v>
+        <v>-0.005697683406345022</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.02561362160751623</v>
+        <v>-0.01621718571661501</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.001337861403220009</v>
+        <v>-0.01234976384861386</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.06696170001619217</v>
+        <v>0.06555120133317138</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1105322994268809</v>
+        <v>0.1229713584868299</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0717765493854603</v>
+        <v>0.06598613828544919</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.1286496752555701</v>
+        <v>0.113887403359533</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6381233494134053</v>
+        <v>0.6128851281678052</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1788237223484332</v>
+        <v>0.1727383998651681</v>
       </c>
     </row>
     <row r="27">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>66.68000000000001</v>
+        <v>66.62</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.001497431505675495</v>
+        <v>-0.0008997834181037057</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.01883459088493911</v>
+        <v>-0.02087004923336588</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.03516134110425406</v>
+        <v>-0.03922690705165588</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.06163801581623141</v>
+        <v>-0.05637387837901942</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.02567460440870062</v>
+        <v>0.01929346477975558</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1581884308122072</v>
+        <v>0.1706178965571004</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.08440717264462538</v>
+        <v>0.08049679245153452</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.128134601456501</v>
+        <v>0.1005733254920367</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8762850124327042</v>
+        <v>0.8960488672422042</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2333876717856278</v>
+        <v>0.2377031857082037</v>
       </c>
     </row>
     <row r="28">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>129.78</v>
+        <v>128.96</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.005364783653916461</v>
+        <v>-0.006318323879969889</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.0006168221506328564</v>
+        <v>-0.006777492674394314</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.03973359496634943</v>
+        <v>-0.0304487479154103</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.01397961104809642</v>
+        <v>-0.02642306977652886</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.07241442919742114</v>
+        <v>0.07492649050333688</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.08121746039312905</v>
+        <v>0.08980994689520094</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.03590730200194936</v>
+        <v>0.02758832794635668</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1041903609682484</v>
+        <v>0.08562781814964637</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.611312753180729</v>
+        <v>0.5853621843517121</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1723571815456508</v>
+        <v>0.1660293932552348</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>91.13</v>
+        <v>178.25</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.002089232536959029</v>
+        <v>0.007973330079781515</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.003689768815581362</v>
+        <v>-0.01399490428355177</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02768066914141065</v>
+        <v>-0.00413433974218369</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.03097002532301163</v>
+        <v>-0.02998473373719523</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.02943101412553539</v>
+        <v>-0.08070104364560071</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.04601145546553354</v>
+        <v>0.07481912133766477</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1086740074011281</v>
+        <v>0.1836580142177267</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1229558941032785</v>
+        <v>0.2038625280347186</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4011411509481282</v>
+        <v>0.8767163979127304</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1189928102362225</v>
+        <v>0.2334821891888961</v>
       </c>
     </row>
     <row r="30">
@@ -2174,37 +2174,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>23.45</v>
+        <v>23.38</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.01823708483593278</v>
+        <v>-0.002985142852680922</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.002127627108959418</v>
+        <v>-0.01141651002616173</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.006776782857936814</v>
+        <v>-0.01225183416107323</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.03656529926331209</v>
+        <v>-0.02866641224785671</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.04334805933060104</v>
+        <v>-0.05465804748375847</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.02309520093900685</v>
+        <v>-0.01703450396214101</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1749195134213741</v>
+        <v>0.1592582511843339</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.26537418508027</v>
+        <v>0.2622703406059774</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.5741260370787669</v>
+        <v>0.5734875843755609</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1632681413914472</v>
+        <v>0.1631108494286988</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>176.84</v>
+        <v>89.72</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.01492189372565522</v>
+        <v>-0.01547235899496269</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.002256878486098124</v>
+        <v>-0.01995724400154275</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.003942756419473503</v>
+        <v>-0.03225379059538824</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.06532769983993592</v>
+        <v>-0.04404304520582281</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.07064424205138209</v>
+        <v>0.01293453745020834</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.05454430307989666</v>
+        <v>0.04754173609952472</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.185975157057934</v>
+        <v>0.09613518433265411</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2062151158730394</v>
+        <v>0.09988097493926684</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.8580796074578834</v>
+        <v>0.3962874444457769</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.2293855541352223</v>
+        <v>0.1176992107847317</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>80.8</v>
+        <v>72.38</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.007984023957211539</v>
+        <v>-0.009036194603456948</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.0127725239025146</v>
+        <v>-0.01157151110303078</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.03131248310155099</v>
+        <v>-0.02232243933410683</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.07258048485184965</v>
+        <v>-0.02192853359967861</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.02805722178797854</v>
+        <v>0.01729281472331956</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.08024893848019987</v>
+        <v>0.03903680419268785</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0912756009754343</v>
+        <v>0.09269398561632336</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1651042272883392</v>
+        <v>0.08710769492385428</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3828997127157585</v>
+        <v>0.206391349681327</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1141155319615381</v>
+        <v>0.06454184696851017</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>111.32</v>
+        <v>184.8</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.02344399310892475</v>
+        <v>0.01254730488108202</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.03006009452951053</v>
+        <v>-0.02732505118949569</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.05963843320151718</v>
+        <v>-0.05678362052073482</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.05740896585009314</v>
+        <v>-0.02676313329630375</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.05907459241807167</v>
+        <v>-0.004275733596293518</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.006275959600919645</v>
+        <v>0.1371866870021661</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1046429582123465</v>
+        <v>0.05206212308004488</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.2732412725732782</v>
+        <v>0.06043257158983018</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>1.124042695326255</v>
+        <v>0.9943635721561321</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.2854477075166471</v>
+        <v>0.2587363606131861</v>
       </c>
     </row>
     <row r="34">
@@ -2401,34 +2401,34 @@
         <v>13.31</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.01603053679632116</v>
+        <v>0</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.02542379730496624</v>
+        <v>0.01992338889515333</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.002996251738580424</v>
+        <v>-0.001500337899761561</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.009863437893083082</v>
+        <v>0.0068078782730705</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.09936028340895153</v>
+        <v>0.09758143615528736</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.08856709283640796</v>
+        <v>0.09278634249131112</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.007642404061993568</v>
+        <v>-0.004918033371299813</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.03383768500078643</v>
+        <v>-0.04498573180027021</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.1610539887246742</v>
+        <v>0.1574302141966404</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.05103570933578716</v>
+        <v>0.04994110454135092</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>73.04000000000001</v>
+        <v>80.27</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.00191308266007939</v>
+        <v>-0.006559485008334698</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.0004295990506393288</v>
+        <v>-0.02056158514663253</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.02207434871176528</v>
+        <v>-0.04418351525628117</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.002287438793894814</v>
+        <v>-0.0664763089665007</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.01944707169960957</v>
+        <v>-0.04156458971556254</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.02211357115212653</v>
+        <v>0.08823302772012265</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.09565936417759446</v>
+        <v>0.07819238446846977</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.08574389256946668</v>
+        <v>0.1447099124642792</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.2198802724371951</v>
+        <v>0.3876238132710272</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.06849477478122967</v>
+        <v>0.1153827272453718</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>100.96</v>
+        <v>70.5</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.007987174452010581</v>
+        <v>-0.00564177034231661</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.008835671711035165</v>
+        <v>-0.01384806117432058</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.03183735839747015</v>
+        <v>-0.04960906295546375</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.08740846433173488</v>
+        <v>-0.04755467174688299</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.09434591256477487</v>
+        <v>-0.1381247191968047</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.1225205650779724</v>
+        <v>0.01948248601857006</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.09822890333291356</v>
+        <v>0.1124305218183808</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.195650472910214</v>
+        <v>0.3517768174193965</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.3313818582540715</v>
+        <v>0.25789030233156</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1001051850529071</v>
+        <v>0.07947914480247475</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>70.90000000000001</v>
+        <v>100.74</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.01503225590114843</v>
+        <v>-0.002179092934807336</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.01267227494294687</v>
+        <v>-0.0163070573051618</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.0478108729836948</v>
+        <v>-0.04529945916759048</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.07004192664633158</v>
+        <v>-0.06989197549126513</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.1428340438869102</v>
+        <v>-0.1115226639827023</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-0.006075099312221055</v>
+        <v>0.1338931899219287</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.1222592262840143</v>
+        <v>0.08562178111557106</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.3581534909918798</v>
+        <v>0.1835884291849064</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.2582530926058477</v>
+        <v>0.3418379863049976</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.07958291296377307</v>
+        <v>0.1029776037727936</v>
       </c>
     </row>
     <row r="38">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2622,37 +2622,37 @@
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>226.3</v>
+        <v>108.68</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.007120632511108393</v>
+        <v>-0.02371540960192065</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.00619210232548606</v>
+        <v>-0.04356241369259817</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.04162961770120299</v>
+        <v>-0.08379701746122803</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.03472103440061547</v>
+        <v>-0.04356241369259817</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.03199916089345789</v>
+        <v>-0.07063446958514397</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.01510494922968419</v>
+        <v>0.008449082751214698</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1056056037400412</v>
+        <v>0.06474531862108845</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1130997975813333</v>
+        <v>0.2243493027823555</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.3276820802899223</v>
+        <v>1.089866624688113</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.09908521198153131</v>
+        <v>0.2785160669057811</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>93.81</v>
+        <v>223.49</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.003530104726249705</v>
+        <v>-0.01241713442642356</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.003293722683189615</v>
+        <v>-0.02171149713870146</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.02948485408171808</v>
+        <v>-0.05083666388937613</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.04255976378311432</v>
+        <v>-0.03501727286970246</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.01017846608809447</v>
+        <v>-0.04254976026223289</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.02473227364821318</v>
+        <v>0.02706304170278284</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.07965559869874417</v>
+        <v>0.09007944594295481</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.05858874853039131</v>
+        <v>0.0980012020060621</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.2913457870743006</v>
+        <v>0.3167124909786756</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.08896565657156175</v>
+        <v>0.09604987912200302</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>182.51</v>
+        <v>92.91</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.007451925466089637</v>
+        <v>-0.009593795116797033</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.03563241271955209</v>
+        <v>-0.01993670178065876</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.07599699213641742</v>
+        <v>-0.03238901363970836</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.04184274508581898</v>
+        <v>-0.04824829903661898</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.02442538567739938</v>
+        <v>-0.0191616219549805</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.1122023009180686</v>
+        <v>0.03013129164112405</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.03540520127510671</v>
+        <v>0.07494895539401858</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.04362330084753463</v>
+        <v>0.04615993097246429</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.9727105331928909</v>
+        <v>0.2904715515870187</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2541643581715025</v>
+        <v>0.08871985942260618</v>
       </c>
     </row>
     <row r="41">
@@ -2793,34 +2793,34 @@
         <v>52.91</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.00303317246278878</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.008433297559823361</v>
+        <v>-0.02163465133188514</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.03254706205875779</v>
+        <v>-0.04079042795910304</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.09909756070470765</v>
+        <v>-0.07677545664707486</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.08584371345980291</v>
+        <v>-0.09489783533059959</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.04192618030109996</v>
+        <v>0.05352379551882214</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1144567127186955</v>
+        <v>0.1047657485029749</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1539831901646631</v>
+        <v>0.136290213766965</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.7465012779518119</v>
+        <v>0.7408747262162132</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.2042675088792101</v>
+        <v>0.2029728895558518</v>
       </c>
     </row>
     <row r="42">
@@ -2846,37 +2846,37 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>71.59</v>
+        <v>70.62</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.01244516001713825</v>
+        <v>-0.01354928957853851</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.01546094096298756</v>
+        <v>-0.001978510251863796</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.005195101247484235</v>
+        <v>-0.01547470456439437</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0.006325512399535826</v>
+        <v>-0.003386930026846091</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.0667560078497158</v>
+        <v>0.04964334167486539</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.0093253028558693</v>
+        <v>0.0195758501546055</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.01613832428601869</v>
+        <v>-0.0001605134529392149</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.02568313948809819</v>
+        <v>-0.02960213530817191</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.008047345796089234</v>
+        <v>-0.004947471213657462</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.002675285066039423</v>
+        <v>-0.001651884290417294</v>
       </c>
     </row>
     <row r="43">
@@ -2905,34 +2905,34 @@
         <v>28.17</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.01330938307149832</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.01185344547045131</v>
+        <v>0</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.008796622073500071</v>
+        <v>-0.02187497143944028</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.08687196992015411</v>
+        <v>-0.07091027836973529</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.06876032805639853</v>
+        <v>-0.09129032011955018</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.1236537861669671</v>
+        <v>0.1455876332448616</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.003204929218225017</v>
+        <v>-0.0048797917369785</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.09867430300667879</v>
+        <v>0.0961300709176276</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.5778184213154938</v>
+        <v>0.6072852415728272</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.164176979865114</v>
+        <v>0.1713795890820653</v>
       </c>
     </row>
     <row r="44">
@@ -2961,34 +2961,34 @@
         <v>56.96</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.005294727106750052</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.01466963300709656</v>
+        <v>-0.01990177305774543</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.0288843349922342</v>
+        <v>-0.03445605018438924</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.07876132675152436</v>
+        <v>-0.06399258100639349</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.0706816059931572</v>
+        <v>-0.07697801723991382</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>-0.006451134677616932</v>
+        <v>0.006443054025132788</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.09434720885696057</v>
+        <v>0.08733085234941607</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.1268241900423019</v>
+        <v>0.1131958283752876</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.575723569968885</v>
+        <v>0.5777763548080597</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1636615302227107</v>
+        <v>0.1641666336608978</v>
       </c>
     </row>
     <row r="45">
@@ -3014,37 +3014,37 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>46.95</v>
+        <v>46.54</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.0004261763825614828</v>
+        <v>-0.008732690963782597</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.001066081778972938</v>
+        <v>-0.01041883641266927</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.02431417695169691</v>
+        <v>-0.02778353971241787</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.01737124398414724</v>
+        <v>-0.0318285581237816</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.006619515314238766</v>
+        <v>0.003190261897823454</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.03605789451012487</v>
+        <v>-0.02821658498895807</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.03828174654125727</v>
+        <v>0.02763790926648557</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.01608728090014533</v>
+        <v>0.007859951192218606</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.1251720761678736</v>
+        <v>0.11010554034491</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.04009493591191959</v>
+        <v>0.0354316201282403</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>62.13</v>
+        <v>112.35</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.003208739885513845</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.004486440954677984</v>
+        <v>-0.002220248697938132</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.04282856935990198</v>
+        <v>0.002856375063027716</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.08940351734862506</v>
+        <v>0.01692609576726767</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.03945374093299447</v>
+        <v>0.02916657290025326</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.05960070889839764</v>
+        <v>-0.005791561575352322</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.02779072480954614</v>
+        <v>-0.02663717614945826</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.01564435862713021</v>
+        <v>-0.04336579943859387</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.5761267845246809</v>
+        <v>0.720169260870835</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.163760778859914</v>
+        <v>0.1981845838437533</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>17.73</v>
+        <v>61.77</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.02367204703442516</v>
+        <v>-0.005794311993603252</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.005050513699729753</v>
+        <v>-0.020922486790802</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.005672171652297386</v>
+        <v>-0.04661213790845786</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.0209829406575518</v>
+        <v>-0.08866920079333096</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-0.1342773467513326</v>
+        <v>-0.05523016834237326</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.05236746908423273</v>
+        <v>0.07278727254598438</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.1110992113101446</v>
+        <v>0.01365659647845763</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.1896348636420877</v>
+        <v>0.004533374641328525</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.1852849168657362</v>
+        <v>0.5725989840468848</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.05829705105396021</v>
+        <v>0.1628918591821096</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>112.35</v>
+        <v>17.56</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.00575222589273372</v>
+        <v>-0.009588273022171911</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0.007623304700637545</v>
+        <v>-0.02008931968855299</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.009084484073453525</v>
+        <v>-0.01181772574066198</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0.01380616119391975</v>
+        <v>-0.01014657877667124</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.03152272536073508</v>
+        <v>-0.1677725522050802</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.02052756841203618</v>
+        <v>-0.04152803790371862</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>-0.02108999415018076</v>
+        <v>0.08820342892048871</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.04264131972239216</v>
+        <v>0.1797951193770055</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.7213952453711447</v>
+        <v>0.1906576314693249</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.1984691695759544</v>
+        <v>0.0598936737628375</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>82.81999999999999</v>
+        <v>35.12</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.001087831913922921</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.009685490675544028</v>
+        <v>-0.004676788734100046</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.04508248023487238</v>
+        <v>-0.02322667779560794</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.0539182221994462</v>
+        <v>-0.03926121993290521</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.01834779339061654</v>
+        <v>-0.08437412996172355</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.03562747652199438</v>
+        <v>0.008107958338663179</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>-0.04415546564408268</v>
+        <v>-0.002142017726497469</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-0.04762237730334773</v>
+        <v>0.007258460115290077</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.3799049329257027</v>
+        <v>0.3886794974726697</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.1133107153244461</v>
+        <v>0.1156655112469454</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>35.12</v>
+        <v>82.03</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.01137674089504759</v>
+        <v>-0.009538769843496109</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0.01021298544521732</v>
+        <v>-0.03255103321652442</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.01940797732955646</v>
+        <v>-0.06347754071304312</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.07152295182930979</v>
+        <v>-0.058533210546165</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.06537481516017551</v>
+        <v>-0.04841998313114604</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>-0.006993728923317177</v>
+        <v>0.04353941512955295</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.008121758921532107</v>
+        <v>-0.05381525425846834</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.02660062801477658</v>
+        <v>-0.06555445787817316</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.3935960679134545</v>
+        <v>0.3888762260794811</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1169806184753519</v>
+        <v>0.1157181926992343</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>43.78</v>
+        <v>213.84</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.008755696775526234</v>
+        <v>-0.0001870607069781594</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.005677947011834883</v>
+        <v>-0.02247436947299253</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.03120159084445617</v>
+        <v>-0.05107094126353218</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.03269994690945877</v>
+        <v>-0.1509839533374372</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.0247271246478904</v>
+        <v>-0.1041973460773032</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.05666884457578569</v>
+        <v>-0.07428524095159939</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>-0.02959841091981918</v>
+        <v>0.02942240928255124</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>-0.04812836087416839</v>
+        <v>0.0562014960536632</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.2456732291916985</v>
+        <v>0.9886656054182135</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.0759730088376469</v>
+        <v>0.2575364658493893</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>213.88</v>
+        <v>43.31</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.006457004515543874</v>
+        <v>-0.01073543670878574</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.01920146539984979</v>
+        <v>-0.01746824922364687</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.05244736973571451</v>
+        <v>-0.04329576020882331</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.1475798367764296</v>
+        <v>-0.03862370462235465</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.1180528407963702</v>
+        <v>-0.03412129291013333</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.07995593820163427</v>
+        <v>-0.05560399483477019</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.04695955128640361</v>
+        <v>-0.04506758105916941</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.06930645030986748</v>
+        <v>-0.05284270897605015</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.9930222806708473</v>
+        <v>0.2415542062640139</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.2584541133474854</v>
+        <v>0.07478573880540917</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>41.69</v>
+        <v>51.77</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.008954475668379924</v>
+        <v>0.001353959260952164</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.01952026862932776</v>
+        <v>0.01908379893302237</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.03114106880320455</v>
+        <v>-0.03317203142448522</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.05636038164932033</v>
+        <v>-0.06473690478192307</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>-0.05631556660356318</v>
+        <v>0.05667384160553568</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.1035531138716037</v>
+        <v>-0.05822639326501711</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.004535197789366618</v>
+        <v>-0.166352207844924</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.01606613848896643</v>
+        <v>-0.1414112273657304</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.4051592831552464</v>
+        <v>0.04266722598494366</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.1200614557995627</v>
+        <v>0.01402479427231151</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>51.7</v>
+        <v>41.1</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.003853579134091678</v>
+        <v>-0.01415207896432746</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.01730595866026041</v>
+        <v>-0.03043172762683166</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.03949402237119337</v>
+        <v>-0.04596107875525401</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.05989696413930301</v>
+        <v>-0.06633352915214674</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.06985280100107727</v>
+        <v>-0.07590609785510327</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.07311562072795141</v>
+        <v>-0.1086748711691908</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1668111889444607</v>
+        <v>-0.02816881462699061</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.1391623794730976</v>
+        <v>0.0009746714560063818</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.04063873973851906</v>
+        <v>0.3863063664914352</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.01336677969566913</v>
+        <v>0.1150296241779416</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>241.32</v>
+        <v>18.88</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.004003409091553167</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.01365158296369262</v>
+        <v>-0.02500125373274908</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.0496592986857719</v>
+        <v>-0.02550464631281701</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.181605414859816</v>
+        <v>-0.01533729542569673</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.1548280642980912</v>
+        <v>-0.03055980145548243</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.1179241052604807</v>
+        <v>0.05211814036278106</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.05531507482957965</v>
+        <v>-0.09644473905746964</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.08639742855604116</v>
+        <v>-0.1877486489339296</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1.103717419455247</v>
+        <v>0.1686387573236725</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.2813343465238016</v>
+        <v>0.05331942921412147</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>42.68</v>
+        <v>25.4</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0.0316654920742907</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.05155554877387147</v>
+        <v>-0.02883474340292902</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.06608315989816682</v>
+        <v>-0.07486339701491962</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.05679557336628105</v>
+        <v>-0.02326921316293573</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.09384285163775241</v>
+        <v>0.01877982805390177</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.1551860665389815</v>
+        <v>0.04902809858282686</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.0470008942498128</v>
+        <v>-0.1469120358481253</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.003757798468028373</v>
+        <v>-0.2679797875835751</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.8258980098696651</v>
+        <v>0.2183509580369993</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.2222466016548086</v>
+        <v>0.06804807854609773</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>18.88</v>
+        <v>239.86</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.01332980512040871</v>
+        <v>-0.006050085652059667</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.01615842974052206</v>
+        <v>-0.02480080475283097</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.03120668315074848</v>
+        <v>-0.05163687194821953</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.03031082188352563</v>
+        <v>-0.1741211078081836</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.03600612494653244</v>
+        <v>-0.1561000207975813</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.03765802341016089</v>
+        <v>-0.1144622918788809</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.08800966406356991</v>
+        <v>0.02998889841231511</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.1877820487345413</v>
+        <v>0.05957344381312746</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.1611388621234899</v>
+        <v>1.090182059457864</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.05106131905484301</v>
+        <v>0.2785803880970577</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>25.4</v>
+        <v>17.68</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.009741584212704435</v>
+        <v>0</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.01607900103703308</v>
+        <v>-0.005512407100169203</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.09027405964948243</v>
+        <v>-0.06849311213984222</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.03569389251519728</v>
+        <v>-0.1190831801688959</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.0290830503623547</v>
+        <v>-0.01848665819567985</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.01959643435533742</v>
+        <v>0.09108860707642341</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.1342095177105972</v>
+        <v>-0.1621249966442198</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.2575708370182598</v>
+        <v>-0.2323056978705195</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.2063783878015857</v>
+        <v>0.01745669086069457</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.06453803435473926</v>
+        <v>0.005785361994010474</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>17.68</v>
+        <v>41.65</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.0004526606929269317</v>
+        <v>-0.0241330546375832</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.0001130472490038503</v>
+        <v>-0.04318854367420999</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.06898364832709247</v>
+        <v>-0.09574467468360415</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.1200039493158475</v>
+        <v>-0.04516271100973956</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.01449276594993665</v>
+        <v>-0.1282963041027557</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.06969992955919557</v>
+        <v>-0.1512125171202713</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.1524448807349381</v>
+        <v>-0.007319342597493783</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.2296296419420548</v>
+        <v>-0.04553282126171032</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.007629007250714803</v>
+        <v>0.7765105602111708</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.002536562825726785</v>
+        <v>0.2111258242449228</v>
       </c>
     </row>
     <row r="60">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>97.06999999999999</v>
+        <v>96.39</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0.002789221431346967</v>
+        <v>-0.007005257106352247</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>0.001650975406756627</v>
+        <v>-0.02102376309234255</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.05084577216122099</v>
+        <v>-0.06644068387749702</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.1027821655943156</v>
+        <v>-0.09023122070748069</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.09428797780018872</v>
+        <v>-0.1306818021527582</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.04482380248617479</v>
+        <v>-0.02780042484574241</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.07516597630265098</v>
+        <v>-0.08794903730628978</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1409007175074048</v>
+        <v>-0.1522060339783795</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2583349182240877</v>
+        <v>0.2466688395005008</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.07960631462145917</v>
+        <v>0.07625959136470484</v>
       </c>
     </row>
     <row r="61">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>88.55</v>
+        <v>87.41</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.004879712798153024</v>
+        <v>-0.0128740751028783</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>0.01221609104621946</v>
+        <v>-0.01554522037360984</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.04616856293219673</v>
+        <v>-0.06135578453940371</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.08730877319960062</v>
+        <v>-0.08446112840825748</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.06777634103836716</v>
+        <v>-0.1118581584408213</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.0507864582639026</v>
+        <v>-0.0335717503766555</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.1026786062882092</v>
+        <v>-0.1144081195846215</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.1869878276104799</v>
+        <v>-0.1994846854773143</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1276161877615094</v>
+        <v>0.1084698892875329</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.04084749329042903</v>
+        <v>0.03492282847404837</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>46.36</v>
+        <v>45.66</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.03899600448496243</v>
+        <v>-0.01509923972656624</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.0144557885191563</v>
+        <v>-0.03160130711022335</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.02849959294974891</v>
+        <v>-0.04954206958280838</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.0895521940802968</v>
+        <v>-0.08441947412557416</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2068434558559257</v>
+        <v>-0.2462859282383555</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1970904180343871</v>
+        <v>-0.1930010892585194</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.01883596591848546</v>
+        <v>-0.05524522827406464</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.08166122142225718</v>
+        <v>0.06657319277497598</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1660867766831391</v>
+        <v>-0.1532391877629482</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.05874574278360223</v>
+        <v>-0.05393658070614404</v>
       </c>
     </row>
   </sheetData>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1278571401323592</v>
+        <v>0.1425470557547552</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.181605414859816</v>
+        <v>-0.1741211078081836</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1154489492243165</v>
+        <v>0.1117287523321022</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1475798367764296</v>
+        <v>-0.1509839533374372</v>
       </c>
     </row>
     <row r="19">
@@ -4692,21 +4692,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05039536365850084</v>
+        <v>0.08762707958313687</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1200039493158475</v>
+        <v>-0.1190831801688959</v>
       </c>
     </row>
     <row r="20">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.04728836924385238</v>
+        <v>0.0734121037968225</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.1027821655943156</v>
+        <v>-0.09023122070748069</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.04385677229366558</v>
+        <v>0.04510760437803363</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.09909756070470765</v>
+        <v>-0.08866920079333096</v>
       </c>
     </row>
     <row r="22">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.04257533664142898</v>
+        <v>0.043308714234082</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.09114580295269525</v>
+        <v>-0.08446112840825748</v>
       </c>
     </row>
     <row r="23">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.03957462634574482</v>
+        <v>0.03432936625823779</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.0895521940802968</v>
+        <v>-0.08441947412557416</v>
       </c>
     </row>
     <row r="24">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.03716051568693768</v>
+        <v>0.02837871234759115</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.08940351734862506</v>
+        <v>-0.07677545664707486</v>
       </c>
     </row>
     <row r="25">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03559058482252708</v>
+        <v>0.0234405591517155</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.08740846433173488</v>
+        <v>-0.07605237734892167</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.02550953591456739</v>
+        <v>0.02165873432659216</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.08730877319960062</v>
+        <v>-0.07091027836973529</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3291245631099993</v>
+        <v>0.3647364199081704</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2068434558559257</v>
+        <v>-0.2462859282383555</v>
       </c>
     </row>
     <row r="32">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.3162224680275894</v>
+        <v>0.3089005464341723</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1581072592931696</v>
+        <v>-0.2034487083308625</v>
       </c>
     </row>
     <row r="33">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.289353991938458</v>
+        <v>0.3029885127626617</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5225,21 +5225,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1548280642980912</v>
+        <v>-0.1677725522050802</v>
       </c>
     </row>
     <row r="34">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2631579663063595</v>
+        <v>0.2550000349680583</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1428340438869102</v>
+        <v>-0.1561000207975813</v>
       </c>
     </row>
     <row r="35">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2425935375296568</v>
+        <v>0.2489843604710456</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1342773467513326</v>
+        <v>-0.1381247191968047</v>
       </c>
     </row>
     <row r="36">
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.20797130991308</v>
+        <v>0.2035418405019245</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.1180528407963702</v>
+        <v>-0.1316603082983875</v>
       </c>
     </row>
     <row r="37">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1939641136999246</v>
+        <v>0.1781329194268173</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.1015433247214843</v>
+        <v>-0.1306818021527582</v>
       </c>
     </row>
     <row r="38">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1864063978751334</v>
+        <v>0.1712874931361994</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.09434591256477487</v>
+        <v>-0.1282963041027557</v>
       </c>
     </row>
     <row r="39">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1370317386789499</v>
+        <v>0.1571930782317597</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.09428797780018872</v>
+        <v>-0.1118581584408213</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1364183445641207</v>
+        <v>0.1389256751862518</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.09384285163775241</v>
+        <v>-0.1115226639827023</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5687909408215208</v>
+        <v>0.569032567412993</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1970904180343871</v>
+        <v>-0.1930010892585194</v>
       </c>
     </row>
     <row r="46">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5535783187077863</v>
+        <v>0.5425026300310289</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1551860665389815</v>
+        <v>-0.1512125171202713</v>
       </c>
     </row>
     <row r="47">
@@ -5714,21 +5714,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5139021572240416</v>
+        <v>0.5420454062752822</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1179241052604807</v>
+        <v>-0.1144622918788809</v>
       </c>
     </row>
     <row r="48">
@@ -5759,21 +5759,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.5032690891051099</v>
+        <v>0.4757009573196866</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1035531138716037</v>
+        <v>-0.1086748711691908</v>
       </c>
     </row>
     <row r="49">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4269888862851456</v>
+        <v>0.4555337730979732</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.07995593820163427</v>
+        <v>-0.07428524095159939</v>
       </c>
     </row>
     <row r="50">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.412542779818537</v>
+        <v>0.4191287494755269</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.07311562072795141</v>
+        <v>-0.05822639326501711</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.357966981324807</v>
+        <v>0.39960488220479</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.05666884457578569</v>
+        <v>-0.05560399483477019</v>
       </c>
     </row>
     <row r="52">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.348120463279231</v>
+        <v>0.3614908963984587</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.05236746908423273</v>
+        <v>-0.04152803790371862</v>
       </c>
     </row>
     <row r="53">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.2952471047018517</v>
+        <v>0.3029733834933299</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.0507864582639026</v>
+        <v>-0.0335717503766555</v>
       </c>
     </row>
     <row r="54">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2755079997262306</v>
+        <v>0.2953004632260816</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.04482380248617479</v>
+        <v>-0.02821658498895807</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9398033533015231</v>
+        <v>0.9256097962358474</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2575708370182598</v>
+        <v>-0.2679797875835751</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.842274784746984</v>
+        <v>0.8133669684588607</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2296296419420548</v>
+        <v>-0.2323056978705195</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7783887913828087</v>
+        <v>0.7415945089520355</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1877820487345413</v>
+        <v>-0.1994846854773143</v>
       </c>
     </row>
     <row r="62">
@@ -6270,21 +6270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.695364238410596</v>
+        <v>0.7014056421108741</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1869878276104799</v>
+        <v>-0.1877486489339296</v>
       </c>
     </row>
     <row r="63">
@@ -6315,21 +6315,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6772018864437233</v>
+        <v>0.6284369803271792</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1409007175074048</v>
+        <v>-0.1522060339783795</v>
       </c>
     </row>
     <row r="64">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.6221786646658571</v>
+        <v>0.5824622543010014</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1391623794730976</v>
+        <v>-0.1414112273657304</v>
       </c>
     </row>
     <row r="65">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.5894590877955688</v>
+        <v>0.5699594055439274</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.06553761190629759</v>
+        <v>-0.09534919837644729</v>
       </c>
     </row>
     <row r="66">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.5244503004839425</v>
+        <v>0.5032387317818325</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6472,21 +6472,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.04812836087416839</v>
+        <v>-0.06555445787817316</v>
       </c>
     </row>
     <row r="67">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.5242149768876483</v>
+        <v>0.4975880657662486</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.04762237730334773</v>
+        <v>-0.05284270897605015</v>
       </c>
     </row>
     <row r="68">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.4939457720935561</v>
+        <v>0.4892834865875435</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.04264131972239216</v>
+        <v>-0.04553282126171032</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.870659759625966</v>
+        <v>2.943044454230621</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1660867766831391</v>
+        <v>-0.1532391877629482</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.752211229485098</v>
+        <v>2.776882209033695</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6713,21 +6713,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.007629007250714803</v>
+        <v>-0.004947471213657462</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.343069485001402</v>
+        <v>2.324378718831347</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6758,21 +6758,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.008047345796089234</v>
+        <v>0.01745669086069457</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.881386844323893</v>
+        <v>1.784832407299326</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.04063873973851906</v>
+        <v>0.04266722598494366</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.521047447008756</v>
+        <v>1.563749630738493</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6848,21 +6848,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1251720761678736</v>
+        <v>0.1084698892875329</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.399430248326846</v>
+        <v>1.442222835389073</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6893,21 +6893,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1276161877615094</v>
+        <v>0.11010554034491</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.341628879289763</v>
+        <v>1.32705916904759</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1610539887246742</v>
+        <v>0.1574302141966404</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.325716906385342</v>
+        <v>1.325133922337083</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1611388621234899</v>
+        <v>0.1686387573236725</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.224829726753839</v>
+        <v>1.226754161863887</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1818633952403903</v>
+        <v>0.1705157267459414</v>
       </c>
     </row>
     <row r="82">
@@ -7051,21 +7051,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.124042695326255</v>
+        <v>1.090182059457864</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.1824969548649971</v>
+        <v>0.174579048206865</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -494,11 +494,11 @@
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>15.79</v>
+        <v>15.72</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0</v>
+        <v>-0.004433166244036113</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.01374142810016521</v>
+        <v>-0.01811367630900285</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.04649755609430739</v>
+        <v>-0.05072459094223603</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.1425470557547552</v>
+        <v>0.1374819547149604</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3647364199081704</v>
+        <v>0.3586863164794267</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4757009573196866</v>
+        <v>0.4691589296494052</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.8241681736762536</v>
+        <v>0.816081332905267</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9256097962358474</v>
+        <v>0.9170732478879893</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1.784832407299326</v>
+        <v>1.772486782275988</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4069101238323851</v>
+        <v>0.4048280218700748</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>40</v>
+        <v>39.83</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0</v>
+        <v>-0.004249954223632835</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.05097211131659063</v>
+        <v>0.04650552795318053</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.005783242131983224</v>
+        <v>0.001508709394025143</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1117287523321022</v>
+        <v>0.1070039560255942</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3089005464341723</v>
+        <v>0.3033377790285392</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.39960488220479</v>
+        <v>0.3936566255242464</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5557188888417419</v>
+        <v>0.5491071547793236</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7415945089520355</v>
+        <v>0.7341928120128591</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.9214913723777369</v>
+        <v>0.9133252973102535</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2432147274793039</v>
+        <v>0.2414510625840194</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>120.48</v>
+        <v>118.67</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0</v>
+        <v>-0.01502328301424405</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.09626935108425227</v>
+        <v>0.07979978636307195</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.08785556078495338</v>
+        <v>0.07151239881666194</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.04510760437803363</v>
+        <v>0.02940665705712386</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2550000349680583</v>
+        <v>0.2361458142598469</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5420454062752822</v>
+        <v>0.5188788217159936</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.486485608772169</v>
+        <v>0.4641537147749839</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.3802959818374783</v>
+        <v>0.3595594046589099</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.32705916904759</v>
+        <v>1.292099100560097</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3251625136462939</v>
+        <v>0.3184929043249196</v>
       </c>
     </row>
     <row r="5">
@@ -760,12 +760,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>101.66</v>
+        <v>573</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0</v>
+        <v>0.02210095248422594</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.07690680104745762</v>
+        <v>0.007862329996276785</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.07474371072986985</v>
+        <v>0.01056417017549838</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.043308714234082</v>
+        <v>0.005668919665880789</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.2035418405019245</v>
+        <v>-0.1316603082983875</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.569032567412993</v>
+        <v>0.4555337730979732</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.4085732096474639</v>
+        <v>0.6552424530510803</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3280445887493779</v>
+        <v>0.8133669684588607</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1.226754161863887</v>
+        <v>2.943044454230621</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3058423752240338</v>
+        <v>0.5798307320443696</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>573</v>
+        <v>190.61</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.02210095248422594</v>
+        <v>-0.01028088563886387</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.007862329996276785</v>
+        <v>-0.02610872970815736</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.01056417017549838</v>
+        <v>-0.000524388338288273</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.005668919665880789</v>
+        <v>0.02837871234759115</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>-0.1316603082983875</v>
+        <v>0.2489843604710456</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.4555337730979732</v>
+        <v>0.1093335642258662</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.6552424530510803</v>
+        <v>0.5486293090944254</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.8133669684588607</v>
+        <v>0.4673395869634622</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2.943044454230621</v>
+        <v>0.3619447311853279</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.5798307320443696</v>
+        <v>0.1084594952344937</v>
       </c>
     </row>
     <row r="7">
@@ -872,51 +872,51 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>190.61</v>
+        <v>99.87</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.01028088563886387</v>
+        <v>-0.01760772035260616</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.02610872970815736</v>
+        <v>0.05794492724879441</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-0.000524388338288273</v>
+        <v>0.05581992402061609</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.02837871234759115</v>
+        <v>0.02493842615241126</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2489843604710456</v>
+        <v>0.1823502123417056</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1093335642258662</v>
+        <v>0.5414054807418531</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5486293090944254</v>
+        <v>0.3837714464758184</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4673395869634622</v>
+        <v>0.3046607510148871</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3619447311853279</v>
+        <v>1.187546097287785</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1084594952344937</v>
+        <v>0.2981326438709135</v>
       </c>
     </row>
     <row r="8">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>28.34</v>
+        <v>27.82</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0</v>
+        <v>-0.01834863990698277</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.04460011165688149</v>
+        <v>0.02543312036129519</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.01979126372584039</v>
+        <v>0.001079481047447928</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.0212612667599239</v>
+        <v>0.002522511525197002</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.3029885127626617</v>
+        <v>0.2790804457390446</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.4191287494755269</v>
+        <v>0.3930896670697537</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2440737181014161</v>
+        <v>0.2212466574302321</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1887583880535972</v>
+        <v>0.1669462884547963</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4653567698548187</v>
+        <v>0.4384694661494932</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.1358329372950091</v>
+        <v>0.128843012968878</v>
       </c>
     </row>
     <row r="10">
@@ -1075,16 +1075,16 @@
         <v>0.5425026300310289</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.5903971146799756</v>
+        <v>0.590397267030742</v>
       </c>
       <c r="N10" s="6" t="n">
         <v>0.5824622543010014</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.563749630738493</v>
+        <v>1.563749234839318</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3686483250990342</v>
+        <v>0.3686482546492569</v>
       </c>
     </row>
     <row r="11">
@@ -1134,7 +1134,7 @@
         <v>0.4749161573658169</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4975880657662486</v>
+        <v>0.497588176359439</v>
       </c>
       <c r="O11" s="6" t="n">
         <v>1.325133922337083</v>
@@ -1193,10 +1193,10 @@
         <v>0.4270741021177493</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6470320839715777</v>
+        <v>0.6470321851466467</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1809568232757424</v>
+        <v>0.1809568474572962</v>
       </c>
     </row>
     <row r="13">
@@ -1249,10 +1249,10 @@
         <v>0.7014056421108741</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.442222835389073</v>
+        <v>1.442222574704173</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3466717897526526</v>
+        <v>0.3466717418376948</v>
       </c>
     </row>
     <row r="14">
@@ -1352,7 +1352,7 @@
         <v>0.0977190198077631</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2640358829930212</v>
+        <v>0.2640359740457972</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>0.216386494915179</v>
@@ -1417,10 +1417,10 @@
         <v>0.5032387317818325</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>2.776882209033695</v>
+        <v>2.776882494832272</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.5573198293850297</v>
+        <v>0.557319868666087</v>
       </c>
     </row>
     <row r="17">
@@ -1526,13 +1526,13 @@
         <v>0.344181034119718</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.320368057361325</v>
+        <v>0.3203681665997631</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.2505625809941889</v>
+        <v>0.2505624830009185</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.07737892664560908</v>
+        <v>0.07737889850470436</v>
       </c>
     </row>
     <row r="19">
@@ -1635,16 +1635,16 @@
         <v>0.3029733834933299</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1863871128861871</v>
+        <v>0.1863872084923428</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1794358306538608</v>
+        <v>0.1794359251429472</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.174579048206865</v>
+        <v>0.174579141919363</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.0551011180773513</v>
+        <v>0.05510114613737804</v>
       </c>
     </row>
     <row r="21">
@@ -1688,7 +1688,7 @@
         <v>0.1056348751735336</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.08761073212791692</v>
+        <v>0.08761065005454394</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>0.2443286720972402</v>
@@ -1697,10 +1697,10 @@
         <v>0.2447849871403307</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.6675597233591444</v>
+        <v>0.66755991629733</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.185842830841928</v>
+        <v>0.1858428765762929</v>
       </c>
     </row>
     <row r="22">
@@ -1977,10 +1977,10 @@
         <v>0.113887403359533</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6128851281678052</v>
+        <v>0.6128852672504761</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1727383998651681</v>
+        <v>0.1727384335744471</v>
       </c>
     </row>
     <row r="27">
@@ -2027,16 +2027,16 @@
         <v>0.1706178965571004</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.08049679245153452</v>
+        <v>0.0804967256013871</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>0.1005733254920367</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8960488672422042</v>
+        <v>0.8960490730939392</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2377031857082037</v>
+        <v>0.2377032305001821</v>
       </c>
     </row>
     <row r="28">
@@ -2086,13 +2086,13 @@
         <v>0.02758832794635668</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.08562781814964637</v>
+        <v>0.08562788787600439</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.5853621843517121</v>
+        <v>0.5853620356582152</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1660293932552348</v>
+        <v>0.1660293568006852</v>
       </c>
     </row>
     <row r="29">
@@ -2198,13 +2198,13 @@
         <v>0.1592582511843339</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2622703406059774</v>
+        <v>0.2622702106218562</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.5734875843755609</v>
+        <v>0.5734876853664661</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1631108494286988</v>
+        <v>0.1631108743126182</v>
       </c>
     </row>
     <row r="31">
@@ -2254,7 +2254,7 @@
         <v>0.09613518433265411</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.09988097493926684</v>
+        <v>0.09988107781009203</v>
       </c>
       <c r="O31" s="6" t="n">
         <v>0.3962874444457769</v>
@@ -2310,7 +2310,7 @@
         <v>0.09269398561632336</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.08710769492385428</v>
+        <v>0.08710781949478252</v>
       </c>
       <c r="O32" s="6" t="n">
         <v>0.206391349681327</v>
@@ -2366,7 +2366,7 @@
         <v>0.05206212308004488</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.06043257158983018</v>
+        <v>0.06043247873934554</v>
       </c>
       <c r="O33" s="6" t="n">
         <v>0.9943635721561321</v>
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>13.31</v>
+        <v>80.27</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0</v>
+        <v>-0.006559485008334698</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.01992338889515333</v>
+        <v>-0.02056158514663253</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.001500337899761561</v>
+        <v>-0.04418351525628117</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.0068078782730705</v>
+        <v>-0.0664763089665007</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.09758143615528736</v>
+        <v>-0.04156458971556254</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.09278634249131112</v>
+        <v>0.08823302772012265</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-0.004918033371299813</v>
+        <v>0.07819238446846977</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-0.04498573180027021</v>
+        <v>0.1447099124642792</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.1574302141966404</v>
+        <v>0.3876236302587353</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.04994110454135092</v>
+        <v>0.1153826782098055</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>80.27</v>
+        <v>70.5</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.006559485008334698</v>
+        <v>-0.00564177034231661</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.02056158514663253</v>
+        <v>-0.01384806117432058</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.04418351525628117</v>
+        <v>-0.04960906295546375</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.0664763089665007</v>
+        <v>-0.04755467174688299</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.04156458971556254</v>
+        <v>-0.1381247191968047</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.08823302772012265</v>
+        <v>0.01948248601857006</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.07819238446846977</v>
+        <v>0.1124305218183808</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1447099124642792</v>
+        <v>0.3517768174193965</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.3876238132710272</v>
+        <v>0.2578901310989661</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1153827272453718</v>
+        <v>0.0794790958204552</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>70.5</v>
+        <v>100.74</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.00564177034231661</v>
+        <v>-0.002179092934807336</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.01384806117432058</v>
+        <v>-0.0163070573051618</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.04960906295546375</v>
+        <v>-0.04529945916759048</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.04755467174688299</v>
+        <v>-0.06989197549126513</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.1381247191968047</v>
+        <v>-0.1115226639827023</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.01948248601857006</v>
+        <v>0.1338931899219287</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.1124305218183808</v>
+        <v>0.08562178111557106</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.3517768174193965</v>
+        <v>0.1835885352786066</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.25789030233156</v>
+        <v>0.3418378499446006</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.07947914480247475</v>
+        <v>0.1029775664104915</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>100.74</v>
+        <v>108.68</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.002179092934807336</v>
+        <v>-0.02371540960192065</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.0163070573051618</v>
+        <v>-0.04356241369259817</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.04529945916759048</v>
+        <v>-0.08379701746122803</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.06989197549126513</v>
+        <v>-0.04356241369259817</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.1115226639827023</v>
+        <v>-0.07063446958514397</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.1338931899219287</v>
+        <v>0.008449082751214698</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.08562178111557106</v>
+        <v>0.06474539820622272</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.1835884291849064</v>
+        <v>0.2243493027823555</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.3418379863049976</v>
+        <v>1.089866624688113</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1029776037727936</v>
+        <v>0.2785160669057811</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>108.68</v>
+        <v>13.08</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.02371540960192065</v>
+        <v>-0.01728027713445168</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.04356241369259817</v>
+        <v>0.002298830079136005</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.08379701746122803</v>
+        <v>-0.01875468877951003</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.04356241369259817</v>
+        <v>-0.01059004088463755</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.07063446958514397</v>
+        <v>0.07861492476089449</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.008449082751214698</v>
+        <v>0.07390269164431751</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.06474531862108845</v>
+        <v>-0.02211332552613898</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.2243493027823555</v>
+        <v>-0.0614886430221171</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.089866624688113</v>
+        <v>0.137429405003392</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.2785160669057811</v>
+        <v>0.04385814395847798</v>
       </c>
     </row>
     <row r="39">
@@ -2702,13 +2702,13 @@
         <v>0.09007944594295481</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.0980012020060621</v>
+        <v>0.09800128431890998</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.3167124909786756</v>
+        <v>0.3167123726080794</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.09604987912200302</v>
+        <v>0.09604984627755586</v>
       </c>
     </row>
     <row r="40">
@@ -2790,37 +2790,37 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>52.91</v>
+        <v>52.96</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>0.0009449865281561109</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.02163465133188514</v>
+        <v>-0.02071010925777905</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.04079042795910304</v>
+        <v>-0.03988398783584601</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.07677545664707486</v>
+        <v>-0.07590302189114329</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.09489783533059959</v>
+        <v>-0.09404252597838203</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.05352379551882214</v>
+        <v>0.05451936131267932</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1047657485029749</v>
+        <v>0.1058097372520785</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.136290213766965</v>
+        <v>0.1373639927110506</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.7408747262162132</v>
+        <v>0.7425198293796949</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.2029728895558518</v>
+        <v>0.203351701315017</v>
       </c>
     </row>
     <row r="42">
@@ -2870,7 +2870,7 @@
         <v>-0.0001605134529392149</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.02960213530817191</v>
+        <v>-0.02960203357512459</v>
       </c>
       <c r="O42" s="6" t="n">
         <v>-0.004947471213657462</v>
@@ -2902,37 +2902,37 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>28.17</v>
+        <v>28.22</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0</v>
+        <v>0.001774910788964634</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0</v>
+        <v>0.001774910788964634</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.02187497143944028</v>
+        <v>-0.0201388867732919</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.07091027836973529</v>
+        <v>-0.06926122699889758</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.09129032011955018</v>
+        <v>-0.08967744150469381</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.1455876332448616</v>
+        <v>0.1476209490948122</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>-0.0048797917369785</v>
+        <v>-0.003113542143015846</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.0961300709176276</v>
+        <v>0.09807560400660775</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.6072852415728272</v>
+        <v>0.6101380294890382</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1713795890820653</v>
+        <v>0.1720722108864567</v>
       </c>
     </row>
     <row r="44">
@@ -2958,37 +2958,37 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>56.96</v>
+        <v>56.62</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0</v>
+        <v>-0.005969103898398331</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.01990177305774543</v>
+        <v>-0.02575208120499972</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.03445605018438924</v>
+        <v>-0.0402194823393085</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.06399258100639349</v>
+        <v>-0.06957970654003798</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.07697801723991382</v>
+        <v>-0.0824876313555144</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.006443054025132788</v>
+        <v>0.000435490867835453</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.08733085234941607</v>
+        <v>0.0808405402268233</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.1131958283752876</v>
+        <v>0.106551129312503</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5777763548080597</v>
+        <v>0.5683581123733037</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1641666336608978</v>
+        <v>0.1618455837748609</v>
       </c>
     </row>
     <row r="45">
@@ -3041,10 +3041,10 @@
         <v>0.007859951192218606</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.11010554034491</v>
+        <v>0.1101057423639513</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.0354316201282403</v>
+        <v>0.03543168293815113</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>112.35</v>
+        <v>61.77</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>-0.005794311993603252</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.002220248697938132</v>
+        <v>-0.020922486790802</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.002856375063027716</v>
+        <v>-0.04661213790845786</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.01692609576726767</v>
+        <v>-0.08866920079333096</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.02916657290025326</v>
+        <v>-0.05523016834237326</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>-0.005791561575352322</v>
+        <v>0.07278727254598438</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>-0.02663717614945826</v>
+        <v>0.0136566599332173</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-0.04336579943859387</v>
+        <v>0.004533312323661498</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.720169260870835</v>
+        <v>0.572599136774826</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.1981845838437533</v>
+        <v>0.1628918968280861</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>61.77</v>
+        <v>110.81</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.005794311993603252</v>
+        <v>-0.0137071734440839</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.020922486790802</v>
+        <v>-0.01589698880803037</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.04661213790845786</v>
+        <v>-0.01088995120946645</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.08866920079333096</v>
+        <v>0.002986913392770463</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-0.05523016834237326</v>
+        <v>0.01505960818265595</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.07278727254598438</v>
+        <v>-0.01941934908041076</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.01365659647845763</v>
+        <v>-0.03997929265595224</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.004533374641328525</v>
+        <v>-0.05647855034823157</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.5725989840468848</v>
+        <v>0.6965906024588968</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.1628918591821096</v>
+        <v>0.1926848033198054</v>
       </c>
     </row>
     <row r="48">
@@ -3238,37 +3238,37 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>35.12</v>
+        <v>35.11</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0</v>
+        <v>-0.0001424197031520968</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.004676788734100046</v>
+        <v>-0.004818542370388923</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.02322667779560794</v>
+        <v>-0.02336578956220325</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.03926121993290521</v>
+        <v>-0.0393980480647691</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.08437412996172355</v>
+        <v>-0.08450453312633277</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.008107958338663179</v>
+        <v>0.007964383902491212</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>-0.002142017726497469</v>
+        <v>-0.00228413236412095</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.007258460115290077</v>
+        <v>0.007114896462948161</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.3886794974726697</v>
+        <v>0.3884817221508663</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.1156655112469454</v>
+        <v>0.1156125444820526</v>
       </c>
     </row>
     <row r="50">
@@ -3312,19 +3312,19 @@
         <v>-0.04841998313114604</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.04353941512955295</v>
+        <v>0.0435395164122192</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.05381525425846834</v>
+        <v>-0.05381533752475831</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>-0.06555445787817316</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.3888762260794811</v>
+        <v>0.3888760466704089</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1157181926992343</v>
+        <v>0.1157181446580025</v>
       </c>
     </row>
     <row r="51">
@@ -3368,19 +3368,19 @@
         <v>-0.1041973460773032</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.07428524095159939</v>
+        <v>-0.07428517980313776</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.02942240928255124</v>
+        <v>0.02942248489936961</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0.0562014960536632</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.9886656054182135</v>
+        <v>0.9886654643189881</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.2575364658493893</v>
+        <v>0.2575364361079342</v>
       </c>
     </row>
     <row r="52">
@@ -3489,10 +3489,10 @@
         <v>-0.1414112273657304</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.04266722598494366</v>
+        <v>0.04266730609248226</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.01402479427231151</v>
+        <v>0.01402482024129648</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>41.1</v>
+        <v>25.76</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.01415207896432746</v>
+        <v>0.01456975488148293</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.03043172762683166</v>
+        <v>-0.01468510366489717</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.04596107875525401</v>
+        <v>-0.06138438347753905</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.06633352915214674</v>
+        <v>-0.009038485013521669</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>-0.07590609785510327</v>
+        <v>0.03362320042684663</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.1086748711691908</v>
+        <v>0.06431218084296697</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.02816881462699061</v>
+        <v>-0.134482753318089</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>0.0009746714560063818</v>
+        <v>-0.2573144325203767</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.3863063664914352</v>
+        <v>0.2361021459672044</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.1150296241779416</v>
+        <v>0.07321018803651635</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>18.88</v>
+        <v>41.1</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>-0.01415207896432746</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.02500125373274908</v>
+        <v>-0.03043172762683166</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.02550464631281701</v>
+        <v>-0.04596107875525401</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.01533729542569673</v>
+        <v>-0.06633352915214674</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.03055980145548243</v>
+        <v>-0.07590609785510327</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.05211814036278106</v>
+        <v>-0.1086748711691908</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.09644473905746964</v>
+        <v>-0.02816881462699061</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-0.1877486489339296</v>
+        <v>0.0009746714560063818</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.1686387573236725</v>
+        <v>0.3863063664914352</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.05331942921412147</v>
+        <v>0.1150296241779416</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>25.4</v>
+        <v>239.86</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0</v>
+        <v>-0.006050085652059667</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.02883474340292902</v>
+        <v>-0.02480080475283097</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.07486339701491962</v>
+        <v>-0.05163687194821953</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.02326921316293573</v>
+        <v>-0.1741211078081836</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>0.01877982805390177</v>
+        <v>-0.1561000207975813</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>0.04902809858282686</v>
+        <v>-0.1144622918788809</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.1469120358481253</v>
+        <v>0.02998889841231511</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.2679797875835751</v>
+        <v>0.05957344381312746</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.2183509580369993</v>
+        <v>1.090181781531073</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.06804807854609773</v>
+        <v>0.2785803314270723</v>
       </c>
     </row>
     <row r="57">
@@ -3672,51 +3672,51 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>239.86</v>
+        <v>17.35</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.006050085652059667</v>
+        <v>-0.01866515373359168</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.02480080475283097</v>
+        <v>-0.02407467090779414</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.05163687194821953</v>
+        <v>-0.0858798314056517</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.1741211078081836</v>
+        <v>-0.1355256280375502</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.1561000207975813</v>
+        <v>-0.03680675561202884</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.1144622918788809</v>
+        <v>0.07072327048837135</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.02998889841231511</v>
+        <v>-0.1777640623913891</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.05957344381312746</v>
+        <v>-0.2466348300401686</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>1.090182059457864</v>
+        <v>-0.0015342946914918</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.2785803880970577</v>
+        <v>-0.0005116933492553821</v>
       </c>
     </row>
     <row r="58">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -3742,37 +3742,37 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>17.68</v>
+        <v>18.22</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0</v>
+        <v>-0.03470202313353687</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.005512407100169203</v>
+        <v>-0.05883568278088469</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.06849311213984222</v>
+        <v>-0.05932160661999375</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.1190831801688959</v>
+        <v>-0.04950708337856513</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.01848665819567985</v>
+        <v>-0.06420133765195479</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.09108860707642341</v>
+        <v>0.0156075123166981</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.1621249966442198</v>
+        <v>-0.1277999346251262</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.2323056978705195</v>
+        <v>-0.215935414108871</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.01745669086069457</v>
+        <v>0.1280846281322785</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.005785361994010474</v>
+        <v>0.04099160482102926</v>
       </c>
     </row>
     <row r="59">
@@ -3825,10 +3825,10 @@
         <v>-0.04553282126171032</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.7765105602111708</v>
+        <v>0.7765104156836302</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.2111258242449228</v>
+        <v>0.2111257914013163</v>
       </c>
     </row>
     <row r="60">
@@ -3872,19 +3872,19 @@
         <v>-0.1306818021527582</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.02780042484574241</v>
+        <v>-0.02780049965733777</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.08794903730628978</v>
+        <v>-0.08794897146530167</v>
       </c>
       <c r="N60" s="6" t="n">
         <v>-0.1522060339783795</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.2466688395005008</v>
+        <v>0.246669085531815</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.07625959136470484</v>
+        <v>0.07625966216499425</v>
       </c>
     </row>
     <row r="61">
@@ -3928,19 +3928,19 @@
         <v>-0.1118581584408213</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.0335717503766555</v>
+        <v>-0.03357183189739887</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.1144081195846215</v>
+        <v>-0.1144080511310328</v>
       </c>
       <c r="N61" s="6" t="n">
         <v>-0.1994846854773143</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1084698892875329</v>
+        <v>0.1084699965324647</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.03492282847404837</v>
+        <v>0.0349228618504549</v>
       </c>
     </row>
     <row r="62">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4338,17 +4338,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1425470557547552</v>
+        <v>0.1374819547149604</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1117287523321022</v>
+        <v>0.1070039560255942</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1190831801688959</v>
+        <v>-0.1355256280375502</v>
       </c>
     </row>
     <row r="20">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.04510760437803363</v>
+        <v>0.03432936625823779</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.043308714234082</v>
+        <v>0.02940665705712386</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.03432936625823779</v>
+        <v>0.02837871234759115</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4917,21 +4917,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02837871234759115</v>
+        <v>0.02493842615241126</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.07677545664707486</v>
+        <v>-0.07605237734892167</v>
       </c>
     </row>
     <row r="25">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.07605237734892167</v>
+        <v>-0.07590302189114329</v>
       </c>
     </row>
     <row r="26">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.07091027836973529</v>
+        <v>-0.06989197549126513</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3647364199081704</v>
+        <v>0.3586863164794267</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.3089005464341723</v>
+        <v>0.3033377790285392</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.3029885127626617</v>
+        <v>0.2790804457390446</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5248,21 +5248,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2550000349680583</v>
+        <v>0.2489843604710456</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5293,21 +5293,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2489843604710456</v>
+        <v>0.2361458142598469</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2035418405019245</v>
+        <v>0.1823502123417056</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.569032567412993</v>
+        <v>0.5425026300310289</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5425026300310289</v>
+        <v>0.5414054807418531</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5420454062752822</v>
+        <v>0.5188788217159936</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4757009573196866</v>
+        <v>0.4691589296494052</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.07428524095159939</v>
+        <v>-0.07428517980313776</v>
       </c>
     </row>
     <row r="50">
@@ -5849,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.4191287494755269</v>
+        <v>0.3936566255242464</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5894,21 +5894,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.39960488220479</v>
+        <v>0.3930896670697537</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.0335717503766555</v>
+        <v>-0.03357183189739887</v>
       </c>
     </row>
     <row r="54">
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9256097962358474</v>
+        <v>0.9170732478879893</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2679797875835751</v>
+        <v>-0.2573144325203767</v>
       </c>
     </row>
     <row r="60">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2323056978705195</v>
+        <v>-0.2466348300401686</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7415945089520355</v>
+        <v>0.7341928120128591</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.1994846854773143</v>
+        <v>-0.215935414108871</v>
       </c>
     </row>
     <row r="62">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1877486489339296</v>
+        <v>-0.1994846854773143</v>
       </c>
     </row>
     <row r="63">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.4975880657662486</v>
+        <v>0.497588176359439</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.05284270897605015</v>
+        <v>-0.0614886430221171</v>
       </c>
     </row>
     <row r="68">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.04553282126171032</v>
+        <v>-0.05647855034823157</v>
       </c>
     </row>
     <row r="69"/>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.776882209033695</v>
+        <v>2.776882494832272</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.01745669086069457</v>
+        <v>-0.0015342946914918</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.784832407299326</v>
+        <v>1.772486782275988</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.04266722598494366</v>
+        <v>0.04266730609248226</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.563749630738493</v>
+        <v>1.563749234839318</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1084698892875329</v>
+        <v>0.1084699965324647</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.442222835389073</v>
+        <v>1.442222574704173</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.11010554034491</v>
+        <v>0.1101057423639513</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.32705916904759</v>
+        <v>1.325133922337083</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6938,21 +6938,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1574302141966404</v>
+        <v>0.1280846281322785</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.325133922337083</v>
+        <v>1.292099100560097</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6983,21 +6983,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1686387573236725</v>
+        <v>0.137429405003392</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.226754161863887</v>
+        <v>1.187546097287785</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.090182059457864</v>
+        <v>1.090181781531073</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.174579048206865</v>
+        <v>0.174579141919363</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -490,15 +490,15 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>15.72</v>
+        <v>16.08</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.004433166244036113</v>
+        <v>0.02290074112990381</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>-0.01811367630900285</v>
+        <v>0.05098037406846112</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.05072459094223603</v>
+        <v>-0.02898548053842054</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.1374819547149604</v>
+        <v>0.09016948635295297</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3586863164794267</v>
+        <v>0.3898012400898647</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.4691589296494052</v>
+        <v>0.6063935620411336</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.816081332905267</v>
+        <v>0.8482758938203108</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9170732478879893</v>
+        <v>0.9705882627933775</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1.772486782275988</v>
+        <v>1.994413457428208</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4048280218700748</v>
+        <v>0.4413537708498165</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>39.83</v>
+        <v>40.63</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-0.004249954223632835</v>
+        <v>0.02008534271361251</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.04650552795318053</v>
+        <v>0.04878676581728114</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.001508709394025143</v>
+        <v>0.02162435505287208</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1070039560255942</v>
+        <v>0.01372253522789002</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3033377790285392</v>
+        <v>0.3295157649919258</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.3936566255242464</v>
+        <v>0.4427623515123225</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5491071547793236</v>
+        <v>0.5420000172283856</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7341928120128591</v>
+        <v>0.7890747109127749</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0.9133252973102535</v>
+        <v>1.027039536450951</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2414510625840194</v>
+        <v>0.2655735990557528</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>118.67</v>
+        <v>122.98</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.01502328301424405</v>
+        <v>0.03631924879490023</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.07979978636307195</v>
+        <v>0.03728075142845233</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.07151239881666194</v>
+        <v>0.1104289242161047</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.02940665705712386</v>
+        <v>0.1017738786133422</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2361458142598469</v>
+        <v>0.2810417016347249</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5188788217159936</v>
+        <v>0.6077919570080763</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.4641537147749839</v>
+        <v>0.5067420559517639</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.3595594046589099</v>
+        <v>0.4023551288396623</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.292099100560097</v>
+        <v>1.404967747359576</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3184929043249196</v>
+        <v>0.339789034018759</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>573</v>
+        <v>596.03</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.02210095248422594</v>
+        <v>0.04019202320571558</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.007862329996276785</v>
+        <v>0.1007018084891504</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.01056417017549838</v>
+        <v>0.05118078875405652</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.005668919665880789</v>
+        <v>0.06354171420120047</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.1316603082983875</v>
+        <v>-0.09675997925907232</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.4555337730979732</v>
+        <v>0.5491761824233214</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.6552424530510803</v>
+        <v>0.6783668547606476</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8133669684588607</v>
+        <v>0.8937779589929113</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>2.943044454230621</v>
+        <v>3.292088735974303</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5798307320443696</v>
+        <v>0.6251354504496789</v>
       </c>
     </row>
     <row r="6">
@@ -816,51 +816,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>190.61</v>
+        <v>103.09</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-0.01028088563886387</v>
+        <v>0.03224184943179842</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.02610872970815736</v>
+        <v>0.03038473956427734</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-0.000524388338288273</v>
+        <v>0.08986151103798168</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.02837871234759115</v>
+        <v>0.08687399047262745</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2489843604710456</v>
+        <v>0.2204713698636818</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.1093335642258662</v>
+        <v>0.6142131676489138</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.5486293090944254</v>
+        <v>0.4135402308662464</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.4673395869634622</v>
+        <v>0.347600870262041</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.3619447311853279</v>
+        <v>1.307978816530349</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.1084594952344937</v>
+        <v>0.3215307495207544</v>
       </c>
     </row>
     <row r="7">
@@ -872,12 +872,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>99.87</v>
+        <v>28.93</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.01760772035260616</v>
+        <v>0.03989937536045596</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.05794492724879441</v>
+        <v>0.020458550825458</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.05581992402061609</v>
+        <v>0.04102192702741059</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.02493842615241126</v>
+        <v>0.03137258795189379</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.1823502123417056</v>
+        <v>0.330114956559806</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.5414054807418531</v>
+        <v>0.4715157950005733</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3837714464758184</v>
+        <v>0.2616659363343172</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3046607510148871</v>
+        <v>0.2186183902314824</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1.187546097287785</v>
+        <v>0.542110871653231</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2981326438709135</v>
+        <v>0.1553277360966723</v>
       </c>
     </row>
     <row r="8">
@@ -928,51 +928,51 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>156.72</v>
+        <v>524.5599999999999</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.009668238731733836</v>
+        <v>0.03570551004247591</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.003329092718441284</v>
+        <v>0.1056225436909441</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.0432818292140843</v>
+        <v>0.06775978063342825</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.02117293970848477</v>
+        <v>0.05322954457553863</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.1147942155055659</v>
+        <v>-0.1750073937822347</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.2953004632260816</v>
+        <v>0.6280829447221463</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.311497603096476</v>
+        <v>0.6064025518844511</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6284369803271792</v>
+        <v>0.6498151241081944</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.076500010058209</v>
+        <v>1.776821509533177</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2757844738021193</v>
+        <v>0.4055597807472235</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>27.82</v>
+        <v>158.23</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.01834863990698277</v>
+        <v>0.009634982740393649</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.02543312036129519</v>
+        <v>0.003997395936708559</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.001079481047447928</v>
+        <v>-0.0340638661511411</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.002522511525197002</v>
+        <v>-0.04525433049747996</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.2790804457390446</v>
+        <v>0.1255352385310526</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.3930896670697537</v>
+        <v>0.3164768363608872</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2212466574302321</v>
+        <v>0.2874447407166825</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1669462884547963</v>
+        <v>0.6627007853676392</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.4384694661494932</v>
+        <v>1.160512034402311</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.128843012968878</v>
+        <v>0.2927629489749082</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>506.66</v>
+        <v>158.53</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.0148016400165305</v>
+        <v>0.02462511329197126</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.002155975081788553</v>
+        <v>0.04035958589983002</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.03094921370898374</v>
+        <v>0.02495636294076431</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.02140067752396302</v>
+        <v>0.04951999719573674</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.2034487083308625</v>
+        <v>0.006428130252800868</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.5425026300310289</v>
+        <v>0.4366207252019625</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.590397267030742</v>
+        <v>0.4910280040396333</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5824622543010014</v>
+        <v>0.5432910157417756</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.563749234839318</v>
+        <v>1.43797244210432</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3686482546492569</v>
+        <v>0.3458900963380191</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>154.72</v>
+        <v>184.75</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.005911065102500279</v>
+        <v>-0.02687867408721567</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.008522920891027241</v>
+        <v>-0.04126402191165579</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.0003232886296615778</v>
+        <v>-0.02738896983420158</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.02165873432659216</v>
+        <v>-0.02138516650136546</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-0.01775964965440491</v>
+        <v>0.2154133078976523</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.3614908963984587</v>
+        <v>0.05659954529076261</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.4749161573658169</v>
+        <v>0.5013629448387711</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.497588176359439</v>
+        <v>0.4588497477449343</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1.325133922337083</v>
+        <v>0.3770278212987883</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.3247969637557717</v>
+        <v>0.1125364233461463</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>204.56</v>
+        <v>207.16</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.01212155153737438</v>
+        <v>0.01271023726313292</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.0080865480743888</v>
+        <v>0.01256665357741249</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.03467816926732414</v>
+        <v>-0.02240869976342996</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.004966569566194901</v>
+        <v>-0.02991600784159276</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1781329194268173</v>
+        <v>0.1931072683602397</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2492353281025774</v>
+        <v>0.2817833737024793</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2320188197011717</v>
+        <v>0.2182821860065567</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4270741021177493</v>
+        <v>0.4544273596642328</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6470321851466467</v>
+        <v>0.6977875575545294</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1809568474572962</v>
+        <v>0.192965219537627</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>87.28</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.007735806075785057</v>
+        <v>0.002406039039982932</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.01411950770626602</v>
+        <v>0.02184063369773903</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.03728220545202943</v>
+        <v>-0.03496586885386066</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.01998362849796864</v>
+        <v>-0.07506077544139833</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.02452729648426621</v>
+        <v>0.02699234915713555</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1687788358006665</v>
+        <v>0.2708064206731784</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2961685296315368</v>
+        <v>0.2780327716113404</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.7014056421108741</v>
+        <v>0.6781042488967195</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.442222574704173</v>
+        <v>1.543340008013165</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3466717418376948</v>
+        <v>0.3650067772858125</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>398.71</v>
+        <v>67.52</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.004717959609688904</v>
+        <v>0.009297647076936588</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.05220248953263862</v>
+        <v>-0.004972226297909721</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.06741049144272204</v>
+        <v>-0.04747799615632331</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.05179671165812294</v>
+        <v>-0.071945264577438</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.03429401944435817</v>
+        <v>0.1079251621861952</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.03998640089994132</v>
+        <v>0.284258261262951</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4355040932141105</v>
+        <v>0.2069468189450416</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.5699594055439274</v>
+        <v>0.4603285630814615</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.1705157267459414</v>
+        <v>0.7156061661538091</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.05388304531168964</v>
+        <v>0.1971241704895166</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>66.94</v>
+        <v>396.63</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.01195568352167897</v>
+        <v>-0.005216790692088691</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.00844318881332573</v>
+        <v>-0.01350542881349426</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.05625261309181728</v>
+        <v>-0.07227561571050323</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.07605237734892167</v>
+        <v>-0.04502439576729045</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.0977190198077631</v>
+        <v>0.02889832403083781</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.2640359740457972</v>
+        <v>0.02496318482475846</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.216386494915179</v>
+        <v>0.4139048784436048</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.4299840034682241</v>
+        <v>0.585393291047305</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.6479488821731838</v>
+        <v>0.2180286015414326</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.1811759038620564</v>
+        <v>0.06795387399782182</v>
       </c>
     </row>
     <row r="16">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>95.2</v>
+        <v>106.08</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.001999734846224843</v>
+        <v>-9.420781582558657e-05</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.01203822804858679</v>
+        <v>-0.0002827139678099888</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.04119250608895453</v>
+        <v>-0.04423818476635555</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.08762707958313687</v>
+        <v>-0.01044771594283023</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.1385559472182418</v>
+        <v>0.006929315306187789</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.0849127956641933</v>
+        <v>0.2376619176778441</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.1756661710448375</v>
+        <v>0.2723391120989509</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.5032387317818325</v>
+        <v>0.4953428488556111</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>2.776882494832272</v>
+        <v>0.7691023001697326</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.557319868666087</v>
+        <v>0.2094399658125319</v>
       </c>
     </row>
     <row r="17">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>106.09</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.0210390915466071</v>
+        <v>-0.01512599640937606</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.02642933697852734</v>
+        <v>0.005253624003432211</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.04414813605000001</v>
+        <v>-0.05569542479913581</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.005623826879609939</v>
+        <v>-0.05816173518866719</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.007024184855126681</v>
+        <v>0.1213341540487451</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1979448877886265</v>
+        <v>0.1856207304045412</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.2699098706814005</v>
+        <v>0.1200294085721778</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.4892834865875435</v>
+        <v>0.4266401738625099</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.7272260516548286</v>
+        <v>2.893075085599392</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.199820818536804</v>
+        <v>0.5731287204744309</v>
       </c>
     </row>
     <row r="18">
@@ -1488,51 +1488,51 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>30.44</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.008791877514302993</v>
+        <v>-0.01099709902431167</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.04366947511718988</v>
+        <v>0.003080528122026305</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.03149856065878354</v>
+        <v>-0.04866010202604765</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.009759246561296675</v>
+        <v>-0.08168823666540193</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1389256751862518</v>
+        <v>0.1444673113601969</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.01434236350084639</v>
+        <v>0.1786070527712784</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.344181034119718</v>
+        <v>0.08344705017392129</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.3203681665997631</v>
+        <v>0.3144806745635931</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.2505624830009185</v>
+        <v>2.383349961289517</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.07737889850470436</v>
+        <v>0.5012360125377417</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>95.48</v>
+        <v>29.82</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.004587101964250939</v>
+        <v>-0.02036796413783615</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.01668378107770263</v>
+        <v>-0.05930602595799139</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.038081792242045</v>
+        <v>-0.05122496324272807</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.0734121037968225</v>
+        <v>-0.05333334302145343</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1571930782317597</v>
+        <v>0.1157280778783973</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.08364547378877418</v>
+        <v>-0.03092807531879216</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.122603633862407</v>
+        <v>0.3087944304610863</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.39807311255597</v>
+        <v>0.328920221953243</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>2.324378718831347</v>
+        <v>0.2830113304190749</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.4924627408571669</v>
+        <v>0.08661783899642894</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>56.16</v>
+        <v>55.86</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.006896541024050906</v>
+        <v>-0.005341866771290116</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.006022466636243728</v>
+        <v>-0.02831892536589253</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.01969779245663072</v>
+        <v>-0.02493443624492897</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.003382621484263271</v>
+        <v>-0.01706002530891726</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.07647636301204996</v>
+        <v>0.07072596969839662</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.3029733834933299</v>
+        <v>0.3223126196941752</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.1863872084923428</v>
+        <v>0.176592001574857</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1794359251429472</v>
+        <v>0.1775383410157296</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.174579141919363</v>
+        <v>0.1562878011945088</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05510114613737804</v>
+        <v>0.04959555131901761</v>
       </c>
     </row>
     <row r="21">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>54.98</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.0005453332160006985</v>
+        <v>0.04326827029096125</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01663388137567356</v>
+        <v>0.03515632274885938</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-0.01328071899237226</v>
+        <v>0.05740387278054193</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.005966404318587526</v>
+        <v>0.07328335470570657</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.1056348751735336</v>
+        <v>0.1231003114364657</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.08761065005454394</v>
+        <v>0.3337781142588556</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.2443286720972402</v>
+        <v>0.1400711471231719</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2447849871403307</v>
+        <v>0.04586268337540944</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.66755991629733</v>
+        <v>1.125777544800182</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1858428765762929</v>
+        <v>0.2857975830021813</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>65.08</v>
+        <v>54.35</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01034063690823905</v>
+        <v>-0.01145873178175016</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.00711852468153884</v>
+        <v>-0.02036771949240879</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01354933435581396</v>
+        <v>-0.02458727057732002</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.03432936625823779</v>
+        <v>-0.007305963942993765</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.07652104699667506</v>
+        <v>0.09296570169037133</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.2449591083405676</v>
+        <v>0.06802915378812147</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1025997581307718</v>
+        <v>0.2332310742329746</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.002950238880931488</v>
+        <v>0.2538624348868379</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.9652138574139533</v>
+        <v>0.6363447381290426</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2525736536570797</v>
+        <v>0.1783969273696513</v>
       </c>
     </row>
     <row r="23">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>104.35</v>
+        <v>296.85</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.01351862659933833</v>
+        <v>0.03022833002110192</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.02787629949402648</v>
+        <v>0.01414374216560654</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.002103865557475104</v>
+        <v>0.020559050733022</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.0234405591517155</v>
+        <v>0.03540283733631266</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.1712874931361994</v>
+        <v>0.1173216436578732</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2374859534550429</v>
+        <v>0.2485279818383439</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>-0.01705063222729253</v>
+        <v>0.09793990259477869</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>-0.09534919837644729</v>
+        <v>0.03309671429953642</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.4834493550035341</v>
+        <v>0.871217897413114</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1404884935842077</v>
+        <v>0.2322763708854085</v>
       </c>
     </row>
     <row r="24">
@@ -1824,51 +1824,51 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>72.75</v>
+        <v>107.13</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.0001375053137779858</v>
+        <v>0.02664110033491096</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.01556159001534241</v>
+        <v>0.004594878718811257</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-0.03347943078855631</v>
+        <v>0.02448118548402811</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.05335066435299607</v>
+        <v>0.03637413569634695</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.02029365619543344</v>
+        <v>0.2024918807618674</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1753504099864789</v>
+        <v>0.2911204375729728</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.09752283300401654</v>
+        <v>-0.005659953414861474</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1261450573029101</v>
+        <v>-0.08567217120499637</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.8454760474887231</v>
+        <v>0.5757828867654371</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2265995592012631</v>
+        <v>0.1636761317280027</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>288.14</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.01186553972104465</v>
+        <v>-0.004810743801129891</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.002699704911553247</v>
+        <v>-0.02307362195981155</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.009385569204723665</v>
+        <v>-0.03812917071571553</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.01543559603916789</v>
+        <v>-0.03286112760726667</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.08453787485633146</v>
+        <v>0.01538518654026189</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.186005426087009</v>
+        <v>0.1619029359623527</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.07526966949976654</v>
+        <v>0.09614147431850939</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.007693964426967792</v>
+        <v>0.134963821338461</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.7309864413482183</v>
+        <v>0.8844739603673974</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2006909079964159</v>
+        <v>0.2351794196686652</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>142.7</v>
+        <v>181.08</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.006129021253586386</v>
+        <v>0.01587658811250869</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.005697683406345022</v>
+        <v>0.04676568634602596</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.01621718571661501</v>
+        <v>0.01167660916112134</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.01234976384861386</v>
+        <v>0.0008291005435581145</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.06555120133317138</v>
+        <v>-0.06610571276330279</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1229713584868299</v>
+        <v>0.1307726676286012</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.06598613828544919</v>
+        <v>0.1909572520207043</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.113887403359533</v>
+        <v>0.2225662864846996</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.6128852672504761</v>
+        <v>0.9611383476311637</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1727384335744471</v>
+        <v>0.2517071815248619</v>
       </c>
     </row>
     <row r="27">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2006,37 +2006,37 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>66.62</v>
+        <v>141.34</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.0008997834181037057</v>
+        <v>-0.009530488012868266</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.02087004923336588</v>
+        <v>-0.02626220449711236</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.03922690705165588</v>
+        <v>-0.0255931160354087</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.05637387837901942</v>
+        <v>-0.01510549154889507</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.01929346477975558</v>
+        <v>0.05539597838176813</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1706178965571004</v>
+        <v>0.1195346010144978</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0804967256013871</v>
+        <v>0.05814736267320253</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1005733254920367</v>
+        <v>0.1029361317199555</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8960490730939392</v>
+        <v>0.6021021535225859</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.2377032305001821</v>
+        <v>0.1701190989682899</v>
       </c>
     </row>
     <row r="28">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>128.96</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.006318323879969889</v>
+        <v>-0.002641754766427917</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.006777492674394314</v>
+        <v>-0.02488984033618835</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.0304487479154103</v>
+        <v>-0.04176501290806522</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.02642306977652886</v>
+        <v>-0.03340107396073277</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.07492649050333688</v>
+        <v>0.01660078466746495</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.08980994689520094</v>
+        <v>0.161470818034414</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.02758832794635668</v>
+        <v>0.08005157850993538</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.08562788787600439</v>
+        <v>0.1091168185855733</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.5853620356582152</v>
+        <v>0.9430257855830535</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1660293568006852</v>
+        <v>0.2478417767268348</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>178.25</v>
+        <v>90.3</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.007973330079781515</v>
+        <v>0.006464576718271831</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.01399490428355177</v>
+        <v>-0.01735677835080218</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.00413433974218369</v>
+        <v>-0.02599772098087516</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.02998473373719523</v>
+        <v>-0.05478490007193848</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>-0.08070104364560071</v>
+        <v>0.01948273047814242</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.07481912133766477</v>
+        <v>0.1036211893964436</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1836580142177267</v>
+        <v>0.1148028821094127</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2038625280347186</v>
+        <v>0.1136679147809614</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.8767163979127304</v>
+        <v>0.4391817587105027</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2334821891888961</v>
+        <v>0.1290293067620425</v>
       </c>
     </row>
     <row r="30">
@@ -2174,37 +2174,37 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>23.38</v>
+        <v>23.54</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.002985142852680922</v>
+        <v>0.006843531244827394</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.01141651002616173</v>
+        <v>0.02749895557884074</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.01225183416107323</v>
+        <v>-0.005492148726133683</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.02866641224785671</v>
+        <v>-0.01341155434360664</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.05465804748375847</v>
+        <v>-0.0481885702946675</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>-0.01703450396214101</v>
+        <v>0.01652149919900503</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1592582511843339</v>
+        <v>0.1591737214608977</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2622702106218562</v>
+        <v>0.2791036675147567</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.5734876853664661</v>
+        <v>0.62310096671363</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1631108743126182</v>
+        <v>0.1752091896663612</v>
       </c>
     </row>
     <row r="31">
@@ -2216,51 +2216,51 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>89.72</v>
+        <v>127.26</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.01547235899496269</v>
+        <v>-0.01041993704266642</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.01995724400154275</v>
+        <v>-0.03372268536229928</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.03225379059538824</v>
+        <v>-0.0405514040721261</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.04404304520582281</v>
+        <v>-0.04785302289494708</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.01293453745020834</v>
+        <v>0.06372582718563713</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.04754173609952472</v>
+        <v>0.07872428460453373</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.09613518433265411</v>
+        <v>0.01751859325665039</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.09988107781009203</v>
+        <v>0.07849732674605292</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3962874444457769</v>
+        <v>0.5620899510167729</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1176992107847317</v>
+        <v>0.1602956913205602</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>72.38</v>
+        <v>187.1</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.009036194603456948</v>
+        <v>0.01244590375419885</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.01157151110303078</v>
+        <v>-0.006668206403723786</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.02232243933410683</v>
+        <v>-0.04504444024235199</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.02192853359967861</v>
+        <v>-0.03556993722600632</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.01729281472331956</v>
+        <v>0.008116954789087139</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.03903680419268785</v>
+        <v>0.1494402450782111</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.09269398561632336</v>
+        <v>0.04871611712025148</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.08710781949478252</v>
+        <v>0.07205016254144847</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.206391349681327</v>
+        <v>1.095928968954857</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.06454184696851017</v>
+        <v>0.2797511253104665</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>184.8</v>
+        <v>70.83</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.01254730488108202</v>
+        <v>0.004680877036236764</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.02732505118949569</v>
+        <v>0.01229099035798065</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.05678362052073482</v>
+        <v>-0.0451603998428044</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.02676313329630375</v>
+        <v>-0.07544705303808441</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.004275733596293518</v>
+        <v>-0.134090386986793</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.1371866870021661</v>
+        <v>0.06202553163450375</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.05206212308004488</v>
+        <v>0.1129293312297897</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.06043247873934554</v>
+        <v>0.3496242926935711</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.9943635721561321</v>
+        <v>0.3386379009012035</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.2587363606131861</v>
+        <v>0.1021000929341263</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>80.27</v>
+        <v>71.91</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.006559485008334698</v>
+        <v>-0.006493418197613954</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.02056158514663253</v>
+        <v>-0.02775703859454837</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.04418351525628117</v>
+        <v>-0.02867090859793364</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.0664763089665007</v>
+        <v>-0.03963255459655224</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.04156458971556254</v>
+        <v>0.01068710704789333</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.08823302772012265</v>
+        <v>0.05032446167933347</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.07819238446846977</v>
+        <v>0.08997012043645114</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1447099124642792</v>
+        <v>0.07910158787984667</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.3876236302587353</v>
+        <v>0.2108445842500206</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1153826782098055</v>
+        <v>0.06585011047134737</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>70.5</v>
+        <v>29.01</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-0.00564177034231661</v>
+        <v>0.02799436338588057</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>-0.01384806117432058</v>
+        <v>0.02945351010353292</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.04960906295546375</v>
+        <v>0.007291701298069997</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.04755467174688299</v>
+        <v>-0.0189380950869743</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.1381247191968047</v>
+        <v>-0.06419354100381169</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.01948248601857006</v>
+        <v>0.2042341239157448</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.1124305218183808</v>
+        <v>0.01766216102199292</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.3517768174193965</v>
+        <v>0.1336283826963007</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.2578901310989661</v>
+        <v>0.6847702132670159</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.0794790958204552</v>
+        <v>0.1899084771235324</v>
       </c>
     </row>
     <row r="36">
@@ -2510,37 +2510,37 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>100.74</v>
+        <v>100.98</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.002179092934807336</v>
+        <v>0.004246612323423271</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.0163070573051618</v>
+        <v>-0.01597316322414233</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.04529945916759048</v>
+        <v>-0.04124521741801168</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.06989197549126513</v>
+        <v>-0.0644738427806697</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.1115226639827023</v>
+        <v>-0.107749684154879</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.1338931899219287</v>
+        <v>0.150320005284172</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.08562178111557106</v>
+        <v>0.09304244776612447</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.1835885352786066</v>
+        <v>0.1943225591517019</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.3418378499446006</v>
+        <v>0.3765422937547576</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1029775664104915</v>
+        <v>0.1124056512180982</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>108.68</v>
+        <v>93.81</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.02371540960192065</v>
+        <v>0.009686727596712075</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.04356241369259817</v>
+        <v>-0.005512607467052399</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.08379701746122803</v>
+        <v>-0.0230160295952504</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.04356241369259817</v>
+        <v>-0.04761423798381981</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.07063446958514397</v>
+        <v>-0.00966050777045746</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.008449082751214698</v>
+        <v>0.0777295626171659</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.06474539820622272</v>
+        <v>0.08952723777334182</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.2243493027823555</v>
+        <v>0.06320897415022975</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.089866624688113</v>
+        <v>0.3539019476099337</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2785160669057811</v>
+        <v>0.1062732326061742</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>13.08</v>
+        <v>79.86</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.01728027713445168</v>
+        <v>-0.005107712094943206</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.002298830079136005</v>
+        <v>-0.03145998611508338</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.01875468877951003</v>
+        <v>-0.04906555067595286</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.01059004088463755</v>
+        <v>-0.08031536382527427</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.07861492476089449</v>
+        <v>-0.04646000185289423</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.07390269164431751</v>
+        <v>0.09719335160624509</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>-0.02211332552613898</v>
+        <v>0.07254229188197114</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>-0.0614886430221171</v>
+        <v>0.1300842623117895</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.137429405003392</v>
+        <v>0.4054822671728282</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.04385814395847798</v>
+        <v>0.1201472667675467</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>223.49</v>
+        <v>13.17</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.01241713442642356</v>
+        <v>0.006880745650829523</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.02171149713870146</v>
+        <v>0.006880745650829523</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.05083666388937613</v>
+        <v>-0.01200298937193289</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.03501727286970246</v>
+        <v>-0.009029336787323095</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>-0.04254976026223289</v>
+        <v>0.08603659971336275</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.02706304170278284</v>
+        <v>0.0983201516584542</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.09007944594295481</v>
+        <v>-0.005832007571653586</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.09800128431890998</v>
+        <v>-0.05985229265804659</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.3167123726080794</v>
+        <v>0.1612023146778252</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.09604984627755586</v>
+        <v>0.05108046442806935</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>92.91</v>
+        <v>109</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.009593795116797033</v>
+        <v>0.003618530421864996</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.01993670178065876</v>
+        <v>-0.009954954446147912</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.03238901363970836</v>
+        <v>-0.08048171505532675</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.04824829903661898</v>
+        <v>-0.08602925159732278</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.0191616219549805</v>
+        <v>-0.06727154405643199</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.03013129164112405</v>
+        <v>0.07358223192358193</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.07494895539401858</v>
+        <v>0.03974189499215619</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.04615993097246429</v>
+        <v>0.2111071071050705</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.2904715515870187</v>
+        <v>1.166850146393238</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.08871985942260618</v>
+        <v>0.2940258713570605</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>52.96</v>
+        <v>70.84</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.0009449865281561109</v>
+        <v>0.003115173927393355</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.02071010925777905</v>
+        <v>0.008254969883655594</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.03988398783584601</v>
+        <v>-0.0124077370331942</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.07590302189114329</v>
+        <v>-0.02276178196307521</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>-0.09404252597838203</v>
+        <v>0.05291316324591278</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.05451936131267932</v>
+        <v>0.06940771830071668</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.1058097372520785</v>
+        <v>0.01189638729556819</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1373639927110506</v>
+        <v>-0.01575301444282495</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.7425198293796949</v>
+        <v>0.00756503362568739</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.203351701315017</v>
+        <v>0.002515345606873831</v>
       </c>
     </row>
     <row r="42">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2846,37 +2846,37 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>70.62</v>
+        <v>223.35</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.01354928957853851</v>
+        <v>-0.0006264234919118872</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.001978510251863796</v>
+        <v>-0.009578238020199303</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.01547470456439437</v>
+        <v>-0.05143124210077732</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.003386930026846091</v>
+        <v>-0.0680935961535144</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.04964334167486539</v>
+        <v>-0.04314952958474128</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.0195758501546055</v>
+        <v>0.06429676160009823</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>-0.0001605134529392149</v>
+        <v>0.08514012518339009</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.02960203357512459</v>
+        <v>0.09715407129617915</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>-0.004947471213657462</v>
+        <v>0.3566786094825265</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-0.001651884290417294</v>
+        <v>0.1070289862986762</v>
       </c>
     </row>
     <row r="43">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2902,37 +2902,37 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>28.22</v>
+        <v>53.08</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.001774910788964634</v>
+        <v>0.002265912927804647</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.001774910788964634</v>
+        <v>0.001131674326159571</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.0201388867732919</v>
+        <v>-0.03770844855169098</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.06926122699889758</v>
+        <v>-0.05869830811172827</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.08967744150469381</v>
+        <v>-0.09198970522595518</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.1476209490948122</v>
+        <v>0.08472221745826491</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>-0.003113542143015846</v>
+        <v>0.1023812985177441</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.09807560400660775</v>
+        <v>0.1433497345487889</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.6101380294890382</v>
+        <v>0.8010091633398067</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.1720722108864567</v>
+        <v>0.2166676875800926</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>56.62</v>
+        <v>114.75</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.005969103898398331</v>
+        <v>0.0389693498587389</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.02575208120499972</v>
+        <v>0.0005056905150100377</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.0402194823393085</v>
+        <v>0.02765500390823572</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.06957970654003798</v>
+        <v>0.03346668997384539</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.0824876313555144</v>
+        <v>0.05461581001799032</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.000435490867835453</v>
+        <v>0.03177441459428154</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0808405402268233</v>
+        <v>-0.002995948218008748</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.106551129312503</v>
+        <v>-0.02373280580350323</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.5683581123733037</v>
+        <v>0.8080473278745546</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.1618455837748609</v>
+        <v>0.2182504996144603</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>46.54</v>
+        <v>62.69</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.008732690963782597</v>
+        <v>0.01581485422601303</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.01041883641266927</v>
+        <v>-0.0143436455606738</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.02778353971241787</v>
+        <v>-0.03153443190700733</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.0318285581237816</v>
+        <v>-0.07670853345052242</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.003190261897823454</v>
+        <v>-0.04028878104615241</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>-0.02821658498895807</v>
+        <v>0.1044718732389587</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.02763790926648557</v>
+        <v>0.02184259273249611</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.007859951192218606</v>
+        <v>0.02025484817648571</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.1101057423639513</v>
+        <v>0.6464054761407658</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.03543168293815113</v>
+        <v>0.1808070405921998</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>61.77</v>
+        <v>56.4</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.005794311993603252</v>
+        <v>-0.003885507067397209</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.020922486790802</v>
+        <v>-0.01314061762438035</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.04661213790845786</v>
+        <v>-0.04394871632382924</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.08866920079333096</v>
+        <v>-0.05115394984842447</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.05523016834237326</v>
+        <v>-0.08605263214830694</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.07278727254598438</v>
+        <v>0.029405504566971</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0136566599332173</v>
+        <v>0.08317708320741368</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.004533312323661498</v>
+        <v>0.1062866896659782</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.572599136774826</v>
+        <v>0.5959466949912269</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.1628918968280861</v>
+        <v>0.1686185987780806</v>
       </c>
     </row>
     <row r="47">
@@ -3112,51 +3112,51 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>110.81</v>
+        <v>45.91</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.0137071734440839</v>
+        <v>-0.009792130932541387</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.01589698880803037</v>
+        <v>-0.02693676277612167</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.01088995120946645</v>
+        <v>-0.03730357063865841</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0.002986913392770463</v>
+        <v>-0.05195897383704973</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.01505960818265595</v>
+        <v>-0.006633131369891854</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.01941934908041076</v>
+        <v>-0.01754929179649645</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>-0.03997929265595224</v>
+        <v>0.01958357890959306</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>-0.05647855034823157</v>
+        <v>0.009861288965672177</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.6965906024588968</v>
+        <v>0.1117208701939212</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.1926848033198054</v>
+        <v>0.03593360032749637</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>17.56</v>
+        <v>35.82</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.009588273022171911</v>
+        <v>0.0202221325015679</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-0.02008931968855299</v>
+        <v>0.03049486261437373</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.01181772574066198</v>
+        <v>-0.003616163153166041</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.01014657877667124</v>
+        <v>-0.006104362239578665</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.1677725522050802</v>
+        <v>-0.06599126249062881</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>-0.04152803790371862</v>
+        <v>0.06660464683054212</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.08820342892048871</v>
+        <v>0.0009082791547643243</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>0.1797951193770055</v>
+        <v>0.02836165088549181</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.1906576314693249</v>
+        <v>0.4773689139644826</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.0598936737628375</v>
+        <v>0.1389281281230352</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>35.11</v>
+        <v>17.8</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.0001424197031520968</v>
+        <v>0.01366741334950738</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.004818542370388923</v>
+        <v>0.01366741334950738</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.02336578956220325</v>
+        <v>0.001688169866296718</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.0393980480647691</v>
+        <v>0.01193854932637728</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.08450453312633277</v>
+        <v>-0.1563981556752615</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.007964383902491212</v>
+        <v>-0.01175108900018473</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>-0.00228413236412095</v>
+        <v>0.08563110631623982</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.007114896462948161</v>
+        <v>0.1856713346715502</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.3884817221508663</v>
+        <v>0.2235836861294944</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.1156125444820526</v>
+        <v>0.06957495742972442</v>
       </c>
     </row>
     <row r="50">
@@ -3294,37 +3294,37 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>82.03</v>
+        <v>82.56</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.009538769843496109</v>
+        <v>0.00858818397712402</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.03255103321652442</v>
+        <v>-0.03257150218624116</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.06347754071304312</v>
+        <v>-0.0554345943711384</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.058533210546165</v>
+        <v>-0.05672685831399871</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.04841998313114604</v>
+        <v>-0.04024771041962283</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.0435395164122192</v>
+        <v>0.05705132870090668</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.05381533752475831</v>
+        <v>-0.04808852026654176</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.06555445787817316</v>
+        <v>-0.04457298088387363</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.3888760466704089</v>
+        <v>0.4288808437831861</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1157181446580025</v>
+        <v>0.1263291861600337</v>
       </c>
     </row>
     <row r="51">
@@ -3350,37 +3350,37 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>213.84</v>
+        <v>216.14</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.0001870607069781594</v>
+        <v>0.01075571965556699</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.02247436947299253</v>
+        <v>-0.001750483974745198</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.05107094126353218</v>
+        <v>-0.04086452633474169</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.1509839533374372</v>
+        <v>-0.08826764718301083</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.1041973460773032</v>
+        <v>-0.09456234386499784</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.07428517980313776</v>
+        <v>-0.02703786302294231</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.02942248489936961</v>
+        <v>0.01296340196693646</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.0562014960536632</v>
+        <v>0.06530488168531901</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.9886654643189881</v>
+        <v>1.064847213897046</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.2575364361079342</v>
+        <v>0.2733935351538264</v>
       </c>
     </row>
     <row r="52">
@@ -3406,37 +3406,37 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>43.31</v>
+        <v>43.67</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.01073543670878574</v>
+        <v>0.008312093840668888</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.01746824922364687</v>
+        <v>-0.007274460043454112</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.04329576020882331</v>
+        <v>-0.03534354478991319</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.03862370462235465</v>
+        <v>-0.04462920490891709</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.03412129291013333</v>
+        <v>-0.0260928184580983</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.05560399483477019</v>
+        <v>-0.01333032478450968</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.04506758105916941</v>
+        <v>-0.03852928380777687</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.05284270897605015</v>
+        <v>-0.04156824830654005</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.2415542062640139</v>
+        <v>0.2674195866210383</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.07478573880540917</v>
+        <v>0.08219819391182703</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>51.77</v>
+        <v>25.99</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.001353959260952164</v>
+        <v>0.008810448110344149</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>0.01908379893302237</v>
+        <v>-0.02263665811632642</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.03317203142448522</v>
+        <v>-0.05311475929260923</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.06473690478192307</v>
+        <v>-0.05665440950726741</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.05667384160553568</v>
+        <v>0.04272988399985533</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.05822639326501711</v>
+        <v>0.08895709296362075</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.166352207844924</v>
+        <v>-0.1363888129813544</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>-0.1414112273657304</v>
+        <v>-0.2541853545019646</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.04266730609248226</v>
+        <v>0.3121018200626988</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.01402482024129648</v>
+        <v>0.09476905398582303</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>25.76</v>
+        <v>51.95</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.01456975488148293</v>
+        <v>0.00347692299756952</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-0.01468510366489717</v>
+        <v>0.00330245097912818</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.06138438347753905</v>
+        <v>-0.02981044502585162</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.009038485013521669</v>
+        <v>-0.07368223795592732</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.03362320042684663</v>
+        <v>0.06034781518634413</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0.06431218084296697</v>
+        <v>-0.04280027839408052</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.134482753318089</v>
+        <v>-0.1673271570441369</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.2573144325203767</v>
+        <v>-0.1347129377065388</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.2361021459672044</v>
+        <v>0.07878874535895375</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.07321018803651635</v>
+        <v>0.02560186595117697</v>
       </c>
     </row>
     <row r="55">
@@ -3560,51 +3560,51 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>41.1</v>
+        <v>243.55</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.01415207896432746</v>
+        <v>0.01593035610502724</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.03043172762683166</v>
+        <v>0.003504751926811878</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.04596107875525401</v>
+        <v>-0.03652912745161896</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.06633352915214674</v>
+        <v>-0.1065444015379178</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.07590609785510327</v>
+        <v>-0.142656383244093</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.1086748711691908</v>
+        <v>-0.05809762699958054</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.02816881462699061</v>
+        <v>0.01109498163769684</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.0009746714560063818</v>
+        <v>0.07759129247144725</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>0.3863063664914352</v>
+        <v>1.201735008723461</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.1150296241779416</v>
+        <v>0.300933256634248</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>239.86</v>
+        <v>40.66</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.006050085652059667</v>
+        <v>-0.003431357653587153</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.02480080475283097</v>
+        <v>-0.02058892526317346</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.05163687194821953</v>
+        <v>-0.0492346976093978</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.1741211078081836</v>
+        <v>-0.04234352354403093</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.1561000207975813</v>
+        <v>-0.07907698047341061</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.1144622918788809</v>
+        <v>-0.07035386694816259</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.02998889841231511</v>
+        <v>-0.0190083003644812</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.05957344381312746</v>
+        <v>-0.00880101727674254</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>1.090181781531073</v>
+        <v>0.4024655968282214</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.2785803314270723</v>
+        <v>0.119345279766164</v>
       </c>
     </row>
     <row r="57">
@@ -3686,37 +3686,37 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>17.35</v>
+        <v>17.53</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.01866515373359168</v>
+        <v>0.0106627931916341</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.02407467090779414</v>
+        <v>-0.01819713056174721</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.0858798314056517</v>
+        <v>-0.0761327570956285</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.1355256280375502</v>
+        <v>-0.1257852550676962</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.03680675561202884</v>
+        <v>-0.02653642524354083</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.07072327048837135</v>
+        <v>0.1059602872078556</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.1777640623913891</v>
+        <v>-0.1703335861123001</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.2466348300401686</v>
+        <v>-0.2401525283837648</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>-0.0015342946914918</v>
+        <v>0.05511850786198069</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>-0.0005116933492553821</v>
+        <v>0.01804524634176286</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>18.22</v>
+        <v>42.98</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.03470202313353687</v>
+        <v>0.03193272431289196</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.05883568278088469</v>
+        <v>0.01872483861678109</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.05932160661999375</v>
+        <v>-0.06686933867181122</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.04950708337856513</v>
+        <v>-0.06707185094544377</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.06420133765195479</v>
+        <v>-0.10046043029914</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0.0156075123166981</v>
+        <v>-0.0745047197844384</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.1277999346251262</v>
+        <v>-0.01870282325187522</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.215935414108871</v>
+        <v>-0.08897983229778805</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.1280846281322785</v>
+        <v>0.8977251701867324</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.04099160482102926</v>
+        <v>0.2380678307330937</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>41.65</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.0241330546375832</v>
+        <v>0.01153841102694053</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.04318854367420999</v>
+        <v>-0.007813288031215948</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.09574467468360415</v>
+        <v>-0.05566889229390348</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.04516271100973956</v>
+        <v>-0.08448649516220963</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.1282963041027557</v>
+        <v>-0.1206512641077321</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.1512125171202713</v>
+        <v>0.01733157191857893</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.007319342597493783</v>
+        <v>-0.06627413968218143</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.04553282126171032</v>
+        <v>-0.1307385234319272</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.7765104156836302</v>
+        <v>0.3072866075226317</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.2111257914013163</v>
+        <v>0.09342820086899906</v>
       </c>
     </row>
     <row r="60">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>96.39</v>
+        <v>88.2</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.007005257106352247</v>
+        <v>0.009037790333319196</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.02102376309234255</v>
+        <v>-0.01227387829640048</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.06644068387749702</v>
+        <v>-0.0528725149224879</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.09023122070748069</v>
+        <v>-0.08765260474232339</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.1306818021527582</v>
+        <v>-0.1038313186905614</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>-0.02780049965733777</v>
+        <v>0.009299431099994981</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.08794897146530167</v>
+        <v>-0.09084052827516587</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1522060339783795</v>
+        <v>-0.1784446351682449</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.246669085531815</v>
+        <v>0.160949563359122</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.07625966216499425</v>
+        <v>0.05100419828926106</v>
       </c>
     </row>
     <row r="61">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>87.41</v>
+        <v>18.15</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.0128740751028783</v>
+        <v>-0.004006583807614428</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.01554522037360984</v>
+        <v>-0.06270340881551495</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.06135578453940371</v>
+        <v>-0.0630905134390829</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.08446112840825748</v>
+        <v>-0.0764885643041977</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.1118581584408213</v>
+        <v>-0.06795069341970572</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.03357183189739887</v>
+        <v>0.02150295427001314</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.1144080511310328</v>
+        <v>-0.1344649336656133</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.1994846854773143</v>
+        <v>-0.2214801906201587</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1084699965324647</v>
+        <v>0.1707238021396702</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.0349228618504549</v>
+        <v>0.05394548905111574</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>45.66</v>
+        <v>46.71</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.01509923972656624</v>
+        <v>0.02299604118636589</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>-0.03160130711022335</v>
+        <v>0.01060142472584036</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.04954206958280838</v>
+        <v>-0.02768529986902657</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.08441947412557416</v>
+        <v>-0.05291972073198259</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2462859282383555</v>
+        <v>-0.2289534884013812</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1930010892585194</v>
+        <v>-0.1530372113851314</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.05524522827406464</v>
+        <v>-0.04654016158150698</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.06657319277497598</v>
+        <v>0.08200141453964371</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1532391877629482</v>
+        <v>-0.1232603391552823</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.05393658070614404</v>
+        <v>-0.04290095176619391</v>
       </c>
     </row>
   </sheetData>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4602,21 +4602,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1374819547149604</v>
+        <v>0.1017738786133422</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4624,21 +4624,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1741211078081836</v>
+        <v>-0.1257852550676962</v>
       </c>
     </row>
     <row r="18">
@@ -4647,21 +4647,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.1070039560255942</v>
+        <v>0.09016948635295297</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1509839533374372</v>
+        <v>-0.1065444015379178</v>
       </c>
     </row>
     <row r="19">
@@ -4692,21 +4692,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.08762707958313687</v>
+        <v>0.08687399047262745</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.1355256280375502</v>
+        <v>-0.08826764718301083</v>
       </c>
     </row>
     <row r="20">
@@ -4737,21 +4737,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.0734121037968225</v>
+        <v>0.07328335470570657</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09023122070748069</v>
+        <v>-0.08765260474232339</v>
       </c>
     </row>
     <row r="21">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.03432936625823779</v>
+        <v>0.06354171420120047</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.08866920079333096</v>
+        <v>-0.08602925159732278</v>
       </c>
     </row>
     <row r="22">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.02940665705712386</v>
+        <v>0.05322954457553863</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.08446112840825748</v>
+        <v>-0.08448649516220963</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.02837871234759115</v>
+        <v>0.04951999719573674</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.08441947412557416</v>
+        <v>-0.08168823666540193</v>
       </c>
     </row>
     <row r="24">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.02493842615241126</v>
+        <v>0.03637413569634695</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.07605237734892167</v>
+        <v>-0.08031536382527427</v>
       </c>
     </row>
     <row r="25">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.0234405591517155</v>
+        <v>0.03540283733631266</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.07590302189114329</v>
+        <v>-0.07670853345052242</v>
       </c>
     </row>
     <row r="26">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.02165873432659216</v>
+        <v>0.03346668997384539</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.06989197549126513</v>
+        <v>-0.0764885643041977</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3586863164794267</v>
+        <v>0.3898012400898647</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2462859282383555</v>
+        <v>-0.2289534884013812</v>
       </c>
     </row>
     <row r="32">
@@ -5158,21 +5158,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.3033377790285392</v>
+        <v>0.330114956559806</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.2034487083308625</v>
+        <v>-0.1750073937822347</v>
       </c>
     </row>
     <row r="33">
@@ -5203,21 +5203,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.2790804457390446</v>
+        <v>0.3295157649919258</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1677725522050802</v>
+        <v>-0.1563981556752615</v>
       </c>
     </row>
     <row r="34">
@@ -5248,21 +5248,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2489843604710456</v>
+        <v>0.2810417016347249</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1561000207975813</v>
+        <v>-0.142656383244093</v>
       </c>
     </row>
     <row r="35">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2361458142598469</v>
+        <v>0.2204713698636818</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.1381247191968047</v>
+        <v>-0.134090386986793</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.1823502123417056</v>
+        <v>0.2154133078976523</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.1316603082983875</v>
+        <v>-0.1206512641077321</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.1781329194268173</v>
+        <v>0.2024918807618674</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.1306818021527582</v>
+        <v>-0.107749684154879</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1712874931361994</v>
+        <v>0.1931072683602397</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.1282963041027557</v>
+        <v>-0.1038313186905614</v>
       </c>
     </row>
     <row r="39">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1571930782317597</v>
+        <v>0.1444673113601969</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.1118581584408213</v>
+        <v>-0.10046043029914</v>
       </c>
     </row>
     <row r="40">
@@ -5518,21 +5518,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1389256751862518</v>
+        <v>0.1255352385310526</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.1115226639827023</v>
+        <v>-0.09675997925907232</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.5425026300310289</v>
+        <v>0.6280829447221463</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1930010892585194</v>
+        <v>-0.1530372113851314</v>
       </c>
     </row>
     <row r="46">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.5414054807418531</v>
+        <v>0.6142131676489138</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1512125171202713</v>
+        <v>-0.0745047197844384</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5188788217159936</v>
+        <v>0.6077919570080763</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5736,21 +5736,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1144622918788809</v>
+        <v>-0.07035386694816259</v>
       </c>
     </row>
     <row r="48">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.4691589296494052</v>
+        <v>0.6063935620411336</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5781,21 +5781,21 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.1086748711691908</v>
+        <v>-0.05809762699958054</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.4555337730979732</v>
+        <v>0.5491761824233214</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.07428517980313776</v>
+        <v>-0.04280027839408052</v>
       </c>
     </row>
     <row r="50">
@@ -5849,21 +5849,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.3936566255242464</v>
+        <v>0.4715157950005733</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.05822639326501711</v>
+        <v>-0.03092807531879216</v>
       </c>
     </row>
     <row r="51">
@@ -5894,21 +5894,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.3930896670697537</v>
+        <v>0.4427623515123225</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.05560399483477019</v>
+        <v>-0.02703786302294231</v>
       </c>
     </row>
     <row r="52">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3614908963984587</v>
+        <v>0.4366207252019625</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.04152803790371862</v>
+        <v>-0.01754929179649645</v>
       </c>
     </row>
     <row r="53">
@@ -5984,21 +5984,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.3029733834933299</v>
+        <v>0.3337781142588556</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.03357183189739887</v>
+        <v>-0.01333032478450968</v>
       </c>
     </row>
     <row r="54">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2953004632260816</v>
+        <v>0.3223126196941752</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.02821658498895807</v>
+        <v>-0.01175108900018473</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9170732478879893</v>
+        <v>0.9705882627933775</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2573144325203767</v>
+        <v>-0.2541853545019646</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8133669684588607</v>
+        <v>0.8937779589929113</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2466348300401686</v>
+        <v>-0.2401525283837648</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7341928120128591</v>
+        <v>0.7890747109127749</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.215935414108871</v>
+        <v>-0.2214801906201587</v>
       </c>
     </row>
     <row r="62">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.7014056421108741</v>
+        <v>0.6781042488967195</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1994846854773143</v>
+        <v>-0.1784446351682449</v>
       </c>
     </row>
     <row r="63">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6284369803271792</v>
+        <v>0.6627007853676392</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6337,21 +6337,21 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1522060339783795</v>
+        <v>-0.1347129377065388</v>
       </c>
     </row>
     <row r="64">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.5824622543010014</v>
+        <v>0.6498151241081944</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6382,21 +6382,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1414112273657304</v>
+        <v>-0.1307385234319272</v>
       </c>
     </row>
     <row r="65">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.5699594055439274</v>
+        <v>0.585393291047305</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6427,21 +6427,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.09534919837644729</v>
+        <v>-0.08897983229778805</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.5032387317818325</v>
+        <v>0.5432910157417756</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6472,21 +6472,21 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.06555445787817316</v>
+        <v>-0.08567217120499637</v>
       </c>
     </row>
     <row r="67">
@@ -6495,21 +6495,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.497588176359439</v>
+        <v>0.4953428488556111</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.0614886430221171</v>
+        <v>-0.05985229265804659</v>
       </c>
     </row>
     <row r="68">
@@ -6540,21 +6540,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.4892834865875435</v>
+        <v>0.4603285630814615</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6562,21 +6562,21 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.05647855034823157</v>
+        <v>-0.04457298088387363</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.943044454230621</v>
+        <v>3.292088735974303</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1532391877629482</v>
+        <v>-0.1232603391552823</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.776882494832272</v>
+        <v>2.893075085599392</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>-0.004947471213657462</v>
+        <v>0.00756503362568739</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.324378718831347</v>
+        <v>2.383349961289517</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>-0.0015342946914918</v>
+        <v>0.05511850786198069</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.772486782275988</v>
+        <v>1.994413457428208</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.04266730609248226</v>
+        <v>0.07878874535895375</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.563749234839318</v>
+        <v>1.776821509533177</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6848,21 +6848,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1084699965324647</v>
+        <v>0.1117208701939212</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.442222574704173</v>
+        <v>1.543340008013165</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6893,21 +6893,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1101057423639513</v>
+        <v>0.1562878011945088</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.325133922337083</v>
+        <v>1.43797244210432</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1280846281322785</v>
+        <v>0.160949563359122</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.292099100560097</v>
+        <v>1.404967747359576</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.137429405003392</v>
+        <v>0.1612023146778252</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.187546097287785</v>
+        <v>1.307978816530349</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,21 +7028,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1705157267459414</v>
+        <v>0.1707238021396702</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.090181781531073</v>
+        <v>1.201735008723461</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,21 +7073,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.174579141919363</v>
+        <v>0.2108445842500206</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -496,8 +496,8 @@
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -686,13 +686,13 @@
         <v>0.5420000172283856</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7890747109127749</v>
+        <v>0.7890745606538887</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.027039536450951</v>
+        <v>1.02703972934007</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2655735990557528</v>
+        <v>0.2655736391989212</v>
       </c>
     </row>
     <row r="4">
@@ -969,10 +969,10 @@
         <v>0.6498151241081944</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.776821509533177</v>
+        <v>1.776822182420259</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.4055597807472235</v>
+        <v>0.405559894280261</v>
       </c>
     </row>
     <row r="9">
@@ -1022,7 +1022,7 @@
         <v>0.2874447407166825</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.6627007853676392</v>
+        <v>0.6627009186674389</v>
       </c>
       <c r="O9" s="6" t="n">
         <v>1.160512034402311</v>
@@ -1078,13 +1078,13 @@
         <v>0.4910280040396333</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5432910157417756</v>
+        <v>0.5432911303654446</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.43797244210432</v>
+        <v>1.437972728150566</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3458900963380191</v>
+        <v>0.3458901489755837</v>
       </c>
     </row>
     <row r="11">
@@ -1128,19 +1128,19 @@
         <v>0.2154133078976523</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.05659954529076261</v>
+        <v>0.05659945308534842</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>0.5013629448387711</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4588497477449343</v>
+        <v>0.4588498356323676</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3770278212987883</v>
+        <v>0.3770276646882427</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1125364233461463</v>
+        <v>0.1125363811695734</v>
       </c>
     </row>
     <row r="12">
@@ -1190,7 +1190,7 @@
         <v>0.2182821860065567</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4544273596642328</v>
+        <v>0.4544275154752908</v>
       </c>
       <c r="O12" s="6" t="n">
         <v>0.6977875575545294</v>
@@ -1249,10 +1249,10 @@
         <v>0.6781042488967195</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.543340008013165</v>
+        <v>1.543339443933534</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3650067772858125</v>
+        <v>0.3650066763722404</v>
       </c>
     </row>
     <row r="14">
@@ -1296,19 +1296,19 @@
         <v>0.1079251621861952</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.284258261262951</v>
+        <v>0.2842581680808773</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>0.2069468189450416</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.4603285630814615</v>
+        <v>0.4603284425976246</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7156061661538091</v>
+        <v>0.7156056672877107</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1971241704895166</v>
+        <v>0.1971240544557529</v>
       </c>
     </row>
     <row r="15">
@@ -1417,10 +1417,10 @@
         <v>0.4953428488556111</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.7691023001697326</v>
+        <v>0.769102412716359</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2094399658125319</v>
+        <v>0.209439991459887</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>0.07072596969839662</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.3223126196941752</v>
+        <v>0.3223125002878349</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>0.176592001574857</v>
@@ -1641,10 +1641,10 @@
         <v>0.1775383410157296</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1562878011945088</v>
+        <v>0.1562877098902584</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.04959555131901761</v>
+        <v>0.04959552369252274</v>
       </c>
     </row>
     <row r="21">
@@ -1747,16 +1747,16 @@
         <v>0.06802915378812147</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2332310742329746</v>
+        <v>0.2332309674875122</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.2538624348868379</v>
+        <v>0.2538625452337953</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6363447381290426</v>
+        <v>0.6363451140012772</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1783969273696513</v>
+        <v>0.1783970175964931</v>
       </c>
     </row>
     <row r="23">
@@ -1912,10 +1912,10 @@
         <v>0.01538518654026189</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1619029359623527</v>
+        <v>0.1619030074988452</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.09614147431850939</v>
+        <v>0.09614160165450381</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>0.134963821338461</v>
@@ -1968,7 +1968,7 @@
         <v>-0.06610571276330279</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1307726676286012</v>
+        <v>0.1307727753743704</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>0.1909572520207043</v>
@@ -1977,10 +1977,10 @@
         <v>0.2225662864846996</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.9611383476311637</v>
+        <v>0.9611386717215247</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2517071815248619</v>
+        <v>0.2517072504756681</v>
       </c>
     </row>
     <row r="27">
@@ -2030,13 +2030,13 @@
         <v>0.05814736267320253</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1029361317199555</v>
+        <v>0.1029362630474848</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.6021021535225859</v>
+        <v>0.6021022920722394</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1701190989682899</v>
+        <v>0.1701191326988878</v>
       </c>
     </row>
     <row r="28">
@@ -2083,16 +2083,16 @@
         <v>0.161470818034414</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.08005157850993538</v>
+        <v>0.08005164586105074</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1091168185855733</v>
+        <v>0.1091167475607231</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.9430257855830535</v>
+        <v>0.9430251316489153</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2478417767268348</v>
+        <v>0.2478416367378831</v>
       </c>
     </row>
     <row r="29">
@@ -2145,10 +2145,10 @@
         <v>0.1136679147809614</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4391817587105027</v>
+        <v>0.4391814962132392</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1290293067620425</v>
+        <v>0.1290292381195379</v>
       </c>
     </row>
     <row r="30">
@@ -2254,13 +2254,13 @@
         <v>0.01751859325665039</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.07849732674605292</v>
+        <v>0.0784972570133875</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.5620899510167729</v>
+        <v>0.5620898047282741</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1602956913205602</v>
+        <v>0.1602956551002985</v>
       </c>
     </row>
     <row r="32">
@@ -2307,16 +2307,16 @@
         <v>0.1494402450782111</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.04871611712025148</v>
+        <v>0.04871620681400324</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.07205016254144847</v>
+        <v>0.07205025627099571</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>1.095928968954857</v>
+        <v>1.095929148085311</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.2797511253104665</v>
+        <v>0.2797511617688258</v>
       </c>
     </row>
     <row r="33">
@@ -2366,7 +2366,7 @@
         <v>0.1129293312297897</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.3496242926935711</v>
+        <v>0.3496241945936704</v>
       </c>
       <c r="O33" s="6" t="n">
         <v>0.3386379009012035</v>
@@ -2422,13 +2422,13 @@
         <v>0.08997012043645114</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.07910158787984667</v>
+        <v>0.07910171142493261</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2108445842500206</v>
+        <v>0.2108445064736726</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.06585011047134737</v>
+        <v>0.06585008765038092</v>
       </c>
     </row>
     <row r="35">
@@ -2528,19 +2528,19 @@
         <v>-0.107749684154879</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.150320005284172</v>
+        <v>0.1503199053090367</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.09304244776612447</v>
+        <v>0.09304235749918588</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>0.1943225591517019</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.3765422937547576</v>
+        <v>0.3765424369187684</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1124056512180982</v>
+        <v>0.1124056897824659</v>
       </c>
     </row>
     <row r="37">
@@ -2593,10 +2593,10 @@
         <v>0.06320897415022975</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.3539019476099337</v>
+        <v>0.3539020966885738</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1062732326061742</v>
+        <v>0.106273273210223</v>
       </c>
     </row>
     <row r="38">
@@ -2643,16 +2643,16 @@
         <v>0.09719335160624509</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.07254229188197114</v>
+        <v>0.07254240177993876</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1300842623117895</v>
+        <v>0.1300843843181481</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.4054822671728282</v>
+        <v>0.4054824558900627</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1201472667675467</v>
+        <v>0.1201473169024339</v>
       </c>
     </row>
     <row r="39">
@@ -2702,13 +2702,13 @@
         <v>-0.005832007571653586</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>-0.05985229265804659</v>
+        <v>-0.05985222865413431</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.1612023146778252</v>
+        <v>0.1612025099589032</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.05108046442806935</v>
+        <v>0.05108052334864155</v>
       </c>
     </row>
     <row r="40">
@@ -2752,10 +2752,10 @@
         <v>-0.06727154405643199</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.07358223192358193</v>
+        <v>0.07358215124947365</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.03974189499215619</v>
+        <v>0.03974181932374221</v>
       </c>
       <c r="N40" s="6" t="n">
         <v>0.2111071071050705</v>
@@ -2817,10 +2817,10 @@
         <v>-0.01575301444282495</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.00756503362568739</v>
+        <v>0.007564924291074471</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.002515345606873831</v>
+        <v>0.002515309344655048</v>
       </c>
     </row>
     <row r="42">
@@ -2870,13 +2870,13 @@
         <v>0.08514012518339009</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.09715407129617915</v>
+        <v>0.09715415353357915</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.3566786094825265</v>
+        <v>0.3566783579941188</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1070289862986762</v>
+        <v>0.1070289178951078</v>
       </c>
     </row>
     <row r="43">
@@ -2929,10 +2929,10 @@
         <v>0.1433497345487889</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.8010091633398067</v>
+        <v>0.8010089302297889</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.2166676875800926</v>
+        <v>0.2166676350877745</v>
       </c>
     </row>
     <row r="44">
@@ -2976,19 +2976,19 @@
         <v>0.05461581001799032</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.03177441459428154</v>
+        <v>0.03177434381488453</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>-0.002995948218008748</v>
+        <v>-0.002995882128693061</v>
       </c>
       <c r="N44" s="6" t="n">
         <v>-0.02373280580350323</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.8080473278745546</v>
+        <v>0.8080477625719806</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.2182504996144603</v>
+        <v>0.2182505972465496</v>
       </c>
     </row>
     <row r="45">
@@ -3032,7 +3032,7 @@
         <v>-0.04028878104615241</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.1044718732389587</v>
+        <v>0.1044719474675413</v>
       </c>
       <c r="M45" s="6" t="n">
         <v>0.02184259273249611</v>
@@ -3094,13 +3094,13 @@
         <v>0.08317708320741368</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.1062866896659782</v>
+        <v>0.1062867724442527</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.5959466949912269</v>
+        <v>0.5959463504448974</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.1686185987780806</v>
+        <v>0.16861851468102</v>
       </c>
     </row>
     <row r="47">
@@ -3203,16 +3203,16 @@
         <v>0.06660464683054212</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0009082791547643243</v>
+        <v>0.000908172464935797</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0.02836165088549181</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.4773689139644826</v>
+        <v>0.4773687977440779</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.1389281281230352</v>
+        <v>0.1389280982576238</v>
       </c>
     </row>
     <row r="49">
@@ -3262,13 +3262,13 @@
         <v>0.08563110631623982</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1856713346715502</v>
+        <v>0.1856714099912831</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.2235836861294944</v>
+        <v>0.2235837663429983</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.06957495742972442</v>
+        <v>0.06957498080214908</v>
       </c>
     </row>
     <row r="50">
@@ -3312,19 +3312,19 @@
         <v>-0.04024771041962283</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.05705132870090668</v>
+        <v>0.05705143195626494</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.04808852026654176</v>
+        <v>-0.04808843653027994</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.04457298088387363</v>
+        <v>-0.0445728965279707</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.4288808437831861</v>
+        <v>0.4288807494461113</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1263291861600337</v>
+        <v>0.1263291613726618</v>
       </c>
     </row>
     <row r="51">
@@ -3377,10 +3377,10 @@
         <v>0.06530488168531901</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>1.064847213897046</v>
+        <v>1.064847364395072</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.2733935351538264</v>
+        <v>0.2733935660912579</v>
       </c>
     </row>
     <row r="52">
@@ -3433,10 +3433,10 @@
         <v>-0.04156824830654005</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.2674195866210383</v>
+        <v>0.2674194463016493</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.08219819391182703</v>
+        <v>0.08219815397414676</v>
       </c>
     </row>
     <row r="53">
@@ -3489,10 +3489,10 @@
         <v>-0.2541853545019646</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.3121018200626988</v>
+        <v>0.3121016937271974</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.09476905398582303</v>
+        <v>0.09476901884927114</v>
       </c>
     </row>
     <row r="54">
@@ -3545,10 +3545,10 @@
         <v>-0.1347129377065388</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.07878874535895375</v>
+        <v>0.07878865990202133</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.02560186595117697</v>
+        <v>0.02560183886994283</v>
       </c>
     </row>
     <row r="55">
@@ -3595,10 +3595,10 @@
         <v>-0.05809762699958054</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.01109498163769684</v>
+        <v>0.0110949175881867</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.07759129247144725</v>
+        <v>0.07759136522263788</v>
       </c>
       <c r="O55" s="6" t="n">
         <v>1.201735008723461</v>
@@ -3654,13 +3654,13 @@
         <v>-0.0190083003644812</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.00880101727674254</v>
+        <v>-0.008800925101467794</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.4024655968282214</v>
+        <v>0.4024656890953853</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.119345279766164</v>
+        <v>0.1193453043131267</v>
       </c>
     </row>
     <row r="57">
@@ -3713,10 +3713,10 @@
         <v>-0.2401525283837648</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.05511850786198069</v>
+        <v>0.05511838676683123</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.01804524634176286</v>
+        <v>0.01804520739500148</v>
       </c>
     </row>
     <row r="58">
@@ -3825,10 +3825,10 @@
         <v>-0.1307385234319272</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.3072866075226317</v>
+        <v>0.3072868764711649</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.09342820086899906</v>
+        <v>0.09342827585278313</v>
       </c>
     </row>
     <row r="60">
@@ -3875,16 +3875,16 @@
         <v>0.009299431099994981</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.09084052827516587</v>
+        <v>-0.09084059977443537</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1784446351682449</v>
+        <v>-0.1784446935524194</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.160949563359122</v>
+        <v>0.1609496799456187</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.05100419828926106</v>
+        <v>0.0510042334710632</v>
       </c>
     </row>
     <row r="61">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.3223126196941752</v>
+        <v>0.3223125002878349</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7890747109127749</v>
+        <v>0.7890745606538887</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1784446351682449</v>
+        <v>-0.1784446935524194</v>
       </c>
     </row>
     <row r="63">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6627007853676392</v>
+        <v>0.6627009186674389</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.5432910157417756</v>
+        <v>0.5432911303654446</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.05985229265804659</v>
+        <v>-0.05985222865413431</v>
       </c>
     </row>
     <row r="68">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.4603285630814615</v>
+        <v>0.4603284425976246</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.04457298088387363</v>
+        <v>-0.0445728965279707</v>
       </c>
     </row>
     <row r="69"/>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.00756503362568739</v>
+        <v>0.007564924291074471</v>
       </c>
     </row>
     <row r="75">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.05511850786198069</v>
+        <v>0.05511838676683123</v>
       </c>
     </row>
     <row r="76">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.07878874535895375</v>
+        <v>0.07878865990202133</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.776821509533177</v>
+        <v>1.776822182420259</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.543340008013165</v>
+        <v>1.543339443933534</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1562878011945088</v>
+        <v>0.1562877098902584</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.43797244210432</v>
+        <v>1.437972728150566</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.160949563359122</v>
+        <v>0.1609496799456187</v>
       </c>
     </row>
     <row r="80">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1612023146778252</v>
+        <v>0.1612025099589032</v>
       </c>
     </row>
     <row r="81">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2108445842500206</v>
+        <v>0.2108445064736726</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -497,7 +497,7 @@
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -745,10 +745,10 @@
         <v>0.4023551288396623</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.404967747359576</v>
+        <v>1.404967567950645</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.339789034018759</v>
+        <v>0.3397890007029798</v>
       </c>
     </row>
     <row r="5">
@@ -857,10 +857,10 @@
         <v>0.347600870262041</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.307978816530349</v>
+        <v>1.3079790136397</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3215307495207544</v>
+        <v>0.321530787141848</v>
       </c>
     </row>
     <row r="7">
@@ -966,13 +966,13 @@
         <v>0.6064025518844511</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6498151241081944</v>
+        <v>0.649815282460904</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.776822182420259</v>
+        <v>1.776821509533177</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.405559894280261</v>
+        <v>0.4055597807472235</v>
       </c>
     </row>
     <row r="9">
@@ -1022,13 +1022,13 @@
         <v>0.2874447407166825</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.6627009186674389</v>
+        <v>0.6627007853676392</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.160512034402311</v>
+        <v>1.160511809333876</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2927629489749082</v>
+        <v>0.2927629040842927</v>
       </c>
     </row>
     <row r="10">
@@ -1072,7 +1072,7 @@
         <v>0.006428130252800868</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.4366207252019625</v>
+        <v>0.4366208245279526</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>0.4910280040396333</v>
@@ -1137,10 +1137,10 @@
         <v>0.4588498356323676</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3770276646882427</v>
+        <v>0.3770278212987883</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1125363811695734</v>
+        <v>0.1125364233461463</v>
       </c>
     </row>
     <row r="12">
@@ -1190,13 +1190,13 @@
         <v>0.2182821860065567</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4544275154752908</v>
+        <v>0.4544273596642328</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6977875575545294</v>
+        <v>0.6977876637120788</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.192965219537627</v>
+        <v>0.1929652444018022</v>
       </c>
     </row>
     <row r="13">
@@ -1249,10 +1249,10 @@
         <v>0.6781042488967195</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.543339443933534</v>
+        <v>1.543339725973317</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3650066763722404</v>
+        <v>0.3650067268290227</v>
       </c>
     </row>
     <row r="14">
@@ -1299,16 +1299,16 @@
         <v>0.2842581680808773</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2069468189450416</v>
+        <v>0.2069469012458243</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.4603284425976246</v>
+        <v>0.4603285630814615</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7156056672877107</v>
+        <v>0.715605833576378</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1971240544557529</v>
+        <v>0.1971240931336691</v>
       </c>
     </row>
     <row r="15">
@@ -1417,10 +1417,10 @@
         <v>0.4953428488556111</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.769102412716359</v>
+        <v>0.7691023001697326</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.209439991459887</v>
+        <v>0.2094399658125319</v>
       </c>
     </row>
     <row r="17">
@@ -1473,10 +1473,10 @@
         <v>0.4266401738625099</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.893075085599392</v>
+        <v>2.893075393916816</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.5731287204744309</v>
+        <v>0.5731287620031258</v>
       </c>
     </row>
     <row r="18">
@@ -1529,10 +1529,10 @@
         <v>0.3144806745635931</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.383349961289517</v>
+        <v>2.38335019250343</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.5012360125377417</v>
+        <v>0.5012360467352726</v>
       </c>
     </row>
     <row r="19">
@@ -1585,10 +1585,10 @@
         <v>0.328920221953243</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2830113304190749</v>
+        <v>0.283011540997318</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.08661783899642894</v>
+        <v>0.08661789844460843</v>
       </c>
     </row>
     <row r="20">
@@ -1694,7 +1694,7 @@
         <v>0.1400711471231719</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.04586268337540944</v>
+        <v>0.04586280637102136</v>
       </c>
       <c r="O21" s="6" t="n">
         <v>1.125777544800182</v>
@@ -1750,7 +1750,7 @@
         <v>0.2332309674875122</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.2538625452337953</v>
+        <v>0.2538624348868379</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>0.6363451140012772</v>
@@ -1915,10 +1915,10 @@
         <v>0.1619030074988452</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.09614160165450381</v>
+        <v>0.09614147431850939</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.134963821338461</v>
+        <v>0.1349638895962129</v>
       </c>
       <c r="O25" s="6" t="n">
         <v>0.8844739603673974</v>
@@ -1974,7 +1974,7 @@
         <v>0.1909572520207043</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.2225662864846996</v>
+        <v>0.2225661605358034</v>
       </c>
       <c r="O26" s="6" t="n">
         <v>0.9611386717215247</v>
@@ -2033,10 +2033,10 @@
         <v>0.1029362630474848</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.6021022920722394</v>
+        <v>0.6021024306219169</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1701191326988878</v>
+        <v>0.1701191664294897</v>
       </c>
     </row>
     <row r="28">
@@ -2080,19 +2080,19 @@
         <v>0.01660078466746495</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.161470818034414</v>
+        <v>0.1614708959227469</v>
       </c>
       <c r="M28" s="6" t="n">
         <v>0.08005164586105074</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1091167475607231</v>
+        <v>0.1091168185855733</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.9430251316489153</v>
+        <v>0.9430253496269125</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2478416367378831</v>
+        <v>0.2478416834008601</v>
       </c>
     </row>
     <row r="29">
@@ -2145,10 +2145,10 @@
         <v>0.1136679147809614</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4391814962132392</v>
+        <v>0.4391816712114043</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1290292381195379</v>
+        <v>0.1290292838812057</v>
       </c>
     </row>
     <row r="30">
@@ -2201,10 +2201,10 @@
         <v>0.2791036675147567</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.62310096671363</v>
+        <v>0.6231010734431885</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1752091896663612</v>
+        <v>0.175209215425604</v>
       </c>
     </row>
     <row r="31">
@@ -2310,7 +2310,7 @@
         <v>0.04871620681400324</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.07205025627099571</v>
+        <v>0.07205035000055959</v>
       </c>
       <c r="O32" s="6" t="n">
         <v>1.095929148085311</v>
@@ -2369,10 +2369,10 @@
         <v>0.3496241945936704</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3386379009012035</v>
+        <v>0.3386379974104869</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1021000929341263</v>
+        <v>0.1021001194194782</v>
       </c>
     </row>
     <row r="34">
@@ -2425,10 +2425,10 @@
         <v>0.07910171142493261</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2108445064736726</v>
+        <v>0.2108446620263784</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.06585008765038092</v>
+        <v>0.06585013329231582</v>
       </c>
     </row>
     <row r="35">
@@ -2528,10 +2528,10 @@
         <v>-0.107749684154879</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.1503199053090367</v>
+        <v>0.150320005284172</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.09304235749918588</v>
+        <v>0.09304226723226239</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>0.1943225591517019</v>
@@ -2640,19 +2640,19 @@
         <v>-0.04646000185289423</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.09719335160624509</v>
+        <v>0.09719323659850931</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.07254240177993876</v>
+        <v>0.07254229188197114</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1300843843181481</v>
+        <v>0.1300842623117895</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.4054824558900627</v>
+        <v>0.4054822671728282</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1201473169024339</v>
+        <v>0.1201472667675467</v>
       </c>
     </row>
     <row r="39">
@@ -2761,10 +2761,10 @@
         <v>0.2111071071050705</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.166850146393238</v>
+        <v>1.166849982072906</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2940258713570605</v>
+        <v>0.2940258386467896</v>
       </c>
     </row>
     <row r="41">
@@ -2817,10 +2817,10 @@
         <v>-0.01575301444282495</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.007564924291074471</v>
+        <v>0.00756503362568739</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.002515309344655048</v>
+        <v>0.002515345606873831</v>
       </c>
     </row>
     <row r="42">
@@ -2867,10 +2867,10 @@
         <v>0.06429676160009823</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.08514012518339009</v>
+        <v>0.08514004473715686</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.09715415353357915</v>
+        <v>0.09715407129617915</v>
       </c>
       <c r="O42" s="6" t="n">
         <v>0.3566783579941188</v>
@@ -2929,10 +2929,10 @@
         <v>0.1433497345487889</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.8010089302297889</v>
+        <v>0.8010090467847903</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.2166676350877745</v>
+        <v>0.2166676613339324</v>
       </c>
     </row>
     <row r="44">
@@ -2979,16 +2979,16 @@
         <v>0.03177434381488453</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>-0.002995882128693061</v>
+        <v>-0.002995816039368604</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>-0.02373280580350323</v>
+        <v>-0.02373274243480294</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.8080477625719806</v>
+        <v>0.8080476538976045</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.2182505972465496</v>
+        <v>0.2182505728385242</v>
       </c>
     </row>
     <row r="45">
@@ -3029,7 +3029,7 @@
         <v>-0.07670853345052242</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.04028878104615241</v>
+        <v>-0.04028866895456806</v>
       </c>
       <c r="L45" s="6" t="n">
         <v>0.1044719474675413</v>
@@ -3038,7 +3038,7 @@
         <v>0.02184259273249611</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.02025484817648571</v>
+        <v>0.02025491151664904</v>
       </c>
       <c r="O45" s="6" t="n">
         <v>0.6464054761407658</v>
@@ -3091,16 +3091,16 @@
         <v>0.029405504566971</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.08317708320741368</v>
+        <v>0.0831770038513977</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.1062867724442527</v>
+        <v>0.1062866896659782</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.5959463504448974</v>
+        <v>0.5959461781717883</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.16861851468102</v>
+        <v>0.1686184726324986</v>
       </c>
     </row>
     <row r="47">
@@ -3150,13 +3150,13 @@
         <v>0.01958357890959306</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.009861288965672177</v>
+        <v>0.009861373703294429</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.1117208701939212</v>
+        <v>0.1117209728877495</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.03593360032749637</v>
+        <v>0.03593363222518664</v>
       </c>
     </row>
     <row r="48">
@@ -3262,7 +3262,7 @@
         <v>0.08563110631623982</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1856714099912831</v>
+        <v>0.1856713346715502</v>
       </c>
       <c r="O49" s="6" t="n">
         <v>0.2235837663429983</v>
@@ -3312,10 +3312,10 @@
         <v>-0.04024771041962283</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.05705143195626494</v>
+        <v>0.05705132870090668</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.04808843653027994</v>
+        <v>-0.04808852026654176</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>-0.0445728965279707</v>
@@ -3368,19 +3368,19 @@
         <v>-0.09456234386499784</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.02703786302294231</v>
+        <v>-0.02703779619211566</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.01296340196693646</v>
+        <v>0.01296332952794388</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0.06530488168531901</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>1.064847364395072</v>
+        <v>1.06484766539119</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.2733935660912579</v>
+        <v>0.2733936279661302</v>
       </c>
     </row>
     <row r="52">
@@ -3542,13 +3542,13 @@
         <v>-0.1673271570441369</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.1347129377065388</v>
+        <v>-0.1347129926852952</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.07878865990202133</v>
+        <v>0.07878883081589971</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.02560183886994283</v>
+        <v>0.025601893032414</v>
       </c>
     </row>
     <row r="55">
@@ -3601,10 +3601,10 @@
         <v>0.07759136522263788</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1.201735008723461</v>
+        <v>1.201734553155478</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.300933256634248</v>
+        <v>0.3009331669074977</v>
       </c>
     </row>
     <row r="56">
@@ -3657,10 +3657,10 @@
         <v>-0.008800925101467794</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.4024656890953853</v>
+        <v>0.4024655968282214</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.1193453043131267</v>
+        <v>0.119345279766164</v>
       </c>
     </row>
     <row r="57">
@@ -3713,10 +3713,10 @@
         <v>-0.2401525283837648</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.05511838676683123</v>
+        <v>0.05511850786198069</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.01804520739500148</v>
+        <v>0.01804524634176286</v>
       </c>
     </row>
     <row r="58">
@@ -3816,19 +3816,19 @@
         <v>-0.1206512641077321</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.01733157191857893</v>
+        <v>0.01733165335572595</v>
       </c>
       <c r="M59" s="6" t="n">
         <v>-0.06627413968218143</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1307385234319272</v>
+        <v>-0.1307385828882858</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.3072868764711649</v>
+        <v>0.3072866075226317</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.09342827585278313</v>
+        <v>0.09342820086899906</v>
       </c>
     </row>
     <row r="60">
@@ -3881,10 +3881,10 @@
         <v>-0.1784446935524194</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.1609496799456187</v>
+        <v>0.160949563359122</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.0510042334710632</v>
+        <v>0.05100419828926106</v>
       </c>
     </row>
     <row r="61">
@@ -3937,10 +3937,10 @@
         <v>-0.2214801906201587</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1707238021396702</v>
+        <v>0.1707238741681394</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.05394548905111574</v>
+        <v>0.05394551066568676</v>
       </c>
     </row>
     <row r="62">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.02703786302294231</v>
+        <v>-0.02703779619211566</v>
       </c>
     </row>
     <row r="52">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.4366207252019625</v>
+        <v>0.4366208245279526</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6627009186674389</v>
+        <v>0.6627007853676392</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1347129377065388</v>
+        <v>-0.1347129926852952</v>
       </c>
     </row>
     <row r="64">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.6498151241081944</v>
+        <v>0.649815282460904</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1307385234319272</v>
+        <v>-0.1307385828882858</v>
       </c>
     </row>
     <row r="65">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.4603284425976246</v>
+        <v>0.4603285630814615</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.893075085599392</v>
+        <v>2.893075393916816</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.007564924291074471</v>
+        <v>0.00756503362568739</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.383349961289517</v>
+        <v>2.38335019250343</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.05511838676683123</v>
+        <v>0.05511850786198069</v>
       </c>
     </row>
     <row r="76">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.07878865990202133</v>
+        <v>0.07878883081589971</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.776822182420259</v>
+        <v>1.776821509533177</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1117208701939212</v>
+        <v>0.1117209728877495</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.543339443933534</v>
+        <v>1.543339725973317</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1609496799456187</v>
+        <v>0.160949563359122</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.404967747359576</v>
+        <v>1.404967567950645</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.307978816530349</v>
+        <v>1.3079790136397</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1707238021396702</v>
+        <v>0.1707238741681394</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.201735008723461</v>
+        <v>1.201734553155478</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2108445064736726</v>
+        <v>0.2108446620263784</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -496,7 +496,7 @@
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
@@ -686,7 +686,7 @@
         <v>0.5420000172283856</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7890745606538887</v>
+        <v>0.7890747109127749</v>
       </c>
       <c r="O3" s="6" t="n">
         <v>1.02703972934007</v>
@@ -745,10 +745,10 @@
         <v>0.4023551288396623</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.404967567950645</v>
+        <v>1.404967747359576</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3397890007029798</v>
+        <v>0.339789034018759</v>
       </c>
     </row>
     <row r="5">
@@ -801,10 +801,10 @@
         <v>0.8937779589929113</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>3.292088735974303</v>
+        <v>3.292089207591205</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.6251354504496789</v>
+        <v>0.6251355099732476</v>
       </c>
     </row>
     <row r="6">
@@ -966,13 +966,13 @@
         <v>0.6064025518844511</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.649815282460904</v>
+        <v>0.6498151241081944</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.776821509533177</v>
+        <v>1.776821733828835</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.4055597807472235</v>
+        <v>0.4055598185915652</v>
       </c>
     </row>
     <row r="9">
@@ -1019,10 +1019,10 @@
         <v>0.3164768363608872</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2874447407166825</v>
+        <v>0.2874448206372353</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.6627007853676392</v>
+        <v>0.6627009186674389</v>
       </c>
       <c r="O9" s="6" t="n">
         <v>1.160511809333876</v>
@@ -1078,13 +1078,13 @@
         <v>0.4910280040396333</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5432911303654446</v>
+        <v>0.5432910157417756</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.437972728150566</v>
+        <v>1.437973014196879</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3458901489755837</v>
+        <v>0.3458902016131564</v>
       </c>
     </row>
     <row r="11">
@@ -1128,19 +1128,19 @@
         <v>0.2154133078976523</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.05659945308534842</v>
+        <v>0.05659954529076261</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>0.5013629448387711</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4588498356323676</v>
+        <v>0.4588500114072662</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3770278212987883</v>
+        <v>0.3770279779093695</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1125364233461463</v>
+        <v>0.1125364655227257</v>
       </c>
     </row>
     <row r="12">
@@ -1190,13 +1190,13 @@
         <v>0.2182821860065567</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4544273596642328</v>
+        <v>0.4544275154752908</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6977876637120788</v>
+        <v>0.6977874513969935</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1929652444018022</v>
+        <v>0.1929651946734541</v>
       </c>
     </row>
     <row r="13">
@@ -1249,10 +1249,10 @@
         <v>0.6781042488967195</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.543339725973317</v>
+        <v>1.543340008013165</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3650067268290227</v>
+        <v>0.3650067772858125</v>
       </c>
     </row>
     <row r="14">
@@ -1299,10 +1299,10 @@
         <v>0.2842581680808773</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2069469012458243</v>
+        <v>0.2069468189450416</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.4603285630814615</v>
+        <v>0.4603284425976246</v>
       </c>
       <c r="O14" s="6" t="n">
         <v>0.715605833576378</v>
@@ -1473,10 +1473,10 @@
         <v>0.4266401738625099</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.893075393916816</v>
+        <v>2.893075085599392</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.5731287620031258</v>
+        <v>0.5731287204744309</v>
       </c>
     </row>
     <row r="18">
@@ -1585,10 +1585,10 @@
         <v>0.328920221953243</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.283011540997318</v>
+        <v>0.2830112251299792</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.08661789844460843</v>
+        <v>0.08661780927234419</v>
       </c>
     </row>
     <row r="20">
@@ -1632,7 +1632,7 @@
         <v>0.07072596969839662</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.3223125002878349</v>
+        <v>0.3223126196941752</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>0.176592001574857</v>
@@ -1688,7 +1688,7 @@
         <v>0.1231003114364657</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.3337781142588556</v>
+        <v>0.3337780142410374</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>0.1400711471231719</v>
@@ -1697,10 +1697,10 @@
         <v>0.04586280637102136</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1.125777544800182</v>
+        <v>1.12577716370185</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.2857975830021813</v>
+        <v>0.2857975061651443</v>
       </c>
     </row>
     <row r="22">
@@ -1747,10 +1747,10 @@
         <v>0.06802915378812147</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2332309674875122</v>
+        <v>0.2332310742329746</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.2538624348868379</v>
+        <v>0.2538625452337953</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>0.6363451140012772</v>
@@ -1918,13 +1918,13 @@
         <v>0.09614147431850939</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1349638895962129</v>
+        <v>0.1349637530807175</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8844739603673974</v>
+        <v>0.8844743367229098</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2351794196686652</v>
+        <v>0.2351795018961307</v>
       </c>
     </row>
     <row r="26">
@@ -1968,7 +1968,7 @@
         <v>-0.06610571276330279</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1307727753743704</v>
+        <v>0.1307726676286012</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>0.1909572520207043</v>
@@ -1977,10 +1977,10 @@
         <v>0.2225661605358034</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.9611386717215247</v>
+        <v>0.9611380235409097</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2517072504756681</v>
+        <v>0.2517071125740711</v>
       </c>
     </row>
     <row r="27">
@@ -2033,10 +2033,10 @@
         <v>0.1029362630474848</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.6021024306219169</v>
+        <v>0.6021022920722394</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1701191664294897</v>
+        <v>0.1701191326988878</v>
       </c>
     </row>
     <row r="28">
@@ -2089,10 +2089,10 @@
         <v>0.1091168185855733</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.9430253496269125</v>
+        <v>0.9430251316489153</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2478416834008601</v>
+        <v>0.2478416367378831</v>
       </c>
     </row>
     <row r="29">
@@ -2139,16 +2139,16 @@
         <v>0.1036211893964436</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1148028821094127</v>
+        <v>0.1148029871116409</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1136679147809614</v>
+        <v>0.1136678099924471</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4391816712114043</v>
+        <v>0.4391818462096118</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1290292838812057</v>
+        <v>0.1290293296428811</v>
       </c>
     </row>
     <row r="30">
@@ -2201,10 +2201,10 @@
         <v>0.2791036675147567</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6231010734431885</v>
+        <v>0.62310096671363</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.175209215425604</v>
+        <v>0.1752091896663612</v>
       </c>
     </row>
     <row r="31">
@@ -2310,13 +2310,13 @@
         <v>0.04871620681400324</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.07205035000055959</v>
+        <v>0.07205025627099571</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>1.095929148085311</v>
+        <v>1.095928968954857</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.2797511617688258</v>
+        <v>0.2797511253104665</v>
       </c>
     </row>
     <row r="33">
@@ -2369,10 +2369,10 @@
         <v>0.3496241945936704</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3386379974104869</v>
+        <v>0.3386378043919342</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1021001194194782</v>
+        <v>0.102100066448777</v>
       </c>
     </row>
     <row r="34">
@@ -2422,13 +2422,13 @@
         <v>0.08997012043645114</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.07910171142493261</v>
+        <v>0.07910158787984667</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2108446620263784</v>
+        <v>0.2108445842500206</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.06585013329231582</v>
+        <v>0.06585011047134737</v>
       </c>
     </row>
     <row r="35">
@@ -2531,7 +2531,7 @@
         <v>0.150320005284172</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.09304226723226239</v>
+        <v>0.09304235749918588</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>0.1943225591517019</v>
@@ -2587,16 +2587,16 @@
         <v>0.0777295626171659</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.08952723777334182</v>
+        <v>0.08952714123116334</v>
       </c>
       <c r="N37" s="6" t="n">
         <v>0.06320897415022975</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.3539020966885738</v>
+        <v>0.3539022457672469</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.106273273210223</v>
+        <v>0.1062733138142782</v>
       </c>
     </row>
     <row r="38">
@@ -2640,7 +2640,7 @@
         <v>-0.04646000185289423</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.09719323659850931</v>
+        <v>0.09719335160624509</v>
       </c>
       <c r="M38" s="6" t="n">
         <v>0.07254229188197114</v>
@@ -2705,10 +2705,10 @@
         <v>-0.05985222865413431</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.1612025099589032</v>
+        <v>0.161202412318356</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.05108052334864155</v>
+        <v>0.05108049388835378</v>
       </c>
     </row>
     <row r="40">
@@ -2755,16 +2755,16 @@
         <v>0.07358215124947365</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.03974181932374221</v>
+        <v>0.03974189499215619</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.2111071071050705</v>
+        <v>0.2111072097715614</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.166849982072906</v>
+        <v>1.166850146393238</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2940258386467896</v>
+        <v>0.2940258713570605</v>
       </c>
     </row>
     <row r="41">
@@ -2867,16 +2867,16 @@
         <v>0.06429676160009823</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.08514004473715686</v>
+        <v>0.08514012518339009</v>
       </c>
       <c r="N42" s="6" t="n">
         <v>0.09715407129617915</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.3566783579941188</v>
+        <v>0.3566787352267653</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1070289178951078</v>
+        <v>0.1070290205004669</v>
       </c>
     </row>
     <row r="43">
@@ -2979,16 +2979,16 @@
         <v>0.03177434381488453</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>-0.002995816039368604</v>
+        <v>-0.002995948218008748</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>-0.02373274243480294</v>
+        <v>-0.02373286917219519</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.8080476538976045</v>
+        <v>0.8080478712463697</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.2182505728385242</v>
+        <v>0.2182506216545768</v>
       </c>
     </row>
     <row r="45">
@@ -3038,13 +3038,13 @@
         <v>0.02184259273249611</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.02025491151664904</v>
+        <v>0.02025497485682015</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.6464054761407658</v>
+        <v>0.6464056410843644</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1808070405921998</v>
+        <v>0.1808070800248829</v>
       </c>
     </row>
     <row r="46">
@@ -3097,10 +3097,10 @@
         <v>0.1062866896659782</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.5959461781717883</v>
+        <v>0.5959465227180436</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.1686184726324986</v>
+        <v>0.1686185567295473</v>
       </c>
     </row>
     <row r="47">
@@ -3147,16 +3147,16 @@
         <v>-0.01754929179649645</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.01958357890959306</v>
+        <v>0.01958340615548915</v>
       </c>
       <c r="N47" s="6" t="n">
         <v>0.009861373703294429</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.1117209728877495</v>
+        <v>0.111721178275463</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.03593363222518664</v>
+        <v>0.03593369602057894</v>
       </c>
     </row>
     <row r="48">
@@ -3209,10 +3209,10 @@
         <v>0.02836165088549181</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.4773687977440779</v>
+        <v>0.4773689139644826</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.1389280982576238</v>
+        <v>0.1389281281230352</v>
       </c>
     </row>
     <row r="49">
@@ -3262,13 +3262,13 @@
         <v>0.08563110631623982</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1856713346715502</v>
+        <v>0.1856714099912831</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.2235837663429983</v>
+        <v>0.2235836861294944</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.06957498080214908</v>
+        <v>0.06957495742972442</v>
       </c>
     </row>
     <row r="50">
@@ -3312,19 +3312,19 @@
         <v>-0.04024771041962283</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.05705132870090668</v>
+        <v>0.05705143195626494</v>
       </c>
       <c r="M50" s="6" t="n">
         <v>-0.04808852026654176</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.0445728965279707</v>
+        <v>-0.04457298088387363</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.4288807494461113</v>
+        <v>0.4288809381202736</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1263291613726618</v>
+        <v>0.1263292109474079</v>
       </c>
     </row>
     <row r="51">
@@ -3368,19 +3368,19 @@
         <v>-0.09456234386499784</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.02703779619211566</v>
+        <v>-0.02703786302294231</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.01296332952794388</v>
+        <v>0.01296340196693646</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0.06530488168531901</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>1.06484766539119</v>
+        <v>1.06484751489312</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.2733936279661302</v>
+        <v>0.2733935970286925</v>
       </c>
     </row>
     <row r="52">
@@ -3433,10 +3433,10 @@
         <v>-0.04156824830654005</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.2674194463016493</v>
+        <v>0.2674195866210383</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.08219815397414676</v>
+        <v>0.08219819391182703</v>
       </c>
     </row>
     <row r="53">
@@ -3542,13 +3542,13 @@
         <v>-0.1673271570441369</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.1347129926852952</v>
+        <v>-0.1347129377065388</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.07878883081589971</v>
+        <v>0.07878891627285922</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.025601893032414</v>
+        <v>0.0256019201136537</v>
       </c>
     </row>
     <row r="55">
@@ -3595,16 +3595,16 @@
         <v>-0.05809762699958054</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.0110949175881867</v>
+        <v>0.01109498163769684</v>
       </c>
       <c r="N55" s="6" t="n">
         <v>0.07759136522263788</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1.201734553155478</v>
+        <v>1.201734705011451</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.3009331669074977</v>
+        <v>0.3009331968164117</v>
       </c>
     </row>
     <row r="56">
@@ -3654,7 +3654,7 @@
         <v>-0.0190083003644812</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.008800925101467794</v>
+        <v>-0.00880101727674254</v>
       </c>
       <c r="O56" s="6" t="n">
         <v>0.4024655968282214</v>
@@ -3816,19 +3816,19 @@
         <v>-0.1206512641077321</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.01733165335572595</v>
+        <v>0.01733173479288608</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.06627413968218143</v>
+        <v>-0.06627420828409236</v>
       </c>
       <c r="N59" s="6" t="n">
         <v>-0.1307385828882858</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.3072866075226317</v>
+        <v>0.3072864730484064</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.09342820086899906</v>
+        <v>0.09342816337711457</v>
       </c>
     </row>
     <row r="60">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.02703779619211566</v>
+        <v>-0.02703786302294231</v>
       </c>
     </row>
     <row r="52">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.3337781142588556</v>
+        <v>0.3337780142410374</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.3223125002878349</v>
+        <v>0.3223126196941752</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7890745606538887</v>
+        <v>0.7890747109127749</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6627007853676392</v>
+        <v>0.6627009186674389</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1347129926852952</v>
+        <v>-0.1347129377065388</v>
       </c>
     </row>
     <row r="64">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.649815282460904</v>
+        <v>0.6498151241081944</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.5432911303654446</v>
+        <v>0.5432910157417756</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.4603285630814615</v>
+        <v>0.4603284425976246</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.0445728965279707</v>
+        <v>-0.04457298088387363</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.292088735974303</v>
+        <v>3.292089207591205</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.893075393916816</v>
+        <v>2.893075085599392</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.07878883081589971</v>
+        <v>0.07878891627285922</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.776821509533177</v>
+        <v>1.776821733828835</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1117209728877495</v>
+        <v>0.111721178275463</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.543339725973317</v>
+        <v>1.543340008013165</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.437972728150566</v>
+        <v>1.437973014196879</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.404967567950645</v>
+        <v>1.404967747359576</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1612025099589032</v>
+        <v>0.161202412318356</v>
       </c>
     </row>
     <row r="81">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.201734553155478</v>
+        <v>1.201734705011451</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2108446620263784</v>
+        <v>0.2108445842500206</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -489,16 +489,16 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>16.08</v>
+        <v>15.96</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.02290074112990381</v>
+        <v>-0.007462679485599422</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.05098037406846112</v>
+        <v>0.04313724439113287</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.02898548053842054</v>
+        <v>-0.008695673292274386</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.09016948635295297</v>
+        <v>0.08203390089132023</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3898012400898647</v>
+        <v>0.3559897550912594</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.6063935620411336</v>
+        <v>0.5975976380188242</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.8482758938203108</v>
+        <v>0.8260870087076797</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9705882627933775</v>
+        <v>0.9345454591693301</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1.994413457428208</v>
+        <v>1.88607584676748</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4413537708498165</v>
+        <v>0.4237571347137767</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>40.63</v>
+        <v>40.78</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.02008534271361251</v>
+        <v>0.003691796880097797</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.04878676581728114</v>
+        <v>0.05374671770935224</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.02162435505287208</v>
+        <v>0.05647669407648648</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.01372253522789002</v>
+        <v>0.01746499292072934</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3295157649919258</v>
+        <v>0.3083092293705743</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.4427623515123225</v>
+        <v>0.4323871654463725</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5420000172283856</v>
+        <v>0.5286281967869475</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.7890747109127749</v>
+        <v>0.790216769780524</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.02703972934007</v>
+        <v>1.042796713366203</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2655736391989212</v>
+        <v>0.2688444473534013</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>122.98</v>
+        <v>124.07</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.03631924879490023</v>
+        <v>0.008863199773438302</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.03728075142845233</v>
+        <v>0.03859032852571631</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1104289242161047</v>
+        <v>0.1181506914070094</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.1017738786133422</v>
+        <v>0.1115391206046483</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2810417016347249</v>
+        <v>0.2929345652203124</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.6077919570080763</v>
+        <v>0.5888078564888253</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5067420559517639</v>
+        <v>0.5171249218795699</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4023551288396623</v>
+        <v>0.4271436044722265</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.404967747359576</v>
+        <v>1.425810417597889</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.339789034018759</v>
+        <v>0.3436483369311099</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>596.03</v>
+        <v>601.41</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.04019202320571558</v>
+        <v>-0.009959583526958915</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.1007018084891504</v>
+        <v>0.1023718304785335</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.05118078875405652</v>
+        <v>0.04722352148707754</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.06354171420120047</v>
+        <v>0.07314155719701798</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.09675997925907232</v>
+        <v>-0.03318063669073956</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.5491761824233214</v>
+        <v>0.5367181000997809</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.6783668547606476</v>
+        <v>0.6560468308181149</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8937779589929113</v>
+        <v>0.8752915541851864</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>3.292089207591205</v>
+        <v>3.294221356225966</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.6251355099732476</v>
+        <v>0.625404567510186</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>103.09</v>
+        <v>104.01</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.03224184943179842</v>
+        <v>0.008924297516942348</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.03038473956427734</v>
+        <v>0.03698902264796722</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.08986151103798168</v>
+        <v>0.1008678920479473</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.08687399047262745</v>
+        <v>0.09657357732703176</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2204713698636818</v>
+        <v>0.2361885875069936</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.6142131676489138</v>
+        <v>0.6043147087454506</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.4135402308662464</v>
+        <v>0.4322273233458702</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.347600870262041</v>
+        <v>0.3731968530332355</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.3079790136397</v>
+        <v>1.320932315896604</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.321530787141848</v>
+        <v>0.3239984962501143</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>28.93</v>
+        <v>29.14</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.03989937536045596</v>
+        <v>0.00725886907215445</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.020458550825458</v>
+        <v>0.03997141019226635</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.04102192702741059</v>
+        <v>0.06505843346448681</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.03137258795189379</v>
+        <v>0.03885918653244547</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.330114956559806</v>
+        <v>0.3553488088208576</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.4715157950005733</v>
+        <v>0.4511951942413268</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2616659363343172</v>
+        <v>0.2741582125199962</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2186183902314824</v>
+        <v>0.2352691479932736</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.542110871653231</v>
+        <v>0.5491759817648947</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1553277360966723</v>
+        <v>0.1570894088037602</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>524.5599999999999</v>
+        <v>527.4400000000001</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.03570551004247591</v>
+        <v>0.005490325027101894</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.1056225436909441</v>
+        <v>0.09969079385731172</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.06775978063342825</v>
+        <v>0.06452459511562303</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.05322954457553863</v>
+        <v>0.05901211710340504</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-0.1750073937822347</v>
+        <v>-0.1259312342653346</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.6280829447221463</v>
+        <v>0.6026746800613949</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.6064025518844511</v>
+        <v>0.5995381806167279</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6498151241081944</v>
+        <v>0.6391199039241318</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.776821733828835</v>
+        <v>1.758582305950276</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.4055598185915652</v>
+        <v>0.4024756038431672</v>
       </c>
     </row>
     <row r="9">
@@ -984,51 +984,51 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>158.23</v>
+        <v>156.47</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.009634982740393649</v>
+        <v>-0.0129943706204253</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.003997395936708559</v>
+        <v>0.02428650724847436</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.0340638661511411</v>
+        <v>0.01498441556641916</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.04525433049747996</v>
+        <v>0.03588214537862755</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1255352385310526</v>
+        <v>0.01649481592915469</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.3164768363608872</v>
+        <v>0.3928540697111753</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2874448206372353</v>
+        <v>0.4604544386056975</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.6627009186674389</v>
+        <v>0.5203226261754073</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.160511809333876</v>
+        <v>1.392571524566373</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2927629040842927</v>
+        <v>0.3374831207939089</v>
       </c>
     </row>
     <row r="10">
@@ -1040,51 +1040,51 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>158.53</v>
+        <v>182.65</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.02462511329197126</v>
+        <v>-0.01136674480928623</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.04035958589983002</v>
+        <v>-0.04390894964290804</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.02495636294076431</v>
+        <v>-0.05964679142072393</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.04951999719573674</v>
+        <v>-0.03250883158032647</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.006428130252800868</v>
+        <v>0.1827804735568381</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.4366208245279526</v>
+        <v>0.05379461668238972</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.4910280040396333</v>
+        <v>0.4628215188247617</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5432910157417756</v>
+        <v>0.3987418258762359</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1.437973014196879</v>
+        <v>0.3653619429917774</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3458902016131564</v>
+        <v>0.1093857876683137</v>
       </c>
     </row>
     <row r="11">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>184.75</v>
+        <v>206.6</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.02687867408721567</v>
+        <v>-0.002703212727815596</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.04126402191165579</v>
+        <v>0.02075104907947423</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.02738896983420158</v>
+        <v>0.005455779919441683</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.02138516650136546</v>
+        <v>-0.0325383512362456</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.2154133078976523</v>
+        <v>0.1601499792771268</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.05659954529076261</v>
+        <v>0.2701466606879188</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.5013629448387711</v>
+        <v>0.2015752477098856</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4588500114072662</v>
+        <v>0.4528371916349725</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3770279779093695</v>
+        <v>0.6999677200769445</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1125364655227257</v>
+        <v>0.1934756378509743</v>
       </c>
     </row>
     <row r="12">
@@ -1152,51 +1152,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>207.16</v>
+        <v>87.03</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.01271023726313292</v>
+        <v>-0.005257733406153653</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.01256665357741249</v>
+        <v>0.03373317799660569</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.02240869976342996</v>
+        <v>-0.08649100613114402</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.02991600784159276</v>
+        <v>-0.07992385930102197</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.1931072683602397</v>
+        <v>0.09871347649528461</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.2817833737024793</v>
+        <v>0.1872976427129207</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2182821860065567</v>
+        <v>0.2087275688039418</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.4544275154752908</v>
+        <v>0.6513919038743419</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.6977874513969935</v>
+        <v>1.533437997519019</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1929651946734541</v>
+        <v>0.3632330086073217</v>
       </c>
     </row>
     <row r="13">
@@ -1208,51 +1208,51 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>87.48999999999999</v>
+        <v>155.2</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.002406039039982932</v>
+        <v>-0.01914933237130534</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.02184063369773903</v>
+        <v>0.006615672077542989</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.03496586885386066</v>
+        <v>-0.02622667716470306</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.07506077544139833</v>
+        <v>-0.06353707265284825</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.02699234915713555</v>
+        <v>0.05556687911838387</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2708064206731784</v>
+        <v>0.2765188911846954</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2780327716113404</v>
+        <v>0.2439134085370809</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6781042488967195</v>
+        <v>0.6106883701522177</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.543340008013165</v>
+        <v>1.140632846229579</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3650067772858125</v>
+        <v>0.2887857585000639</v>
       </c>
     </row>
     <row r="14">
@@ -1264,51 +1264,51 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>67.52</v>
+        <v>395.66</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.009297647076936588</v>
+        <v>-0.002445607263095839</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.004972226297909721</v>
+        <v>-0.0104789355444489</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.04747799615632331</v>
+        <v>-0.07846745536853128</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.071945264577438</v>
+        <v>-0.04735989104108129</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.1079251621861952</v>
+        <v>0.02897122377698125</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.2842581680808773</v>
+        <v>-0.007998000232143254</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.2069468189450416</v>
+        <v>0.3944456801287903</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.4603284425976246</v>
+        <v>0.5376555195128265</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.715605833576378</v>
+        <v>0.206849119972</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1971240931336691</v>
+        <v>0.06467647824048472</v>
       </c>
     </row>
     <row r="15">
@@ -1320,51 +1320,51 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>SLX</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Steel Industry</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>396.63</v>
+        <v>104.8</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.005216790692088691</v>
+        <v>-0.01206635329188088</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01350542881349426</v>
+        <v>-0.01308973874838559</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.07227561571050323</v>
+        <v>-0.05670563014301711</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.04502439576729045</v>
+        <v>-0.02238800340305169</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.02889832403083781</v>
+        <v>0.02967188355945671</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.02496318482475846</v>
+        <v>0.1843146748980327</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.4139048784436048</v>
+        <v>0.2310584568655099</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.585393291047305</v>
+        <v>0.4814111099152178</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.2180286015414326</v>
+        <v>0.7397152187304958</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.06795387399782182</v>
+        <v>0.2027057506964969</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>SLX</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Steel Industry</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>106.08</v>
+        <v>66.23</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-9.420781582558657e-05</v>
+        <v>-0.01910535175160266</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.0002827139678099888</v>
+        <v>-0.007761972575232257</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.04423818476635555</v>
+        <v>-0.04397607060012154</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.01044771594283023</v>
+        <v>-0.0896760767424265</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.006929315306187789</v>
+        <v>0.04843510091894032</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.2376619176778441</v>
+        <v>0.2587419857759485</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2723391120989509</v>
+        <v>0.174611692684395</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4953428488556111</v>
+        <v>0.4243648306596579</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.7691023001697326</v>
+        <v>0.6898908176891054</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2094399658125319</v>
+        <v>0.191112773510711</v>
       </c>
     </row>
     <row r="17">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>93.76000000000001</v>
+        <v>92.22</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.01512599640937606</v>
+        <v>-0.01642492406612539</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.005253624003432211</v>
+        <v>0.01418674707135037</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.05569542479913581</v>
+        <v>-0.07881329878678067</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.05816173518866719</v>
+        <v>-0.07363135717076463</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1213341540487451</v>
+        <v>0.1759478730620023</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1856207304045412</v>
+        <v>0.1162477918537053</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1200294085721778</v>
+        <v>0.05553959930492658</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.4266401738625099</v>
+        <v>0.3610580604799341</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.893075085599392</v>
+        <v>2.836771838207835</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.5731287204744309</v>
+        <v>0.5655081200370875</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>94.43000000000001</v>
+        <v>93.56</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.01099709902431167</v>
+        <v>-0.04364718585853578</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.003080528122026305</v>
+        <v>0.008189595709517938</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.04866010202604765</v>
+        <v>-0.05941493505158724</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.08168823666540193</v>
+        <v>-0.09014882920736655</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.1444673113601969</v>
+        <v>0.2047385159246657</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1786070527712784</v>
+        <v>0.1220916363697586</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.08344705017392129</v>
+        <v>0.03644622840229217</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.3144806745635931</v>
+        <v>0.2695607414267793</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.38335019250343</v>
+        <v>2.356823155684697</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.5012360467352726</v>
+        <v>0.4973022853077387</v>
       </c>
     </row>
     <row r="19">
@@ -1544,51 +1544,51 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>29.82</v>
+        <v>67.06</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.02036796413783615</v>
+        <v>-0.01164334463218386</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.05930602595799139</v>
+        <v>0.03461869946049601</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-0.05122496324272807</v>
+        <v>0.046232749937688</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.05333334302145343</v>
+        <v>0.06078674671888162</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1157280778783973</v>
+        <v>0.1360312599337601</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>-0.03092807531879216</v>
+        <v>0.2973521563820922</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.3087944304610863</v>
+        <v>0.1243429267877112</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.328920221953243</v>
+        <v>0.03663936713455862</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.2830112251299792</v>
+        <v>1.086046664787813</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.08661780927234419</v>
+        <v>0.2777366138472792</v>
       </c>
     </row>
     <row r="20">
@@ -1600,51 +1600,51 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>55.86</v>
+        <v>29.68</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.005341866771290116</v>
+        <v>-0.00469481526093829</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.02831892536589253</v>
+        <v>-0.03322476978551092</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.02493443624492897</v>
+        <v>-0.06871667638494783</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.01706002530891726</v>
+        <v>-0.05777776808965773</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.07072596969839662</v>
+        <v>0.08981271744700536</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.3223126196941752</v>
+        <v>-0.02954690226323731</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.176592001574857</v>
+        <v>0.2809483230391223</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1775383410157296</v>
+        <v>0.2906808666820113</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.1562877098902584</v>
+        <v>0.2774475198253967</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.04959552369252274</v>
+        <v>0.08504484792015354</v>
       </c>
     </row>
     <row r="21">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>67.84999999999999</v>
+        <v>108.1</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.04326827029096125</v>
+        <v>0.01264635572947159</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.03515632274885938</v>
+        <v>0.02991615298244565</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.05740387278054193</v>
+        <v>0.06157317617914715</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.07328335470570657</v>
+        <v>0.04575791430648346</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.1231003114364657</v>
+        <v>0.2379752502510439</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.3337780142410374</v>
+        <v>0.280438962211421</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1400711471231719</v>
+        <v>0.0004651081999698103</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.04586280637102136</v>
+        <v>-0.07113174376607823</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1.12577716370185</v>
+        <v>0.5873428944393135</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.2857975061651443</v>
+        <v>0.1665147933811046</v>
       </c>
     </row>
     <row r="22">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>AMLP</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Midstream Energy &amp; MLPs</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>54.35</v>
+        <v>54.96</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01145873178175016</v>
+        <v>-0.01611173498111496</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.02036771949240879</v>
+        <v>-0.03017468042569516</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.02458727057732002</v>
+        <v>-0.02914714760002657</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.007305963942993765</v>
+        <v>-0.03289689368348392</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.09296570169037133</v>
+        <v>0.03428827611011065</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.06802915378812147</v>
+        <v>0.305938073007598</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.2332310742329746</v>
+        <v>0.1586049134723431</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.2538625452337953</v>
+        <v>0.1376911479918899</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6363451140012772</v>
+        <v>0.1387972349093953</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1783970175964931</v>
+        <v>0.04427641121239678</v>
       </c>
     </row>
     <row r="23">
@@ -1768,51 +1768,51 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>AMLP</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>Midstream Energy &amp; MLPs</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>296.85</v>
+        <v>53.58</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.03022833002110192</v>
+        <v>-0.01416737193531004</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.01414374216560654</v>
+        <v>-0.02101220027042316</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.020559050733022</v>
+        <v>-0.04644949029085188</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.03540283733631266</v>
+        <v>-0.0213698295697774</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.1173216436578732</v>
+        <v>0.05703714668945059</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.2485279818383439</v>
+        <v>0.04794179439140489</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.09793990259477869</v>
+        <v>0.2031354195870956</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.03309671429953642</v>
+        <v>0.2419215762281213</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.871217897413114</v>
+        <v>0.6212278400536313</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2322763708854085</v>
+        <v>0.1747569353999294</v>
       </c>
     </row>
     <row r="24">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>FDN</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Internet &amp; Digital Services</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>107.13</v>
+        <v>290.32</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.02664110033491096</v>
+        <v>-0.02199763734220639</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.004594878718811257</v>
+        <v>0.00575072279169131</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.02448118548402811</v>
+        <v>0.008300679711157111</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.03637413569634695</v>
+        <v>0.01262642121749691</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.2024918807618674</v>
+        <v>0.1233120279044833</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.2911204375729728</v>
+        <v>0.1982830146399479</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>-0.005659953414861474</v>
+        <v>0.06821697191917919</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>-0.08567217120499637</v>
+        <v>0.0247794558197445</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.5757828867654371</v>
+        <v>0.8290179243912705</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1636761317280027</v>
+        <v>0.2229423570268925</v>
       </c>
     </row>
     <row r="25">
@@ -1880,51 +1880,51 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>GRID</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Smart Grid &amp; Electric Infrastructure</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>71.98999999999999</v>
+        <v>179.59</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.004810743801129891</v>
+        <v>-0.008228437586135118</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.02307362195981155</v>
+        <v>0.03070472151090731</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.03812917071571553</v>
+        <v>-0.002997882253282458</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.03286112760726667</v>
+        <v>-0.007406159244652377</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.01538518654026189</v>
+        <v>-0.04453949214738873</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.1619030074988452</v>
+        <v>0.09379698975607065</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.09614147431850939</v>
+        <v>0.166721502081284</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.1349637530807175</v>
+        <v>0.2087027427267472</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.8844743367229098</v>
+        <v>0.9536482020321768</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2351795018961307</v>
+        <v>0.2501116064684314</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>GRID</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Smart Grid &amp; Electric Infrastructure</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>181.08</v>
+        <v>109.58</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.01587658811250869</v>
+        <v>0.005321117716098112</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.04676568634602596</v>
+        <v>0.008124095212191929</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.01167660916112134</v>
+        <v>-0.08000965156307216</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.0008291005435581145</v>
+        <v>-0.0811659056560019</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.06610571276330279</v>
+        <v>-0.01123844417928233</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.1307726676286012</v>
+        <v>0.05905484232747904</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1909572520207043</v>
+        <v>0.01654161669020304</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.2225661605358034</v>
+        <v>0.2014373546758319</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.9611380235409097</v>
+        <v>1.157674347614203</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2517071125740711</v>
+        <v>0.2921967153622347</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>141.34</v>
+        <v>23.2</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.009530488012868266</v>
+        <v>-0.01444350634513447</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.02626220449711236</v>
+        <v>0.007381679167405508</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.0255931160354087</v>
+        <v>-0.02684561181007228</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.01510549154889507</v>
+        <v>-0.0276613508184812</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.05539597838176813</v>
+        <v>-0.05584967716740974</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.1195346010144978</v>
+        <v>-0.01719100192126177</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.05814736267320253</v>
+        <v>0.1340840138065038</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.1029362630474848</v>
+        <v>0.2478885839595784</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.6021022920722394</v>
+        <v>0.6029681740467425</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1701191326988878</v>
+        <v>0.1703298979735937</v>
       </c>
     </row>
     <row r="28">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>66.06999999999999</v>
+        <v>70.38</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.002641754766427917</v>
+        <v>-0.01137807501348187</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.02488984033618835</v>
+        <v>-0.02693365729332442</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.04176501290806522</v>
+        <v>-0.03633973510341948</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.03340107396073277</v>
+        <v>-0.05449044030419981</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.01660078466746495</v>
+        <v>-0.03199069352484951</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1614708959227469</v>
+        <v>0.1157309117196685</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.08005164586105074</v>
+        <v>0.07407027924311071</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1091168185855733</v>
+        <v>0.1248236603905344</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.9430251316489153</v>
+        <v>0.8544144893184455</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2478416367378831</v>
+        <v>0.2285766886870946</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>90.3</v>
+        <v>72.16</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.006464576718271831</v>
+        <v>0.003476567755088755</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.01735677835080218</v>
+        <v>-0.01393818855989082</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.02599772098087516</v>
+        <v>-0.01027598696867438</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.05478490007193848</v>
+        <v>-0.03629377210282569</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.01948273047814242</v>
+        <v>0.002297042965173413</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.1036211893964436</v>
+        <v>0.05139535470557255</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1148029871116409</v>
+        <v>0.09473921549767739</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1136678099924471</v>
+        <v>0.08459693634514065</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.4391818462096118</v>
+        <v>0.2230557332701428</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1290293296428811</v>
+        <v>0.06942110161534476</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>23.54</v>
+        <v>89.09</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.006843531244827394</v>
+        <v>-0.01339985241388797</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.02749895557884074</v>
+        <v>-0.02034314992137376</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.005492148726133683</v>
+        <v>-0.0287376996315889</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.01341155434360664</v>
+        <v>-0.06745064291035285</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.0481885702946675</v>
+        <v>-0.02280628362156711</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.01652149919900503</v>
+        <v>0.08372529561091024</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.1591737214608977</v>
+        <v>0.09491932366166811</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2791036675147567</v>
+        <v>0.08448579025239189</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.62310096671363</v>
+        <v>0.4306186867488029</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1752091896663612</v>
+        <v>0.1267856250242529</v>
       </c>
     </row>
     <row r="31">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2230,37 +2230,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>127.26</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.01041993704266642</v>
+        <v>-0.023611284483114</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.03372268536229928</v>
+        <v>-0.02852378719071547</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.0405514040721261</v>
+        <v>-0.04130065427284213</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.04785302289494708</v>
+        <v>-0.05622371618451838</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.06372582718563713</v>
+        <v>-0.02939584261699824</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.07872428460453373</v>
+        <v>0.1155050218441862</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.01751859325665039</v>
+        <v>0.05388955931464845</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.0784972570133875</v>
+        <v>0.09639603350317816</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.5620898047282741</v>
+        <v>0.9070103385747923</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.1602956551002985</v>
+        <v>0.2400837479368665</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>187.1</v>
+        <v>224.98</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.01244590375419885</v>
+        <v>0.007297916183033326</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.006668206403723786</v>
+        <v>0.0012461005033364</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.04504444024235199</v>
+        <v>-0.02744998942313226</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.03556993722600632</v>
+        <v>-0.06129262132781066</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.008116954789087139</v>
+        <v>-0.01698802607677508</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.1494402450782111</v>
+        <v>0.0527392460838283</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.04871620681400324</v>
+        <v>0.07813369239219892</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.07205025627099571</v>
+        <v>0.1087563034651038</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>1.095928968954857</v>
+        <v>0.3680828917276031</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.2797511253104665</v>
+        <v>0.1101222416918222</v>
       </c>
     </row>
     <row r="33">
@@ -2328,51 +2328,51 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>70.83</v>
+        <v>138.23</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.004680877036236764</v>
+        <v>-0.02200368396017727</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.01229099035798065</v>
+        <v>-0.03913530417715982</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.0451603998428044</v>
+        <v>-0.02956643486989086</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.07544705303808441</v>
+        <v>-0.03677679904696729</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>-0.134090386986793</v>
+        <v>0.001326621892532964</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.06202553163450375</v>
+        <v>0.08592682248089711</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.1129293312297897</v>
+        <v>0.0283849536576124</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.3496241945936704</v>
+        <v>0.07858540812348891</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.3386378043919342</v>
+        <v>0.5645201457610141</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.102100066448777</v>
+        <v>0.1608970829572491</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>71.91</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.006493418197613954</v>
+        <v>-0.001252172218342507</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.02775703859454837</v>
+        <v>-0.004990038767525462</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.02867090859793364</v>
+        <v>-0.02166288532020288</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.03963255459655224</v>
+        <v>-0.08146696737632875</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.01068710704789333</v>
+        <v>-0.04765399814765237</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.05032446167933347</v>
+        <v>0.0801522253445921</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.08997012043645114</v>
+        <v>0.06721656569372825</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.07910158787984667</v>
+        <v>0.1225335365159648</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2108445842500206</v>
+        <v>0.4128919068331967</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.06585011047134737</v>
+        <v>0.1221122730933426</v>
       </c>
     </row>
     <row r="35">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2454,37 +2454,37 @@
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>29.01</v>
+        <v>53.39</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.02799436338588057</v>
+        <v>0.005840194949134014</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.02945351010353292</v>
+        <v>0.01213268985115512</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.007291701298069997</v>
+        <v>-0.01476285767363439</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.0189380950869743</v>
+        <v>-0.05320092272515098</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.06419354100381169</v>
+        <v>-0.07483789845027278</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.2042341239157448</v>
+        <v>0.06541079563019125</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.01766216102199292</v>
+        <v>0.09550899694074899</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1336283826963007</v>
+        <v>0.1461104839307996</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.6847702132670159</v>
+        <v>0.8073242000358472</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.1899084771235324</v>
+        <v>0.2180880650165327</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>100.98</v>
+        <v>69.58</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.004246612323423271</v>
+        <v>-0.0176478888562156</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.01597316322414233</v>
+        <v>-0.003865377937931402</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.04124521741801168</v>
+        <v>-0.05679808869024172</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.0644738427806697</v>
+        <v>-0.09176346068775487</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.107749684154879</v>
+        <v>-0.1090258515651072</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.150320005284172</v>
+        <v>-0.0001558969159599632</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.09304235749918588</v>
+        <v>0.05113791566960213</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.1943225591517019</v>
+        <v>0.3198126674369441</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.3765424369187684</v>
+        <v>0.3051695935222301</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.1124056897824659</v>
+        <v>0.09283765108729303</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>REITs - Broad</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>93.81</v>
+        <v>182.83</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.009686727596712075</v>
+        <v>-0.02282204240067476</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.005512607467052399</v>
+        <v>0.009218360207477794</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.0230160295952504</v>
+        <v>-0.04331826471761002</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.04761423798381981</v>
+        <v>-0.05758020101111971</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.00966050777045746</v>
+        <v>-0.01165072793128474</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.0777295626171659</v>
+        <v>0.1095117580338794</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.08952714123116334</v>
+        <v>0.008709778550940239</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.06320897415022975</v>
+        <v>0.05055763007459424</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.3539022457672469</v>
+        <v>1.060484480822079</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1062733138142782</v>
+        <v>0.2724960686967817</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>79.86</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.005107712094943206</v>
+        <v>-0.003811358794805431</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.03145998611508338</v>
+        <v>-0.001979909368704513</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.04906555067595286</v>
+        <v>-0.005636205706619268</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.08031536382527427</v>
+        <v>-0.0264863874400102</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>-0.04646000185289423</v>
+        <v>0.06681780902478351</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.09719335160624509</v>
+        <v>0.03725191490268354</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.07254229188197114</v>
+        <v>-0.001008630437764446</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1300842623117895</v>
+        <v>-0.02518956884712864</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.4054822671728282</v>
+        <v>0.01272930998540756</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1201472667675467</v>
+        <v>0.004225225652991993</v>
       </c>
     </row>
     <row r="39">
@@ -2678,37 +2678,37 @@
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>13.17</v>
+        <v>12.94</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.006880745650829523</v>
+        <v>-0.01746397073487083</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.006880745650829523</v>
+        <v>-0.01221380125398708</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.01200298937193289</v>
+        <v>-0.009188425373490183</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.009029336787323095</v>
+        <v>-0.02633561944878482</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.08603659971336275</v>
+        <v>0.07227523750984077</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.0983201516584542</v>
+        <v>0.06076368163579615</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>-0.005832007571653586</v>
+        <v>-0.01774848039047483</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>-0.05985222865413431</v>
+        <v>-0.04710051773095614</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.161202412318356</v>
+        <v>0.1330349666980448</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.05108049388835378</v>
+        <v>0.04251209986145366</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>109</v>
+        <v>99.81</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.003618530421864996</v>
+        <v>-0.01158650979842246</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.009954954446147912</v>
+        <v>-0.001641279253053463</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.08048171505532675</v>
+        <v>-0.02118625172646504</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.08602925159732278</v>
+        <v>-0.07531332576797189</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.06727154405643199</v>
+        <v>-0.118826121357974</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.07358215124947365</v>
+        <v>0.1081737613058569</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.03974189499215619</v>
+        <v>0.07915793269958504</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.2111072097715614</v>
+        <v>0.1787550296659852</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.166850146393238</v>
+        <v>0.3729986127591316</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2940258713570605</v>
+        <v>0.1114502626537814</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>70.84</v>
+        <v>124.22</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.003115173927393355</v>
+        <v>-0.02388810988917833</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.008254969883655594</v>
+        <v>-0.04531159225008341</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.0124077370331942</v>
+        <v>-0.03719478892605388</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.02276178196307521</v>
+        <v>-0.07059801451468151</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.05291316324591278</v>
+        <v>0.01036373187181572</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.06940771830071668</v>
+        <v>0.04630577441019779</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.01189638729556819</v>
+        <v>-0.01366220621313374</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>-0.01575301444282495</v>
+        <v>0.04929969089613961</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.00756503362568739</v>
+        <v>0.5217651460446524</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.002515345606873831</v>
+        <v>0.1502243156743328</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>223.35</v>
+        <v>28.25</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.0006264234919118872</v>
+        <v>-0.02619787048899069</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-0.009578238020199303</v>
+        <v>0.01618707824781351</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-0.05143124210077732</v>
+        <v>0.008208406084183384</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.0680935961535144</v>
+        <v>-0.04463982781356823</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.04314952958474128</v>
+        <v>-0.09397050277415842</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.06429676160009823</v>
+        <v>0.1331728702038943</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.08514012518339009</v>
+        <v>-0.006925176646146669</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.09715407129617915</v>
+        <v>0.1095202797784276</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.3566787352267653</v>
+        <v>0.6587876748873209</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1070290205004669</v>
+        <v>0.1837598341111217</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>53.08</v>
+        <v>112.56</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.002265912927804647</v>
+        <v>-0.01908498859613295</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.001131674326159571</v>
+        <v>-0.0006108728870930502</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-0.03770844855169098</v>
+        <v>0.01895663862212493</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.05869830811172827</v>
+        <v>0.01374298998121137</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>-0.09198970522595518</v>
+        <v>0.05277307748652826</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.08472221745826491</v>
+        <v>0.004567153981826388</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.1023812985177441</v>
+        <v>-0.03240409752467066</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.1433497345487889</v>
+        <v>-0.03763371141425886</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.8010090467847903</v>
+        <v>0.7757032270131416</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.2166676613339324</v>
+        <v>0.210942331529572</v>
       </c>
     </row>
     <row r="44">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>REITs - Broad</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>114.75</v>
+        <v>91.45</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.0389693498587389</v>
+        <v>-0.02515723986537266</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.0005056905150100377</v>
+        <v>-0.02171594283047096</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.02765500390823572</v>
+        <v>-0.03676011589864847</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>0.03346668997384539</v>
+        <v>-0.07157363504322656</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.05461581001799032</v>
+        <v>-0.05726509419575343</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.03177434381488453</v>
+        <v>0.04251172729957053</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>-0.002995948218008748</v>
+        <v>0.05740810349963898</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>-0.02373286917219519</v>
+        <v>0.03061422421575877</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.8080478712463697</v>
+        <v>0.3298972343452795</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.2182506216545768</v>
+        <v>0.09969612387025406</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>62.69</v>
+        <v>55.92</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.01581485422601303</v>
+        <v>-0.008510697587718052</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.0143436455606738</v>
+        <v>-0.01306038970101753</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.03153443190700733</v>
+        <v>-0.04418206290675719</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.07670853345052242</v>
+        <v>-0.05922929163856538</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.04028866895456806</v>
+        <v>-0.09790558363339374</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.1044719474675413</v>
+        <v>0.001058620188082227</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.02184259273249611</v>
+        <v>0.06346701419381118</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.02025497485682015</v>
+        <v>0.09035877926699398</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.6464056410843644</v>
+        <v>0.5832066023588647</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1808070800248829</v>
+        <v>0.1655006787402107</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>56.4</v>
+        <v>61.49</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.003885507067397209</v>
+        <v>-0.01914176064012429</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.01314061762438035</v>
+        <v>-0.01258148503643852</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.04394871632382924</v>
+        <v>-0.02090681815876438</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.05115394984842447</v>
+        <v>-0.09438195770428193</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.08605263214830694</v>
+        <v>-0.05430556039572265</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.029405504566971</v>
+        <v>0.05277713844728638</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0831770038513977</v>
+        <v>-0.002412209964815393</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.1062866896659782</v>
+        <v>-0.002406900404168133</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.5959465227180436</v>
+        <v>0.6331207541404413</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.1686185567295473</v>
+        <v>0.1776225121880928</v>
       </c>
     </row>
     <row r="47">
@@ -3126,37 +3126,37 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>45.91</v>
+        <v>45.42</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.009792130932541387</v>
+        <v>-0.01067309257450189</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.02693676277612167</v>
+        <v>-0.02850171517475597</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.03730357063865841</v>
+        <v>-0.02788033370182708</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.05195897383704973</v>
+        <v>-0.06207750347371266</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-0.006633131369891854</v>
+        <v>-0.02767297692987636</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.01754929179649645</v>
+        <v>-0.0387211949309989</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.01958340615548915</v>
+        <v>0.01970977455457312</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.009861373703294429</v>
+        <v>0.006053772669961655</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.111721178275463</v>
+        <v>0.1060082228532377</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.03593369602057894</v>
+        <v>0.03415614909168063</v>
       </c>
     </row>
     <row r="48">
@@ -3182,37 +3182,37 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>35.82</v>
+        <v>35.29</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.0202221325015679</v>
+        <v>-0.01479616928565908</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0.03049486261437373</v>
+        <v>0.01641704132442068</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-0.003616163153166041</v>
+        <v>0.003126793899867586</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.006104362239578665</v>
+        <v>-0.02081021034815989</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.06599126249062881</v>
+        <v>-0.03636326705141735</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.06660464683054212</v>
+        <v>0.03118135071255934</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.000908172464935797</v>
+        <v>-0.0335212613972633</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>0.02836165088549181</v>
+        <v>-0.005605697730450721</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.4773689139644826</v>
+        <v>0.4489930380353033</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.1389281281230352</v>
+        <v>0.1315891281383297</v>
       </c>
     </row>
     <row r="49">
@@ -3238,37 +3238,37 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>17.8</v>
+        <v>17.42</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.01366741334950738</v>
+        <v>-0.02134826837382231</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0.01366741334950738</v>
+        <v>0.005773694181969935</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.001688169866296718</v>
+        <v>-0.03275958606828522</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.01193854932637728</v>
+        <v>-0.009664586402458597</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.1563981556752615</v>
+        <v>-0.1572327038221624</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.01175108900018473</v>
+        <v>-0.03923241660409238</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.08563110631623982</v>
+        <v>0.05603114802074027</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1856714099912831</v>
+        <v>0.1588315782501817</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.2235836861294944</v>
+        <v>0.207778311227002</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.06957495742972442</v>
+        <v>0.06494965082697557</v>
       </c>
     </row>
     <row r="50">
@@ -3294,37 +3294,37 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>82.56</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.00858818397712402</v>
+        <v>-0.005571694501882551</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.03257150218624116</v>
+        <v>-0.005517840867861112</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.0554345943711384</v>
+        <v>-0.02403903404541252</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.05672685831399871</v>
+        <v>-0.06198248809130413</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.04024771041962283</v>
+        <v>-0.04087767847179469</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.05705143195626494</v>
+        <v>0.03244469240404135</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.04808852026654176</v>
+        <v>-0.04290478855741864</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.04457298088387363</v>
+        <v>-0.04718606734398056</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.4288809381202736</v>
+        <v>0.4275962930027954</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1263292109474079</v>
+        <v>0.1259915650958663</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>216.14</v>
+        <v>43.22</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.01075571965556699</v>
+        <v>-0.01030448745386459</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.001750483974745198</v>
+        <v>-0.004147472323669188</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.04086452633474169</v>
+        <v>-0.03028939832543609</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.08826764718301083</v>
+        <v>-0.05447381128072182</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.09456234386499784</v>
+        <v>-0.02349745007387638</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.02703786302294231</v>
+        <v>-0.03072435360387082</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.01296340196693646</v>
+        <v>-0.05900281006894026</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.06530488168531901</v>
+        <v>-0.05322968706233278</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>1.06484751489312</v>
+        <v>0.2477193058192322</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.2733935970286925</v>
+        <v>0.07656179860585244</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>43.67</v>
+        <v>213.92</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0.008312093840668888</v>
+        <v>-0.01027112624674809</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.007274460043454112</v>
+        <v>-0.006271222542491128</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.03534354478991319</v>
+        <v>-0.02406937922230656</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.04462920490891709</v>
+        <v>-0.09763216528203877</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.0260928184580983</v>
+        <v>-0.09223928637681744</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.01333032478450968</v>
+        <v>-0.04043733373414748</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.03852928380777687</v>
+        <v>-0.023818015413963</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-0.04156824830654005</v>
+        <v>0.04024747563338082</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0.2674195866210383</v>
+        <v>1.06270268727379</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.08219819391182703</v>
+        <v>0.2729525384758582</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>25.99</v>
+        <v>51.78</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.008810448110344149</v>
+        <v>-0.003272415421480712</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.02263665811632642</v>
+        <v>-0.002312191581000156</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0.05311475929260923</v>
+        <v>0.007400942326738935</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.05665440950726741</v>
+        <v>-0.0767135344856319</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.04272988399985533</v>
+        <v>0.05580216422932049</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.08895709296362075</v>
+        <v>-0.04698295877959369</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.1363888129813544</v>
+        <v>-0.1701845352676965</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>-0.2541853545019646</v>
+        <v>-0.139398968482073</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.3121016937271974</v>
+        <v>0.07856414103049003</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.09476901884927114</v>
+        <v>0.02553068407926729</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>51.95</v>
+        <v>25.43</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.00347692299756952</v>
+        <v>-0.02169902549985347</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.00330245097912818</v>
+        <v>0.01105367324637485</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.02981044502585162</v>
+        <v>-0.02387715005057223</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.07368223795592732</v>
+        <v>-0.07712408953054362</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.06034781518634413</v>
+        <v>0.04866142938814266</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>-0.04280027839408052</v>
+        <v>0.03967293135688621</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1673271570441369</v>
+        <v>-0.1565747696215726</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.1347129377065388</v>
+        <v>-0.2507354615670468</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.07878891627285922</v>
+        <v>0.2861887858721011</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.0256019201136537</v>
+        <v>0.08751412451736584</v>
       </c>
     </row>
     <row r="55">
@@ -3574,37 +3574,37 @@
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>243.55</v>
+        <v>239.37</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.01593035610502724</v>
+        <v>-0.01716283261011498</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0.003504751926811878</v>
+        <v>-0.01152003534680179</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.03652912745161896</v>
+        <v>-0.02919010762770746</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.1065444015379178</v>
+        <v>-0.1218786304188926</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.142656383244093</v>
+        <v>-0.1301075299822532</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.05809762699958054</v>
+        <v>-0.08860509454079324</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.01109498163769684</v>
+        <v>-0.04187938162999005</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.07759136522263788</v>
+        <v>0.04193461935569154</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1.201734705011451</v>
+        <v>1.183186335372176</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.3009331968164117</v>
+        <v>0.2972696809906001</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>40.66</v>
+        <v>97.09</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.003431357653587153</v>
+        <v>0.001340730761607345</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.02058892526317346</v>
+        <v>0.008604433814876522</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.0492346976093978</v>
+        <v>-0.01609485114756126</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.04234352354403093</v>
+        <v>-0.08325903804360668</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.07907698047341061</v>
+        <v>-0.09766252548105114</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.07035386694816259</v>
+        <v>-0.01561620466378255</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.0190083003644812</v>
+        <v>-0.05801739063493505</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.00880101727674254</v>
+        <v>-0.1175159537788389</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.4024655968282214</v>
+        <v>0.3076647371616259</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.119345279766164</v>
+        <v>0.09353361456864207</v>
       </c>
     </row>
     <row r="57">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3686,37 +3686,37 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>17.53</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.0106627931916341</v>
+        <v>0.006689387615641085</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.01819713056174721</v>
+        <v>0.007603247254452716</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.0761327570956285</v>
+        <v>-0.008529137592287905</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.1257852550676962</v>
+        <v>-0.08154955937532427</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.02653642524354083</v>
+        <v>-0.08003979314520782</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.1059602872078556</v>
+        <v>-0.01842160641245849</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.1703335861123001</v>
+        <v>-0.07457896617233251</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.2401525283837648</v>
+        <v>-0.1590398274301739</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.05511850786198069</v>
+        <v>0.1669378652984406</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.01804524634176286</v>
+        <v>0.05280816415065259</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>42.98</v>
+        <v>39.75</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.03193272431289196</v>
+        <v>-0.02238071448172985</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>0.01872483861678109</v>
+        <v>-0.03092257721437341</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.06686933867181122</v>
+        <v>-0.06748298036413736</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.06707185094544377</v>
+        <v>-0.06377655971517138</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.10046043029914</v>
+        <v>-0.1115536384549517</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.0745047197844384</v>
+        <v>-0.1000900322432019</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.01870282325187522</v>
+        <v>-0.04787165512715574</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.08897983229778805</v>
+        <v>-0.04521899566527743</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.8977251701867324</v>
+        <v>0.3736769086448033</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.2380678307330937</v>
+        <v>0.1116332606602641</v>
       </c>
     </row>
     <row r="59">
@@ -3784,51 +3784,51 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>96.95999999999999</v>
+        <v>41.99</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.01153841102694053</v>
+        <v>-0.02303391983047054</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>-0.007813288031215948</v>
+        <v>0.01498677211964305</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.05566889229390348</v>
+        <v>-0.1039265656946868</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.08448649516220963</v>
+        <v>-0.08856084313835566</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.1206512641077321</v>
+        <v>-0.07876261536571383</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.01733173479288608</v>
+        <v>-0.1279335337944139</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.06627420828409236</v>
+        <v>-0.05510157113851166</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1307385828882858</v>
+        <v>-0.1264005065363056</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.3072864730484064</v>
+        <v>0.7903440004332962</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.09342816337711457</v>
+        <v>0.2142613223959253</v>
       </c>
     </row>
     <row r="60">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>88.2</v>
+        <v>16.75</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0.009037790333319196</v>
+        <v>-0.04505269546924473</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.01227387829640048</v>
+        <v>-0.05245586234452337</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.0528725149224879</v>
+        <v>-0.06536054381791656</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.08765260474232339</v>
+        <v>-0.1651709857458548</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.1038313186905614</v>
+        <v>-0.04396223678261257</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>0.009299431099994981</v>
+        <v>0.02849952079052165</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.09084059977443537</v>
+        <v>-0.1968053922488893</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.1784446935524194</v>
+        <v>-0.2648285320659323</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.160949563359122</v>
+        <v>0.001574257159167924</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.05100419828926106</v>
+        <v>0.0005244772619006355</v>
       </c>
     </row>
     <row r="61">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>18.15</v>
+        <v>17.73</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.004006583807614428</v>
+        <v>-0.02319940165566314</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.06270340881551495</v>
+        <v>-0.07339254522774474</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.0630905134390829</v>
+        <v>-0.07777955293758076</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.0764885643041977</v>
+        <v>-0.09791347703450282</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.06795069341970572</v>
+        <v>-0.05662591971960862</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>0.02150295427001314</v>
+        <v>-0.03558211961234958</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.1344649336656133</v>
+        <v>-0.1557004058094462</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.2214801906201587</v>
+        <v>-0.2492453903681557</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1707238741681394</v>
+        <v>0.1544413774547564</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.05394551066568676</v>
+        <v>0.04903656977352577</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>46.71</v>
+        <v>45.05</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.02299604118636589</v>
+        <v>-0.03553842603186708</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>0.01060142472584036</v>
+        <v>0.009636941180393155</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.02768529986902657</v>
+        <v>-0.05634692808608721</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.05291972073198259</v>
+        <v>-0.08657746318298898</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2289534884013812</v>
+        <v>-0.2307035829816823</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1530372113851314</v>
+        <v>-0.1807601770868575</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.04654016158150698</v>
+        <v>-0.1061508358501</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.08200141453964371</v>
+        <v>0.06325230995365905</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1232603391552823</v>
+        <v>-0.1420915362953737</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.04290095176619391</v>
+        <v>-0.04980300901146784</v>
       </c>
     </row>
   </sheetData>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1017738786133422</v>
+        <v>0.1115391206046483</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1257852550676962</v>
+        <v>-0.1651709857458548</v>
       </c>
     </row>
     <row r="18">
@@ -4647,21 +4647,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.09016948635295297</v>
+        <v>0.09657357732703176</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1065444015379178</v>
+        <v>-0.1218786304188926</v>
       </c>
     </row>
     <row r="19">
@@ -4692,21 +4692,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.08687399047262745</v>
+        <v>0.08203390089132023</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.08826764718301083</v>
+        <v>-0.09791347703450282</v>
       </c>
     </row>
     <row r="20">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.07328335470570657</v>
+        <v>0.07314155719701798</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.08765260474232339</v>
+        <v>-0.09763216528203877</v>
       </c>
     </row>
     <row r="21">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.06354171420120047</v>
+        <v>0.06078674671888162</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.08602925159732278</v>
+        <v>-0.09438195770428193</v>
       </c>
     </row>
     <row r="22">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.05322954457553863</v>
+        <v>0.05901211710340504</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.08448649516220963</v>
+        <v>-0.09176346068775487</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.04951999719573674</v>
+        <v>0.04575791430648346</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.08168823666540193</v>
+        <v>-0.09014882920736655</v>
       </c>
     </row>
     <row r="24">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.03637413569634695</v>
+        <v>0.03885918653244547</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.08031536382527427</v>
+        <v>-0.0896760767424265</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FDN</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Internet &amp; Digital Services</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03540283733631266</v>
+        <v>0.03588214537862755</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.07670853345052242</v>
+        <v>-0.08856084313835566</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.03346668997384539</v>
+        <v>0.01746499292072934</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.0764885643041977</v>
+        <v>-0.08657746318298898</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3898012400898647</v>
+        <v>0.3559897550912594</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2289534884013812</v>
+        <v>-0.2307035829816823</v>
       </c>
     </row>
     <row r="32">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.330114956559806</v>
+        <v>0.3553488088208576</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5180,21 +5180,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1750073937822347</v>
+        <v>-0.1572327038221624</v>
       </c>
     </row>
     <row r="33">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.3295157649919258</v>
+        <v>0.3083092293705743</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5225,21 +5225,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1563981556752615</v>
+        <v>-0.1301075299822532</v>
       </c>
     </row>
     <row r="34">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2810417016347249</v>
+        <v>0.2929345652203124</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.142656383244093</v>
+        <v>-0.1259312342653346</v>
       </c>
     </row>
     <row r="35">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2204713698636818</v>
+        <v>0.2379752502510439</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5315,21 +5315,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.134090386986793</v>
+        <v>-0.118826121357974</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration &amp; Production</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2154133078976523</v>
+        <v>0.2361885875069936</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5360,21 +5360,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.1206512641077321</v>
+        <v>-0.1115536384549517</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.2024918807618674</v>
+        <v>0.2047385159246657</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5405,21 +5405,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.107749684154879</v>
+        <v>-0.1090258515651072</v>
       </c>
     </row>
     <row r="38">
@@ -5428,21 +5428,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Biotechnology (Market Weight)</t>
+          <t>Oil &amp; Gas Exploration &amp; Production</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1931072683602397</v>
+        <v>0.1827804735568381</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,21 +5450,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.1038313186905614</v>
+        <v>-0.09790558363339374</v>
       </c>
     </row>
     <row r="39">
@@ -5473,12 +5473,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1444673113601969</v>
+        <v>0.1759478730620023</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.10046043029914</v>
+        <v>-0.09766252548105114</v>
       </c>
     </row>
     <row r="40">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1255352385310526</v>
+        <v>0.1601499792771268</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,21 +5540,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.09675997925907232</v>
+        <v>-0.09397050277415842</v>
       </c>
     </row>
     <row r="41"/>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.6280829447221463</v>
+        <v>0.6043147087454506</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1530372113851314</v>
+        <v>-0.1807601770868575</v>
       </c>
     </row>
     <row r="46">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.6142131676489138</v>
+        <v>0.6026746800613949</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.0745047197844384</v>
+        <v>-0.1279335337944139</v>
       </c>
     </row>
     <row r="47">
@@ -5714,21 +5714,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.6077919570080763</v>
+        <v>0.5975976380188242</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.07035386694816259</v>
+        <v>-0.1000900322432019</v>
       </c>
     </row>
     <row r="48">
@@ -5759,21 +5759,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.6063935620411336</v>
+        <v>0.5888078564888253</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.05809762699958054</v>
+        <v>-0.08860509454079324</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.5491761824233214</v>
+        <v>0.5367181000997809</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.04280027839408052</v>
+        <v>-0.04698295877959369</v>
       </c>
     </row>
     <row r="50">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.4715157950005733</v>
+        <v>0.4511951942413268</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FCG</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Natural Gas Producers</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.03092807531879216</v>
+        <v>-0.04043733373414748</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.4427623515123225</v>
+        <v>0.4323871654463725</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.02703786302294231</v>
+        <v>-0.03923241660409238</v>
       </c>
     </row>
     <row r="52">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.4366208245279526</v>
+        <v>0.3928540697111753</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.01754929179649645</v>
+        <v>-0.0387211949309989</v>
       </c>
     </row>
     <row r="53">
@@ -5984,21 +5984,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.3337780142410374</v>
+        <v>0.305938073007598</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6006,21 +6006,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.01333032478450968</v>
+        <v>-0.03558211961234958</v>
       </c>
     </row>
     <row r="54">
@@ -6029,21 +6029,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.3223126196941752</v>
+        <v>0.2973521563820922</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.01175108900018473</v>
+        <v>-0.03072435360387082</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9705882627933775</v>
+        <v>0.9345454591693301</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6157,21 +6157,21 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2541853545019646</v>
+        <v>-0.2648285320659323</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8937779589929113</v>
+        <v>0.8752915541851864</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6202,21 +6202,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2401525283837648</v>
+        <v>-0.2507354615670468</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7890747109127749</v>
+        <v>0.790216769780524</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.2214801906201587</v>
+        <v>-0.2492453903681557</v>
       </c>
     </row>
     <row r="62">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6781042488967195</v>
+        <v>0.6513919038743419</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1784446935524194</v>
+        <v>-0.1590398274301739</v>
       </c>
     </row>
     <row r="63">
@@ -6315,21 +6315,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6627009186674389</v>
+        <v>0.6391199039241318</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.1347129377065388</v>
+        <v>-0.139398968482073</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.6498151241081944</v>
+        <v>0.6106883701522177</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6382,21 +6382,21 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1307385828882858</v>
+        <v>-0.1264005065363056</v>
       </c>
     </row>
     <row r="65">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.585393291047305</v>
+        <v>0.5376555195128265</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6427,21 +6427,21 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.08897983229778805</v>
+        <v>-0.1175159537788389</v>
       </c>
     </row>
     <row r="66">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.5432910157417756</v>
+        <v>0.5203226261754073</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.08567217120499637</v>
+        <v>-0.07113174376607823</v>
       </c>
     </row>
     <row r="67">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.4953428488556111</v>
+        <v>0.4814111099152178</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.05985222865413431</v>
+        <v>-0.05322968706233278</v>
       </c>
     </row>
     <row r="68">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology (Market Weight)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.4603284425976246</v>
+        <v>0.4528371916349725</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.04457298088387363</v>
+        <v>-0.04718606734398056</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.292089207591205</v>
+        <v>3.294221356225966</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1232603391552823</v>
+        <v>-0.1420915362953737</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.893075085599392</v>
+        <v>2.836771838207835</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6713,21 +6713,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.00756503362568739</v>
+        <v>0.001574257159167924</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.38335019250343</v>
+        <v>2.356823155684697</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6758,21 +6758,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.05511850786198069</v>
+        <v>0.01272930998540756</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.994413457428208</v>
+        <v>1.88607584676748</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.07878891627285922</v>
+        <v>0.07856414103049003</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.776821733828835</v>
+        <v>1.758582305950276</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.111721178275463</v>
+        <v>0.1060082228532377</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.543340008013165</v>
+        <v>1.533437997519019</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6893,21 +6893,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1562877098902584</v>
+        <v>0.1330349666980448</v>
       </c>
     </row>
     <row r="79">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.437973014196879</v>
+        <v>1.425810417597889</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6938,21 +6938,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.160949563359122</v>
+        <v>0.1387972349093953</v>
       </c>
     </row>
     <row r="80">
@@ -6961,21 +6961,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.404967747359576</v>
+        <v>1.392571524566373</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6983,21 +6983,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.161202412318356</v>
+        <v>0.1544413774547564</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.3079790136397</v>
+        <v>1.320932315896604</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1707238741681394</v>
+        <v>0.1669378652984406</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.201734705011451</v>
+        <v>1.183186335372176</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,21 +7073,21 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.2108445842500206</v>
+        <v>0.206849119972</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -489,15 +489,15 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>15.96</v>
+        <v>15.77</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-0.007462679485599422</v>
+        <v>-0.01190473558453453</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0.04313724439113287</v>
+        <v>-0.001266593042284492</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-0.008695673292274386</v>
+        <v>-0.009422086545943786</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.08203390089132023</v>
+        <v>0.07351946277946664</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.3559897550912594</v>
+        <v>0.3478633089613843</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>0.5975976380188242</v>
+        <v>0.6091836888608408</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.8260870087076797</v>
+        <v>0.7981755569696951</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.9345454591693301</v>
+        <v>0.8818616041052152</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1.88607584676748</v>
+        <v>1.851717876934801</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.4237571347137767</v>
+        <v>0.4180847479781793</v>
       </c>
     </row>
     <row r="3">
@@ -662,37 +662,37 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>40.78</v>
+        <v>41.69</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.003691796880097797</v>
+        <v>0.02231485715183723</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.05374671770935224</v>
+        <v>0.04224996566772465</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.05647669407648648</v>
+        <v>0.1005807141278237</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.01746499292072934</v>
+        <v>0.05092010463829522</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3083092293705743</v>
+        <v>0.3147272100402931</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0.4323871654463725</v>
+        <v>0.4893556449934702</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>0.5286281967869475</v>
+        <v>0.5540380943835601</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0.790216769780524</v>
+        <v>0.8389564467943529</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1.042796713366203</v>
+        <v>1.088381430215212</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.2688444473534013</v>
+        <v>0.2782131297126653</v>
       </c>
     </row>
     <row r="4">
@@ -718,37 +718,37 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>124.07</v>
+        <v>122.18</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.008863199773438302</v>
+        <v>-0.01523333113804526</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.03859032852571631</v>
+        <v>0.0141102000404647</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1181506914070094</v>
+        <v>0.1057013602278352</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.1115391206046483</v>
+        <v>0.115086252126249</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2929345652203124</v>
+        <v>0.2724432886553156</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>0.5888078564888253</v>
+        <v>0.6165651937702634</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5171249218795699</v>
+        <v>0.4923727142465215</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4271436044722265</v>
+        <v>0.4153270102623374</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1.425810417597889</v>
+        <v>1.388857422400881</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3436483369311099</v>
+        <v>0.3367906828908409</v>
       </c>
     </row>
     <row r="5">
@@ -774,37 +774,37 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>601.41</v>
+        <v>600.52</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.009959583526958915</v>
+        <v>-0.001479778608638682</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.1023718304785335</v>
+        <v>0.07119037338348444</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.04722352148707754</v>
+        <v>0.07182121105561134</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.07314155719701798</v>
+        <v>0.09824439088799131</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>-0.03318063669073956</v>
+        <v>-0.02972914736472032</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.5367181000997809</v>
+        <v>0.5218835376075268</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.6560468308181149</v>
+        <v>0.6490100705406288</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8752915541851864</v>
+        <v>0.8759572078459845</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>3.294221356225966</v>
+        <v>3.287866859322264</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.625404567510186</v>
+        <v>0.6246024254126123</v>
       </c>
     </row>
     <row r="6">
@@ -830,37 +830,37 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>104.01</v>
+        <v>103.19</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.008924297516942348</v>
+        <v>-0.007855253137267204</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.03698902264796722</v>
+        <v>0.01507940772699934</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.1008678920479473</v>
+        <v>0.09593219042532031</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.09657357732703176</v>
+        <v>0.1068645254425511</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.2361885875069936</v>
+        <v>0.2324787134775763</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.6043147087454506</v>
+        <v>0.6401602626037575</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.4322273233458702</v>
+        <v>0.4201965547529258</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3731968530332355</v>
+        <v>0.3703280391459771</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1.320932315896604</v>
+        <v>1.302700676254414</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3239984962501143</v>
+        <v>0.3205225732139507</v>
       </c>
     </row>
     <row r="7">
@@ -886,37 +886,37 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>29.14</v>
+        <v>28.94</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.00725886907215445</v>
+        <v>-0.006863378853119273</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.03997141019226635</v>
+        <v>0.02117150240787624</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.06505843346448681</v>
+        <v>0.06514539760005422</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.03885918653244547</v>
+        <v>0.04476533346443778</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.3553488088208576</v>
+        <v>0.3429235062007863</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.4511951942413268</v>
+        <v>0.4994819522316869</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2741582125199962</v>
+        <v>0.2649707232242746</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2352691479932736</v>
+        <v>0.2257517910172848</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5491759817648947</v>
+        <v>0.5385434000918894</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1570894088037602</v>
+        <v>0.1544361484101375</v>
       </c>
     </row>
     <row r="8">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>527.4400000000001</v>
+        <v>526.7</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.005490325027101894</v>
+        <v>-0.001402984663563145</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.09969079385731172</v>
+        <v>0.05532355513470377</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.06452459511562303</v>
+        <v>0.07425809871402045</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.05901211710340504</v>
+        <v>0.09404350005052198</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-0.1259312342653346</v>
+        <v>-0.1069335328078361</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0.6026746800613949</v>
+        <v>0.5739969078028957</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.5995381806167279</v>
+        <v>0.5970039195699328</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6391199039241318</v>
+        <v>0.6494058369922486</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.758582305950276</v>
+        <v>1.754711397758295</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.4024756038431672</v>
+        <v>0.4018193010781861</v>
       </c>
     </row>
     <row r="9">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>156.47</v>
+        <v>155.34</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.0129943706204253</v>
+        <v>-0.003195633329642011</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.02428650724847436</v>
+        <v>0.002120127290324181</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.01498441556641916</v>
+        <v>0.02322363687184925</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.03588214537862755</v>
+        <v>0.04216204285979575</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.01649481592915469</v>
+        <v>0.01686599061799687</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.3928540697111753</v>
+        <v>0.3880344910215563</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.4604544386056975</v>
+        <v>0.453494401818374</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.5203226261754073</v>
+        <v>0.5249468234899368</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.392571524566373</v>
+        <v>1.384926023068771</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3374831207939089</v>
+        <v>0.3360569508567144</v>
       </c>
     </row>
     <row r="10">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>182.65</v>
+        <v>184.05</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.01136674480928623</v>
+        <v>0.00766498331265697</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.04390894964290804</v>
+        <v>-0.04053239037145429</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.05964679142072393</v>
+        <v>-0.05466890960626347</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.03250883158032647</v>
+        <v>-0.007818653886270122</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.1827804735568381</v>
+        <v>0.2075009630454823</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.05379461668238972</v>
+        <v>0.03023493597876925</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.4628215188247617</v>
+        <v>0.4805894444104497</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3987418258762359</v>
+        <v>0.3882090115322883</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3653619429917774</v>
+        <v>0.3758275764327996</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1093857876683137</v>
+        <v>0.1122130930884302</v>
       </c>
     </row>
     <row r="11">
@@ -1110,37 +1110,37 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>206.6</v>
+        <v>209.25</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.002703212727815596</v>
+        <v>0.01282668837461998</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.02075104907947423</v>
+        <v>0.01052780508365925</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.005455779919441683</v>
+        <v>0.03267494765051793</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-0.0325383512362456</v>
+        <v>-0.01538016158830324</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.1601499792771268</v>
+        <v>0.1527640548044698</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.2701466606879188</v>
+        <v>0.2947951030952169</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2015752477098856</v>
+        <v>0.2089093252418539</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4528371916349725</v>
+        <v>0.4803029387127695</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6999677200769445</v>
+        <v>0.7217728924446891</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1934756378509743</v>
+        <v>0.1985568049369049</v>
       </c>
     </row>
     <row r="12">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>87.03</v>
+        <v>86.25</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.005257733406153653</v>
+        <v>-0.008962412848871892</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.03373317799660569</v>
+        <v>-0.004156570925003988</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-0.08649100613114402</v>
+        <v>-0.02663356950790796</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>-0.07992385930102197</v>
+        <v>-0.08759122909361861</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.09871347649528461</v>
+        <v>0.1432378430559964</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.1872976427129207</v>
+        <v>0.185521879484065</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.2087275688039418</v>
+        <v>0.2009805900452857</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.6513919038743419</v>
+        <v>0.5833450281389629</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.533437997519019</v>
+        <v>1.510732559064054</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3632330086073217</v>
+        <v>0.3591482121302545</v>
       </c>
     </row>
     <row r="13">
@@ -1222,37 +1222,37 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>155.2</v>
+        <v>156.05</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.01914933237130534</v>
+        <v>0.005476843558180677</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.006615672077542989</v>
+        <v>-0.0139020344280707</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-0.02622667716470306</v>
+        <v>-0.004910115014017169</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.06353707265284825</v>
+        <v>-0.04946089546051713</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.05556687911838387</v>
+        <v>0.04234851415114771</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.2765188911846954</v>
+        <v>0.3067022824598076</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.2439134085370809</v>
+        <v>0.2367630981923019</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6106883701522177</v>
+        <v>0.608373917271281</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.140632846229579</v>
+        <v>1.152356983936918</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2887857585000639</v>
+        <v>0.2911343474505712</v>
       </c>
     </row>
     <row r="14">
@@ -1278,37 +1278,37 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>395.66</v>
+        <v>394.2</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.002445607263095839</v>
+        <v>-0.003690015269587232</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.0104789355444489</v>
+        <v>-0.01597602046673607</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-0.07846745536853128</v>
+        <v>-0.06191992037048699</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.04735989104108129</v>
+        <v>-0.03550189511244595</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.02897122377698125</v>
+        <v>0.06176104687124329</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>-0.007998000232143254</v>
+        <v>-0.03073518471800996</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.3944456801287903</v>
+        <v>0.3937208927697271</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.5376555195128265</v>
+        <v>0.5213464865443564</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.206849119972</v>
+        <v>0.2023958282912153</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.06467647824048472</v>
+        <v>0.06336530668059548</v>
       </c>
     </row>
     <row r="15">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>104.8</v>
+        <v>104.83</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.01206635329188088</v>
+        <v>0.0002862478857186268</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01308973874838559</v>
+        <v>-0.03266587455760672</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-0.05670563014301711</v>
+        <v>-0.03498108734642091</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.02238800340305169</v>
+        <v>-0.02628647347938651</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.02967188355945671</v>
+        <v>0.04641646547927447</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1843146748980327</v>
+        <v>0.1768073605327352</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.2310584568655099</v>
+        <v>0.2265122304182448</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.4814111099152178</v>
+        <v>0.4810106798757787</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0.7397152187304958</v>
+        <v>0.7402132085336099</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0.2027057506964969</v>
+        <v>0.2028204970746499</v>
       </c>
     </row>
     <row r="16">
@@ -1376,51 +1376,51 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>66.23</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.01910535175160266</v>
+        <v>-0.01366300281448707</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.007761972575232257</v>
+        <v>-0.04262712304701033</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-0.04397607060012154</v>
+        <v>-0.05446983399166605</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.0896760767424265</v>
+        <v>-0.09375314740070406</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.04843510091894032</v>
+        <v>0.2053122746479821</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.2587419857759485</v>
+        <v>0.091497271693747</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.174611692684395</v>
+        <v>0.0501431688028362</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4243648306596579</v>
+        <v>0.3698265884929046</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.6898908176891054</v>
+        <v>2.784350013783857</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.191112773510711</v>
+        <v>0.5583455522996852</v>
       </c>
     </row>
     <row r="17">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>XPH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>92.22</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.01642492406612539</v>
+        <v>0.002566784845670966</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.01418674707135037</v>
+        <v>-0.01931093574586318</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-0.07881329878678067</v>
+        <v>-0.02306004054053745</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.07363135717076463</v>
+        <v>-0.08583257985852599</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1759478730620023</v>
+        <v>0.03090287114041335</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.1162477918537053</v>
+        <v>0.267021710707239</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.05553959930492658</v>
+        <v>0.1567583660712535</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3610580604799341</v>
+        <v>0.4329280781546154</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.836771838207835</v>
+        <v>0.6942280740192714</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.5655081200370875</v>
+        <v>0.1921309355222562</v>
       </c>
     </row>
     <row r="18">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>93.56</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.04364718585853578</v>
+        <v>-0.01293286785001113</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.008189595709517938</v>
+        <v>-0.03721851295843781</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-0.05941493505158724</v>
+        <v>-0.03832136157403709</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.09014882920736655</v>
+        <v>-0.1080741968559144</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.2047385159246657</v>
+        <v>0.2381016625309667</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.1220916363697586</v>
+        <v>0.1059880056780969</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.03644622840229217</v>
+        <v>0.02954293886328663</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2695607414267793</v>
+        <v>0.2862377280350543</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>2.356823155684697</v>
+        <v>2.31340980541637</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.4973022853077387</v>
+        <v>0.4908194530646128</v>
       </c>
     </row>
     <row r="19">
@@ -1558,37 +1558,37 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>67.06</v>
+        <v>67.33</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.01164334463218386</v>
+        <v>0.004026309011195828</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.03461869946049601</v>
+        <v>0.0245673403558242</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.046232749937688</v>
+        <v>0.05538150717671031</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.06078674671888162</v>
+        <v>0.07320096170117085</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.1360312599337601</v>
+        <v>0.1499497056187349</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.2973521563820922</v>
+        <v>0.3259000452980545</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1243429267877112</v>
+        <v>0.1260401664227997</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.03663936713455862</v>
+        <v>0.04695836665973041</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>1.086046664787813</v>
+        <v>1.09444548473584</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.2777366138472792</v>
+        <v>0.279449121009764</v>
       </c>
     </row>
     <row r="20">
@@ -1614,37 +1614,37 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>29.68</v>
+        <v>29.84</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.00469481526093829</v>
+        <v>0.005390830382983713</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.03322476978551092</v>
+        <v>-0.0283295004174926</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-0.06871667638494783</v>
+        <v>-0.06604070610223789</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.05777776808965773</v>
+        <v>-0.04143909550131009</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.08981271744700536</v>
+        <v>0.1168918321261978</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>-0.02954690226323731</v>
+        <v>-0.04653215641433406</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.2809483230391223</v>
+        <v>0.2956017583029131</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.2906808666820113</v>
+        <v>0.2706720145377886</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.2774475198253967</v>
+        <v>0.2843340227279387</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.08504484792015354</v>
+        <v>0.08699111900383794</v>
       </c>
     </row>
     <row r="21">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>108.1</v>
+        <v>107.15</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01264635572947159</v>
+        <v>-0.008788131005104671</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.02991615298244565</v>
+        <v>0.01295143469835391</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.06157317617914715</v>
+        <v>0.05879451340971675</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.04575791430648346</v>
+        <v>0.04587608313947689</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.2379752502510439</v>
+        <v>0.2434722502349378</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.280438962211421</v>
+        <v>0.32603432285113</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0004651081999698103</v>
+        <v>-0.009793161856114341</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>-0.07113174376607823</v>
+        <v>-0.06986555985929133</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.5873428944393135</v>
+        <v>0.5733931171329587</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.1665147933811046</v>
+        <v>0.1630875724578862</v>
       </c>
     </row>
     <row r="22">
@@ -1726,37 +1726,37 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>54.96</v>
+        <v>54.97</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.01611173498111496</v>
+        <v>0.0001819893813153062</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.03017468042569516</v>
+        <v>-0.02793984151501028</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-0.02914714760002657</v>
+        <v>-0.02811397042631769</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.03289689368348392</v>
+        <v>-0.03795676430265993</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.03428827611011065</v>
+        <v>0.02983582150992059</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.305938073007598</v>
+        <v>0.304013858509526</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.1586049134723431</v>
+        <v>0.1532596946666789</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1376911479918899</v>
+        <v>0.129801805621687</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.1387972349093953</v>
+        <v>0.139004573943202</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.04427641121239678</v>
+        <v>0.04433978395818472</v>
       </c>
     </row>
     <row r="23">
@@ -1782,37 +1782,37 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>53.58</v>
+        <v>53.4</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.01416737193531004</v>
+        <v>-0.003359468066898352</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.02101220027042316</v>
+        <v>-0.0292673485689614</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-0.04644949029085188</v>
+        <v>-0.04215243899768784</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.0213698295697774</v>
+        <v>-0.02767656033764931</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.05703714668945059</v>
+        <v>0.07982853250206356</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.04794179439140489</v>
+        <v>0.03622669163748871</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.2031354195870956</v>
+        <v>0.1993476901027635</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2419215762281213</v>
+        <v>0.2189561509850488</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.6212278400536313</v>
+        <v>0.6157817499003302</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1747569353999294</v>
+        <v>0.1734400303220167</v>
       </c>
     </row>
     <row r="24">
@@ -1838,37 +1838,37 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>290.32</v>
+        <v>292.55</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.02199763734220639</v>
+        <v>0.007681111919577877</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.00575072279169131</v>
+        <v>0.003257824655586328</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.008300679711157111</v>
+        <v>0.0246934773834282</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.01262642121749691</v>
+        <v>0.02111688583933247</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.1233120279044833</v>
+        <v>0.1299729420230833</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.1982830146399479</v>
+        <v>0.2364227506796677</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.06821697191917919</v>
+        <v>0.07515612359697377</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.0247794558197445</v>
+        <v>0.03678624187999602</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.8290179243912705</v>
+        <v>0.8430668157714341</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2229423570268925</v>
+        <v>0.226065559772715</v>
       </c>
     </row>
     <row r="25">
@@ -1894,37 +1894,37 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>179.59</v>
+        <v>178.26</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.008228437586135118</v>
+        <v>-0.005450911405258885</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.03070472151090731</v>
+        <v>0.01001512457500509</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-0.002997882253282458</v>
+        <v>0.007735597273127892</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.007406159244652377</v>
+        <v>0.002306796069858397</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>-0.04453949214738873</v>
+        <v>-0.04686873440318939</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.09379698975607065</v>
+        <v>0.08507197963166924</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.166721502081284</v>
+        <v>0.1594621222624983</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.2087027427267472</v>
+        <v>0.2025157990139994</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.9536482020321768</v>
+        <v>0.9429988978950903</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.2501116064684314</v>
+        <v>0.2478360208013202</v>
       </c>
     </row>
     <row r="26">
@@ -1936,51 +1936,51 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>KRE</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>109.58</v>
+        <v>70.94</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.005321117716098112</v>
+        <v>0.007956879935244521</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.008124095212191929</v>
+        <v>-0.01919108523537993</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-0.08000965156307216</v>
+        <v>-0.03340958015459217</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.0811659056560019</v>
+        <v>-0.04569234159279734</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>-0.01123844417928233</v>
+        <v>-0.03550037762607272</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.05905484232747904</v>
+        <v>0.1153447820457549</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.01654161669020304</v>
+        <v>0.08164302521133537</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.2014373546758319</v>
+        <v>0.1360791798455301</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.157674347614203</v>
+        <v>0.8691702185079704</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2921967153622347</v>
+        <v>0.2318267123477271</v>
       </c>
     </row>
     <row r="27">
@@ -1992,51 +1992,51 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Wind Energy</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>23.2</v>
+        <v>107.96</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.01444350634513447</v>
+        <v>-0.01478374447446784</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.007381679167405508</v>
+        <v>-0.02953137938379824</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-0.02684561181007228</v>
+        <v>-0.05870380480207948</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.0276613508184812</v>
+        <v>-0.08346008959083051</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>-0.05584967716740974</v>
+        <v>0.007578484915373718</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>-0.01719100192126177</v>
+        <v>0.01204336303002518</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.1340840138065038</v>
+        <v>0.002813228075218221</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.2478885839595784</v>
+        <v>0.1970192382930218</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.6029681740467425</v>
+        <v>1.125775681726732</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.1703298979735937</v>
+        <v>0.2857972073692676</v>
       </c>
     </row>
     <row r="28">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>KRE</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Commercial Banking</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>70.38</v>
+        <v>64.8</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.01137807501348187</v>
+        <v>0.004495441108728127</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.02693365729332442</v>
+        <v>-0.02269314789340537</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-0.03633973510341948</v>
+        <v>-0.04110025478938106</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.05449044030419981</v>
+        <v>-0.05267012354877321</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>-0.03199069352484951</v>
+        <v>-0.03442249002558473</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.1157309117196685</v>
+        <v>0.1123393217551445</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.07407027924311071</v>
+        <v>0.05709887644756595</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1248236603905344</v>
+        <v>0.1049941159331917</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.8544144893184455</v>
+        <v>0.9155834072621956</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.2285766886870946</v>
+        <v>0.2419392581691007</v>
       </c>
     </row>
     <row r="29">
@@ -2104,51 +2104,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>IYK</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples Products</t>
+          <t>Residential &amp; Healthcare REITs</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>72.16</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.003476567755088755</v>
+        <v>0.0001122700262836673</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.01393818855989082</v>
+        <v>-0.02227585691297429</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-0.01027598696867438</v>
+        <v>-0.02588343296637774</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.03629377210282569</v>
+        <v>-0.07380404610345892</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.002297042965173413</v>
+        <v>-0.03135828881618175</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.05139535470557255</v>
+        <v>0.08606757092048856</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.09473921549767739</v>
+        <v>0.08724702814717267</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.08459693634514065</v>
+        <v>0.09490611720641562</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2230557332701428</v>
+        <v>0.430779302346366</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.06942110161534476</v>
+        <v>0.1268277915301932</v>
       </c>
     </row>
     <row r="30">
@@ -2160,51 +2160,51 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>IYK</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Residential &amp; Healthcare REITs</t>
+          <t>Consumer Staples Products</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>89.09</v>
+        <v>71.69</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.01339985241388797</v>
+        <v>-0.006513320355468921</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.02034314992137376</v>
+        <v>-0.01848300187841456</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-0.0287376996315889</v>
+        <v>-0.01806134310783514</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.06745064291035285</v>
+        <v>-0.05400007309020871</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>-0.02280628362156711</v>
+        <v>-0.01078773874160766</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.08372529561091024</v>
+        <v>0.04394568734996795</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.09491932366166811</v>
+        <v>0.08195600073784237</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.08448579025239189</v>
+        <v>0.07580018815093337</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.4306186867488029</v>
+        <v>0.2150895009037634</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1267856250242529</v>
+        <v>0.06709419195186461</v>
       </c>
     </row>
     <row r="31">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>BIZD</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Commercial Banking</t>
+          <t>Business Development Companies (BDCs)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2230,37 +2230,37 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>64.51000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.023611284483114</v>
+        <v>-0.003091187260443662</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.02852378719071547</v>
+        <v>-0.03080396605263469</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-0.04130065427284213</v>
+        <v>-0.006163322536779647</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.05622371618451838</v>
+        <v>-0.04017856984468948</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>-0.02939584261699824</v>
+        <v>0.07684001423088538</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.1155050218441862</v>
+        <v>0.07665110718531243</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.05388955931464845</v>
+        <v>-0.02282767899874483</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.09639603350317816</v>
+        <v>-0.03738009354043526</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.9070103385747923</v>
+        <v>0.1295328264060884</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.2400837479368665</v>
+        <v>0.0414368780294172</v>
       </c>
     </row>
     <row r="32">
@@ -2272,51 +2272,51 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>VAW</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Chemicals &amp; Raw Materials</t>
+          <t>Property &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>224.98</v>
+        <v>137.69</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.007297916183033326</v>
+        <v>-0.003906484141091737</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.0012461005033364</v>
+        <v>-0.04102242174769566</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-0.02744998942313226</v>
+        <v>-0.03565128643565152</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.06129262132781066</v>
+        <v>-0.05594505020036311</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>-0.01698802607677508</v>
+        <v>-0.006100645002114713</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.0527392460838283</v>
+        <v>0.08185358014549471</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.07813369239219892</v>
+        <v>0.02377138158193293</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1087563034651038</v>
+        <v>0.0693341325207788</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.3680828917276031</v>
+        <v>0.5584082380525848</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1101222416918222</v>
+        <v>0.1593834015093489</v>
       </c>
     </row>
     <row r="33">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>IAI</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty Insurance</t>
+          <t>Broker-Dealers &amp; Securities Exchanges</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2342,37 +2342,37 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>138.23</v>
+        <v>181.08</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.02200368396017727</v>
+        <v>-0.009571733208300737</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.03913530417715982</v>
+        <v>-0.007835147218349658</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-0.02956643486989086</v>
+        <v>-0.04318837473849912</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.03677679904696729</v>
+        <v>-0.06770306201049492</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.001326621892532964</v>
+        <v>0.001015164285381731</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.08592682248089711</v>
+        <v>0.1117094161615433</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.0283849536576124</v>
+        <v>-0.006051087875830086</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.07858540812348891</v>
+        <v>0.05251255169433788</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.5645201457610141</v>
+        <v>1.040761897621232</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.1608970829572491</v>
+        <v>0.2684230116526274</v>
       </c>
     </row>
     <row r="34">
@@ -2384,51 +2384,51 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>IYT</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Transportation &amp; Freight</t>
+          <t>Wind Energy</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>79.76000000000001</v>
+        <v>22.79</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-0.001252172218342507</v>
+        <v>-0.01767240663487646</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-0.004990038767525462</v>
+        <v>-0.02814498191638348</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-0.02166288532020288</v>
+        <v>-0.03021272699883648</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.08146696737632875</v>
+        <v>-0.040824886532425</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>-0.04765399814765237</v>
+        <v>-0.0657155231658062</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.0801522253445921</v>
+        <v>-0.03780887734582183</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.06721656569372825</v>
+        <v>0.1134996687977676</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1225335365159648</v>
+        <v>0.2129317542631697</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.4128919068331967</v>
+        <v>0.5746398686522232</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1221122730933426</v>
+        <v>0.1633947002692273</v>
       </c>
     </row>
     <row r="35">
@@ -2440,51 +2440,51 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>VAW</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Development</t>
+          <t>Chemicals &amp; Raw Materials</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>53.39</v>
+        <v>222.52</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.005840194949134014</v>
+        <v>-0.01093426749841919</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.01213268985115512</v>
+        <v>-0.01670348532179355</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-0.01476285767363439</v>
+        <v>-0.02279215795697476</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.05320092272515098</v>
+        <v>-0.07031544350066132</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>-0.07483789845027278</v>
+        <v>-0.03125813135034172</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.06541079563019125</v>
+        <v>0.02351267305775862</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.09550899694074899</v>
+        <v>0.06401636459853921</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1461104839307996</v>
+        <v>0.1124702478783413</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.8073242000358472</v>
+        <v>0.3531240329821796</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.2180880650165327</v>
+        <v>0.106061314008699</v>
       </c>
     </row>
     <row r="36">
@@ -2496,51 +2496,51 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Media &amp; Interactive Media</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>69.58</v>
+        <v>113.99</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-0.0176478888562156</v>
+        <v>0.012704338452312</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-0.003865377937931402</v>
+        <v>0.01794112306775686</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-0.05679808869024172</v>
+        <v>0.02570119699145712</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.09176346068775487</v>
+        <v>0.01821299219021633</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>-0.1090258515651072</v>
+        <v>0.07345296801625523</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>-0.0001558969159599632</v>
+        <v>0.03179342001166807</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.05113791566960213</v>
+        <v>-0.02591999071615358</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.3198126674369441</v>
+        <v>-0.01727408724450985</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.3051695935222301</v>
+        <v>0.7982621453640359</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.09283765108729303</v>
+        <v>0.2160487922093217</v>
       </c>
     </row>
     <row r="37">
@@ -2552,51 +2552,51 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>IAI</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Broker-Dealers &amp; Securities Exchanges</t>
+          <t>Infrastructure Development</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>182.83</v>
+        <v>53.07</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.02282204240067476</v>
+        <v>-0.005993626118794504</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.009218360207477794</v>
+        <v>0.003024000148809991</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-0.04331826471761002</v>
+        <v>-0.005434799704089333</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.05758020101111971</v>
+        <v>-0.05096563961806089</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>-0.01165072793128474</v>
+        <v>-0.08982941279724266</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.1095117580338794</v>
+        <v>0.04302655027818836</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.008709778550940239</v>
+        <v>0.0871734157935744</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.05055763007459424</v>
+        <v>0.1477921226310874</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.060484480822079</v>
+        <v>0.7964918904983056</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.2724960686967817</v>
+        <v>0.2156496247724564</v>
       </c>
     </row>
     <row r="38">
@@ -2608,51 +2608,51 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>IYT</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Transportation &amp; Freight</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>70.56999999999999</v>
+        <v>78.92</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.003811358794805431</v>
+        <v>-0.01053164424256692</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.001979909368704513</v>
+        <v>-0.02326738628472858</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-0.005636205706619268</v>
+        <v>-0.03574272693977243</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.0264863874400102</v>
+        <v>-0.08904723986879859</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.06681780902478351</v>
+        <v>-0.07270782494170025</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.03725191490268354</v>
+        <v>0.06993088509710743</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>-0.001008630437764446</v>
+        <v>0.05234403938196541</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>-0.02518956884712864</v>
+        <v>0.1139723041567458</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.01272930998540756</v>
+        <v>0.3980119263874058</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.004225225652991993</v>
+        <v>0.1181591588558941</v>
       </c>
     </row>
     <row r="39">
@@ -2664,51 +2664,51 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>BIZD</t>
+          <t>XTN</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Business Development Companies (BDCs)</t>
+          <t>Trucking &amp; Logistics</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>12.94</v>
+        <v>98.55</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-0.01746397073487083</v>
+        <v>-0.01262393084516666</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.01221380125398708</v>
+        <v>-0.02205547730186663</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-0.009188425373490183</v>
+        <v>-0.03069627218119242</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.02633561944878482</v>
+        <v>-0.07932412876943085</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.07227523750984077</v>
+        <v>-0.1333104088464812</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.06076368163579615</v>
+        <v>0.08173256811480023</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>-0.01774848039047483</v>
+        <v>0.06324792600266593</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>-0.04710051773095614</v>
+        <v>0.1719779492441387</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.1330349666980448</v>
+        <v>0.3556659732211507</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.04251209986145366</v>
+        <v>0.1067534858438339</v>
       </c>
     </row>
     <row r="40">
@@ -2720,51 +2720,51 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>XTN</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Trucking &amp; Logistics</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>99.81</v>
+        <v>123.5</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-0.01158650979842246</v>
+        <v>-0.005796177858860996</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>-0.001641279253053463</v>
+        <v>-0.04572565362407366</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-0.02118625172646504</v>
+        <v>-0.04513696440305837</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.07531332576797189</v>
+        <v>-0.09170723594469643</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>-0.118826121357974</v>
+        <v>-0.00756694254701562</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.1081737613058569</v>
+        <v>0.0421590679807069</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.07915793269958504</v>
+        <v>-0.02213212924047114</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.1787550296659852</v>
+        <v>0.0347355779910099</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.3729986127591316</v>
+        <v>0.5129447245987619</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.1114502626537814</v>
+        <v>0.1479977066060065</v>
       </c>
     </row>
     <row r="41">
@@ -2776,51 +2776,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>KBWP</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Insurance Underwriters</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>124.22</v>
+        <v>28.46</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-0.02388810988917833</v>
+        <v>0.007433595910536495</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-0.04531159225008341</v>
+        <v>0.01029460445130614</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-0.03719478892605388</v>
+        <v>0.02227007645426093</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.07059801451468151</v>
+        <v>-0.0407819679376431</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.01036373187181572</v>
+        <v>-0.1237684887444701</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.04630577441019779</v>
+        <v>0.1461940866661429</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>-0.01366220621313374</v>
+        <v>-0.002803147459296773</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.04929969089613961</v>
+        <v>0.1332189828835073</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.5217651460446524</v>
+        <v>0.6711184321638115</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1502243156743328</v>
+        <v>0.1866857933311872</v>
       </c>
     </row>
     <row r="42">
@@ -2832,51 +2832,51 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>28.25</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-0.02619787048899069</v>
+        <v>-0.01856309429302472</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.01618707824781351</v>
+        <v>-0.03254636570538494</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.008208406084183384</v>
+        <v>-0.01758862218112811</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.04463982781356823</v>
+        <v>-0.0435022975634406</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>-0.09397050277415842</v>
+        <v>0.03203697669982253</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.1331728702038943</v>
+        <v>0.01474627282762087</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>-0.006925176646146669</v>
+        <v>-0.02256887338348668</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.1095202797784276</v>
+        <v>-0.03324726175999415</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.6587876748873209</v>
+        <v>-0.006070079689161512</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.1837598341111217</v>
+        <v>-0.002027467743785705</v>
       </c>
     </row>
     <row r="43">
@@ -2888,51 +2888,51 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Interactive Media</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>112.56</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.01908498859613295</v>
+        <v>-0.010922709345076</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.0006108728870930502</v>
+        <v>-0.02933711969379116</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.01895663862212493</v>
+        <v>-0.04163762658994419</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0.01374298998121137</v>
+        <v>-0.1065818410304744</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.05277307748652826</v>
+        <v>-0.1241182558210215</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.004567153981826388</v>
+        <v>-0.02295960311712752</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>-0.03240409752467066</v>
+        <v>0.03283925899268469</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-0.03763371141425886</v>
+        <v>0.2568646585117376</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.7757032270131416</v>
+        <v>0.2909137901499359</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.210942331529572</v>
+        <v>0.08884421161936951</v>
       </c>
     </row>
     <row r="44">
@@ -2958,37 +2958,37 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>91.45</v>
+        <v>91.17</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.02515723986537266</v>
+        <v>-0.003061769148612892</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.02171594283047096</v>
+        <v>-0.02814198335310147</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-0.03676011589864847</v>
+        <v>-0.03134301414737106</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.07157363504322656</v>
+        <v>-0.08002018594628557</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>-0.05726509419575343</v>
+        <v>-0.06020001895355165</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.04251172729957053</v>
+        <v>0.04622413776800793</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.05740810349963898</v>
+        <v>0.04728206809093161</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.03061422421575877</v>
+        <v>0.03766507353196569</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.3298972343452795</v>
+        <v>0.3258255431217156</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.09969612387025406</v>
+        <v>0.09857267854433793</v>
       </c>
     </row>
     <row r="45">
@@ -3000,51 +3000,51 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>55.92</v>
+        <v>62</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.008510697587718052</v>
+        <v>0.008294004026865975</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.01306038970101753</v>
+        <v>-0.001186867869029218</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0.04418206290675719</v>
+        <v>-0.005668017185079144</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.05922929163856538</v>
+        <v>-0.09815049284271349</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>-0.09790558363339374</v>
+        <v>-0.06032320445949813</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.001058620188082227</v>
+        <v>0.06205325018616881</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.06346701419381118</v>
+        <v>0.002622758755298715</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.09035877926699398</v>
+        <v>0.01536885297109003</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.5832066023588647</v>
+        <v>0.6466661979157062</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0.1655006787402107</v>
+        <v>0.1808693674536661</v>
       </c>
     </row>
     <row r="46">
@@ -3056,51 +3056,51 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Robotics &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>61.49</v>
+        <v>35.22</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-0.01914176064012429</v>
+        <v>-0.001983556050105362</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-0.01258148503643852</v>
+        <v>0.002990161959773419</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0.02090681815876438</v>
+        <v>0.01323368588556462</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.09438195770428193</v>
+        <v>-0.0008510291999113129</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>-0.05430556039572265</v>
+        <v>-0.03669731183945635</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0.05277713844728638</v>
+        <v>0.04191640958376319</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>-0.002412209964815393</v>
+        <v>-0.03517544669070949</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-0.002406900404168133</v>
+        <v>0.007968362365503578</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0.6331207541404413</v>
+        <v>0.4461187658754193</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.1776225121880928</v>
+        <v>0.1308404132257441</v>
       </c>
     </row>
     <row r="47">
@@ -3126,37 +3126,37 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>45.42</v>
+        <v>45.38</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-0.01067309257450189</v>
+        <v>-0.0008806055139258806</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-0.02850171517475597</v>
+        <v>-0.02977069707433666</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-0.02788033370182708</v>
+        <v>-0.02873638764016506</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.06207750347371266</v>
+        <v>-0.07017220513982125</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>-0.02767297692987636</v>
+        <v>-0.03531844819528707</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>-0.0387211949309989</v>
+        <v>-0.05034784643985468</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.01970977455457312</v>
+        <v>0.01430286930484481</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.006053772669961655</v>
+        <v>0.003631216056216413</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0.1060082228532377</v>
+        <v>0.1050344712081648</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0.03415614909168063</v>
+        <v>0.03385256276318382</v>
       </c>
     </row>
     <row r="48">
@@ -3168,51 +3168,51 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Robotics &amp; Artificial Intelligence</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>35.29</v>
+        <v>55.49</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-0.01479616928565908</v>
+        <v>-0.007689494001401953</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0.01641704132442068</v>
+        <v>-0.02580753914384426</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.003126793899867586</v>
+        <v>-0.04009858502288433</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.02081021034815989</v>
+        <v>-0.0664633423572053</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>-0.03636326705141735</v>
+        <v>-0.1138080608146349</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0.03118135071255934</v>
+        <v>-0.01780817052565165</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>-0.0335212613972633</v>
+        <v>0.05271853321388442</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>-0.005605697730450721</v>
+        <v>0.08280395450820843</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0.4489930380353033</v>
+        <v>0.5710327143612228</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0.1315891281383297</v>
+        <v>0.1625056604307504</v>
       </c>
     </row>
     <row r="49">
@@ -3224,51 +3224,51 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Retail - Broad / Omnichannel</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>17.42</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.02134826837382231</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0.005773694181969935</v>
+        <v>-0.006598483506422226</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-0.03275958606828522</v>
+        <v>-0.01622005638284751</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.009664586402458597</v>
+        <v>-0.07401783260331607</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>-0.1572327038221624</v>
+        <v>-0.06740519040782889</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>-0.03923241660409238</v>
+        <v>0.03921148255568307</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.05603114802074027</v>
+        <v>-0.05266544422691255</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.1588315782501817</v>
+        <v>-0.04948200311150563</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0.207778311227002</v>
+        <v>0.4275961036125135</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0.06494965082697557</v>
+        <v>0.1259915153031084</v>
       </c>
     </row>
     <row r="50">
@@ -3280,51 +3280,51 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>VNQI</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Retail - Broad / Omnichannel</t>
+          <t>International Real Estate</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>82.09999999999999</v>
+        <v>42.98</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.005571694501882551</v>
+        <v>-0.005553023407871449</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.005517840867861112</v>
+        <v>-0.01827316718516814</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-0.02403903404541252</v>
+        <v>-0.02384736012198718</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.06198248809130413</v>
+        <v>-0.06157204676419137</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>-0.04087767847179469</v>
+        <v>-0.03697068085122024</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.03244469240404135</v>
+        <v>-0.02979683335344019</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>-0.04290478855741864</v>
+        <v>-0.06666666114412256</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>-0.04718606734398056</v>
+        <v>-0.04793512443232439</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0.4275962930027954</v>
+        <v>0.240790691307565</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1259915650958663</v>
+        <v>0.07456537434690103</v>
       </c>
     </row>
     <row r="51">
@@ -3336,51 +3336,51 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>43.22</v>
+        <v>212.76</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.01030448745386459</v>
+        <v>-0.005422605048796103</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.004147472323669188</v>
+        <v>-0.0052366296540447</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-0.03028939832543609</v>
+        <v>-0.02433754409078059</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.05447381128072182</v>
+        <v>-0.08737516928320532</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>-0.02349745007387638</v>
+        <v>-0.09815558800273594</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>-0.03072435360387082</v>
+        <v>-0.04259714624244082</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>-0.05900281006894026</v>
+        <v>-0.03136014345116422</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>-0.05322968706233278</v>
+        <v>0.04725531683339135</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0.2477193058192322</v>
+        <v>1.051517616188926</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0.07656179860585244</v>
+        <v>0.270647491803913</v>
       </c>
     </row>
     <row r="52">
@@ -3392,51 +3392,51 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>213.92</v>
+        <v>25.44</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-0.01027112624674809</v>
+        <v>0.0005899519149810128</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0.006271222542491128</v>
+        <v>0.001890149038319189</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-0.02406937922230656</v>
+        <v>-0.01421924370706107</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.09763216528203877</v>
+        <v>-0.07210063009978385</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>-0.09223928637681744</v>
+        <v>0.04733987279879925</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>-0.04043733373414748</v>
+        <v>0.08409249292446597</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.023818015413963</v>
+        <v>-0.1582113121543178</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.04024747563338082</v>
+        <v>-0.2483146972822715</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>1.06270268727379</v>
+        <v>0.2869476995698681</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0.2729525384758582</v>
+        <v>0.08772797780229635</v>
       </c>
     </row>
     <row r="53">
@@ -3448,51 +3448,51 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>51.78</v>
+        <v>16.97</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-0.003272415421480712</v>
+        <v>-0.02583242026226151</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-0.002312191581000156</v>
+        <v>-0.04286521424162293</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.007400942326738935</v>
+        <v>-0.04769923658958353</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.0767135344856319</v>
+        <v>-0.02639133584436559</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.05580216422932049</v>
+        <v>-0.1713867337566629</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>-0.04698295877959369</v>
+        <v>-0.07069645590732243</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>-0.1701845352676965</v>
+        <v>0.02626944390551356</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>-0.139398968482073</v>
+        <v>0.1326242884472708</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0.07856414103049003</v>
+        <v>0.1765785521042469</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>0.02553068407926729</v>
+        <v>0.0556994835993001</v>
       </c>
     </row>
     <row r="54">
@@ -3504,51 +3504,51 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>25.43</v>
+        <v>51.34</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-0.02169902549985347</v>
+        <v>-0.008497463056814647</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.01105367324637485</v>
+        <v>-0.006963261219323336</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-0.02387715005057223</v>
+        <v>0.01022219153013482</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.07712408953054362</v>
+        <v>-0.07980833501074269</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.04866142938814266</v>
+        <v>0.03628199277307642</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0.03967293135688621</v>
+        <v>-0.04809477468513368</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-0.1565747696215726</v>
+        <v>-0.1784163307365454</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>-0.2507354615670468</v>
+        <v>-0.1394529010569305</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.2861887858721011</v>
+        <v>0.06939916706124771</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.08751412451736584</v>
+        <v>0.02261764124861854</v>
       </c>
     </row>
     <row r="55">
@@ -3574,37 +3574,37 @@
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>239.37</v>
+        <v>239.46</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.01716283261011498</v>
+        <v>0.0003760354201269855</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.01152003534680179</v>
+        <v>-0.007173629920890212</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0.02919010762770746</v>
+        <v>-0.02072732593820503</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.1218786304188926</v>
+        <v>-0.09796740411092209</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>-0.1301075299822532</v>
+        <v>-0.1204843227562985</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>-0.08860509454079324</v>
+        <v>-0.08418580559139011</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>-0.04187938162999005</v>
+        <v>-0.0430875661178538</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.04193461935569154</v>
+        <v>0.0591254960964902</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1.183186335372176</v>
+        <v>1.184007290763013</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0.2972696809906001</v>
+        <v>0.2974322670627654</v>
       </c>
     </row>
     <row r="56">
@@ -3616,51 +3616,51 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>97.09</v>
+        <v>39.36</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0.001340730761607345</v>
+        <v>-0.009811305399960668</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.008604433814876522</v>
+        <v>-0.04894667357236526</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-0.01609485114756126</v>
+        <v>-0.0675115045156337</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.08325903804360668</v>
+        <v>-0.08261432992225148</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>-0.09766252548105114</v>
+        <v>-0.1293497649418833</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>-0.01561620466378255</v>
+        <v>-0.115045656509864</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-0.05801739063493505</v>
+        <v>-0.06139765492869598</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>-0.1175159537788389</v>
+        <v>-0.06127306550198153</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0.3076647371616259</v>
+        <v>0.3601996139417327</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.09353361456864207</v>
+        <v>0.1079858542393235</v>
       </c>
     </row>
     <row r="57">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3686,37 +3686,37 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>88.79000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.006689387615641085</v>
+        <v>-0.002986850314872669</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0.007603247254452716</v>
+        <v>0.002794803740536755</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.008529137592287905</v>
+        <v>0.004450442122956533</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.08154955937532427</v>
+        <v>-0.08419145624931923</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>-0.08003979314520782</v>
+        <v>-0.1482210803797681</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>-0.01842160641245849</v>
+        <v>-0.02141148526483383</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>-0.07457896617233251</v>
+        <v>-0.06692534561452845</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>-0.1590398274301739</v>
+        <v>-0.114744220423196</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0.1669378652984406</v>
+        <v>0.3037590723002384</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0.05280816415065259</v>
+        <v>0.09244382580995092</v>
       </c>
     </row>
     <row r="58">
@@ -3728,51 +3728,51 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>39.75</v>
+        <v>16.8</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-0.02238071448172985</v>
+        <v>0.003045606759520147</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>-0.03092257721437341</v>
+        <v>-0.05000004315268325</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-0.06748298036413736</v>
+        <v>-0.05010743803435858</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.06377655971517138</v>
+        <v>-0.1706088596822034</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>-0.1115536384549517</v>
+        <v>-0.0598376858570604</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>-0.1000900322432019</v>
+        <v>0.05955079967082244</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-0.04787165512715574</v>
+        <v>-0.1901639482963211</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-0.04521899566527743</v>
+        <v>-0.2495420607818757</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0.3736769086448033</v>
+        <v>0.004624658486933386</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0.1116332606602641</v>
+        <v>0.001539182530631455</v>
       </c>
     </row>
     <row r="59">
@@ -3798,37 +3798,37 @@
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>41.99</v>
+        <v>40.86</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>-0.02303391983047054</v>
+        <v>-0.02691119368768013</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>0.01498677211964305</v>
+        <v>-0.04264291663098951</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>-0.1039265656946868</v>
+        <v>-0.09199998643663199</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.08856084313835566</v>
+        <v>-0.1057123694797827</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>-0.07876261536571383</v>
+        <v>-0.08631485923494508</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>-0.1279335337944139</v>
+        <v>-0.1521062092808365</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>-0.05510157113851166</v>
+        <v>-0.08052991577278779</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>-0.1264005065363056</v>
+        <v>-0.118943634277186</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0.7903440004332962</v>
+        <v>0.7421637062700597</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>0.2142613223959253</v>
+        <v>0.2032697184034566</v>
       </c>
     </row>
     <row r="60">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3854,37 +3854,37 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>16.75</v>
+        <v>88.31</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>-0.04505269546924473</v>
+        <v>-0.005406051942608459</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>-0.05245586234452337</v>
+        <v>-0.002710395086308215</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>-0.06536054381791656</v>
+        <v>0.009472585526765664</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.1651709857458548</v>
+        <v>-0.0895033645991794</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>-0.04396223678261257</v>
+        <v>-0.1380596884332205</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>0.02849952079052165</v>
+        <v>-0.02190821797944686</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>-0.1968053922488893</v>
+        <v>-0.08859273210733298</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>-0.2648285320659323</v>
+        <v>-0.1643669186567603</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0.001574257159167924</v>
+        <v>0.1606294549618876</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0.0005244772619006355</v>
+        <v>0.05090759168190528</v>
       </c>
     </row>
     <row r="61">
@@ -3910,37 +3910,37 @@
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>17.73</v>
+        <v>17.43</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>-0.02319940165566314</v>
+        <v>-0.01641658405542179</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>-0.07339254522774474</v>
+        <v>-0.07629141902292014</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>-0.07777955293758076</v>
+        <v>-0.09121709922935561</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.09791347703450282</v>
+        <v>-0.1216182856387292</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>-0.05662591971960862</v>
+        <v>-0.06061422588208454</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>-0.03558211961234958</v>
+        <v>-0.04413378921475897</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>-0.1557004058094462</v>
+        <v>-0.1699390241743011</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-0.2492453903681557</v>
+        <v>-0.2553864964608102</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0.1544413774547564</v>
+        <v>0.1354893935447135</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0.04903656977352577</v>
+        <v>0.04326433444793776</v>
       </c>
     </row>
     <row r="62">
@@ -3966,37 +3966,37 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>45.05</v>
+        <v>43.47</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>-0.03553842603186708</v>
+        <v>-0.035072098626311</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>0.009636941180393155</v>
+        <v>-0.06233820861950423</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>-0.05634692808608721</v>
+        <v>-0.07589284917819383</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.08657746318298898</v>
+        <v>-0.1003724856115965</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>-0.2307035829816823</v>
+        <v>-0.2525790692099293</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>-0.1807601770868575</v>
+        <v>-0.2157676171500199</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>-0.1061508358501</v>
+        <v>-0.1453008120519831</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0.06325230995365905</v>
+        <v>0.002768229545698109</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>-0.1420915362953737</v>
+        <v>-0.1721801865467694</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>-0.04980300901146784</v>
+        <v>-0.06104393339234571</v>
       </c>
     </row>
   </sheetData>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Electric &amp; Gas Utilities</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ITB</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Home Construction</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1115391206046483</v>
+        <v>0.115086252126249</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.1651709857458548</v>
+        <v>-0.1706088596822034</v>
       </c>
     </row>
     <row r="18">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.09657357732703176</v>
+        <v>0.1068645254425511</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
@@ -4669,21 +4669,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.1218786304188926</v>
+        <v>-0.1216182856387292</v>
       </c>
     </row>
     <row r="19">
@@ -4692,21 +4692,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
+          <t>Semiconductor Manufacturers</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.08203390089132023</v>
+        <v>0.09824439088799131</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
@@ -4714,21 +4714,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.09791347703450282</v>
+        <v>-0.1080741968559144</v>
       </c>
     </row>
     <row r="20">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturers</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.07314155719701798</v>
+        <v>0.09404350005052198</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
@@ -4759,21 +4759,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Lithium &amp; Battery Tech</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.09763216528203877</v>
+        <v>-0.1065818410304744</v>
       </c>
     </row>
     <row r="21">
@@ -4782,21 +4782,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GGME</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Next-Gen Media &amp; Gaming</t>
+          <t>Dry Bulk Shipping &amp; Maritime Freight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.06078674671888162</v>
+        <v>0.07351946277946664</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
@@ -4804,21 +4804,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PEJ</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Leisure &amp; Entertainment</t>
+          <t>Uranium &amp; Nuclear Energy</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.09438195770428193</v>
+        <v>-0.1057123694797827</v>
       </c>
     </row>
     <row r="22">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>GGME</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Next-Gen Media &amp; Gaming</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.05901211710340504</v>
+        <v>0.07320096170117085</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
@@ -4849,21 +4849,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery Tech</t>
+          <t>Solar Energy</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.09176346068775487</v>
+        <v>-0.1003724856115965</v>
       </c>
     </row>
     <row r="23">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IGV</t>
+          <t>IDNA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Software &amp; Cloud Applications</t>
+          <t>Genomics &amp; Immunology</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.04575791430648346</v>
+        <v>0.05092010463829522</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
@@ -4894,21 +4894,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>PEJ</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Leisure &amp; Entertainment</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K23" s="11" t="n">
-        <v>-0.09014882920736655</v>
+        <v>-0.09815049284271349</v>
       </c>
     </row>
     <row r="24">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CLOU</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; SaaS</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.03885918653244547</v>
+        <v>0.04587608313947689</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
@@ -4939,21 +4939,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>XPH</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K24" s="11" t="n">
-        <v>-0.0896760767424265</v>
+        <v>-0.09796740411092209</v>
       </c>
     </row>
     <row r="25">
@@ -4962,21 +4962,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>CLOU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Cloud Computing &amp; SaaS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.03588214537862755</v>
+        <v>0.04476533346443778</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
@@ -4984,21 +4984,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Uranium &amp; Nuclear Energy</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K25" s="11" t="n">
-        <v>-0.08856084313835566</v>
+        <v>-0.09375314740070406</v>
       </c>
     </row>
     <row r="26">
@@ -5007,21 +5007,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IDNA</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Genomics &amp; Immunology</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.01746499292072934</v>
+        <v>0.04216204285979575</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
@@ -5029,21 +5029,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>KBWP</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Solar Energy</t>
+          <t>Insurance Underwriters</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K26" s="11" t="n">
-        <v>-0.08657746318298898</v>
+        <v>-0.09170723594469643</v>
       </c>
     </row>
     <row r="27"/>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.3559897550912594</v>
+        <v>0.3478633089613843</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K31" s="11" t="n">
-        <v>-0.2307035829816823</v>
+        <v>-0.2525790692099293</v>
       </c>
     </row>
     <row r="32">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.3553488088208576</v>
+        <v>0.3429235062007863</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="K32" s="11" t="n">
-        <v>-0.1572327038221624</v>
+        <v>-0.1713867337566629</v>
       </c>
     </row>
     <row r="33">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.3083092293705743</v>
+        <v>0.3147272100402931</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
@@ -5225,21 +5225,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XHB</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense (Equal Weight)</t>
+          <t>Homebuilders &amp; Residential Construction</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K33" s="11" t="n">
-        <v>-0.1301075299822532</v>
+        <v>-0.1482210803797681</v>
       </c>
     </row>
     <row r="34">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.2929345652203124</v>
+        <v>0.2724432886553156</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
@@ -5270,21 +5270,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>ITB</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Home Construction</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K34" s="11" t="n">
-        <v>-0.1259312342653346</v>
+        <v>-0.1380596884332205</v>
       </c>
     </row>
     <row r="35">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.2379752502510439</v>
+        <v>0.2434722502349378</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="K35" s="11" t="n">
-        <v>-0.118826121357974</v>
+        <v>-0.1333104088464812</v>
       </c>
     </row>
     <row r="36">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CIBR</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cybersecurity Leaders</t>
+          <t>Gold Miners</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.2361885875069936</v>
+        <v>0.2381016625309667</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="n">
-        <v>-0.1115536384549517</v>
+        <v>-0.1293497649418833</v>
       </c>
     </row>
     <row r="37">
@@ -5383,21 +5383,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>CIBR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gold Miners</t>
+          <t>Cybersecurity Leaders</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.2047385159246657</v>
+        <v>0.2324787134775763</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="n">
-        <v>-0.1090258515651072</v>
+        <v>-0.1241182558210215</v>
       </c>
     </row>
     <row r="38">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.1827804735568381</v>
+        <v>0.2075009630454823</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>IFRA</t>
+          <t>JETS</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>US Infrastructure &amp; Engineering</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="K38" s="11" t="n">
-        <v>-0.09790558363339374</v>
+        <v>-0.1237684887444701</v>
       </c>
     </row>
     <row r="39">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.1759478730620023</v>
+        <v>0.2053122746479821</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -5495,21 +5495,21 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>XHB</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Homebuilders &amp; Residential Construction</t>
+          <t>Aerospace &amp; Defense (Equal Weight)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
-        <v>-0.09766252548105114</v>
+        <v>-0.1204843227562985</v>
       </c>
     </row>
     <row r="40">
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1601499792771268</v>
+        <v>0.1527640548044698</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>JETS</t>
+          <t>IFRA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>US Infrastructure &amp; Engineering</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="K40" s="11" t="n">
-        <v>-0.09397050277415842</v>
+        <v>-0.1138080608146349</v>
       </c>
     </row>
     <row r="41"/>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.6043147087454506</v>
+        <v>0.6401602626037575</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="K45" s="11" t="n">
-        <v>-0.1807601770868575</v>
+        <v>-0.2157676171500199</v>
       </c>
     </row>
     <row r="46">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>HACK</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.6026746800613949</v>
+        <v>0.6165651937702634</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="n">
-        <v>-0.1279335337944139</v>
+        <v>-0.1521062092808365</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.5975976380188242</v>
+        <v>0.6091836888608408</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="n">
-        <v>-0.1000900322432019</v>
+        <v>-0.115045656509864</v>
       </c>
     </row>
     <row r="48">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HACK</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.5888078564888253</v>
+        <v>0.5739969078028957</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K48" s="11" t="n">
-        <v>-0.08860509454079324</v>
+        <v>-0.08418580559139011</v>
       </c>
     </row>
     <row r="49">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.5367181000997809</v>
+        <v>0.5218835376075268</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -5826,21 +5826,21 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Medical Devices &amp; Equipment</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K49" s="11" t="n">
-        <v>-0.04698295877959369</v>
+        <v>-0.07069645590732243</v>
       </c>
     </row>
     <row r="50">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.4511951942413268</v>
+        <v>0.4994819522316869</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -5871,21 +5871,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>PBJ</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Food &amp; Beverage Manufacturers</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="K50" s="11" t="n">
-        <v>-0.04043733373414748</v>
+        <v>-0.05034784643985468</v>
       </c>
     </row>
     <row r="51">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.4323871654463725</v>
+        <v>0.4893556449934702</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -5916,21 +5916,21 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Clean &amp; Renewable Energy</t>
+          <t>Medical Devices &amp; Equipment</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K51" s="11" t="n">
-        <v>-0.03923241660409238</v>
+        <v>-0.04809477468513368</v>
       </c>
     </row>
     <row r="52">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.3928540697111753</v>
+        <v>0.3880344910215563</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -5961,21 +5961,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>PBJ</t>
+          <t>FCG</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Manufacturers</t>
+          <t>Natural Gas Producers</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="K52" s="11" t="n">
-        <v>-0.0387211949309989</v>
+        <v>-0.04653215641433406</v>
       </c>
     </row>
     <row r="53">
@@ -5984,21 +5984,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>IGV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Software &amp; Cloud Applications</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.305938073007598</v>
+        <v>0.32603432285113</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="K53" s="11" t="n">
-        <v>-0.03558211961234958</v>
+        <v>-0.04413378921475897</v>
       </c>
     </row>
     <row r="54">
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.2973521563820922</v>
+        <v>0.3259000452980545</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -6051,21 +6051,21 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K54" s="11" t="n">
-        <v>-0.03072435360387082</v>
+        <v>-0.04259714624244082</v>
       </c>
     </row>
     <row r="55"/>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.9345454591693301</v>
+        <v>0.8818616041052152</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="K59" s="11" t="n">
-        <v>-0.2648285320659323</v>
+        <v>-0.2553864964608102</v>
       </c>
     </row>
     <row r="60">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.8752915541851864</v>
+        <v>0.8759572078459845</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -6202,21 +6202,21 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FINX</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FinTech &amp; Digital Payments</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K60" s="11" t="n">
-        <v>-0.2507354615670468</v>
+        <v>-0.2495420607818757</v>
       </c>
     </row>
     <row r="61">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.790216769780524</v>
+        <v>0.8389564467943529</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -6247,21 +6247,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>FINX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>FinTech &amp; Digital Payments</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="K61" s="11" t="n">
-        <v>-0.2492453903681557</v>
+        <v>-0.2483146972822715</v>
       </c>
     </row>
     <row r="62">
@@ -6270,21 +6270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>XSD</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Semiconductors - Equal Weight</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.6513919038743419</v>
+        <v>0.6494058369922486</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="K62" s="11" t="n">
-        <v>-0.1590398274301739</v>
+        <v>-0.1643669186567603</v>
       </c>
     </row>
     <row r="63">
@@ -6315,21 +6315,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>XSD</t>
+          <t>XBI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Semiconductors - Equal Weight</t>
+          <t>Biotechnology (Equal Weight)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.6391199039241318</v>
+        <v>0.608373917271281</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="K63" s="11" t="n">
-        <v>-0.139398968482073</v>
+        <v>-0.1394529010569305</v>
       </c>
     </row>
     <row r="64">
@@ -6360,21 +6360,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>XBI</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Biotechnology (Equal Weight)</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.6106883701522177</v>
+        <v>0.5833450281389629</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="K64" s="11" t="n">
-        <v>-0.1264005065363056</v>
+        <v>-0.118943634277186</v>
       </c>
     </row>
     <row r="65">
@@ -6405,21 +6405,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>NXTG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>NextGen 5G &amp; Telecom Infrastructure</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.5376555195128265</v>
+        <v>0.5249468234899368</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="K65" s="11" t="n">
-        <v>-0.1175159537788389</v>
+        <v>-0.114744220423196</v>
       </c>
     </row>
     <row r="66">
@@ -6450,21 +6450,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NXTG</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NextGen 5G &amp; Telecom Infrastructure</t>
+          <t>Oil Services &amp; Equipment</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.5203226261754073</v>
+        <v>0.5213464865443564</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="K66" s="11" t="n">
-        <v>-0.07113174376607823</v>
+        <v>-0.06986555985929133</v>
       </c>
     </row>
     <row r="67">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.4814111099152178</v>
+        <v>0.4810106798757787</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -6517,21 +6517,21 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>VNQI</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>International Real Estate</t>
+          <t>Electric &amp; Gas Utilities</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="K67" s="11" t="n">
-        <v>-0.05322968706233278</v>
+        <v>-0.06127306550198153</v>
       </c>
     </row>
     <row r="68">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.4528371916349725</v>
+        <v>0.4803029387127695</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="K68" s="11" t="n">
-        <v>-0.04718606734398056</v>
+        <v>-0.04948200311150563</v>
       </c>
     </row>
     <row r="69"/>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>3.294221356225966</v>
+        <v>3.287866859322264</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="K73" s="11" t="n">
-        <v>-0.1420915362953737</v>
+        <v>-0.1721801865467694</v>
       </c>
     </row>
     <row r="74">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2.836771838207835</v>
+        <v>2.784350013783857</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -6713,21 +6713,21 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Travel Tech &amp; Bookings</t>
+          <t>Timber &amp; Forestry</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.001574257159167924</v>
+        <v>-0.006070079689161512</v>
       </c>
     </row>
     <row r="75">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2.356823155684697</v>
+        <v>2.31340980541637</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -6758,21 +6758,21 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Timber &amp; Forestry</t>
+          <t>Travel Tech &amp; Bookings</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.01272930998540756</v>
+        <v>0.004624658486933386</v>
       </c>
     </row>
     <row r="76">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1.88607584676748</v>
+        <v>1.851717876934801</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.07856414103049003</v>
+        <v>0.06939916706124771</v>
       </c>
     </row>
     <row r="77">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.758582305950276</v>
+        <v>1.754711397758295</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.1060082228532377</v>
+        <v>0.1050344712081648</v>
       </c>
     </row>
     <row r="78">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1.533437997519019</v>
+        <v>1.510732559064054</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.1330349666980448</v>
+        <v>0.1295328264060884</v>
       </c>
     </row>
     <row r="79">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.425810417597889</v>
+        <v>1.388857422400881</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -6938,21 +6938,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>IHF</t>
+          <t>BETZ</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Health Care Providers &amp; Managed Care</t>
+          <t>Casinos, Gaming &amp; Sports Betting</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1387972349093953</v>
+        <v>0.1354893935447135</v>
       </c>
     </row>
     <row r="80">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.392571524566373</v>
+        <v>1.384926023068771</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -6983,21 +6983,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>BETZ</t>
+          <t>IHF</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Casinos, Gaming &amp; Sports Betting</t>
+          <t>Health Care Providers &amp; Managed Care</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="K80" s="11" t="n">
-        <v>0.1544413774547564</v>
+        <v>0.139004573943202</v>
       </c>
     </row>
     <row r="81">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1.320932315896604</v>
+        <v>1.302700676254414</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1669378652984406</v>
+        <v>0.1606294549618876</v>
       </c>
     </row>
     <row r="82">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1.183186335372176</v>
+        <v>1.184007290763013</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Oil Services &amp; Equipment</t>
+          <t>Clean &amp; Renewable Energy</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="K82" s="11" t="n">
-        <v>0.206849119972</v>
+        <v>0.1765785521042469</v>
       </c>
     </row>
   </sheetData>

--- a/Subgroup_RS_Leaderboard.xlsx
+++ b/Subgroup_RS_Leaderboard.xlsx
@@ -801,10 +801,10 @@
         <v>0.8759572078459845</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>3.287866859322264</v>
+        <v>3.287866392152082</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.6246024254126123</v>
+        <v>0.6246023664115703</v>
       </c>
     </row>
     <row r="6">
@@ -848,13 +848,13 @@
         <v>0.2324787134775763</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0.6401602626037575</v>
+        <v>0.6401603620515284</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>0.4201965547529258</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3703280391459771</v>
+        <v>0.370327900310168</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>1.302700676254414</v>
@@ -966,13 +966,13 @@
         <v>0.5970039195699328</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6494058369922486</v>
+        <v>0.6494056793612057</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>1.754711397758295</v>
+        <v>1.7547109580761</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.4018193010781861</v>
+        <v>0.4018192264962632</v>
       </c>
     </row>
     <row r="9">
@@ -1016,19 +1016,19 @@
         <v>0.01686599061799687</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.3880344910215563</v>
+        <v>0.3880343963962565</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>0.453494401818374</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.5249468234899368</v>
+        <v>0.5249467092767763</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1.384926023068771</v>
+        <v>1.384925743713701</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3360569508567144</v>
+        <v>0.3360568986909738</v>
       </c>
     </row>
     <row r="10">
@@ -1078,13 +1078,13 @@
         <v>0.4805894444104497</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3882090115322883</v>
+        <v>0.3882088517627762</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3758275764327996</v>
+        <v>0.3758277333650888</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1122130930884302</v>
+        <v>0.1122131353762243</v>
       </c>
     </row>
     <row r="11">
@@ -1134,13 +1134,13 @@
         <v>0.2089093252418539</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4803029387127695</v>
+        <v>0.4803027789205025</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7217728924446891</v>
+        <v>0.7217726762692847</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1985568049369049</v>
+        <v>0.1985567547757183</v>
       </c>
     </row>
     <row r="12">
@@ -1193,10 +1193,10 @@
         <v>0.5833450281389629</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.510732559064054</v>
+        <v>1.510732280258234</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3591482121302545</v>
+        <v>0.3591481618211068</v>
       </c>
     </row>
     <row r="13">
@@ -1249,10 +1249,10 @@
         <v>0.608373917271281</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1.152356983936918</v>
+        <v>1.152356757443882</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2911343474505712</v>
+        <v>0.2911343021617783</v>
       </c>
     </row>
     <row r="14">
@@ -1417,10 +1417,10 @@
         <v>0.3698265884929046</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>2.784350013783857</v>
+        <v>2.784349713479111</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.5583455522996852</v>
+        <v>0.5583455110791697</v>
       </c>
     </row>
     <row r=